--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -26,15 +26,15 @@
     <sheet name="Scoringstidspunkt" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Heatmap" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Klubber" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Nivå 2 og lavere" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Aldersfordeling" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Alder" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Spillere etter klubbland" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Alder" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Spillere etter klubbland" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Nivå 2 og lavere" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Klubber'!$A$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Nivå 2 og lavere'!$A$3:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Spillere etter klubbland'!$A$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Spillere etter klubbland'!$A$3:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Nivå 2 og lavere'!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="53">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -338,8 +338,14 @@
       <color rgb="006B7A99"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="50">
+  <fills count="56">
     <fill>
       <patternFill/>
     </fill>
@@ -586,8 +592,38 @@
         <fgColor rgb="00F0F5FB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EBF5EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2DCE8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -763,11 +799,25 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="173">
+  <cellXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1255,6 +1305,38 @@
     <xf numFmtId="0" fontId="47" fillId="49" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="50" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="52" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="52" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="51" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="52" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="53" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="55" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="54" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -47028,1943 +47110,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="8" customWidth="1" style="143" min="1" max="1"/>
-    <col width="26" customWidth="1" style="143" min="2" max="2"/>
-    <col width="16" customWidth="1" style="143" min="3" max="3"/>
-    <col width="22" customWidth="1" style="143" min="4" max="4"/>
-    <col width="30" customWidth="1" style="143" min="5" max="5"/>
-    <col width="22" customWidth="1" style="143" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="18" customHeight="1" s="143">
-      <c r="A1" s="149" t="inlineStr">
-        <is>
-          <t>FIFA World Cup 2026 — Spillere på nivå 2 og lavere</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="128" t="inlineStr">
-        <is>
-          <t>Nivå</t>
-        </is>
-      </c>
-      <c r="B3" s="128" t="inlineStr">
-        <is>
-          <t>Klubb</t>
-        </is>
-      </c>
-      <c r="C3" s="128" t="inlineStr">
-        <is>
-          <t>Land</t>
-        </is>
-      </c>
-      <c r="D3" s="128" t="inlineStr">
-        <is>
-          <t>Liga</t>
-        </is>
-      </c>
-      <c r="E3" s="128" t="inlineStr">
-        <is>
-          <t>Spiller</t>
-        </is>
-      </c>
-      <c r="F3" s="128" t="inlineStr">
-        <is>
-          <t>Nasjonallag</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="130" t="inlineStr">
-        <is>
-          <t>Charlton Athletic</t>
-        </is>
-      </c>
-      <c r="C4" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D4" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E4" s="130" t="inlineStr">
-        <is>
-          <t>Lyndon Dykes</t>
-        </is>
-      </c>
-      <c r="F4" s="130" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="130" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="C5" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D5" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E5" s="130" t="inlineStr">
-        <is>
-          <t>Brandon Thomas-Asante</t>
-        </is>
-      </c>
-      <c r="F5" s="130" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="130" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="C6" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D6" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E6" s="130" t="inlineStr">
-        <is>
-          <t>Haji Wright</t>
-        </is>
-      </c>
-      <c r="F6" s="130" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="130" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="C7" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D7" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E7" s="130" t="inlineStr">
-        <is>
-          <t>Jacob Widell Zetterström</t>
-        </is>
-      </c>
-      <c r="F7" s="130" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="130" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="C8" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D8" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E8" s="130" t="inlineStr">
-        <is>
-          <t>Sondre Langås</t>
-        </is>
-      </c>
-      <c r="F8" s="130" t="inlineStr">
-        <is>
-          <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="130" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C9" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D9" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E9" s="130" t="inlineStr">
-        <is>
-          <t>Amir Hadžiahmetović</t>
-        </is>
-      </c>
-      <c r="F9" s="130" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="130" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C10" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D10" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E10" s="130" t="inlineStr">
-        <is>
-          <t>Ivor Pandur</t>
-        </is>
-      </c>
-      <c r="F10" s="130" t="inlineStr">
-        <is>
-          <t>Kroatia</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="130" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C11" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D11" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E11" s="130" t="inlineStr">
-        <is>
-          <t>Liam Miller</t>
-        </is>
-      </c>
-      <c r="F11" s="130" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="130" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="C12" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D12" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E12" s="130" t="inlineStr">
-        <is>
-          <t>Alfie Jones</t>
-        </is>
-      </c>
-      <c r="F12" s="130" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="130" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="C13" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D13" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E13" s="130" t="inlineStr">
-        <is>
-          <t>Sontje Hansen</t>
-        </is>
-      </c>
-      <c r="F13" s="130" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="130" t="inlineStr">
-        <is>
-          <t>Millwall FC</t>
-        </is>
-      </c>
-      <c r="C14" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D14" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E14" s="130" t="inlineStr">
-        <is>
-          <t>Max Crocombe</t>
-        </is>
-      </c>
-      <c r="F14" s="130" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="130" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C15" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D15" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E15" s="130" t="inlineStr">
-        <is>
-          <t>Ali Ahmed</t>
-        </is>
-      </c>
-      <c r="F15" s="130" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="130" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C16" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D16" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E16" s="130" t="inlineStr">
-        <is>
-          <t>José Córdoba</t>
-        </is>
-      </c>
-      <c r="F16" s="130" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="130" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C17" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D17" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E17" s="130" t="inlineStr">
-        <is>
-          <t>Kenny McLean</t>
-        </is>
-      </c>
-      <c r="F17" s="130" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="130" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C18" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D18" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E18" s="130" t="inlineStr">
-        <is>
-          <t>Toure</t>
-        </is>
-      </c>
-      <c r="F18" s="130" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="130" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="C19" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D19" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E19" s="130" t="inlineStr">
-        <is>
-          <t>Gustavo Caballero</t>
-        </is>
-      </c>
-      <c r="F19" s="130" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="130" t="inlineStr">
-        <is>
-          <t>Sheffield United</t>
-        </is>
-      </c>
-      <c r="C20" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D20" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E20" s="130" t="inlineStr">
-        <is>
-          <t>Tahith Chong</t>
-        </is>
-      </c>
-      <c r="F20" s="130" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="130" t="inlineStr">
-        <is>
-          <t>Stoke City</t>
-        </is>
-      </c>
-      <c r="C21" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D21" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E21" s="130" t="inlineStr">
-        <is>
-          <t>Viktor Johansson</t>
-        </is>
-      </c>
-      <c r="F21" s="130" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="130" t="inlineStr">
-        <is>
-          <t>Swansea</t>
-        </is>
-      </c>
-      <c r="C22" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D22" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E22" s="130" t="inlineStr">
-        <is>
-          <t>Eom Jisung</t>
-        </is>
-      </c>
-      <c r="F22" s="130" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="130" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="C23" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D23" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E23" s="130" t="inlineStr">
-        <is>
-          <t>Burgess</t>
-        </is>
-      </c>
-      <c r="F23" s="130" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="130" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="C24" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D24" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E24" s="130" t="inlineStr">
-        <is>
-          <t>Marko Stamenić</t>
-        </is>
-      </c>
-      <c r="F24" s="130" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="130" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C25" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D25" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E25" s="130" t="inlineStr">
-        <is>
-          <t>Edo Kayembe</t>
-        </is>
-      </c>
-      <c r="F25" s="130" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="130" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C26" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D26" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E26" s="130" t="inlineStr">
-        <is>
-          <t>Egil Selvik</t>
-        </is>
-      </c>
-      <c r="F26" s="130" t="inlineStr">
-        <is>
-          <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" s="130" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C27" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D27" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E27" s="130" t="inlineStr">
-        <is>
-          <t>Irankunda</t>
-        </is>
-      </c>
-      <c r="F27" s="130" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="130" t="inlineStr">
-        <is>
-          <t>Wrexham</t>
-        </is>
-      </c>
-      <c r="C28" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D28" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E28" s="130" t="inlineStr">
-        <is>
-          <t>Dom Hyam</t>
-        </is>
-      </c>
-      <c r="F28" s="130" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="130" t="inlineStr">
-        <is>
-          <t>Wrexham AFC</t>
-        </is>
-      </c>
-      <c r="C29" s="130" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D29" s="130" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E29" s="130" t="inlineStr">
-        <is>
-          <t>Liberato Cacace</t>
-        </is>
-      </c>
-      <c r="F29" s="130" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="130" t="inlineStr">
-        <is>
-          <t>AS Nancy-Lorraine</t>
-        </is>
-      </c>
-      <c r="C30" s="130" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D30" s="130" t="inlineStr">
-        <is>
-          <t>Ligue 2</t>
-        </is>
-      </c>
-      <c r="E30" s="130" t="inlineStr">
-        <is>
-          <t>Martin Experience</t>
-        </is>
-      </c>
-      <c r="F30" s="130" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="130" t="inlineStr">
-        <is>
-          <t>SC Bastia</t>
-        </is>
-      </c>
-      <c r="C31" s="130" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D31" s="130" t="inlineStr">
-        <is>
-          <t>Ligue 2</t>
-        </is>
-      </c>
-      <c r="E31" s="130" t="inlineStr">
-        <is>
-          <t>Johnny Placide</t>
-        </is>
-      </c>
-      <c r="F31" s="130" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="130" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
-      <c r="C32" s="130" t="inlineStr">
-        <is>
-          <t>Italia</t>
-        </is>
-      </c>
-      <c r="D32" s="130" t="inlineStr">
-        <is>
-          <t>Serie B</t>
-        </is>
-      </c>
-      <c r="E32" s="130" t="inlineStr">
-        <is>
-          <t>Farès Ghedjemis</t>
-        </is>
-      </c>
-      <c r="F32" s="130" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="130" t="inlineStr">
-        <is>
-          <t>UC Sampdoria</t>
-        </is>
-      </c>
-      <c r="C33" s="130" t="inlineStr">
-        <is>
-          <t>Italia</t>
-        </is>
-      </c>
-      <c r="D33" s="130" t="inlineStr">
-        <is>
-          <t>Serie B</t>
-        </is>
-      </c>
-      <c r="E33" s="130" t="inlineStr">
-        <is>
-          <t>Dennis Hadžikadunić</t>
-        </is>
-      </c>
-      <c r="F33" s="130" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="130" t="inlineStr">
-        <is>
-          <t>Albirex Niigata</t>
-        </is>
-      </c>
-      <c r="C34" s="130" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D34" s="130" t="inlineStr">
-        <is>
-          <t>J2 League</t>
-        </is>
-      </c>
-      <c r="E34" s="130" t="inlineStr">
-        <is>
-          <t>Geria</t>
-        </is>
-      </c>
-      <c r="F34" s="130" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="130" t="inlineStr">
-        <is>
-          <t>FC Den Bosch</t>
-        </is>
-      </c>
-      <c r="C35" s="130" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D35" s="130" t="inlineStr">
-        <is>
-          <t>Eerste Divisie</t>
-        </is>
-      </c>
-      <c r="E35" s="130" t="inlineStr">
-        <is>
-          <t>Kevin Felida</t>
-        </is>
-      </c>
-      <c r="F35" s="130" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B36" s="130" t="inlineStr">
-        <is>
-          <t>VVV-Venlo</t>
-        </is>
-      </c>
-      <c r="C36" s="130" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D36" s="130" t="inlineStr">
-        <is>
-          <t>Eerste Divisie</t>
-        </is>
-      </c>
-      <c r="E36" s="130" t="inlineStr">
-        <is>
-          <t>Trevor Doornbusch</t>
-        </is>
-      </c>
-      <c r="F36" s="130" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" s="130" t="inlineStr">
-        <is>
-          <t>Chaves</t>
-        </is>
-      </c>
-      <c r="C37" s="130" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D37" s="130" t="inlineStr">
-        <is>
-          <t>Liga Portugal 2</t>
-        </is>
-      </c>
-      <c r="E37" s="130" t="inlineStr">
-        <is>
-          <t>Josimar Dias "Vozinha"</t>
-        </is>
-      </c>
-      <c r="F37" s="130" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" s="130" t="inlineStr">
-        <is>
-          <t>Torreense</t>
-        </is>
-      </c>
-      <c r="C38" s="130" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D38" s="130" t="inlineStr">
-        <is>
-          <t>Liga Portugal 2</t>
-        </is>
-      </c>
-      <c r="E38" s="130" t="inlineStr">
-        <is>
-          <t>Ianique Tavares "Stopira"</t>
-        </is>
-      </c>
-      <c r="F38" s="130" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" s="130" t="inlineStr">
-        <is>
-          <t>Castellón</t>
-        </is>
-      </c>
-      <c r="C39" s="130" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D39" s="130" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E39" s="130" t="inlineStr">
-        <is>
-          <t>Brian Cipenga</t>
-        </is>
-      </c>
-      <c r="F39" s="130" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" s="130" t="inlineStr">
-        <is>
-          <t>Castellón</t>
-        </is>
-      </c>
-      <c r="C40" s="130" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D40" s="130" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E40" s="130" t="inlineStr">
-        <is>
-          <t>Mabil</t>
-        </is>
-      </c>
-      <c r="F40" s="130" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" s="130" t="inlineStr">
-        <is>
-          <t>Cultural Leonesa</t>
-        </is>
-      </c>
-      <c r="C41" s="130" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D41" s="130" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E41" s="130" t="inlineStr">
-        <is>
-          <t>Homam Al-Amin</t>
-        </is>
-      </c>
-      <c r="F41" s="130" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" s="130" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C42" s="130" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D42" s="130" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E42" s="130" t="inlineStr">
-        <is>
-          <t>Federico Viñas</t>
-        </is>
-      </c>
-      <c r="F42" s="130" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" s="130" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C43" s="130" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D43" s="130" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E43" s="130" t="inlineStr">
-        <is>
-          <t>Haissem Hassan</t>
-        </is>
-      </c>
-      <c r="F43" s="130" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="130" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C44" s="130" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D44" s="130" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E44" s="130" t="inlineStr">
-        <is>
-          <t>Kwasi Sibo</t>
-        </is>
-      </c>
-      <c r="F44" s="130" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="130" t="inlineStr">
-        <is>
-          <t>Stade Nyonnais</t>
-        </is>
-      </c>
-      <c r="C45" s="130" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D45" s="130" t="inlineStr">
-        <is>
-          <t>Challenge League</t>
-        </is>
-      </c>
-      <c r="E45" s="130" t="inlineStr">
-        <is>
-          <t>Melvin Mastil</t>
-        </is>
-      </c>
-      <c r="F45" s="130" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" s="130" t="inlineStr">
-        <is>
-          <t>IFK Norrköping</t>
-        </is>
-      </c>
-      <c r="C46" s="130" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D46" s="130" t="inlineStr">
-        <is>
-          <t>Superettan</t>
-        </is>
-      </c>
-      <c r="E46" s="130" t="inlineStr">
-        <is>
-          <t>Moutaz Neffati</t>
-        </is>
-      </c>
-      <c r="F46" s="130" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="130" t="inlineStr">
-        <is>
-          <t>Siwelele FC</t>
-        </is>
-      </c>
-      <c r="C47" s="130" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D47" s="130" t="inlineStr">
-        <is>
-          <t>National First Division</t>
-        </is>
-      </c>
-      <c r="E47" s="130" t="inlineStr">
-        <is>
-          <t>Ricardo Goss</t>
-        </is>
-      </c>
-      <c r="F47" s="130" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B48" s="130" t="inlineStr">
-        <is>
-          <t>Iğdır</t>
-        </is>
-      </c>
-      <c r="C48" s="130" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D48" s="130" t="inlineStr">
-        <is>
-          <t>TFF 1. Lig</t>
-        </is>
-      </c>
-      <c r="E48" s="130" t="inlineStr">
-        <is>
-          <t>Leandro Bacuna</t>
-        </is>
-      </c>
-      <c r="F48" s="130" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B49" s="130" t="inlineStr">
-        <is>
-          <t>Iğdır</t>
-        </is>
-      </c>
-      <c r="C49" s="130" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D49" s="130" t="inlineStr">
-        <is>
-          <t>TFF 1. Lig</t>
-        </is>
-      </c>
-      <c r="E49" s="130" t="inlineStr">
-        <is>
-          <t>Ryan Mendes</t>
-        </is>
-      </c>
-      <c r="F49" s="130" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" s="130" t="inlineStr">
-        <is>
-          <t>Fortuna Düsseldorf</t>
-        </is>
-      </c>
-      <c r="C50" s="130" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D50" s="130" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E50" s="130" t="inlineStr">
-        <is>
-          <t>Cedric Itten</t>
-        </is>
-      </c>
-      <c r="F50" s="130" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" s="130" t="inlineStr">
-        <is>
-          <t>Hannover 96</t>
-        </is>
-      </c>
-      <c r="C51" s="130" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D51" s="130" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E51" s="130" t="inlineStr">
-        <is>
-          <t>Ime Okon</t>
-        </is>
-      </c>
-      <c r="F51" s="130" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B52" s="130" t="inlineStr">
-        <is>
-          <t>Hannover 96</t>
-        </is>
-      </c>
-      <c r="C52" s="130" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D52" s="130" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E52" s="130" t="inlineStr">
-        <is>
-          <t>​Elias Saad</t>
-        </is>
-      </c>
-      <c r="F52" s="130" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="130" t="inlineStr">
-        <is>
-          <t>Karlsruher SC</t>
-        </is>
-      </c>
-      <c r="C53" s="130" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D53" s="130" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E53" s="130" t="inlineStr">
-        <is>
-          <t>Dženis Burnić</t>
-        </is>
-      </c>
-      <c r="F53" s="130" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" s="130" t="inlineStr">
-        <is>
-          <t>Schalke 04</t>
-        </is>
-      </c>
-      <c r="C54" s="130" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D54" s="130" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E54" s="130" t="inlineStr">
-        <is>
-          <t>Edin Džeko</t>
-        </is>
-      </c>
-      <c r="F54" s="130" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" s="130" t="inlineStr">
-        <is>
-          <t>Schalke 04</t>
-        </is>
-      </c>
-      <c r="C55" s="130" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D55" s="130" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E55" s="130" t="inlineStr">
-        <is>
-          <t>Nikola Katić</t>
-        </is>
-      </c>
-      <c r="F55" s="130" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" s="130" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive FC</t>
-        </is>
-      </c>
-      <c r="C56" s="130" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D56" s="130" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E56" s="130" t="inlineStr">
-        <is>
-          <t>Carl-Fred Sainthe</t>
-        </is>
-      </c>
-      <c r="F56" s="130" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" s="130" t="inlineStr">
-        <is>
-          <t>Miami FC</t>
-        </is>
-      </c>
-      <c r="C57" s="130" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D57" s="130" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E57" s="130" t="inlineStr">
-        <is>
-          <t>Eloy Room</t>
-        </is>
-      </c>
-      <c r="F57" s="130" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="129" t="n">
-        <v>2</v>
-      </c>
-      <c r="B58" s="130" t="inlineStr">
-        <is>
-          <t>Miami FC</t>
-        </is>
-      </c>
-      <c r="C58" s="130" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D58" s="130" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E58" s="130" t="inlineStr">
-        <is>
-          <t>Jürgen Locadia</t>
-        </is>
-      </c>
-      <c r="F58" s="130" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="131" t="n">
-        <v>3</v>
-      </c>
-      <c r="B59" s="132" t="inlineStr">
-        <is>
-          <t>Port Vale</t>
-        </is>
-      </c>
-      <c r="C59" s="132" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D59" s="132" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E59" s="132" t="inlineStr">
-        <is>
-          <t>Ben Waine</t>
-        </is>
-      </c>
-      <c r="F59" s="132" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="131" t="n">
-        <v>3</v>
-      </c>
-      <c r="B60" s="132" t="inlineStr">
-        <is>
-          <t>Rotherham United</t>
-        </is>
-      </c>
-      <c r="C60" s="132" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D60" s="132" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E60" s="132" t="inlineStr">
-        <is>
-          <t>Ar’Jany Martha</t>
-        </is>
-      </c>
-      <c r="F60" s="132" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="131" t="n">
-        <v>3</v>
-      </c>
-      <c r="B61" s="132" t="inlineStr">
-        <is>
-          <t>FC Sochaux</t>
-        </is>
-      </c>
-      <c r="C61" s="132" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D61" s="132" t="inlineStr">
-        <is>
-          <t>National</t>
-        </is>
-      </c>
-      <c r="E61" s="132" t="inlineStr">
-        <is>
-          <t>Alexandre Pierre</t>
-        </is>
-      </c>
-      <c r="F61" s="132" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="131" t="n">
-        <v>3</v>
-      </c>
-      <c r="B62" s="132" t="inlineStr">
-        <is>
-          <t>BSC Young Boys II</t>
-        </is>
-      </c>
-      <c r="C62" s="132" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D62" s="132" t="inlineStr">
-        <is>
-          <t>Promotion League</t>
-        </is>
-      </c>
-      <c r="E62" s="132" t="inlineStr">
-        <is>
-          <t>Keeto Thermoncy</t>
-        </is>
-      </c>
-      <c r="F62" s="132" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="133" t="n">
-        <v>4</v>
-      </c>
-      <c r="B63" s="134" t="inlineStr">
-        <is>
-          <t>FC Cosmos Koblenz</t>
-        </is>
-      </c>
-      <c r="C63" s="134" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D63" s="134" t="inlineStr">
-        <is>
-          <t>Regionalliga</t>
-        </is>
-      </c>
-      <c r="E63" s="134" t="inlineStr">
-        <is>
-          <t>Josué Duverger</t>
-        </is>
-      </c>
-      <c r="F63" s="134" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="135" t="n">
-        <v>6</v>
-      </c>
-      <c r="B64" s="136" t="inlineStr">
-        <is>
-          <t>Braintree Town</t>
-        </is>
-      </c>
-      <c r="C64" s="136" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D64" s="136" t="inlineStr">
-        <is>
-          <t>National League South</t>
-        </is>
-      </c>
-      <c r="E64" s="136" t="inlineStr">
-        <is>
-          <t>Tommy Smith</t>
-        </is>
-      </c>
-      <c r="F64" s="136" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="32" t="inlineStr">
-        <is>
-          <t>Fargeforklaring:</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="137" t="inlineStr">
-        <is>
-          <t>Nivå 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="138" t="inlineStr">
-        <is>
-          <t>Nivå 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="139" t="inlineStr">
-        <is>
-          <t>Nivå 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="140" t="inlineStr">
-        <is>
-          <t>Nivå 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="141" t="inlineStr">
-        <is>
-          <t>Nivå 6</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A3:F3"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
@@ -51201,7 +49346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -51911,7 +50056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -53461,6 +51606,1933 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="143" min="1" max="1"/>
+    <col width="26" customWidth="1" style="143" min="2" max="2"/>
+    <col width="16" customWidth="1" style="143" min="3" max="3"/>
+    <col width="22" customWidth="1" style="143" min="4" max="4"/>
+    <col width="30" customWidth="1" style="143" min="5" max="5"/>
+    <col width="22" customWidth="1" style="143" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="173" t="inlineStr">
+        <is>
+          <t>Nivå</t>
+        </is>
+      </c>
+      <c r="B1" s="173" t="inlineStr">
+        <is>
+          <t>Klubb</t>
+        </is>
+      </c>
+      <c r="C1" s="173" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D1" s="173" t="inlineStr">
+        <is>
+          <t>Liga</t>
+        </is>
+      </c>
+      <c r="E1" s="173" t="inlineStr">
+        <is>
+          <t>Spiller</t>
+        </is>
+      </c>
+      <c r="F1" s="173" t="inlineStr">
+        <is>
+          <t>Nasjonallag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="175" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="C2" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D2" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E2" s="175" t="inlineStr">
+        <is>
+          <t>Lyndon Dykes</t>
+        </is>
+      </c>
+      <c r="F2" s="175" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="175" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="C3" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D3" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E3" s="175" t="inlineStr">
+        <is>
+          <t>Brandon Thomas-Asante</t>
+        </is>
+      </c>
+      <c r="F3" s="175" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="175" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="C4" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D4" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E4" s="175" t="inlineStr">
+        <is>
+          <t>Haji Wright</t>
+        </is>
+      </c>
+      <c r="F4" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="175" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="C5" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D5" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E5" s="175" t="inlineStr">
+        <is>
+          <t>Jacob Widell Zetterström</t>
+        </is>
+      </c>
+      <c r="F5" s="175" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="175" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="C6" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D6" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E6" s="175" t="inlineStr">
+        <is>
+          <t>Sondre Langås</t>
+        </is>
+      </c>
+      <c r="F6" s="175" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="175" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C7" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D7" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E7" s="175" t="inlineStr">
+        <is>
+          <t>Amir Hadžiahmetović</t>
+        </is>
+      </c>
+      <c r="F7" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="175" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C8" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D8" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E8" s="175" t="inlineStr">
+        <is>
+          <t>Ivor Pandur</t>
+        </is>
+      </c>
+      <c r="F8" s="175" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="175" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C9" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D9" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E9" s="175" t="inlineStr">
+        <is>
+          <t>Liam Miller</t>
+        </is>
+      </c>
+      <c r="F9" s="175" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="175" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C10" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D10" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E10" s="175" t="inlineStr">
+        <is>
+          <t>Alfie Jones</t>
+        </is>
+      </c>
+      <c r="F10" s="175" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="175" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C11" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D11" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E11" s="175" t="inlineStr">
+        <is>
+          <t>Sontje Hansen</t>
+        </is>
+      </c>
+      <c r="F11" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="175" t="inlineStr">
+        <is>
+          <t>Millwall FC</t>
+        </is>
+      </c>
+      <c r="C12" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D12" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E12" s="175" t="inlineStr">
+        <is>
+          <t>Max Crocombe</t>
+        </is>
+      </c>
+      <c r="F12" s="175" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C13" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D13" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E13" s="175" t="inlineStr">
+        <is>
+          <t>Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="F13" s="175" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C14" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D14" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E14" s="175" t="inlineStr">
+        <is>
+          <t>José Córdoba</t>
+        </is>
+      </c>
+      <c r="F14" s="175" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C15" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D15" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E15" s="175" t="inlineStr">
+        <is>
+          <t>Kenny McLean</t>
+        </is>
+      </c>
+      <c r="F15" s="175" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C16" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D16" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E16" s="175" t="inlineStr">
+        <is>
+          <t>Toure</t>
+        </is>
+      </c>
+      <c r="F16" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="175" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="C17" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D17" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E17" s="175" t="inlineStr">
+        <is>
+          <t>Gustavo Caballero</t>
+        </is>
+      </c>
+      <c r="F17" s="175" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="175" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="C18" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D18" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E18" s="175" t="inlineStr">
+        <is>
+          <t>Tahith Chong</t>
+        </is>
+      </c>
+      <c r="F18" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="175" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="C19" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D19" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E19" s="175" t="inlineStr">
+        <is>
+          <t>Viktor Johansson</t>
+        </is>
+      </c>
+      <c r="F19" s="175" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="175" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="C20" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D20" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E20" s="175" t="inlineStr">
+        <is>
+          <t>Eom Jisung</t>
+        </is>
+      </c>
+      <c r="F20" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="175" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="C21" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D21" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E21" s="175" t="inlineStr">
+        <is>
+          <t>Burgess</t>
+        </is>
+      </c>
+      <c r="F21" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="175" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="C22" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D22" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E22" s="175" t="inlineStr">
+        <is>
+          <t>Marko Stamenić</t>
+        </is>
+      </c>
+      <c r="F22" s="175" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="175" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C23" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D23" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E23" s="175" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="F23" s="175" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="175" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C24" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D24" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E24" s="175" t="inlineStr">
+        <is>
+          <t>Egil Selvik</t>
+        </is>
+      </c>
+      <c r="F24" s="175" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="175" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C25" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D25" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E25" s="175" t="inlineStr">
+        <is>
+          <t>Irankunda</t>
+        </is>
+      </c>
+      <c r="F25" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="175" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="C26" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D26" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E26" s="175" t="inlineStr">
+        <is>
+          <t>Dom Hyam</t>
+        </is>
+      </c>
+      <c r="F26" s="175" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="175" t="inlineStr">
+        <is>
+          <t>Wrexham AFC</t>
+        </is>
+      </c>
+      <c r="C27" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D27" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E27" s="175" t="inlineStr">
+        <is>
+          <t>Liberato Cacace</t>
+        </is>
+      </c>
+      <c r="F27" s="175" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="175" t="inlineStr">
+        <is>
+          <t>AS Nancy-Lorraine</t>
+        </is>
+      </c>
+      <c r="C28" s="175" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D28" s="175" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="E28" s="175" t="inlineStr">
+        <is>
+          <t>Martin Experience</t>
+        </is>
+      </c>
+      <c r="F28" s="175" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="175" t="inlineStr">
+        <is>
+          <t>SC Bastia</t>
+        </is>
+      </c>
+      <c r="C29" s="175" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D29" s="175" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="E29" s="175" t="inlineStr">
+        <is>
+          <t>Johnny Placide</t>
+        </is>
+      </c>
+      <c r="F29" s="175" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="175" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="C30" s="175" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D30" s="175" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="E30" s="175" t="inlineStr">
+        <is>
+          <t>Farès Ghedjemis</t>
+        </is>
+      </c>
+      <c r="F30" s="175" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="175" t="inlineStr">
+        <is>
+          <t>UC Sampdoria</t>
+        </is>
+      </c>
+      <c r="C31" s="175" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D31" s="175" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="E31" s="175" t="inlineStr">
+        <is>
+          <t>Dennis Hadžikadunić</t>
+        </is>
+      </c>
+      <c r="F31" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="175" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="C32" s="175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D32" s="175" t="inlineStr">
+        <is>
+          <t>J2 League</t>
+        </is>
+      </c>
+      <c r="E32" s="175" t="inlineStr">
+        <is>
+          <t>Geria</t>
+        </is>
+      </c>
+      <c r="F32" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="175" t="inlineStr">
+        <is>
+          <t>FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="C33" s="175" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D33" s="175" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="E33" s="175" t="inlineStr">
+        <is>
+          <t>Kevin Felida</t>
+        </is>
+      </c>
+      <c r="F33" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="175" t="inlineStr">
+        <is>
+          <t>VVV-Venlo</t>
+        </is>
+      </c>
+      <c r="C34" s="175" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D34" s="175" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="E34" s="175" t="inlineStr">
+        <is>
+          <t>Trevor Doornbusch</t>
+        </is>
+      </c>
+      <c r="F34" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="175" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="C35" s="175" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D35" s="175" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2</t>
+        </is>
+      </c>
+      <c r="E35" s="175" t="inlineStr">
+        <is>
+          <t>Josimar Dias "Vozinha"</t>
+        </is>
+      </c>
+      <c r="F35" s="175" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="175" t="inlineStr">
+        <is>
+          <t>Torreense</t>
+        </is>
+      </c>
+      <c r="C36" s="175" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D36" s="175" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2</t>
+        </is>
+      </c>
+      <c r="E36" s="175" t="inlineStr">
+        <is>
+          <t>Ianique Tavares "Stopira"</t>
+        </is>
+      </c>
+      <c r="F36" s="175" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="175" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C37" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D37" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E37" s="175" t="inlineStr">
+        <is>
+          <t>Brian Cipenga</t>
+        </is>
+      </c>
+      <c r="F37" s="175" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="175" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C38" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D38" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E38" s="175" t="inlineStr">
+        <is>
+          <t>Mabil</t>
+        </is>
+      </c>
+      <c r="F38" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="175" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa</t>
+        </is>
+      </c>
+      <c r="C39" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D39" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E39" s="175" t="inlineStr">
+        <is>
+          <t>Homam Al-Amin</t>
+        </is>
+      </c>
+      <c r="F39" s="175" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="175" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C40" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D40" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E40" s="175" t="inlineStr">
+        <is>
+          <t>Federico Viñas</t>
+        </is>
+      </c>
+      <c r="F40" s="175" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="175" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C41" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D41" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E41" s="175" t="inlineStr">
+        <is>
+          <t>Haissem Hassan</t>
+        </is>
+      </c>
+      <c r="F41" s="175" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="175" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C42" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D42" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E42" s="175" t="inlineStr">
+        <is>
+          <t>Kwasi Sibo</t>
+        </is>
+      </c>
+      <c r="F42" s="175" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="175" t="inlineStr">
+        <is>
+          <t>Stade Nyonnais</t>
+        </is>
+      </c>
+      <c r="C43" s="175" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D43" s="175" t="inlineStr">
+        <is>
+          <t>Challenge League</t>
+        </is>
+      </c>
+      <c r="E43" s="175" t="inlineStr">
+        <is>
+          <t>Melvin Mastil</t>
+        </is>
+      </c>
+      <c r="F43" s="175" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="175" t="inlineStr">
+        <is>
+          <t>IFK Norrköping</t>
+        </is>
+      </c>
+      <c r="C44" s="175" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D44" s="175" t="inlineStr">
+        <is>
+          <t>Superettan</t>
+        </is>
+      </c>
+      <c r="E44" s="175" t="inlineStr">
+        <is>
+          <t>Moutaz Neffati</t>
+        </is>
+      </c>
+      <c r="F44" s="175" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="175" t="inlineStr">
+        <is>
+          <t>Siwelele FC</t>
+        </is>
+      </c>
+      <c r="C45" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D45" s="175" t="inlineStr">
+        <is>
+          <t>National First Division</t>
+        </is>
+      </c>
+      <c r="E45" s="175" t="inlineStr">
+        <is>
+          <t>Ricardo Goss</t>
+        </is>
+      </c>
+      <c r="F45" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="175" t="inlineStr">
+        <is>
+          <t>Iğdır</t>
+        </is>
+      </c>
+      <c r="C46" s="175" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D46" s="175" t="inlineStr">
+        <is>
+          <t>TFF 1. Lig</t>
+        </is>
+      </c>
+      <c r="E46" s="175" t="inlineStr">
+        <is>
+          <t>Leandro Bacuna</t>
+        </is>
+      </c>
+      <c r="F46" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="175" t="inlineStr">
+        <is>
+          <t>Iğdır</t>
+        </is>
+      </c>
+      <c r="C47" s="175" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D47" s="175" t="inlineStr">
+        <is>
+          <t>TFF 1. Lig</t>
+        </is>
+      </c>
+      <c r="E47" s="175" t="inlineStr">
+        <is>
+          <t>Ryan Mendes</t>
+        </is>
+      </c>
+      <c r="F47" s="175" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="175" t="inlineStr">
+        <is>
+          <t>Fortuna Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C48" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D48" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E48" s="175" t="inlineStr">
+        <is>
+          <t>Cedric Itten</t>
+        </is>
+      </c>
+      <c r="F48" s="175" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" s="175" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="C49" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D49" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E49" s="175" t="inlineStr">
+        <is>
+          <t>Ime Okon</t>
+        </is>
+      </c>
+      <c r="F49" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" s="175" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="C50" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D50" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E50" s="175" t="inlineStr">
+        <is>
+          <t>​Elias Saad</t>
+        </is>
+      </c>
+      <c r="F50" s="175" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" s="175" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="C51" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D51" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E51" s="175" t="inlineStr">
+        <is>
+          <t>Dženis Burnić</t>
+        </is>
+      </c>
+      <c r="F51" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="175" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="C52" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D52" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E52" s="175" t="inlineStr">
+        <is>
+          <t>Edin Džeko</t>
+        </is>
+      </c>
+      <c r="F52" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" s="175" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="C53" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D53" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E53" s="175" t="inlineStr">
+        <is>
+          <t>Nikola Katić</t>
+        </is>
+      </c>
+      <c r="F53" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="175" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="C54" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D54" s="175" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E54" s="175" t="inlineStr">
+        <is>
+          <t>Carl-Fred Sainthe</t>
+        </is>
+      </c>
+      <c r="F54" s="175" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" s="175" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C55" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D55" s="175" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E55" s="175" t="inlineStr">
+        <is>
+          <t>Eloy Room</t>
+        </is>
+      </c>
+      <c r="F55" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="175" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C56" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D56" s="175" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E56" s="175" t="inlineStr">
+        <is>
+          <t>Jürgen Locadia</t>
+        </is>
+      </c>
+      <c r="F56" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="177" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="C57" s="177" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D57" s="177" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="E57" s="177" t="inlineStr">
+        <is>
+          <t>Ben Waine</t>
+        </is>
+      </c>
+      <c r="F57" s="177" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="177" t="inlineStr">
+        <is>
+          <t>Rotherham United</t>
+        </is>
+      </c>
+      <c r="C58" s="177" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D58" s="177" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="E58" s="177" t="inlineStr">
+        <is>
+          <t>Ar’Jany Martha</t>
+        </is>
+      </c>
+      <c r="F58" s="177" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" s="177" t="inlineStr">
+        <is>
+          <t>FC Sochaux</t>
+        </is>
+      </c>
+      <c r="C59" s="177" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D59" s="177" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="E59" s="177" t="inlineStr">
+        <is>
+          <t>Alexandre Pierre</t>
+        </is>
+      </c>
+      <c r="F59" s="177" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="177" t="inlineStr">
+        <is>
+          <t>BSC Young Boys II</t>
+        </is>
+      </c>
+      <c r="C60" s="177" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D60" s="177" t="inlineStr">
+        <is>
+          <t>Promotion League</t>
+        </is>
+      </c>
+      <c r="E60" s="177" t="inlineStr">
+        <is>
+          <t>Keeto Thermoncy</t>
+        </is>
+      </c>
+      <c r="F60" s="177" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="178" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" s="179" t="inlineStr">
+        <is>
+          <t>FC Cosmos Koblenz</t>
+        </is>
+      </c>
+      <c r="C61" s="179" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D61" s="179" t="inlineStr">
+        <is>
+          <t>Regionalliga</t>
+        </is>
+      </c>
+      <c r="E61" s="179" t="inlineStr">
+        <is>
+          <t>Josué Duverger</t>
+        </is>
+      </c>
+      <c r="F61" s="179" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="180" t="n">
+        <v>6</v>
+      </c>
+      <c r="B62" s="181" t="inlineStr">
+        <is>
+          <t>Braintree Town</t>
+        </is>
+      </c>
+      <c r="C62" s="181" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D62" s="181" t="inlineStr">
+        <is>
+          <t>National League South</t>
+        </is>
+      </c>
+      <c r="E62" s="181" t="inlineStr">
+        <is>
+          <t>Tommy Smith</t>
+        </is>
+      </c>
+      <c r="F62" s="181" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>Fargeforklaring:</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="182" t="inlineStr">
+        <is>
+          <t>Nivå 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="183" t="inlineStr">
+        <is>
+          <t>Nivå 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="184" t="inlineStr">
+        <is>
+          <t>Nivå 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="185" t="inlineStr">
+        <is>
+          <t>Nivå 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="186" t="inlineStr">
+        <is>
+          <t>Nivå 6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -28,13 +28,13 @@
     <sheet name="Klubber" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="Alder" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Spillere etter klubbland" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Nivå 2 og lavere" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Nivå 2 og lavere" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Spillere etter klubbland" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Klubber'!$A$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Spillere etter klubbland'!$A$3:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Nivå 2 og lavere'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Nivå 2 og lavere'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Spillere etter klubbland'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -50062,7 +50062,1934 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:F69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="143" min="1" max="1"/>
+    <col width="26" customWidth="1" style="143" min="2" max="2"/>
+    <col width="16" customWidth="1" style="143" min="3" max="3"/>
+    <col width="22" customWidth="1" style="143" min="4" max="4"/>
+    <col width="30" customWidth="1" style="143" min="5" max="5"/>
+    <col width="22" customWidth="1" style="143" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="173" t="inlineStr">
+        <is>
+          <t>Nivå</t>
+        </is>
+      </c>
+      <c r="B1" s="173" t="inlineStr">
+        <is>
+          <t>Klubb</t>
+        </is>
+      </c>
+      <c r="C1" s="173" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D1" s="173" t="inlineStr">
+        <is>
+          <t>Liga</t>
+        </is>
+      </c>
+      <c r="E1" s="173" t="inlineStr">
+        <is>
+          <t>Spiller</t>
+        </is>
+      </c>
+      <c r="F1" s="173" t="inlineStr">
+        <is>
+          <t>Nasjonallag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="175" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="C2" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D2" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E2" s="175" t="inlineStr">
+        <is>
+          <t>Lyndon Dykes</t>
+        </is>
+      </c>
+      <c r="F2" s="175" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="175" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="C3" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D3" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E3" s="175" t="inlineStr">
+        <is>
+          <t>Brandon Thomas-Asante</t>
+        </is>
+      </c>
+      <c r="F3" s="175" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="175" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="C4" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D4" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E4" s="175" t="inlineStr">
+        <is>
+          <t>Haji Wright</t>
+        </is>
+      </c>
+      <c r="F4" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="175" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="C5" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D5" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E5" s="175" t="inlineStr">
+        <is>
+          <t>Jacob Widell Zetterström</t>
+        </is>
+      </c>
+      <c r="F5" s="175" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="175" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="C6" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D6" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E6" s="175" t="inlineStr">
+        <is>
+          <t>Sondre Langås</t>
+        </is>
+      </c>
+      <c r="F6" s="175" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="175" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C7" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D7" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E7" s="175" t="inlineStr">
+        <is>
+          <t>Amir Hadžiahmetović</t>
+        </is>
+      </c>
+      <c r="F7" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="175" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C8" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D8" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E8" s="175" t="inlineStr">
+        <is>
+          <t>Ivor Pandur</t>
+        </is>
+      </c>
+      <c r="F8" s="175" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="175" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C9" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D9" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E9" s="175" t="inlineStr">
+        <is>
+          <t>Liam Miller</t>
+        </is>
+      </c>
+      <c r="F9" s="175" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="175" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C10" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D10" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E10" s="175" t="inlineStr">
+        <is>
+          <t>Alfie Jones</t>
+        </is>
+      </c>
+      <c r="F10" s="175" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="175" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C11" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D11" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E11" s="175" t="inlineStr">
+        <is>
+          <t>Sontje Hansen</t>
+        </is>
+      </c>
+      <c r="F11" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="175" t="inlineStr">
+        <is>
+          <t>Millwall FC</t>
+        </is>
+      </c>
+      <c r="C12" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D12" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E12" s="175" t="inlineStr">
+        <is>
+          <t>Max Crocombe</t>
+        </is>
+      </c>
+      <c r="F12" s="175" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C13" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D13" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E13" s="175" t="inlineStr">
+        <is>
+          <t>Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="F13" s="175" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C14" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D14" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E14" s="175" t="inlineStr">
+        <is>
+          <t>José Córdoba</t>
+        </is>
+      </c>
+      <c r="F14" s="175" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C15" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D15" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E15" s="175" t="inlineStr">
+        <is>
+          <t>Kenny McLean</t>
+        </is>
+      </c>
+      <c r="F15" s="175" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="175" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C16" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D16" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E16" s="175" t="inlineStr">
+        <is>
+          <t>Toure</t>
+        </is>
+      </c>
+      <c r="F16" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="175" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="C17" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D17" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E17" s="175" t="inlineStr">
+        <is>
+          <t>Gustavo Caballero</t>
+        </is>
+      </c>
+      <c r="F17" s="175" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="175" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="C18" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D18" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E18" s="175" t="inlineStr">
+        <is>
+          <t>Tahith Chong</t>
+        </is>
+      </c>
+      <c r="F18" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="175" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="C19" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D19" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E19" s="175" t="inlineStr">
+        <is>
+          <t>Viktor Johansson</t>
+        </is>
+      </c>
+      <c r="F19" s="175" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="175" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="C20" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D20" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E20" s="175" t="inlineStr">
+        <is>
+          <t>Eom Jisung</t>
+        </is>
+      </c>
+      <c r="F20" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="175" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="C21" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D21" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E21" s="175" t="inlineStr">
+        <is>
+          <t>Burgess</t>
+        </is>
+      </c>
+      <c r="F21" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="175" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="C22" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D22" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E22" s="175" t="inlineStr">
+        <is>
+          <t>Marko Stamenić</t>
+        </is>
+      </c>
+      <c r="F22" s="175" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="175" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C23" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D23" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E23" s="175" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="F23" s="175" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="175" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C24" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D24" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E24" s="175" t="inlineStr">
+        <is>
+          <t>Egil Selvik</t>
+        </is>
+      </c>
+      <c r="F24" s="175" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="175" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C25" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D25" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E25" s="175" t="inlineStr">
+        <is>
+          <t>Irankunda</t>
+        </is>
+      </c>
+      <c r="F25" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="175" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="C26" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D26" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E26" s="175" t="inlineStr">
+        <is>
+          <t>Dom Hyam</t>
+        </is>
+      </c>
+      <c r="F26" s="175" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="175" t="inlineStr">
+        <is>
+          <t>Wrexham AFC</t>
+        </is>
+      </c>
+      <c r="C27" s="175" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D27" s="175" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E27" s="175" t="inlineStr">
+        <is>
+          <t>Liberato Cacace</t>
+        </is>
+      </c>
+      <c r="F27" s="175" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="175" t="inlineStr">
+        <is>
+          <t>AS Nancy-Lorraine</t>
+        </is>
+      </c>
+      <c r="C28" s="175" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D28" s="175" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="E28" s="175" t="inlineStr">
+        <is>
+          <t>Martin Experience</t>
+        </is>
+      </c>
+      <c r="F28" s="175" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="175" t="inlineStr">
+        <is>
+          <t>SC Bastia</t>
+        </is>
+      </c>
+      <c r="C29" s="175" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D29" s="175" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="E29" s="175" t="inlineStr">
+        <is>
+          <t>Johnny Placide</t>
+        </is>
+      </c>
+      <c r="F29" s="175" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="175" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="C30" s="175" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D30" s="175" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="E30" s="175" t="inlineStr">
+        <is>
+          <t>Farès Ghedjemis</t>
+        </is>
+      </c>
+      <c r="F30" s="175" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="175" t="inlineStr">
+        <is>
+          <t>UC Sampdoria</t>
+        </is>
+      </c>
+      <c r="C31" s="175" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D31" s="175" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="E31" s="175" t="inlineStr">
+        <is>
+          <t>Dennis Hadžikadunić</t>
+        </is>
+      </c>
+      <c r="F31" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="175" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="C32" s="175" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D32" s="175" t="inlineStr">
+        <is>
+          <t>J2 League</t>
+        </is>
+      </c>
+      <c r="E32" s="175" t="inlineStr">
+        <is>
+          <t>Geria</t>
+        </is>
+      </c>
+      <c r="F32" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="175" t="inlineStr">
+        <is>
+          <t>FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="C33" s="175" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D33" s="175" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="E33" s="175" t="inlineStr">
+        <is>
+          <t>Kevin Felida</t>
+        </is>
+      </c>
+      <c r="F33" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="175" t="inlineStr">
+        <is>
+          <t>VVV-Venlo</t>
+        </is>
+      </c>
+      <c r="C34" s="175" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D34" s="175" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="E34" s="175" t="inlineStr">
+        <is>
+          <t>Trevor Doornbusch</t>
+        </is>
+      </c>
+      <c r="F34" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="175" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="C35" s="175" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D35" s="175" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2</t>
+        </is>
+      </c>
+      <c r="E35" s="175" t="inlineStr">
+        <is>
+          <t>Josimar Dias "Vozinha"</t>
+        </is>
+      </c>
+      <c r="F35" s="175" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="175" t="inlineStr">
+        <is>
+          <t>Torreense</t>
+        </is>
+      </c>
+      <c r="C36" s="175" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D36" s="175" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2</t>
+        </is>
+      </c>
+      <c r="E36" s="175" t="inlineStr">
+        <is>
+          <t>Ianique Tavares "Stopira"</t>
+        </is>
+      </c>
+      <c r="F36" s="175" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="175" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C37" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D37" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E37" s="175" t="inlineStr">
+        <is>
+          <t>Brian Cipenga</t>
+        </is>
+      </c>
+      <c r="F37" s="175" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="175" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C38" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D38" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E38" s="175" t="inlineStr">
+        <is>
+          <t>Mabil</t>
+        </is>
+      </c>
+      <c r="F38" s="175" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="175" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa</t>
+        </is>
+      </c>
+      <c r="C39" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D39" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E39" s="175" t="inlineStr">
+        <is>
+          <t>Homam Al-Amin</t>
+        </is>
+      </c>
+      <c r="F39" s="175" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="175" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C40" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D40" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E40" s="175" t="inlineStr">
+        <is>
+          <t>Federico Viñas</t>
+        </is>
+      </c>
+      <c r="F40" s="175" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="175" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C41" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D41" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E41" s="175" t="inlineStr">
+        <is>
+          <t>Haissem Hassan</t>
+        </is>
+      </c>
+      <c r="F41" s="175" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="175" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C42" s="175" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D42" s="175" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E42" s="175" t="inlineStr">
+        <is>
+          <t>Kwasi Sibo</t>
+        </is>
+      </c>
+      <c r="F42" s="175" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="175" t="inlineStr">
+        <is>
+          <t>Stade Nyonnais</t>
+        </is>
+      </c>
+      <c r="C43" s="175" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D43" s="175" t="inlineStr">
+        <is>
+          <t>Challenge League</t>
+        </is>
+      </c>
+      <c r="E43" s="175" t="inlineStr">
+        <is>
+          <t>Melvin Mastil</t>
+        </is>
+      </c>
+      <c r="F43" s="175" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="175" t="inlineStr">
+        <is>
+          <t>IFK Norrköping</t>
+        </is>
+      </c>
+      <c r="C44" s="175" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D44" s="175" t="inlineStr">
+        <is>
+          <t>Superettan</t>
+        </is>
+      </c>
+      <c r="E44" s="175" t="inlineStr">
+        <is>
+          <t>Moutaz Neffati</t>
+        </is>
+      </c>
+      <c r="F44" s="175" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="175" t="inlineStr">
+        <is>
+          <t>Siwelele FC</t>
+        </is>
+      </c>
+      <c r="C45" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D45" s="175" t="inlineStr">
+        <is>
+          <t>National First Division</t>
+        </is>
+      </c>
+      <c r="E45" s="175" t="inlineStr">
+        <is>
+          <t>Ricardo Goss</t>
+        </is>
+      </c>
+      <c r="F45" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="175" t="inlineStr">
+        <is>
+          <t>Iğdır</t>
+        </is>
+      </c>
+      <c r="C46" s="175" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D46" s="175" t="inlineStr">
+        <is>
+          <t>TFF 1. Lig</t>
+        </is>
+      </c>
+      <c r="E46" s="175" t="inlineStr">
+        <is>
+          <t>Leandro Bacuna</t>
+        </is>
+      </c>
+      <c r="F46" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="175" t="inlineStr">
+        <is>
+          <t>Iğdır</t>
+        </is>
+      </c>
+      <c r="C47" s="175" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D47" s="175" t="inlineStr">
+        <is>
+          <t>TFF 1. Lig</t>
+        </is>
+      </c>
+      <c r="E47" s="175" t="inlineStr">
+        <is>
+          <t>Ryan Mendes</t>
+        </is>
+      </c>
+      <c r="F47" s="175" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="175" t="inlineStr">
+        <is>
+          <t>Fortuna Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C48" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D48" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E48" s="175" t="inlineStr">
+        <is>
+          <t>Cedric Itten</t>
+        </is>
+      </c>
+      <c r="F48" s="175" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" s="175" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="C49" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D49" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E49" s="175" t="inlineStr">
+        <is>
+          <t>Ime Okon</t>
+        </is>
+      </c>
+      <c r="F49" s="175" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" s="175" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="C50" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D50" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E50" s="175" t="inlineStr">
+        <is>
+          <t>​Elias Saad</t>
+        </is>
+      </c>
+      <c r="F50" s="175" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" s="175" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="C51" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D51" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E51" s="175" t="inlineStr">
+        <is>
+          <t>Dženis Burnić</t>
+        </is>
+      </c>
+      <c r="F51" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="175" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="C52" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D52" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E52" s="175" t="inlineStr">
+        <is>
+          <t>Edin Džeko</t>
+        </is>
+      </c>
+      <c r="F52" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" s="175" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="C53" s="175" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D53" s="175" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E53" s="175" t="inlineStr">
+        <is>
+          <t>Nikola Katić</t>
+        </is>
+      </c>
+      <c r="F53" s="175" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="175" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="C54" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D54" s="175" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E54" s="175" t="inlineStr">
+        <is>
+          <t>Carl-Fred Sainthe</t>
+        </is>
+      </c>
+      <c r="F54" s="175" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" s="175" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C55" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D55" s="175" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E55" s="175" t="inlineStr">
+        <is>
+          <t>Eloy Room</t>
+        </is>
+      </c>
+      <c r="F55" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="175" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C56" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D56" s="175" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E56" s="175" t="inlineStr">
+        <is>
+          <t>Jürgen Locadia</t>
+        </is>
+      </c>
+      <c r="F56" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" s="177" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="C57" s="177" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D57" s="177" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="E57" s="177" t="inlineStr">
+        <is>
+          <t>Ben Waine</t>
+        </is>
+      </c>
+      <c r="F57" s="177" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="177" t="inlineStr">
+        <is>
+          <t>Rotherham United</t>
+        </is>
+      </c>
+      <c r="C58" s="177" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D58" s="177" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="E58" s="177" t="inlineStr">
+        <is>
+          <t>Ar’Jany Martha</t>
+        </is>
+      </c>
+      <c r="F58" s="177" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" s="177" t="inlineStr">
+        <is>
+          <t>FC Sochaux</t>
+        </is>
+      </c>
+      <c r="C59" s="177" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D59" s="177" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="E59" s="177" t="inlineStr">
+        <is>
+          <t>Alexandre Pierre</t>
+        </is>
+      </c>
+      <c r="F59" s="177" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="177" t="inlineStr">
+        <is>
+          <t>BSC Young Boys II</t>
+        </is>
+      </c>
+      <c r="C60" s="177" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D60" s="177" t="inlineStr">
+        <is>
+          <t>Promotion League</t>
+        </is>
+      </c>
+      <c r="E60" s="177" t="inlineStr">
+        <is>
+          <t>Keeto Thermoncy</t>
+        </is>
+      </c>
+      <c r="F60" s="177" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="178" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" s="179" t="inlineStr">
+        <is>
+          <t>FC Cosmos Koblenz</t>
+        </is>
+      </c>
+      <c r="C61" s="179" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D61" s="179" t="inlineStr">
+        <is>
+          <t>Regionalliga</t>
+        </is>
+      </c>
+      <c r="E61" s="179" t="inlineStr">
+        <is>
+          <t>Josué Duverger</t>
+        </is>
+      </c>
+      <c r="F61" s="179" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="180" t="n">
+        <v>6</v>
+      </c>
+      <c r="B62" s="181" t="inlineStr">
+        <is>
+          <t>Braintree Town</t>
+        </is>
+      </c>
+      <c r="C62" s="181" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D62" s="181" t="inlineStr">
+        <is>
+          <t>National League South</t>
+        </is>
+      </c>
+      <c r="E62" s="181" t="inlineStr">
+        <is>
+          <t>Tommy Smith</t>
+        </is>
+      </c>
+      <c r="F62" s="181" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>Fargeforklaring:</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="182" t="inlineStr">
+        <is>
+          <t>Nivå 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="183" t="inlineStr">
+        <is>
+          <t>Nivå 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="184" t="inlineStr">
+        <is>
+          <t>Nivå 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="185" t="inlineStr">
+        <is>
+          <t>Nivå 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="186" t="inlineStr">
+        <is>
+          <t>Nivå 6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="143" min="1" max="1"/>
@@ -50076,155 +52003,193 @@
     <col width="8" customWidth="1" style="143" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" s="143">
-      <c r="A1" s="150" t="inlineStr">
-        <is>
-          <t>VM 2026 — Spillere etter klubbland   68 land, 1248 spillere</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1" s="143"/>
-    <row r="3" ht="20" customHeight="1" s="143">
-      <c r="A3" s="151" t="inlineStr">
+    <row r="1" ht="20" customHeight="1" s="143">
+      <c r="A1" s="151" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="152" t="inlineStr">
+      <c r="B1" s="152" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="C3" s="151" t="inlineStr">
+      <c r="C1" s="151" t="inlineStr">
         <is>
           <t>Spillere</t>
         </is>
       </c>
-      <c r="D3" s="151" t="inlineStr">
+      <c r="D1" s="151" t="inlineStr">
         <is>
           <t>Nivå 1</t>
         </is>
       </c>
-      <c r="E3" s="151" t="inlineStr">
+      <c r="E1" s="151" t="inlineStr">
         <is>
           <t>Nivå 2</t>
         </is>
       </c>
-      <c r="F3" s="151" t="inlineStr">
+      <c r="F1" s="151" t="inlineStr">
         <is>
           <t>Nivå 3</t>
         </is>
       </c>
-      <c r="G3" s="151" t="inlineStr">
+      <c r="G1" s="151" t="inlineStr">
         <is>
           <t>Nivå 4</t>
         </is>
       </c>
-      <c r="H3" s="151" t="inlineStr">
+      <c r="H1" s="151" t="inlineStr">
         <is>
           <t>Nivå 5</t>
         </is>
       </c>
-      <c r="I3" s="151" t="inlineStr">
+      <c r="I1" s="151" t="inlineStr">
         <is>
           <t>Nivå 6</t>
         </is>
       </c>
     </row>
+    <row r="2" ht="17" customHeight="1" s="143">
+      <c r="A2" s="153" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="154" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C2" s="155" t="n">
+        <v>205</v>
+      </c>
+      <c r="D2" s="156" t="n">
+        <v>168</v>
+      </c>
+      <c r="E2" s="156" t="n">
+        <v>34</v>
+      </c>
+      <c r="F2" s="156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="156" t="inlineStr"/>
+      <c r="H2" s="156" t="inlineStr"/>
+      <c r="I2" s="156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1" s="143">
+      <c r="A3" s="157" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="158" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C3" s="159" t="n">
+        <v>111</v>
+      </c>
+      <c r="D3" s="160" t="n">
+        <v>101</v>
+      </c>
+      <c r="E3" s="160" t="n">
+        <v>9</v>
+      </c>
+      <c r="F3" s="160" t="inlineStr"/>
+      <c r="G3" s="160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="160" t="inlineStr"/>
+      <c r="I3" s="160" t="inlineStr"/>
+    </row>
     <row r="4" ht="17" customHeight="1" s="143">
-      <c r="A4" s="153" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="154" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C4" s="155" t="n">
-        <v>205</v>
-      </c>
-      <c r="D4" s="156" t="n">
-        <v>168</v>
-      </c>
-      <c r="E4" s="156" t="n">
-        <v>34</v>
-      </c>
-      <c r="F4" s="156" t="n">
+      <c r="A4" s="161" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="162" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C4" s="163" t="n">
+        <v>86</v>
+      </c>
+      <c r="D4" s="164" t="n">
+        <v>78</v>
+      </c>
+      <c r="E4" s="164" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="164" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="156" t="inlineStr"/>
-      <c r="H4" s="156" t="inlineStr"/>
-      <c r="I4" s="156" t="n">
-        <v>1</v>
-      </c>
+      <c r="G4" s="164" t="inlineStr"/>
+      <c r="H4" s="164" t="inlineStr"/>
+      <c r="I4" s="164" t="inlineStr"/>
     </row>
     <row r="5" ht="17" customHeight="1" s="143">
-      <c r="A5" s="157" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="158" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="C5" s="159" t="n">
-        <v>111</v>
-      </c>
-      <c r="D5" s="160" t="n">
-        <v>101</v>
-      </c>
-      <c r="E5" s="160" t="n">
-        <v>9</v>
-      </c>
-      <c r="F5" s="160" t="inlineStr"/>
-      <c r="G5" s="160" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="160" t="inlineStr"/>
-      <c r="I5" s="160" t="inlineStr"/>
+      <c r="A5" s="165" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="166" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C5" s="167" t="n">
+        <v>85</v>
+      </c>
+      <c r="D5" s="168" t="n">
+        <v>77</v>
+      </c>
+      <c r="E5" s="168" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="168" t="inlineStr"/>
+      <c r="G5" s="168" t="inlineStr"/>
+      <c r="H5" s="168" t="inlineStr"/>
+      <c r="I5" s="168" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1" s="143">
-      <c r="A6" s="161" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="162" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C6" s="163" t="n">
-        <v>86</v>
-      </c>
-      <c r="D6" s="164" t="n">
-        <v>78</v>
-      </c>
-      <c r="E6" s="164" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="164" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="164" t="inlineStr"/>
-      <c r="H6" s="164" t="inlineStr"/>
-      <c r="I6" s="164" t="inlineStr"/>
+      <c r="A6" s="169" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="170" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="C6" s="171" t="n">
+        <v>70</v>
+      </c>
+      <c r="D6" s="172" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" s="172" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="172" t="inlineStr"/>
+      <c r="G6" s="172" t="inlineStr"/>
+      <c r="H6" s="172" t="inlineStr"/>
+      <c r="I6" s="172" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="143">
       <c r="A7" s="165" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="166" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
       <c r="C7" s="167" t="n">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="D7" s="168" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="E7" s="168" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F7" s="168" t="inlineStr"/>
       <c r="G7" s="168" t="inlineStr"/>
@@ -50233,21 +52198,21 @@
     </row>
     <row r="8" ht="17" customHeight="1" s="143">
       <c r="A8" s="169" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="170" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>Tyrkia</t>
         </is>
       </c>
       <c r="C8" s="171" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D8" s="172" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E8" s="172" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F8" s="172" t="inlineStr"/>
       <c r="G8" s="172" t="inlineStr"/>
@@ -50256,21 +52221,21 @@
     </row>
     <row r="9" ht="17" customHeight="1" s="143">
       <c r="A9" s="165" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="166" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C9" s="167" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D9" s="168" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E9" s="168" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F9" s="168" t="inlineStr"/>
       <c r="G9" s="168" t="inlineStr"/>
@@ -50279,21 +52244,21 @@
     </row>
     <row r="10" ht="17" customHeight="1" s="143">
       <c r="A10" s="169" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="170" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="C10" s="171" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D10" s="172" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E10" s="172" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F10" s="172" t="inlineStr"/>
       <c r="G10" s="172" t="inlineStr"/>
@@ -50302,45 +52267,45 @@
     </row>
     <row r="11" ht="17" customHeight="1" s="143">
       <c r="A11" s="165" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" s="166" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C11" s="167" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D11" s="168" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E11" s="168" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="168" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F11" s="168" t="n">
+        <v>1</v>
+      </c>
       <c r="G11" s="168" t="inlineStr"/>
       <c r="H11" s="168" t="inlineStr"/>
       <c r="I11" s="168" t="inlineStr"/>
     </row>
     <row r="12" ht="17" customHeight="1" s="143">
       <c r="A12" s="169" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="170" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="C12" s="171" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D12" s="172" t="n">
-        <v>33</v>
-      </c>
-      <c r="E12" s="172" t="n">
-        <v>5</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E12" s="172" t="inlineStr"/>
       <c r="F12" s="172" t="inlineStr"/>
       <c r="G12" s="172" t="inlineStr"/>
       <c r="H12" s="172" t="inlineStr"/>
@@ -50348,43 +52313,41 @@
     </row>
     <row r="13" ht="17" customHeight="1" s="143">
       <c r="A13" s="165" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="166" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="C13" s="167" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" s="168" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E13" s="168" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="168" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F13" s="168" t="inlineStr"/>
       <c r="G13" s="168" t="inlineStr"/>
       <c r="H13" s="168" t="inlineStr"/>
       <c r="I13" s="168" t="inlineStr"/>
     </row>
     <row r="14" ht="17" customHeight="1" s="143">
       <c r="A14" s="169" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" s="170" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C14" s="171" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D14" s="172" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" s="172" t="inlineStr"/>
       <c r="F14" s="172" t="inlineStr"/>
@@ -50394,22 +52357,20 @@
     </row>
     <row r="15" ht="17" customHeight="1" s="143">
       <c r="A15" s="165" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B15" s="166" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C15" s="167" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D15" s="168" t="n">
-        <v>28</v>
-      </c>
-      <c r="E15" s="168" t="n">
-        <v>1</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E15" s="168" t="inlineStr"/>
       <c r="F15" s="168" t="inlineStr"/>
       <c r="G15" s="168" t="inlineStr"/>
       <c r="H15" s="168" t="inlineStr"/>
@@ -50417,18 +52378,18 @@
     </row>
     <row r="16" ht="17" customHeight="1" s="143">
       <c r="A16" s="169" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B16" s="170" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Tsjekkia</t>
         </is>
       </c>
       <c r="C16" s="171" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D16" s="172" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E16" s="172" t="inlineStr"/>
       <c r="F16" s="172" t="inlineStr"/>
@@ -50438,18 +52399,18 @@
     </row>
     <row r="17" ht="17" customHeight="1" s="143">
       <c r="A17" s="165" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" s="166" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C17" s="167" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D17" s="168" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E17" s="168" t="inlineStr"/>
       <c r="F17" s="168" t="inlineStr"/>
@@ -50459,18 +52420,18 @@
     </row>
     <row r="18" ht="17" customHeight="1" s="143">
       <c r="A18" s="169" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B18" s="170" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C18" s="171" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" s="172" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E18" s="172" t="inlineStr"/>
       <c r="F18" s="172" t="inlineStr"/>
@@ -50480,18 +52441,18 @@
     </row>
     <row r="19" ht="17" customHeight="1" s="143">
       <c r="A19" s="165" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B19" s="166" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C19" s="167" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D19" s="168" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" s="168" t="inlineStr"/>
       <c r="F19" s="168" t="inlineStr"/>
@@ -50501,20 +52462,22 @@
     </row>
     <row r="20" ht="17" customHeight="1" s="143">
       <c r="A20" s="169" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="170" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
       <c r="C20" s="171" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D20" s="172" t="n">
-        <v>21</v>
-      </c>
-      <c r="E20" s="172" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="E20" s="172" t="n">
+        <v>1</v>
+      </c>
       <c r="F20" s="172" t="inlineStr"/>
       <c r="G20" s="172" t="inlineStr"/>
       <c r="H20" s="172" t="inlineStr"/>
@@ -50522,18 +52485,18 @@
     </row>
     <row r="21" ht="17" customHeight="1" s="143">
       <c r="A21" s="165" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B21" s="166" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C21" s="167" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D21" s="168" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E21" s="168" t="inlineStr"/>
       <c r="F21" s="168" t="inlineStr"/>
@@ -50543,22 +52506,20 @@
     </row>
     <row r="22" ht="17" customHeight="1" s="143">
       <c r="A22" s="169" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B22" s="170" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Russland</t>
         </is>
       </c>
       <c r="C22" s="171" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D22" s="172" t="n">
-        <v>18</v>
-      </c>
-      <c r="E22" s="172" t="n">
-        <v>1</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E22" s="172" t="inlineStr"/>
       <c r="F22" s="172" t="inlineStr"/>
       <c r="G22" s="172" t="inlineStr"/>
       <c r="H22" s="172" t="inlineStr"/>
@@ -50566,18 +52527,18 @@
     </row>
     <row r="23" ht="17" customHeight="1" s="143">
       <c r="A23" s="165" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B23" s="166" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="C23" s="167" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D23" s="168" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E23" s="168" t="inlineStr"/>
       <c r="F23" s="168" t="inlineStr"/>
@@ -50587,18 +52548,18 @@
     </row>
     <row r="24" ht="17" customHeight="1" s="143">
       <c r="A24" s="169" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" s="170" t="inlineStr">
         <is>
-          <t>Russland</t>
+          <t>Usbekistan</t>
         </is>
       </c>
       <c r="C24" s="171" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="172" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="172" t="inlineStr"/>
       <c r="F24" s="172" t="inlineStr"/>
@@ -50608,20 +52569,22 @@
     </row>
     <row r="25" ht="17" customHeight="1" s="143">
       <c r="A25" s="165" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="166" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>UAE</t>
         </is>
       </c>
       <c r="C25" s="167" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="168" t="n">
-        <v>14</v>
-      </c>
-      <c r="E25" s="168" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="E25" s="168" t="n">
+        <v>3</v>
+      </c>
       <c r="F25" s="168" t="inlineStr"/>
       <c r="G25" s="168" t="inlineStr"/>
       <c r="H25" s="168" t="inlineStr"/>
@@ -50629,18 +52592,18 @@
     </row>
     <row r="26" ht="17" customHeight="1" s="143">
       <c r="A26" s="169" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B26" s="170" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>Hellas</t>
         </is>
       </c>
       <c r="C26" s="171" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="172" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" s="172" t="inlineStr"/>
       <c r="F26" s="172" t="inlineStr"/>
@@ -50650,22 +52613,20 @@
     </row>
     <row r="27" ht="17" customHeight="1" s="143">
       <c r="A27" s="165" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" s="166" t="inlineStr">
         <is>
-          <t>UAE</t>
+          <t>Danmark</t>
         </is>
       </c>
       <c r="C27" s="167" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" s="168" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="168" t="n">
-        <v>3</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="E27" s="168" t="inlineStr"/>
       <c r="F27" s="168" t="inlineStr"/>
       <c r="G27" s="168" t="inlineStr"/>
       <c r="H27" s="168" t="inlineStr"/>
@@ -50677,16 +52638,18 @@
       </c>
       <c r="B28" s="170" t="inlineStr">
         <is>
-          <t>Hellas</t>
+          <t>Sveits</t>
         </is>
       </c>
       <c r="C28" s="171" t="n">
         <v>12</v>
       </c>
       <c r="D28" s="172" t="n">
-        <v>12</v>
-      </c>
-      <c r="E28" s="172" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="E28" s="172" t="n">
+        <v>1</v>
+      </c>
       <c r="F28" s="172" t="inlineStr"/>
       <c r="G28" s="172" t="inlineStr"/>
       <c r="H28" s="172" t="inlineStr"/>
@@ -50698,7 +52661,7 @@
       </c>
       <c r="B29" s="166" t="inlineStr">
         <is>
-          <t>Danmark</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C29" s="167" t="n">
@@ -50715,22 +52678,20 @@
     </row>
     <row r="30" ht="17" customHeight="1" s="143">
       <c r="A30" s="169" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B30" s="170" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Kypros</t>
         </is>
       </c>
       <c r="C30" s="171" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D30" s="172" t="n">
-        <v>11</v>
-      </c>
-      <c r="E30" s="172" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E30" s="172" t="inlineStr"/>
       <c r="F30" s="172" t="inlineStr"/>
       <c r="G30" s="172" t="inlineStr"/>
       <c r="H30" s="172" t="inlineStr"/>
@@ -50738,18 +52699,18 @@
     </row>
     <row r="31" ht="17" customHeight="1" s="143">
       <c r="A31" s="165" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B31" s="166" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="C31" s="167" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="168" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E31" s="168" t="inlineStr"/>
       <c r="F31" s="168" t="inlineStr"/>
@@ -50759,18 +52720,18 @@
     </row>
     <row r="32" ht="17" customHeight="1" s="143">
       <c r="A32" s="169" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" s="170" t="inlineStr">
         <is>
-          <t>Kypros</t>
+          <t>Ny-Zealand</t>
         </is>
       </c>
       <c r="C32" s="171" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="172" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" s="172" t="inlineStr"/>
       <c r="F32" s="172" t="inlineStr"/>
@@ -50780,18 +52741,18 @@
     </row>
     <row r="33" ht="17" customHeight="1" s="143">
       <c r="A33" s="165" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B33" s="166" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="C33" s="167" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="168" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E33" s="168" t="inlineStr"/>
       <c r="F33" s="168" t="inlineStr"/>
@@ -50801,18 +52762,18 @@
     </row>
     <row r="34" ht="17" customHeight="1" s="143">
       <c r="A34" s="169" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B34" s="170" t="inlineStr">
         <is>
-          <t>Ny-Zealand</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C34" s="171" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" s="172" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E34" s="172" t="inlineStr"/>
       <c r="F34" s="172" t="inlineStr"/>
@@ -50822,20 +52783,22 @@
     </row>
     <row r="35" ht="17" customHeight="1" s="143">
       <c r="A35" s="165" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="166" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C35" s="167" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" s="168" t="n">
-        <v>8</v>
-      </c>
-      <c r="E35" s="168" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E35" s="168" t="n">
+        <v>1</v>
+      </c>
       <c r="F35" s="168" t="inlineStr"/>
       <c r="G35" s="168" t="inlineStr"/>
       <c r="H35" s="168" t="inlineStr"/>
@@ -50847,7 +52810,7 @@
       </c>
       <c r="B36" s="170" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C36" s="171" t="n">
@@ -50868,18 +52831,16 @@
       </c>
       <c r="B37" s="166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Polen</t>
         </is>
       </c>
       <c r="C37" s="167" t="n">
         <v>7</v>
       </c>
       <c r="D37" s="168" t="n">
-        <v>6</v>
-      </c>
-      <c r="E37" s="168" t="n">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E37" s="168" t="inlineStr"/>
       <c r="F37" s="168" t="inlineStr"/>
       <c r="G37" s="168" t="inlineStr"/>
       <c r="H37" s="168" t="inlineStr"/>
@@ -50891,7 +52852,7 @@
       </c>
       <c r="B38" s="170" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C38" s="171" t="n">
@@ -50908,18 +52869,18 @@
     </row>
     <row r="39" ht="17" customHeight="1" s="143">
       <c r="A39" s="165" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B39" s="166" t="inlineStr">
         <is>
-          <t>Polen</t>
+          <t>Kroatia</t>
         </is>
       </c>
       <c r="C39" s="167" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D39" s="168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39" s="168" t="inlineStr"/>
       <c r="F39" s="168" t="inlineStr"/>
@@ -50929,18 +52890,18 @@
     </row>
     <row r="40" ht="17" customHeight="1" s="143">
       <c r="A40" s="169" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B40" s="170" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C40" s="171" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D40" s="172" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="172" t="inlineStr"/>
       <c r="F40" s="172" t="inlineStr"/>
@@ -50950,18 +52911,18 @@
     </row>
     <row r="41" ht="17" customHeight="1" s="143">
       <c r="A41" s="165" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B41" s="166" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C41" s="167" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" s="168" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E41" s="168" t="inlineStr"/>
       <c r="F41" s="168" t="inlineStr"/>
@@ -50971,18 +52932,18 @@
     </row>
     <row r="42" ht="17" customHeight="1" s="143">
       <c r="A42" s="169" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B42" s="170" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C42" s="171" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" s="172" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E42" s="172" t="inlineStr"/>
       <c r="F42" s="172" t="inlineStr"/>
@@ -50996,16 +52957,18 @@
       </c>
       <c r="B43" s="166" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C43" s="167" t="n">
         <v>4</v>
       </c>
       <c r="D43" s="168" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="168" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E43" s="168" t="n">
+        <v>1</v>
+      </c>
       <c r="F43" s="168" t="inlineStr"/>
       <c r="G43" s="168" t="inlineStr"/>
       <c r="H43" s="168" t="inlineStr"/>
@@ -51017,7 +52980,7 @@
       </c>
       <c r="B44" s="170" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Aserbajdsjan</t>
         </is>
       </c>
       <c r="C44" s="171" t="n">
@@ -51038,18 +53001,16 @@
       </c>
       <c r="B45" s="166" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="C45" s="167" t="n">
         <v>4</v>
       </c>
       <c r="D45" s="168" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" s="168" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E45" s="168" t="inlineStr"/>
       <c r="F45" s="168" t="inlineStr"/>
       <c r="G45" s="168" t="inlineStr"/>
       <c r="H45" s="168" t="inlineStr"/>
@@ -51057,18 +53018,18 @@
     </row>
     <row r="46" ht="17" customHeight="1" s="143">
       <c r="A46" s="169" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B46" s="170" t="inlineStr">
         <is>
-          <t>Aserbajdsjan</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="C46" s="171" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D46" s="172" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" s="172" t="inlineStr"/>
       <c r="F46" s="172" t="inlineStr"/>
@@ -51078,18 +53039,18 @@
     </row>
     <row r="47" ht="17" customHeight="1" s="143">
       <c r="A47" s="165" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B47" s="166" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Ungarn</t>
         </is>
       </c>
       <c r="C47" s="167" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D47" s="168" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" s="168" t="inlineStr"/>
       <c r="F47" s="168" t="inlineStr"/>
@@ -51103,7 +53064,7 @@
       </c>
       <c r="B48" s="170" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C48" s="171" t="n">
@@ -51124,7 +53085,7 @@
       </c>
       <c r="B49" s="166" t="inlineStr">
         <is>
-          <t>Ungarn</t>
+          <t>Algerie</t>
         </is>
       </c>
       <c r="C49" s="167" t="n">
@@ -51141,18 +53102,18 @@
     </row>
     <row r="50" ht="17" customHeight="1" s="143">
       <c r="A50" s="169" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B50" s="170" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C50" s="171" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D50" s="172" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="172" t="inlineStr"/>
       <c r="F50" s="172" t="inlineStr"/>
@@ -51162,18 +53123,18 @@
     </row>
     <row r="51" ht="17" customHeight="1" s="143">
       <c r="A51" s="165" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B51" s="166" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C51" s="167" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D51" s="168" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" s="168" t="inlineStr"/>
       <c r="F51" s="168" t="inlineStr"/>
@@ -51187,7 +53148,7 @@
       </c>
       <c r="B52" s="170" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="C52" s="171" t="n">
@@ -51208,7 +53169,7 @@
       </c>
       <c r="B53" s="166" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C53" s="167" t="n">
@@ -51229,7 +53190,7 @@
       </c>
       <c r="B54" s="170" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Irland</t>
         </is>
       </c>
       <c r="C54" s="171" t="n">
@@ -51250,7 +53211,7 @@
       </c>
       <c r="B55" s="166" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C55" s="167" t="n">
@@ -51271,7 +53232,7 @@
       </c>
       <c r="B56" s="170" t="inlineStr">
         <is>
-          <t>Irland</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C56" s="171" t="n">
@@ -51292,7 +53253,7 @@
       </c>
       <c r="B57" s="166" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="C57" s="167" t="n">
@@ -51313,7 +53274,7 @@
       </c>
       <c r="B58" s="170" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C58" s="171" t="n">
@@ -51330,18 +53291,18 @@
     </row>
     <row r="59" ht="17" customHeight="1" s="143">
       <c r="A59" s="165" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B59" s="166" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Bosnia og Hercegovina</t>
         </is>
       </c>
       <c r="C59" s="167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D59" s="168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="168" t="inlineStr"/>
       <c r="F59" s="168" t="inlineStr"/>
@@ -51351,18 +53312,18 @@
     </row>
     <row r="60" ht="17" customHeight="1" s="143">
       <c r="A60" s="169" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B60" s="170" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Kasakhstan</t>
         </is>
       </c>
       <c r="C60" s="171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D60" s="172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" s="172" t="inlineStr"/>
       <c r="F60" s="172" t="inlineStr"/>
@@ -51376,7 +53337,7 @@
       </c>
       <c r="B61" s="166" t="inlineStr">
         <is>
-          <t>Bosnia og Hercegovina</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="C61" s="167" t="n">
@@ -51397,7 +53358,7 @@
       </c>
       <c r="B62" s="170" t="inlineStr">
         <is>
-          <t>Kasakhstan</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C62" s="171" t="n">
@@ -51418,7 +53379,7 @@
       </c>
       <c r="B63" s="166" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C63" s="167" t="n">
@@ -51439,7 +53400,7 @@
       </c>
       <c r="B64" s="170" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C64" s="171" t="n">
@@ -51460,7 +53421,7 @@
       </c>
       <c r="B65" s="166" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="C65" s="167" t="n">
@@ -51481,7 +53442,7 @@
       </c>
       <c r="B66" s="170" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C66" s="171" t="n">
@@ -51502,7 +53463,7 @@
       </c>
       <c r="B67" s="166" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C67" s="167" t="n">
@@ -51523,7 +53484,7 @@
       </c>
       <c r="B68" s="170" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C68" s="171" t="n">
@@ -51544,7 +53505,7 @@
       </c>
       <c r="B69" s="166" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C69" s="167" t="n">
@@ -51559,1980 +53520,8 @@
       <c r="H69" s="168" t="inlineStr"/>
       <c r="I69" s="168" t="inlineStr"/>
     </row>
-    <row r="70" ht="17" customHeight="1" s="143">
-      <c r="A70" s="169" t="n">
-        <v>58</v>
-      </c>
-      <c r="B70" s="170" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="C70" s="171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D70" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="172" t="inlineStr"/>
-      <c r="F70" s="172" t="inlineStr"/>
-      <c r="G70" s="172" t="inlineStr"/>
-      <c r="H70" s="172" t="inlineStr"/>
-      <c r="I70" s="172" t="inlineStr"/>
-    </row>
-    <row r="71" ht="17" customHeight="1" s="143">
-      <c r="A71" s="165" t="n">
-        <v>58</v>
-      </c>
-      <c r="B71" s="166" t="inlineStr">
-        <is>
-          <t>Honduras</t>
-        </is>
-      </c>
-      <c r="C71" s="167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="168" t="inlineStr"/>
-      <c r="F71" s="168" t="inlineStr"/>
-      <c r="G71" s="168" t="inlineStr"/>
-      <c r="H71" s="168" t="inlineStr"/>
-      <c r="I71" s="168" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:I3"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" style="143" min="1" max="1"/>
-    <col width="26" customWidth="1" style="143" min="2" max="2"/>
-    <col width="16" customWidth="1" style="143" min="3" max="3"/>
-    <col width="22" customWidth="1" style="143" min="4" max="4"/>
-    <col width="30" customWidth="1" style="143" min="5" max="5"/>
-    <col width="22" customWidth="1" style="143" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="173" t="inlineStr">
-        <is>
-          <t>Nivå</t>
-        </is>
-      </c>
-      <c r="B1" s="173" t="inlineStr">
-        <is>
-          <t>Klubb</t>
-        </is>
-      </c>
-      <c r="C1" s="173" t="inlineStr">
-        <is>
-          <t>Land</t>
-        </is>
-      </c>
-      <c r="D1" s="173" t="inlineStr">
-        <is>
-          <t>Liga</t>
-        </is>
-      </c>
-      <c r="E1" s="173" t="inlineStr">
-        <is>
-          <t>Spiller</t>
-        </is>
-      </c>
-      <c r="F1" s="173" t="inlineStr">
-        <is>
-          <t>Nasjonallag</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" s="175" t="inlineStr">
-        <is>
-          <t>Charlton Athletic</t>
-        </is>
-      </c>
-      <c r="C2" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D2" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E2" s="175" t="inlineStr">
-        <is>
-          <t>Lyndon Dykes</t>
-        </is>
-      </c>
-      <c r="F2" s="175" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="175" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="C3" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D3" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E3" s="175" t="inlineStr">
-        <is>
-          <t>Brandon Thomas-Asante</t>
-        </is>
-      </c>
-      <c r="F3" s="175" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="175" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="C4" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D4" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E4" s="175" t="inlineStr">
-        <is>
-          <t>Haji Wright</t>
-        </is>
-      </c>
-      <c r="F4" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="175" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="C5" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D5" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E5" s="175" t="inlineStr">
-        <is>
-          <t>Jacob Widell Zetterström</t>
-        </is>
-      </c>
-      <c r="F5" s="175" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="175" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="C6" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D6" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E6" s="175" t="inlineStr">
-        <is>
-          <t>Sondre Langås</t>
-        </is>
-      </c>
-      <c r="F6" s="175" t="inlineStr">
-        <is>
-          <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="175" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C7" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D7" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E7" s="175" t="inlineStr">
-        <is>
-          <t>Amir Hadžiahmetović</t>
-        </is>
-      </c>
-      <c r="F7" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="175" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C8" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D8" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E8" s="175" t="inlineStr">
-        <is>
-          <t>Ivor Pandur</t>
-        </is>
-      </c>
-      <c r="F8" s="175" t="inlineStr">
-        <is>
-          <t>Kroatia</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="175" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C9" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D9" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E9" s="175" t="inlineStr">
-        <is>
-          <t>Liam Miller</t>
-        </is>
-      </c>
-      <c r="F9" s="175" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="175" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="C10" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D10" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E10" s="175" t="inlineStr">
-        <is>
-          <t>Alfie Jones</t>
-        </is>
-      </c>
-      <c r="F10" s="175" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="175" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="C11" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D11" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E11" s="175" t="inlineStr">
-        <is>
-          <t>Sontje Hansen</t>
-        </is>
-      </c>
-      <c r="F11" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="175" t="inlineStr">
-        <is>
-          <t>Millwall FC</t>
-        </is>
-      </c>
-      <c r="C12" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D12" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E12" s="175" t="inlineStr">
-        <is>
-          <t>Max Crocombe</t>
-        </is>
-      </c>
-      <c r="F12" s="175" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C13" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D13" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E13" s="175" t="inlineStr">
-        <is>
-          <t>Ali Ahmed</t>
-        </is>
-      </c>
-      <c r="F13" s="175" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C14" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D14" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E14" s="175" t="inlineStr">
-        <is>
-          <t>José Córdoba</t>
-        </is>
-      </c>
-      <c r="F14" s="175" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C15" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D15" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E15" s="175" t="inlineStr">
-        <is>
-          <t>Kenny McLean</t>
-        </is>
-      </c>
-      <c r="F15" s="175" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C16" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D16" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E16" s="175" t="inlineStr">
-        <is>
-          <t>Toure</t>
-        </is>
-      </c>
-      <c r="F16" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="175" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="C17" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D17" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E17" s="175" t="inlineStr">
-        <is>
-          <t>Gustavo Caballero</t>
-        </is>
-      </c>
-      <c r="F17" s="175" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="175" t="inlineStr">
-        <is>
-          <t>Sheffield United</t>
-        </is>
-      </c>
-      <c r="C18" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D18" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E18" s="175" t="inlineStr">
-        <is>
-          <t>Tahith Chong</t>
-        </is>
-      </c>
-      <c r="F18" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="175" t="inlineStr">
-        <is>
-          <t>Stoke City</t>
-        </is>
-      </c>
-      <c r="C19" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D19" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E19" s="175" t="inlineStr">
-        <is>
-          <t>Viktor Johansson</t>
-        </is>
-      </c>
-      <c r="F19" s="175" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="175" t="inlineStr">
-        <is>
-          <t>Swansea</t>
-        </is>
-      </c>
-      <c r="C20" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D20" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E20" s="175" t="inlineStr">
-        <is>
-          <t>Eom Jisung</t>
-        </is>
-      </c>
-      <c r="F20" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="175" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="C21" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D21" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E21" s="175" t="inlineStr">
-        <is>
-          <t>Burgess</t>
-        </is>
-      </c>
-      <c r="F21" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="175" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="C22" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D22" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E22" s="175" t="inlineStr">
-        <is>
-          <t>Marko Stamenić</t>
-        </is>
-      </c>
-      <c r="F22" s="175" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="175" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C23" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D23" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E23" s="175" t="inlineStr">
-        <is>
-          <t>Edo Kayembe</t>
-        </is>
-      </c>
-      <c r="F23" s="175" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="175" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C24" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D24" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E24" s="175" t="inlineStr">
-        <is>
-          <t>Egil Selvik</t>
-        </is>
-      </c>
-      <c r="F24" s="175" t="inlineStr">
-        <is>
-          <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="175" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C25" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D25" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E25" s="175" t="inlineStr">
-        <is>
-          <t>Irankunda</t>
-        </is>
-      </c>
-      <c r="F25" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="175" t="inlineStr">
-        <is>
-          <t>Wrexham</t>
-        </is>
-      </c>
-      <c r="C26" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D26" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E26" s="175" t="inlineStr">
-        <is>
-          <t>Dom Hyam</t>
-        </is>
-      </c>
-      <c r="F26" s="175" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" s="175" t="inlineStr">
-        <is>
-          <t>Wrexham AFC</t>
-        </is>
-      </c>
-      <c r="C27" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D27" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E27" s="175" t="inlineStr">
-        <is>
-          <t>Liberato Cacace</t>
-        </is>
-      </c>
-      <c r="F27" s="175" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="175" t="inlineStr">
-        <is>
-          <t>AS Nancy-Lorraine</t>
-        </is>
-      </c>
-      <c r="C28" s="175" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D28" s="175" t="inlineStr">
-        <is>
-          <t>Ligue 2</t>
-        </is>
-      </c>
-      <c r="E28" s="175" t="inlineStr">
-        <is>
-          <t>Martin Experience</t>
-        </is>
-      </c>
-      <c r="F28" s="175" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="175" t="inlineStr">
-        <is>
-          <t>SC Bastia</t>
-        </is>
-      </c>
-      <c r="C29" s="175" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D29" s="175" t="inlineStr">
-        <is>
-          <t>Ligue 2</t>
-        </is>
-      </c>
-      <c r="E29" s="175" t="inlineStr">
-        <is>
-          <t>Johnny Placide</t>
-        </is>
-      </c>
-      <c r="F29" s="175" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="175" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
-      <c r="C30" s="175" t="inlineStr">
-        <is>
-          <t>Italia</t>
-        </is>
-      </c>
-      <c r="D30" s="175" t="inlineStr">
-        <is>
-          <t>Serie B</t>
-        </is>
-      </c>
-      <c r="E30" s="175" t="inlineStr">
-        <is>
-          <t>Farès Ghedjemis</t>
-        </is>
-      </c>
-      <c r="F30" s="175" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="175" t="inlineStr">
-        <is>
-          <t>UC Sampdoria</t>
-        </is>
-      </c>
-      <c r="C31" s="175" t="inlineStr">
-        <is>
-          <t>Italia</t>
-        </is>
-      </c>
-      <c r="D31" s="175" t="inlineStr">
-        <is>
-          <t>Serie B</t>
-        </is>
-      </c>
-      <c r="E31" s="175" t="inlineStr">
-        <is>
-          <t>Dennis Hadžikadunić</t>
-        </is>
-      </c>
-      <c r="F31" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="175" t="inlineStr">
-        <is>
-          <t>Albirex Niigata</t>
-        </is>
-      </c>
-      <c r="C32" s="175" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D32" s="175" t="inlineStr">
-        <is>
-          <t>J2 League</t>
-        </is>
-      </c>
-      <c r="E32" s="175" t="inlineStr">
-        <is>
-          <t>Geria</t>
-        </is>
-      </c>
-      <c r="F32" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="175" t="inlineStr">
-        <is>
-          <t>FC Den Bosch</t>
-        </is>
-      </c>
-      <c r="C33" s="175" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D33" s="175" t="inlineStr">
-        <is>
-          <t>Eerste Divisie</t>
-        </is>
-      </c>
-      <c r="E33" s="175" t="inlineStr">
-        <is>
-          <t>Kevin Felida</t>
-        </is>
-      </c>
-      <c r="F33" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="175" t="inlineStr">
-        <is>
-          <t>VVV-Venlo</t>
-        </is>
-      </c>
-      <c r="C34" s="175" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D34" s="175" t="inlineStr">
-        <is>
-          <t>Eerste Divisie</t>
-        </is>
-      </c>
-      <c r="E34" s="175" t="inlineStr">
-        <is>
-          <t>Trevor Doornbusch</t>
-        </is>
-      </c>
-      <c r="F34" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="175" t="inlineStr">
-        <is>
-          <t>Chaves</t>
-        </is>
-      </c>
-      <c r="C35" s="175" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D35" s="175" t="inlineStr">
-        <is>
-          <t>Liga Portugal 2</t>
-        </is>
-      </c>
-      <c r="E35" s="175" t="inlineStr">
-        <is>
-          <t>Josimar Dias "Vozinha"</t>
-        </is>
-      </c>
-      <c r="F35" s="175" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B36" s="175" t="inlineStr">
-        <is>
-          <t>Torreense</t>
-        </is>
-      </c>
-      <c r="C36" s="175" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D36" s="175" t="inlineStr">
-        <is>
-          <t>Liga Portugal 2</t>
-        </is>
-      </c>
-      <c r="E36" s="175" t="inlineStr">
-        <is>
-          <t>Ianique Tavares "Stopira"</t>
-        </is>
-      </c>
-      <c r="F36" s="175" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" s="175" t="inlineStr">
-        <is>
-          <t>Castellón</t>
-        </is>
-      </c>
-      <c r="C37" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D37" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E37" s="175" t="inlineStr">
-        <is>
-          <t>Brian Cipenga</t>
-        </is>
-      </c>
-      <c r="F37" s="175" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" s="175" t="inlineStr">
-        <is>
-          <t>Castellón</t>
-        </is>
-      </c>
-      <c r="C38" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D38" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E38" s="175" t="inlineStr">
-        <is>
-          <t>Mabil</t>
-        </is>
-      </c>
-      <c r="F38" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" s="175" t="inlineStr">
-        <is>
-          <t>Cultural Leonesa</t>
-        </is>
-      </c>
-      <c r="C39" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D39" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E39" s="175" t="inlineStr">
-        <is>
-          <t>Homam Al-Amin</t>
-        </is>
-      </c>
-      <c r="F39" s="175" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" s="175" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C40" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D40" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E40" s="175" t="inlineStr">
-        <is>
-          <t>Federico Viñas</t>
-        </is>
-      </c>
-      <c r="F40" s="175" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" s="175" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C41" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D41" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E41" s="175" t="inlineStr">
-        <is>
-          <t>Haissem Hassan</t>
-        </is>
-      </c>
-      <c r="F41" s="175" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" s="175" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C42" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D42" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E42" s="175" t="inlineStr">
-        <is>
-          <t>Kwasi Sibo</t>
-        </is>
-      </c>
-      <c r="F42" s="175" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" s="175" t="inlineStr">
-        <is>
-          <t>Stade Nyonnais</t>
-        </is>
-      </c>
-      <c r="C43" s="175" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D43" s="175" t="inlineStr">
-        <is>
-          <t>Challenge League</t>
-        </is>
-      </c>
-      <c r="E43" s="175" t="inlineStr">
-        <is>
-          <t>Melvin Mastil</t>
-        </is>
-      </c>
-      <c r="F43" s="175" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="175" t="inlineStr">
-        <is>
-          <t>IFK Norrköping</t>
-        </is>
-      </c>
-      <c r="C44" s="175" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D44" s="175" t="inlineStr">
-        <is>
-          <t>Superettan</t>
-        </is>
-      </c>
-      <c r="E44" s="175" t="inlineStr">
-        <is>
-          <t>Moutaz Neffati</t>
-        </is>
-      </c>
-      <c r="F44" s="175" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="175" t="inlineStr">
-        <is>
-          <t>Siwelele FC</t>
-        </is>
-      </c>
-      <c r="C45" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D45" s="175" t="inlineStr">
-        <is>
-          <t>National First Division</t>
-        </is>
-      </c>
-      <c r="E45" s="175" t="inlineStr">
-        <is>
-          <t>Ricardo Goss</t>
-        </is>
-      </c>
-      <c r="F45" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" s="175" t="inlineStr">
-        <is>
-          <t>Iğdır</t>
-        </is>
-      </c>
-      <c r="C46" s="175" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D46" s="175" t="inlineStr">
-        <is>
-          <t>TFF 1. Lig</t>
-        </is>
-      </c>
-      <c r="E46" s="175" t="inlineStr">
-        <is>
-          <t>Leandro Bacuna</t>
-        </is>
-      </c>
-      <c r="F46" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="175" t="inlineStr">
-        <is>
-          <t>Iğdır</t>
-        </is>
-      </c>
-      <c r="C47" s="175" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D47" s="175" t="inlineStr">
-        <is>
-          <t>TFF 1. Lig</t>
-        </is>
-      </c>
-      <c r="E47" s="175" t="inlineStr">
-        <is>
-          <t>Ryan Mendes</t>
-        </is>
-      </c>
-      <c r="F47" s="175" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B48" s="175" t="inlineStr">
-        <is>
-          <t>Fortuna Düsseldorf</t>
-        </is>
-      </c>
-      <c r="C48" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D48" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E48" s="175" t="inlineStr">
-        <is>
-          <t>Cedric Itten</t>
-        </is>
-      </c>
-      <c r="F48" s="175" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B49" s="175" t="inlineStr">
-        <is>
-          <t>Hannover 96</t>
-        </is>
-      </c>
-      <c r="C49" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D49" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E49" s="175" t="inlineStr">
-        <is>
-          <t>Ime Okon</t>
-        </is>
-      </c>
-      <c r="F49" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" s="175" t="inlineStr">
-        <is>
-          <t>Hannover 96</t>
-        </is>
-      </c>
-      <c r="C50" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D50" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E50" s="175" t="inlineStr">
-        <is>
-          <t>​Elias Saad</t>
-        </is>
-      </c>
-      <c r="F50" s="175" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" s="175" t="inlineStr">
-        <is>
-          <t>Karlsruher SC</t>
-        </is>
-      </c>
-      <c r="C51" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D51" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E51" s="175" t="inlineStr">
-        <is>
-          <t>Dženis Burnić</t>
-        </is>
-      </c>
-      <c r="F51" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B52" s="175" t="inlineStr">
-        <is>
-          <t>Schalke 04</t>
-        </is>
-      </c>
-      <c r="C52" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D52" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E52" s="175" t="inlineStr">
-        <is>
-          <t>Edin Džeko</t>
-        </is>
-      </c>
-      <c r="F52" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="175" t="inlineStr">
-        <is>
-          <t>Schalke 04</t>
-        </is>
-      </c>
-      <c r="C53" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D53" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E53" s="175" t="inlineStr">
-        <is>
-          <t>Nikola Katić</t>
-        </is>
-      </c>
-      <c r="F53" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" s="175" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive FC</t>
-        </is>
-      </c>
-      <c r="C54" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D54" s="175" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E54" s="175" t="inlineStr">
-        <is>
-          <t>Carl-Fred Sainthe</t>
-        </is>
-      </c>
-      <c r="F54" s="175" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" s="175" t="inlineStr">
-        <is>
-          <t>Miami FC</t>
-        </is>
-      </c>
-      <c r="C55" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D55" s="175" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E55" s="175" t="inlineStr">
-        <is>
-          <t>Eloy Room</t>
-        </is>
-      </c>
-      <c r="F55" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" s="175" t="inlineStr">
-        <is>
-          <t>Miami FC</t>
-        </is>
-      </c>
-      <c r="C56" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D56" s="175" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E56" s="175" t="inlineStr">
-        <is>
-          <t>Jürgen Locadia</t>
-        </is>
-      </c>
-      <c r="F56" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="177" t="inlineStr">
-        <is>
-          <t>Port Vale</t>
-        </is>
-      </c>
-      <c r="C57" s="177" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D57" s="177" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E57" s="177" t="inlineStr">
-        <is>
-          <t>Ben Waine</t>
-        </is>
-      </c>
-      <c r="F57" s="177" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="177" t="inlineStr">
-        <is>
-          <t>Rotherham United</t>
-        </is>
-      </c>
-      <c r="C58" s="177" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D58" s="177" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E58" s="177" t="inlineStr">
-        <is>
-          <t>Ar’Jany Martha</t>
-        </is>
-      </c>
-      <c r="F58" s="177" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B59" s="177" t="inlineStr">
-        <is>
-          <t>FC Sochaux</t>
-        </is>
-      </c>
-      <c r="C59" s="177" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D59" s="177" t="inlineStr">
-        <is>
-          <t>National</t>
-        </is>
-      </c>
-      <c r="E59" s="177" t="inlineStr">
-        <is>
-          <t>Alexandre Pierre</t>
-        </is>
-      </c>
-      <c r="F59" s="177" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B60" s="177" t="inlineStr">
-        <is>
-          <t>BSC Young Boys II</t>
-        </is>
-      </c>
-      <c r="C60" s="177" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D60" s="177" t="inlineStr">
-        <is>
-          <t>Promotion League</t>
-        </is>
-      </c>
-      <c r="E60" s="177" t="inlineStr">
-        <is>
-          <t>Keeto Thermoncy</t>
-        </is>
-      </c>
-      <c r="F60" s="177" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="178" t="n">
-        <v>4</v>
-      </c>
-      <c r="B61" s="179" t="inlineStr">
-        <is>
-          <t>FC Cosmos Koblenz</t>
-        </is>
-      </c>
-      <c r="C61" s="179" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D61" s="179" t="inlineStr">
-        <is>
-          <t>Regionalliga</t>
-        </is>
-      </c>
-      <c r="E61" s="179" t="inlineStr">
-        <is>
-          <t>Josué Duverger</t>
-        </is>
-      </c>
-      <c r="F61" s="179" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="180" t="n">
-        <v>6</v>
-      </c>
-      <c r="B62" s="181" t="inlineStr">
-        <is>
-          <t>Braintree Town</t>
-        </is>
-      </c>
-      <c r="C62" s="181" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D62" s="181" t="inlineStr">
-        <is>
-          <t>National League South</t>
-        </is>
-      </c>
-      <c r="E62" s="181" t="inlineStr">
-        <is>
-          <t>Tommy Smith</t>
-        </is>
-      </c>
-      <c r="F62" s="181" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="32" t="inlineStr">
-        <is>
-          <t>Fargeforklaring:</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="182" t="inlineStr">
-        <is>
-          <t>Nivå 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="183" t="inlineStr">
-        <is>
-          <t>Nivå 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="184" t="inlineStr">
-        <is>
-          <t>Nivå 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="185" t="inlineStr">
-        <is>
-          <t>Nivå 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="186" t="inlineStr">
-        <is>
-          <t>Nivå 6</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -33,8 +33,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Klubber'!$A$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Nivå 2 og lavere'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Spillere etter klubbland'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Nivå 2 og lavere'!$A$2:$F$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -817,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="188">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1337,6 +1337,9 @@
     <xf numFmtId="0" fontId="16" fillId="53" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="55" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="54" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="44" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -50062,7 +50065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="143" min="1" max="1"/>
@@ -50073,65 +50076,42 @@
     <col width="22" customWidth="1" style="143" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="173" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="143">
+      <c r="A1" s="150" t="inlineStr">
+        <is>
+          <t>VM 2026 — Spillere på nivå 2 og lavere   61 spillere</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="143">
+      <c r="A2" s="187" t="inlineStr">
         <is>
           <t>Nivå</t>
         </is>
       </c>
-      <c r="B1" s="173" t="inlineStr">
+      <c r="B2" s="187" t="inlineStr">
         <is>
           <t>Klubb</t>
         </is>
       </c>
-      <c r="C1" s="173" t="inlineStr">
+      <c r="C2" s="187" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="D1" s="173" t="inlineStr">
+      <c r="D2" s="187" t="inlineStr">
         <is>
           <t>Liga</t>
         </is>
       </c>
-      <c r="E1" s="173" t="inlineStr">
+      <c r="E2" s="187" t="inlineStr">
         <is>
           <t>Spiller</t>
         </is>
       </c>
-      <c r="F1" s="173" t="inlineStr">
+      <c r="F2" s="187" t="inlineStr">
         <is>
           <t>Nasjonallag</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" s="175" t="inlineStr">
-        <is>
-          <t>Charlton Athletic</t>
-        </is>
-      </c>
-      <c r="C2" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D2" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E2" s="175" t="inlineStr">
-        <is>
-          <t>Lyndon Dykes</t>
-        </is>
-      </c>
-      <c r="F2" s="175" t="inlineStr">
-        <is>
-          <t>Skottland</t>
         </is>
       </c>
     </row>
@@ -50141,7 +50121,7 @@
       </c>
       <c r="B3" s="175" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="C3" s="175" t="inlineStr">
@@ -50156,12 +50136,12 @@
       </c>
       <c r="E3" s="175" t="inlineStr">
         <is>
-          <t>Brandon Thomas-Asante</t>
+          <t>Lyndon Dykes</t>
         </is>
       </c>
       <c r="F3" s="175" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Skottland</t>
         </is>
       </c>
     </row>
@@ -50186,12 +50166,12 @@
       </c>
       <c r="E4" s="175" t="inlineStr">
         <is>
-          <t>Haji Wright</t>
+          <t>Brandon Thomas-Asante</t>
         </is>
       </c>
       <c r="F4" s="175" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ghana</t>
         </is>
       </c>
     </row>
@@ -50201,7 +50181,7 @@
       </c>
       <c r="B5" s="175" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="C5" s="175" t="inlineStr">
@@ -50216,12 +50196,12 @@
       </c>
       <c r="E5" s="175" t="inlineStr">
         <is>
-          <t>Jacob Widell Zetterström</t>
+          <t>Haji Wright</t>
         </is>
       </c>
       <c r="F5" s="175" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>USA</t>
         </is>
       </c>
     </row>
@@ -50246,12 +50226,12 @@
       </c>
       <c r="E6" s="175" t="inlineStr">
         <is>
-          <t>Sondre Langås</t>
+          <t>Jacob Widell Zetterström</t>
         </is>
       </c>
       <c r="F6" s="175" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Sverige</t>
         </is>
       </c>
     </row>
@@ -50261,7 +50241,7 @@
       </c>
       <c r="B7" s="175" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="C7" s="175" t="inlineStr">
@@ -50276,12 +50256,12 @@
       </c>
       <c r="E7" s="175" t="inlineStr">
         <is>
-          <t>Amir Hadžiahmetović</t>
+          <t>Sondre Langås</t>
         </is>
       </c>
       <c r="F7" s="175" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Norge</t>
         </is>
       </c>
     </row>
@@ -50306,12 +50286,12 @@
       </c>
       <c r="E8" s="175" t="inlineStr">
         <is>
-          <t>Ivor Pandur</t>
+          <t>Amir Hadžiahmetović</t>
         </is>
       </c>
       <c r="F8" s="175" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
     </row>
@@ -50336,12 +50316,12 @@
       </c>
       <c r="E9" s="175" t="inlineStr">
         <is>
-          <t>Liam Miller</t>
+          <t>Ivor Pandur</t>
         </is>
       </c>
       <c r="F9" s="175" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Kroatia</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50331,7 @@
       </c>
       <c r="B10" s="175" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="C10" s="175" t="inlineStr">
@@ -50366,7 +50346,7 @@
       </c>
       <c r="E10" s="175" t="inlineStr">
         <is>
-          <t>Alfie Jones</t>
+          <t>Liam Miller</t>
         </is>
       </c>
       <c r="F10" s="175" t="inlineStr">
@@ -50396,12 +50376,12 @@
       </c>
       <c r="E11" s="175" t="inlineStr">
         <is>
-          <t>Sontje Hansen</t>
+          <t>Alfie Jones</t>
         </is>
       </c>
       <c r="F11" s="175" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -50411,7 +50391,7 @@
       </c>
       <c r="B12" s="175" t="inlineStr">
         <is>
-          <t>Millwall FC</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="C12" s="175" t="inlineStr">
@@ -50426,12 +50406,12 @@
       </c>
       <c r="E12" s="175" t="inlineStr">
         <is>
-          <t>Max Crocombe</t>
+          <t>Sontje Hansen</t>
         </is>
       </c>
       <c r="F12" s="175" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -50441,7 +50421,7 @@
       </c>
       <c r="B13" s="175" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall FC</t>
         </is>
       </c>
       <c r="C13" s="175" t="inlineStr">
@@ -50456,12 +50436,12 @@
       </c>
       <c r="E13" s="175" t="inlineStr">
         <is>
-          <t>Ali Ahmed</t>
+          <t>Max Crocombe</t>
         </is>
       </c>
       <c r="F13" s="175" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
@@ -50486,12 +50466,12 @@
       </c>
       <c r="E14" s="175" t="inlineStr">
         <is>
-          <t>José Córdoba</t>
+          <t>Ali Ahmed</t>
         </is>
       </c>
       <c r="F14" s="175" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
@@ -50516,12 +50496,12 @@
       </c>
       <c r="E15" s="175" t="inlineStr">
         <is>
-          <t>Kenny McLean</t>
+          <t>José Córdoba</t>
         </is>
       </c>
       <c r="F15" s="175" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Panama</t>
         </is>
       </c>
     </row>
@@ -50546,12 +50526,12 @@
       </c>
       <c r="E16" s="175" t="inlineStr">
         <is>
-          <t>Toure</t>
+          <t>Kenny McLean</t>
         </is>
       </c>
       <c r="F16" s="175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Skottland</t>
         </is>
       </c>
     </row>
@@ -50561,7 +50541,7 @@
       </c>
       <c r="B17" s="175" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="C17" s="175" t="inlineStr">
@@ -50576,12 +50556,12 @@
       </c>
       <c r="E17" s="175" t="inlineStr">
         <is>
-          <t>Gustavo Caballero</t>
+          <t>Toure</t>
         </is>
       </c>
       <c r="F17" s="175" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -50591,7 +50571,7 @@
       </c>
       <c r="B18" s="175" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C18" s="175" t="inlineStr">
@@ -50606,12 +50586,12 @@
       </c>
       <c r="E18" s="175" t="inlineStr">
         <is>
-          <t>Tahith Chong</t>
+          <t>Gustavo Caballero</t>
         </is>
       </c>
       <c r="F18" s="175" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -50621,7 +50601,7 @@
       </c>
       <c r="B19" s="175" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="C19" s="175" t="inlineStr">
@@ -50636,12 +50616,12 @@
       </c>
       <c r="E19" s="175" t="inlineStr">
         <is>
-          <t>Viktor Johansson</t>
+          <t>Tahith Chong</t>
         </is>
       </c>
       <c r="F19" s="175" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -50651,7 +50631,7 @@
       </c>
       <c r="B20" s="175" t="inlineStr">
         <is>
-          <t>Swansea</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="C20" s="175" t="inlineStr">
@@ -50666,12 +50646,12 @@
       </c>
       <c r="E20" s="175" t="inlineStr">
         <is>
-          <t>Eom Jisung</t>
+          <t>Viktor Johansson</t>
         </is>
       </c>
       <c r="F20" s="175" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Sverige</t>
         </is>
       </c>
     </row>
@@ -50681,7 +50661,7 @@
       </c>
       <c r="B21" s="175" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Swansea</t>
         </is>
       </c>
       <c r="C21" s="175" t="inlineStr">
@@ -50696,12 +50676,12 @@
       </c>
       <c r="E21" s="175" t="inlineStr">
         <is>
-          <t>Burgess</t>
+          <t>Eom Jisung</t>
         </is>
       </c>
       <c r="F21" s="175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
     </row>
@@ -50726,12 +50706,12 @@
       </c>
       <c r="E22" s="175" t="inlineStr">
         <is>
-          <t>Marko Stamenić</t>
+          <t>Burgess</t>
         </is>
       </c>
       <c r="F22" s="175" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -50741,7 +50721,7 @@
       </c>
       <c r="B23" s="175" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="C23" s="175" t="inlineStr">
@@ -50756,12 +50736,12 @@
       </c>
       <c r="E23" s="175" t="inlineStr">
         <is>
-          <t>Edo Kayembe</t>
+          <t>Marko Stamenić</t>
         </is>
       </c>
       <c r="F23" s="175" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
@@ -50786,12 +50766,12 @@
       </c>
       <c r="E24" s="175" t="inlineStr">
         <is>
-          <t>Egil Selvik</t>
+          <t>Edo Kayembe</t>
         </is>
       </c>
       <c r="F24" s="175" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -50816,12 +50796,12 @@
       </c>
       <c r="E25" s="175" t="inlineStr">
         <is>
-          <t>Irankunda</t>
+          <t>Egil Selvik</t>
         </is>
       </c>
       <c r="F25" s="175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Norge</t>
         </is>
       </c>
     </row>
@@ -50831,7 +50811,7 @@
       </c>
       <c r="B26" s="175" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C26" s="175" t="inlineStr">
@@ -50846,12 +50826,12 @@
       </c>
       <c r="E26" s="175" t="inlineStr">
         <is>
-          <t>Dom Hyam</t>
+          <t>Irankunda</t>
         </is>
       </c>
       <c r="F26" s="175" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -50861,7 +50841,7 @@
       </c>
       <c r="B27" s="175" t="inlineStr">
         <is>
-          <t>Wrexham AFC</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="C27" s="175" t="inlineStr">
@@ -50876,12 +50856,12 @@
       </c>
       <c r="E27" s="175" t="inlineStr">
         <is>
-          <t>Liberato Cacace</t>
+          <t>Dom Hyam</t>
         </is>
       </c>
       <c r="F27" s="175" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Skottland</t>
         </is>
       </c>
     </row>
@@ -50891,27 +50871,27 @@
       </c>
       <c r="B28" s="175" t="inlineStr">
         <is>
-          <t>AS Nancy-Lorraine</t>
+          <t>Wrexham AFC</t>
         </is>
       </c>
       <c r="C28" s="175" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D28" s="175" t="inlineStr">
         <is>
-          <t>Ligue 2</t>
+          <t>Championship</t>
         </is>
       </c>
       <c r="E28" s="175" t="inlineStr">
         <is>
-          <t>Martin Experience</t>
+          <t>Liberato Cacace</t>
         </is>
       </c>
       <c r="F28" s="175" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
@@ -50921,7 +50901,7 @@
       </c>
       <c r="B29" s="175" t="inlineStr">
         <is>
-          <t>SC Bastia</t>
+          <t>AS Nancy-Lorraine</t>
         </is>
       </c>
       <c r="C29" s="175" t="inlineStr">
@@ -50936,7 +50916,7 @@
       </c>
       <c r="E29" s="175" t="inlineStr">
         <is>
-          <t>Johnny Placide</t>
+          <t>Martin Experience</t>
         </is>
       </c>
       <c r="F29" s="175" t="inlineStr">
@@ -50951,27 +50931,27 @@
       </c>
       <c r="B30" s="175" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>SC Bastia</t>
         </is>
       </c>
       <c r="C30" s="175" t="inlineStr">
         <is>
-          <t>Italia</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="D30" s="175" t="inlineStr">
         <is>
-          <t>Serie B</t>
+          <t>Ligue 2</t>
         </is>
       </c>
       <c r="E30" s="175" t="inlineStr">
         <is>
-          <t>Farès Ghedjemis</t>
+          <t>Johnny Placide</t>
         </is>
       </c>
       <c r="F30" s="175" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Haiti</t>
         </is>
       </c>
     </row>
@@ -50981,7 +50961,7 @@
       </c>
       <c r="B31" s="175" t="inlineStr">
         <is>
-          <t>UC Sampdoria</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="C31" s="175" t="inlineStr">
@@ -50996,12 +50976,12 @@
       </c>
       <c r="E31" s="175" t="inlineStr">
         <is>
-          <t>Dennis Hadžikadunić</t>
+          <t>Farès Ghedjemis</t>
         </is>
       </c>
       <c r="F31" s="175" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -51011,27 +50991,27 @@
       </c>
       <c r="B32" s="175" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>UC Sampdoria</t>
         </is>
       </c>
       <c r="C32" s="175" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Italia</t>
         </is>
       </c>
       <c r="D32" s="175" t="inlineStr">
         <is>
-          <t>J2 League</t>
+          <t>Serie B</t>
         </is>
       </c>
       <c r="E32" s="175" t="inlineStr">
         <is>
-          <t>Geria</t>
+          <t>Dennis Hadžikadunić</t>
         </is>
       </c>
       <c r="F32" s="175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
     </row>
@@ -51041,27 +51021,27 @@
       </c>
       <c r="B33" s="175" t="inlineStr">
         <is>
-          <t>FC Den Bosch</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="C33" s="175" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D33" s="175" t="inlineStr">
         <is>
-          <t>Eerste Divisie</t>
+          <t>J2 League</t>
         </is>
       </c>
       <c r="E33" s="175" t="inlineStr">
         <is>
-          <t>Kevin Felida</t>
+          <t>Geria</t>
         </is>
       </c>
       <c r="F33" s="175" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -51071,7 +51051,7 @@
       </c>
       <c r="B34" s="175" t="inlineStr">
         <is>
-          <t>VVV-Venlo</t>
+          <t>FC Den Bosch</t>
         </is>
       </c>
       <c r="C34" s="175" t="inlineStr">
@@ -51086,7 +51066,7 @@
       </c>
       <c r="E34" s="175" t="inlineStr">
         <is>
-          <t>Trevor Doornbusch</t>
+          <t>Kevin Felida</t>
         </is>
       </c>
       <c r="F34" s="175" t="inlineStr">
@@ -51101,27 +51081,27 @@
       </c>
       <c r="B35" s="175" t="inlineStr">
         <is>
-          <t>Chaves</t>
+          <t>VVV-Venlo</t>
         </is>
       </c>
       <c r="C35" s="175" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="D35" s="175" t="inlineStr">
         <is>
-          <t>Liga Portugal 2</t>
+          <t>Eerste Divisie</t>
         </is>
       </c>
       <c r="E35" s="175" t="inlineStr">
         <is>
-          <t>Josimar Dias "Vozinha"</t>
+          <t>Trevor Doornbusch</t>
         </is>
       </c>
       <c r="F35" s="175" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -51131,7 +51111,7 @@
       </c>
       <c r="B36" s="175" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Chaves</t>
         </is>
       </c>
       <c r="C36" s="175" t="inlineStr">
@@ -51146,7 +51126,7 @@
       </c>
       <c r="E36" s="175" t="inlineStr">
         <is>
-          <t>Ianique Tavares "Stopira"</t>
+          <t>Josimar Dias "Vozinha"</t>
         </is>
       </c>
       <c r="F36" s="175" t="inlineStr">
@@ -51161,27 +51141,27 @@
       </c>
       <c r="B37" s="175" t="inlineStr">
         <is>
-          <t>Castellón</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="C37" s="175" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D37" s="175" t="inlineStr">
         <is>
-          <t>Segunda División</t>
+          <t>Liga Portugal 2</t>
         </is>
       </c>
       <c r="E37" s="175" t="inlineStr">
         <is>
-          <t>Brian Cipenga</t>
+          <t>Ianique Tavares "Stopira"</t>
         </is>
       </c>
       <c r="F37" s="175" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
@@ -51206,12 +51186,12 @@
       </c>
       <c r="E38" s="175" t="inlineStr">
         <is>
-          <t>Mabil</t>
+          <t>Brian Cipenga</t>
         </is>
       </c>
       <c r="F38" s="175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -51221,7 +51201,7 @@
       </c>
       <c r="B39" s="175" t="inlineStr">
         <is>
-          <t>Cultural Leonesa</t>
+          <t>Castellón</t>
         </is>
       </c>
       <c r="C39" s="175" t="inlineStr">
@@ -51236,12 +51216,12 @@
       </c>
       <c r="E39" s="175" t="inlineStr">
         <is>
-          <t>Homam Al-Amin</t>
+          <t>Mabil</t>
         </is>
       </c>
       <c r="F39" s="175" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
@@ -51251,7 +51231,7 @@
       </c>
       <c r="B40" s="175" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Cultural Leonesa</t>
         </is>
       </c>
       <c r="C40" s="175" t="inlineStr">
@@ -51266,12 +51246,12 @@
       </c>
       <c r="E40" s="175" t="inlineStr">
         <is>
-          <t>Federico Viñas</t>
+          <t>Homam Al-Amin</t>
         </is>
       </c>
       <c r="F40" s="175" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Qatar</t>
         </is>
       </c>
     </row>
@@ -51296,12 +51276,12 @@
       </c>
       <c r="E41" s="175" t="inlineStr">
         <is>
-          <t>Haissem Hassan</t>
+          <t>Federico Viñas</t>
         </is>
       </c>
       <c r="F41" s="175" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Uruguay</t>
         </is>
       </c>
     </row>
@@ -51326,12 +51306,12 @@
       </c>
       <c r="E42" s="175" t="inlineStr">
         <is>
-          <t>Kwasi Sibo</t>
+          <t>Haissem Hassan</t>
         </is>
       </c>
       <c r="F42" s="175" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Egypt</t>
         </is>
       </c>
     </row>
@@ -51341,27 +51321,27 @@
       </c>
       <c r="B43" s="175" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="C43" s="175" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Spania</t>
         </is>
       </c>
       <c r="D43" s="175" t="inlineStr">
         <is>
-          <t>Challenge League</t>
+          <t>Segunda División</t>
         </is>
       </c>
       <c r="E43" s="175" t="inlineStr">
         <is>
-          <t>Melvin Mastil</t>
+          <t>Kwasi Sibo</t>
         </is>
       </c>
       <c r="F43" s="175" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Ghana</t>
         </is>
       </c>
     </row>
@@ -51371,27 +51351,27 @@
       </c>
       <c r="B44" s="175" t="inlineStr">
         <is>
-          <t>IFK Norrköping</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="C44" s="175" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Sveits</t>
         </is>
       </c>
       <c r="D44" s="175" t="inlineStr">
         <is>
-          <t>Superettan</t>
+          <t>Challenge League</t>
         </is>
       </c>
       <c r="E44" s="175" t="inlineStr">
         <is>
-          <t>Moutaz Neffati</t>
+          <t>Melvin Mastil</t>
         </is>
       </c>
       <c r="F44" s="175" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -51401,27 +51381,27 @@
       </c>
       <c r="B45" s="175" t="inlineStr">
         <is>
-          <t>Siwelele FC</t>
+          <t>IFK Norrköping</t>
         </is>
       </c>
       <c r="C45" s="175" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="D45" s="175" t="inlineStr">
         <is>
-          <t>National First Division</t>
+          <t>Superettan</t>
         </is>
       </c>
       <c r="E45" s="175" t="inlineStr">
         <is>
-          <t>Ricardo Goss</t>
+          <t>Moutaz Neffati</t>
         </is>
       </c>
       <c r="F45" s="175" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Tunisia</t>
         </is>
       </c>
     </row>
@@ -51431,27 +51411,27 @@
       </c>
       <c r="B46" s="175" t="inlineStr">
         <is>
-          <t>Iğdır</t>
+          <t>Siwelele FC</t>
         </is>
       </c>
       <c r="C46" s="175" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
       <c r="D46" s="175" t="inlineStr">
         <is>
-          <t>TFF 1. Lig</t>
+          <t>National First Division</t>
         </is>
       </c>
       <c r="E46" s="175" t="inlineStr">
         <is>
-          <t>Leandro Bacuna</t>
+          <t>Ricardo Goss</t>
         </is>
       </c>
       <c r="F46" s="175" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
     </row>
@@ -51476,12 +51456,12 @@
       </c>
       <c r="E47" s="175" t="inlineStr">
         <is>
-          <t>Ryan Mendes</t>
+          <t>Leandro Bacuna</t>
         </is>
       </c>
       <c r="F47" s="175" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -51491,27 +51471,27 @@
       </c>
       <c r="B48" s="175" t="inlineStr">
         <is>
-          <t>Fortuna Düsseldorf</t>
+          <t>Iğdır</t>
         </is>
       </c>
       <c r="C48" s="175" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Tyrkia</t>
         </is>
       </c>
       <c r="D48" s="175" t="inlineStr">
         <is>
-          <t>2. Bundesliga</t>
+          <t>TFF 1. Lig</t>
         </is>
       </c>
       <c r="E48" s="175" t="inlineStr">
         <is>
-          <t>Cedric Itten</t>
+          <t>Ryan Mendes</t>
         </is>
       </c>
       <c r="F48" s="175" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
@@ -51521,7 +51501,7 @@
       </c>
       <c r="B49" s="175" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Fortuna Düsseldorf</t>
         </is>
       </c>
       <c r="C49" s="175" t="inlineStr">
@@ -51536,12 +51516,12 @@
       </c>
       <c r="E49" s="175" t="inlineStr">
         <is>
-          <t>Ime Okon</t>
+          <t>Cedric Itten</t>
         </is>
       </c>
       <c r="F49" s="175" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Sveits</t>
         </is>
       </c>
     </row>
@@ -51566,12 +51546,12 @@
       </c>
       <c r="E50" s="175" t="inlineStr">
         <is>
-          <t>​Elias Saad</t>
+          <t>Ime Okon</t>
         </is>
       </c>
       <c r="F50" s="175" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
     </row>
@@ -51581,7 +51561,7 @@
       </c>
       <c r="B51" s="175" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="C51" s="175" t="inlineStr">
@@ -51596,12 +51576,12 @@
       </c>
       <c r="E51" s="175" t="inlineStr">
         <is>
-          <t>Dženis Burnić</t>
+          <t>​Elias Saad</t>
         </is>
       </c>
       <c r="F51" s="175" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Tunisia</t>
         </is>
       </c>
     </row>
@@ -51611,7 +51591,7 @@
       </c>
       <c r="B52" s="175" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="C52" s="175" t="inlineStr">
@@ -51626,7 +51606,7 @@
       </c>
       <c r="E52" s="175" t="inlineStr">
         <is>
-          <t>Edin Džeko</t>
+          <t>Dženis Burnić</t>
         </is>
       </c>
       <c r="F52" s="175" t="inlineStr">
@@ -51656,7 +51636,7 @@
       </c>
       <c r="E53" s="175" t="inlineStr">
         <is>
-          <t>Nikola Katić</t>
+          <t>Edin Džeko</t>
         </is>
       </c>
       <c r="F53" s="175" t="inlineStr">
@@ -51671,27 +51651,27 @@
       </c>
       <c r="B54" s="175" t="inlineStr">
         <is>
-          <t>El Paso Locomotive FC</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="C54" s="175" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="D54" s="175" t="inlineStr">
         <is>
-          <t>USL Championship</t>
+          <t>2. Bundesliga</t>
         </is>
       </c>
       <c r="E54" s="175" t="inlineStr">
         <is>
-          <t>Carl-Fred Sainthe</t>
+          <t>Nikola Katić</t>
         </is>
       </c>
       <c r="F54" s="175" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
     </row>
@@ -51701,7 +51681,7 @@
       </c>
       <c r="B55" s="175" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>El Paso Locomotive FC</t>
         </is>
       </c>
       <c r="C55" s="175" t="inlineStr">
@@ -51716,12 +51696,12 @@
       </c>
       <c r="E55" s="175" t="inlineStr">
         <is>
-          <t>Eloy Room</t>
+          <t>Carl-Fred Sainthe</t>
         </is>
       </c>
       <c r="F55" s="175" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Haiti</t>
         </is>
       </c>
     </row>
@@ -51746,42 +51726,42 @@
       </c>
       <c r="E56" s="175" t="inlineStr">
         <is>
+          <t>Eloy Room</t>
+        </is>
+      </c>
+      <c r="F56" s="175" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" s="175" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C57" s="175" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D57" s="175" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E57" s="175" t="inlineStr">
+        <is>
           <t>Jürgen Locadia</t>
         </is>
       </c>
-      <c r="F56" s="175" t="inlineStr">
+      <c r="F57" s="175" t="inlineStr">
         <is>
           <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B57" s="177" t="inlineStr">
-        <is>
-          <t>Port Vale</t>
-        </is>
-      </c>
-      <c r="C57" s="177" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D57" s="177" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E57" s="177" t="inlineStr">
-        <is>
-          <t>Ben Waine</t>
-        </is>
-      </c>
-      <c r="F57" s="177" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
         </is>
       </c>
     </row>
@@ -51791,7 +51771,7 @@
       </c>
       <c r="B58" s="177" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="C58" s="177" t="inlineStr">
@@ -51806,12 +51786,12 @@
       </c>
       <c r="E58" s="177" t="inlineStr">
         <is>
-          <t>Ar’Jany Martha</t>
+          <t>Ben Waine</t>
         </is>
       </c>
       <c r="F58" s="177" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
@@ -51821,27 +51801,27 @@
       </c>
       <c r="B59" s="177" t="inlineStr">
         <is>
-          <t>FC Sochaux</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="C59" s="177" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D59" s="177" t="inlineStr">
         <is>
-          <t>National</t>
+          <t>League One</t>
         </is>
       </c>
       <c r="E59" s="177" t="inlineStr">
         <is>
-          <t>Alexandre Pierre</t>
+          <t>Ar’Jany Martha</t>
         </is>
       </c>
       <c r="F59" s="177" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -51851,134 +51831,167 @@
       </c>
       <c r="B60" s="177" t="inlineStr">
         <is>
+          <t>FC Sochaux</t>
+        </is>
+      </c>
+      <c r="C60" s="177" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D60" s="177" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="E60" s="177" t="inlineStr">
+        <is>
+          <t>Alexandre Pierre</t>
+        </is>
+      </c>
+      <c r="F60" s="177" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="177" t="inlineStr">
+        <is>
           <t>BSC Young Boys II</t>
         </is>
       </c>
-      <c r="C60" s="177" t="inlineStr">
+      <c r="C61" s="177" t="inlineStr">
         <is>
           <t>Sveits</t>
         </is>
       </c>
-      <c r="D60" s="177" t="inlineStr">
+      <c r="D61" s="177" t="inlineStr">
         <is>
           <t>Promotion League</t>
         </is>
       </c>
-      <c r="E60" s="177" t="inlineStr">
+      <c r="E61" s="177" t="inlineStr">
         <is>
           <t>Keeto Thermoncy</t>
         </is>
       </c>
-      <c r="F60" s="177" t="inlineStr">
+      <c r="F61" s="177" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="178" t="n">
+    <row r="62">
+      <c r="A62" s="178" t="n">
         <v>4</v>
       </c>
-      <c r="B61" s="179" t="inlineStr">
+      <c r="B62" s="179" t="inlineStr">
         <is>
           <t>FC Cosmos Koblenz</t>
         </is>
       </c>
-      <c r="C61" s="179" t="inlineStr">
+      <c r="C62" s="179" t="inlineStr">
         <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="D61" s="179" t="inlineStr">
+      <c r="D62" s="179" t="inlineStr">
         <is>
           <t>Regionalliga</t>
         </is>
       </c>
-      <c r="E61" s="179" t="inlineStr">
+      <c r="E62" s="179" t="inlineStr">
         <is>
           <t>Josué Duverger</t>
         </is>
       </c>
-      <c r="F61" s="179" t="inlineStr">
+      <c r="F62" s="179" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="180" t="n">
+    <row r="63">
+      <c r="A63" s="180" t="n">
         <v>6</v>
       </c>
-      <c r="B62" s="181" t="inlineStr">
+      <c r="B63" s="181" t="inlineStr">
         <is>
           <t>Braintree Town</t>
         </is>
       </c>
-      <c r="C62" s="181" t="inlineStr">
+      <c r="C63" s="181" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D62" s="181" t="inlineStr">
+      <c r="D63" s="181" t="inlineStr">
         <is>
           <t>National League South</t>
         </is>
       </c>
-      <c r="E62" s="181" t="inlineStr">
+      <c r="E63" s="181" t="inlineStr">
         <is>
           <t>Tommy Smith</t>
         </is>
       </c>
-      <c r="F62" s="181" t="inlineStr">
+      <c r="F63" s="181" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="32" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="32" t="inlineStr">
         <is>
           <t>Fargeforklaring:</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="182" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="182" t="inlineStr">
         <is>
           <t>Nivå 2</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="183" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="183" t="inlineStr">
         <is>
           <t>Nivå 3</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="184" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="184" t="inlineStr">
         <is>
           <t>Nivå 4</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="185" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="185" t="inlineStr">
         <is>
           <t>Nivå 5</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="186" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="186" t="inlineStr">
         <is>
           <t>Nivå 6</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A2:F2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -51989,7 +52002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="143" min="1" max="1"/>
@@ -52003,1525 +52016,1535 @@
     <col width="8" customWidth="1" style="143" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" s="143">
-      <c r="A1" s="151" t="inlineStr">
+    <row r="1" ht="28" customHeight="1" s="143">
+      <c r="A1" s="150" t="inlineStr">
+        <is>
+          <t>VM 2026 — Spillere etter klubbland   68 land, 1248 spillere</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="143">
+      <c r="A2" s="151" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="152" t="inlineStr">
+      <c r="B2" s="152" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="C1" s="151" t="inlineStr">
+      <c r="C2" s="151" t="inlineStr">
         <is>
           <t>Spillere</t>
         </is>
       </c>
-      <c r="D1" s="151" t="inlineStr">
+      <c r="D2" s="151" t="inlineStr">
         <is>
           <t>Nivå 1</t>
         </is>
       </c>
-      <c r="E1" s="151" t="inlineStr">
+      <c r="E2" s="151" t="inlineStr">
         <is>
           <t>Nivå 2</t>
         </is>
       </c>
-      <c r="F1" s="151" t="inlineStr">
+      <c r="F2" s="151" t="inlineStr">
         <is>
           <t>Nivå 3</t>
         </is>
       </c>
-      <c r="G1" s="151" t="inlineStr">
+      <c r="G2" s="151" t="inlineStr">
         <is>
           <t>Nivå 4</t>
         </is>
       </c>
-      <c r="H1" s="151" t="inlineStr">
+      <c r="H2" s="151" t="inlineStr">
         <is>
           <t>Nivå 5</t>
         </is>
       </c>
-      <c r="I1" s="151" t="inlineStr">
+      <c r="I2" s="151" t="inlineStr">
         <is>
           <t>Nivå 6</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17" customHeight="1" s="143">
-      <c r="A2" s="153" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="154" t="inlineStr">
+    <row r="3" ht="17" customHeight="1" s="143">
+      <c r="A3" s="153" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="154" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="C2" s="155" t="n">
+      <c r="C3" s="155" t="n">
         <v>205</v>
       </c>
-      <c r="D2" s="156" t="n">
+      <c r="D3" s="156" t="n">
         <v>168</v>
       </c>
-      <c r="E2" s="156" t="n">
+      <c r="E3" s="156" t="n">
         <v>34</v>
       </c>
-      <c r="F2" s="156" t="n">
+      <c r="F3" s="156" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="156" t="inlineStr"/>
-      <c r="H2" s="156" t="inlineStr"/>
-      <c r="I2" s="156" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="17" customHeight="1" s="143">
-      <c r="A3" s="157" t="n">
+      <c r="G3" s="156" t="inlineStr"/>
+      <c r="H3" s="156" t="inlineStr"/>
+      <c r="I3" s="156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1" s="143">
+      <c r="A4" s="157" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="158" t="inlineStr">
+      <c r="B4" s="158" t="inlineStr">
         <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="C3" s="159" t="n">
+      <c r="C4" s="159" t="n">
         <v>111</v>
       </c>
-      <c r="D3" s="160" t="n">
+      <c r="D4" s="160" t="n">
         <v>101</v>
       </c>
-      <c r="E3" s="160" t="n">
+      <c r="E4" s="160" t="n">
         <v>9</v>
       </c>
-      <c r="F3" s="160" t="inlineStr"/>
-      <c r="G3" s="160" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="160" t="inlineStr"/>
-      <c r="I3" s="160" t="inlineStr"/>
-    </row>
-    <row r="4" ht="17" customHeight="1" s="143">
-      <c r="A4" s="161" t="n">
+      <c r="F4" s="160" t="inlineStr"/>
+      <c r="G4" s="160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="160" t="inlineStr"/>
+      <c r="I4" s="160" t="inlineStr"/>
+    </row>
+    <row r="5" ht="17" customHeight="1" s="143">
+      <c r="A5" s="161" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="162" t="inlineStr">
+      <c r="B5" s="162" t="inlineStr">
         <is>
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="C4" s="163" t="n">
+      <c r="C5" s="163" t="n">
         <v>86</v>
       </c>
-      <c r="D4" s="164" t="n">
+      <c r="D5" s="164" t="n">
         <v>78</v>
       </c>
-      <c r="E4" s="164" t="n">
+      <c r="E5" s="164" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="164" t="n">
+      <c r="F5" s="164" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="164" t="inlineStr"/>
-      <c r="H4" s="164" t="inlineStr"/>
-      <c r="I4" s="164" t="inlineStr"/>
-    </row>
-    <row r="5" ht="17" customHeight="1" s="143">
-      <c r="A5" s="165" t="n">
+      <c r="G5" s="164" t="inlineStr"/>
+      <c r="H5" s="164" t="inlineStr"/>
+      <c r="I5" s="164" t="inlineStr"/>
+    </row>
+    <row r="6" ht="17" customHeight="1" s="143">
+      <c r="A6" s="165" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="166" t="inlineStr">
+      <c r="B6" s="166" t="inlineStr">
         <is>
           <t>Spania</t>
         </is>
       </c>
-      <c r="C5" s="167" t="n">
+      <c r="C6" s="167" t="n">
         <v>85</v>
       </c>
-      <c r="D5" s="168" t="n">
+      <c r="D6" s="168" t="n">
         <v>77</v>
       </c>
-      <c r="E5" s="168" t="n">
+      <c r="E6" s="168" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="168" t="inlineStr"/>
-      <c r="G5" s="168" t="inlineStr"/>
-      <c r="H5" s="168" t="inlineStr"/>
-      <c r="I5" s="168" t="inlineStr"/>
-    </row>
-    <row r="6" ht="17" customHeight="1" s="143">
-      <c r="A6" s="169" t="n">
+      <c r="F6" s="168" t="inlineStr"/>
+      <c r="G6" s="168" t="inlineStr"/>
+      <c r="H6" s="168" t="inlineStr"/>
+      <c r="I6" s="168" t="inlineStr"/>
+    </row>
+    <row r="7" ht="17" customHeight="1" s="143">
+      <c r="A7" s="169" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="170" t="inlineStr">
+      <c r="B7" s="170" t="inlineStr">
         <is>
           <t>Italia</t>
         </is>
       </c>
-      <c r="C6" s="171" t="n">
+      <c r="C7" s="171" t="n">
         <v>70</v>
       </c>
-      <c r="D6" s="172" t="n">
+      <c r="D7" s="172" t="n">
         <v>65</v>
       </c>
-      <c r="E6" s="172" t="n">
+      <c r="E7" s="172" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="172" t="inlineStr"/>
-      <c r="G6" s="172" t="inlineStr"/>
-      <c r="H6" s="172" t="inlineStr"/>
-      <c r="I6" s="172" t="inlineStr"/>
-    </row>
-    <row r="7" ht="17" customHeight="1" s="143">
-      <c r="A7" s="165" t="n">
+      <c r="F7" s="172" t="inlineStr"/>
+      <c r="G7" s="172" t="inlineStr"/>
+      <c r="H7" s="172" t="inlineStr"/>
+      <c r="I7" s="172" t="inlineStr"/>
+    </row>
+    <row r="8" ht="17" customHeight="1" s="143">
+      <c r="A8" s="165" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="166" t="inlineStr">
+      <c r="B8" s="166" t="inlineStr">
         <is>
           <t>Saudi-Arabia</t>
         </is>
       </c>
-      <c r="C7" s="167" t="n">
+      <c r="C8" s="167" t="n">
         <v>51</v>
       </c>
-      <c r="D7" s="168" t="n">
+      <c r="D8" s="168" t="n">
         <v>50</v>
       </c>
-      <c r="E7" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="168" t="inlineStr"/>
-      <c r="G7" s="168" t="inlineStr"/>
-      <c r="H7" s="168" t="inlineStr"/>
-      <c r="I7" s="168" t="inlineStr"/>
-    </row>
-    <row r="8" ht="17" customHeight="1" s="143">
-      <c r="A8" s="169" t="n">
+      <c r="E8" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="168" t="inlineStr"/>
+      <c r="G8" s="168" t="inlineStr"/>
+      <c r="H8" s="168" t="inlineStr"/>
+      <c r="I8" s="168" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="143">
+      <c r="A9" s="169" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="170" t="inlineStr">
+      <c r="B9" s="170" t="inlineStr">
         <is>
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="C8" s="171" t="n">
+      <c r="C9" s="171" t="n">
         <v>45</v>
       </c>
-      <c r="D8" s="172" t="n">
+      <c r="D9" s="172" t="n">
         <v>43</v>
       </c>
-      <c r="E8" s="172" t="n">
+      <c r="E9" s="172" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="172" t="inlineStr"/>
-      <c r="G8" s="172" t="inlineStr"/>
-      <c r="H8" s="172" t="inlineStr"/>
-      <c r="I8" s="172" t="inlineStr"/>
-    </row>
-    <row r="9" ht="17" customHeight="1" s="143">
-      <c r="A9" s="165" t="n">
+      <c r="F9" s="172" t="inlineStr"/>
+      <c r="G9" s="172" t="inlineStr"/>
+      <c r="H9" s="172" t="inlineStr"/>
+      <c r="I9" s="172" t="inlineStr"/>
+    </row>
+    <row r="10" ht="17" customHeight="1" s="143">
+      <c r="A10" s="165" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="166" t="inlineStr">
+      <c r="B10" s="166" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C9" s="167" t="n">
+      <c r="C10" s="167" t="n">
         <v>41</v>
       </c>
-      <c r="D9" s="168" t="n">
+      <c r="D10" s="168" t="n">
         <v>36</v>
       </c>
-      <c r="E9" s="168" t="n">
+      <c r="E10" s="168" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="168" t="inlineStr"/>
-      <c r="G9" s="168" t="inlineStr"/>
-      <c r="H9" s="168" t="inlineStr"/>
-      <c r="I9" s="168" t="inlineStr"/>
-    </row>
-    <row r="10" ht="17" customHeight="1" s="143">
-      <c r="A10" s="169" t="n">
+      <c r="F10" s="168" t="inlineStr"/>
+      <c r="G10" s="168" t="inlineStr"/>
+      <c r="H10" s="168" t="inlineStr"/>
+      <c r="I10" s="168" t="inlineStr"/>
+    </row>
+    <row r="11" ht="17" customHeight="1" s="143">
+      <c r="A11" s="169" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="170" t="inlineStr">
+      <c r="B11" s="170" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="C10" s="171" t="n">
+      <c r="C11" s="171" t="n">
         <v>38</v>
       </c>
-      <c r="D10" s="172" t="n">
+      <c r="D11" s="172" t="n">
         <v>33</v>
       </c>
-      <c r="E10" s="172" t="n">
+      <c r="E11" s="172" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="172" t="inlineStr"/>
-      <c r="G10" s="172" t="inlineStr"/>
-      <c r="H10" s="172" t="inlineStr"/>
-      <c r="I10" s="172" t="inlineStr"/>
-    </row>
-    <row r="11" ht="17" customHeight="1" s="143">
-      <c r="A11" s="165" t="n">
+      <c r="F11" s="172" t="inlineStr"/>
+      <c r="G11" s="172" t="inlineStr"/>
+      <c r="H11" s="172" t="inlineStr"/>
+      <c r="I11" s="172" t="inlineStr"/>
+    </row>
+    <row r="12" ht="17" customHeight="1" s="143">
+      <c r="A12" s="165" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="166" t="inlineStr">
+      <c r="B12" s="166" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="C11" s="167" t="n">
+      <c r="C12" s="167" t="n">
         <v>32</v>
       </c>
-      <c r="D11" s="168" t="n">
+      <c r="D12" s="168" t="n">
         <v>29</v>
       </c>
-      <c r="E11" s="168" t="n">
+      <c r="E12" s="168" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="168" t="inlineStr"/>
-      <c r="H11" s="168" t="inlineStr"/>
-      <c r="I11" s="168" t="inlineStr"/>
-    </row>
-    <row r="12" ht="17" customHeight="1" s="143">
-      <c r="A12" s="169" t="n">
+      <c r="F12" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="168" t="inlineStr"/>
+      <c r="H12" s="168" t="inlineStr"/>
+      <c r="I12" s="168" t="inlineStr"/>
+    </row>
+    <row r="13" ht="17" customHeight="1" s="143">
+      <c r="A13" s="169" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="170" t="inlineStr">
+      <c r="B13" s="170" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
       </c>
-      <c r="C12" s="171" t="n">
+      <c r="C13" s="171" t="n">
         <v>31</v>
       </c>
-      <c r="D12" s="172" t="n">
+      <c r="D13" s="172" t="n">
         <v>31</v>
       </c>
-      <c r="E12" s="172" t="inlineStr"/>
-      <c r="F12" s="172" t="inlineStr"/>
-      <c r="G12" s="172" t="inlineStr"/>
-      <c r="H12" s="172" t="inlineStr"/>
-      <c r="I12" s="172" t="inlineStr"/>
-    </row>
-    <row r="13" ht="17" customHeight="1" s="143">
-      <c r="A13" s="165" t="n">
+      <c r="E13" s="172" t="inlineStr"/>
+      <c r="F13" s="172" t="inlineStr"/>
+      <c r="G13" s="172" t="inlineStr"/>
+      <c r="H13" s="172" t="inlineStr"/>
+      <c r="I13" s="172" t="inlineStr"/>
+    </row>
+    <row r="14" ht="17" customHeight="1" s="143">
+      <c r="A14" s="165" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="166" t="inlineStr">
+      <c r="B14" s="166" t="inlineStr">
         <is>
           <t>Belgia</t>
         </is>
       </c>
-      <c r="C13" s="167" t="n">
+      <c r="C14" s="167" t="n">
         <v>29</v>
       </c>
-      <c r="D13" s="168" t="n">
+      <c r="D14" s="168" t="n">
         <v>28</v>
       </c>
-      <c r="E13" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="168" t="inlineStr"/>
-      <c r="G13" s="168" t="inlineStr"/>
-      <c r="H13" s="168" t="inlineStr"/>
-      <c r="I13" s="168" t="inlineStr"/>
-    </row>
-    <row r="14" ht="17" customHeight="1" s="143">
-      <c r="A14" s="169" t="n">
+      <c r="E14" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="168" t="inlineStr"/>
+      <c r="G14" s="168" t="inlineStr"/>
+      <c r="H14" s="168" t="inlineStr"/>
+      <c r="I14" s="168" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1" s="143">
+      <c r="A15" s="169" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="170" t="inlineStr">
+      <c r="B15" s="170" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="C14" s="171" t="n">
+      <c r="C15" s="171" t="n">
         <v>29</v>
       </c>
-      <c r="D14" s="172" t="n">
+      <c r="D15" s="172" t="n">
         <v>29</v>
       </c>
-      <c r="E14" s="172" t="inlineStr"/>
-      <c r="F14" s="172" t="inlineStr"/>
-      <c r="G14" s="172" t="inlineStr"/>
-      <c r="H14" s="172" t="inlineStr"/>
-      <c r="I14" s="172" t="inlineStr"/>
-    </row>
-    <row r="15" ht="17" customHeight="1" s="143">
-      <c r="A15" s="165" t="n">
+      <c r="E15" s="172" t="inlineStr"/>
+      <c r="F15" s="172" t="inlineStr"/>
+      <c r="G15" s="172" t="inlineStr"/>
+      <c r="H15" s="172" t="inlineStr"/>
+      <c r="I15" s="172" t="inlineStr"/>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="143">
+      <c r="A16" s="165" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="166" t="inlineStr">
+      <c r="B16" s="166" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C15" s="167" t="n">
+      <c r="C16" s="167" t="n">
         <v>27</v>
       </c>
-      <c r="D15" s="168" t="n">
+      <c r="D16" s="168" t="n">
         <v>27</v>
       </c>
-      <c r="E15" s="168" t="inlineStr"/>
-      <c r="F15" s="168" t="inlineStr"/>
-      <c r="G15" s="168" t="inlineStr"/>
-      <c r="H15" s="168" t="inlineStr"/>
-      <c r="I15" s="168" t="inlineStr"/>
-    </row>
-    <row r="16" ht="17" customHeight="1" s="143">
-      <c r="A16" s="169" t="n">
+      <c r="E16" s="168" t="inlineStr"/>
+      <c r="F16" s="168" t="inlineStr"/>
+      <c r="G16" s="168" t="inlineStr"/>
+      <c r="H16" s="168" t="inlineStr"/>
+      <c r="I16" s="168" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17" customHeight="1" s="143">
+      <c r="A17" s="169" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="170" t="inlineStr">
+      <c r="B17" s="170" t="inlineStr">
         <is>
           <t>Tsjekkia</t>
         </is>
       </c>
-      <c r="C16" s="171" t="n">
+      <c r="C17" s="171" t="n">
         <v>22</v>
       </c>
-      <c r="D16" s="172" t="n">
+      <c r="D17" s="172" t="n">
         <v>22</v>
       </c>
-      <c r="E16" s="172" t="inlineStr"/>
-      <c r="F16" s="172" t="inlineStr"/>
-      <c r="G16" s="172" t="inlineStr"/>
-      <c r="H16" s="172" t="inlineStr"/>
-      <c r="I16" s="172" t="inlineStr"/>
-    </row>
-    <row r="17" ht="17" customHeight="1" s="143">
-      <c r="A17" s="165" t="n">
+      <c r="E17" s="172" t="inlineStr"/>
+      <c r="F17" s="172" t="inlineStr"/>
+      <c r="G17" s="172" t="inlineStr"/>
+      <c r="H17" s="172" t="inlineStr"/>
+      <c r="I17" s="172" t="inlineStr"/>
+    </row>
+    <row r="18" ht="17" customHeight="1" s="143">
+      <c r="A18" s="165" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="166" t="inlineStr">
+      <c r="B18" s="166" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="C17" s="167" t="n">
+      <c r="C18" s="167" t="n">
         <v>22</v>
       </c>
-      <c r="D17" s="168" t="n">
+      <c r="D18" s="168" t="n">
         <v>22</v>
       </c>
-      <c r="E17" s="168" t="inlineStr"/>
-      <c r="F17" s="168" t="inlineStr"/>
-      <c r="G17" s="168" t="inlineStr"/>
-      <c r="H17" s="168" t="inlineStr"/>
-      <c r="I17" s="168" t="inlineStr"/>
-    </row>
-    <row r="18" ht="17" customHeight="1" s="143">
-      <c r="A18" s="169" t="n">
+      <c r="E18" s="168" t="inlineStr"/>
+      <c r="F18" s="168" t="inlineStr"/>
+      <c r="G18" s="168" t="inlineStr"/>
+      <c r="H18" s="168" t="inlineStr"/>
+      <c r="I18" s="168" t="inlineStr"/>
+    </row>
+    <row r="19" ht="17" customHeight="1" s="143">
+      <c r="A19" s="169" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="170" t="inlineStr">
+      <c r="B19" s="170" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C18" s="171" t="n">
+      <c r="C19" s="171" t="n">
         <v>21</v>
       </c>
-      <c r="D18" s="172" t="n">
+      <c r="D19" s="172" t="n">
         <v>21</v>
       </c>
-      <c r="E18" s="172" t="inlineStr"/>
-      <c r="F18" s="172" t="inlineStr"/>
-      <c r="G18" s="172" t="inlineStr"/>
-      <c r="H18" s="172" t="inlineStr"/>
-      <c r="I18" s="172" t="inlineStr"/>
-    </row>
-    <row r="19" ht="17" customHeight="1" s="143">
-      <c r="A19" s="165" t="n">
+      <c r="E19" s="172" t="inlineStr"/>
+      <c r="F19" s="172" t="inlineStr"/>
+      <c r="G19" s="172" t="inlineStr"/>
+      <c r="H19" s="172" t="inlineStr"/>
+      <c r="I19" s="172" t="inlineStr"/>
+    </row>
+    <row r="20" ht="17" customHeight="1" s="143">
+      <c r="A20" s="165" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="166" t="inlineStr">
+      <c r="B20" s="166" t="inlineStr">
         <is>
           <t>Skottland</t>
         </is>
       </c>
-      <c r="C19" s="167" t="n">
+      <c r="C20" s="167" t="n">
         <v>20</v>
       </c>
-      <c r="D19" s="168" t="n">
+      <c r="D20" s="168" t="n">
         <v>20</v>
       </c>
-      <c r="E19" s="168" t="inlineStr"/>
-      <c r="F19" s="168" t="inlineStr"/>
-      <c r="G19" s="168" t="inlineStr"/>
-      <c r="H19" s="168" t="inlineStr"/>
-      <c r="I19" s="168" t="inlineStr"/>
-    </row>
-    <row r="20" ht="17" customHeight="1" s="143">
-      <c r="A20" s="169" t="n">
+      <c r="E20" s="168" t="inlineStr"/>
+      <c r="F20" s="168" t="inlineStr"/>
+      <c r="G20" s="168" t="inlineStr"/>
+      <c r="H20" s="168" t="inlineStr"/>
+      <c r="I20" s="168" t="inlineStr"/>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="143">
+      <c r="A21" s="169" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="170" t="inlineStr">
+      <c r="B21" s="170" t="inlineStr">
         <is>
           <t>Sør-Afrika</t>
         </is>
       </c>
-      <c r="C20" s="171" t="n">
+      <c r="C21" s="171" t="n">
         <v>19</v>
       </c>
-      <c r="D20" s="172" t="n">
+      <c r="D21" s="172" t="n">
         <v>18</v>
       </c>
-      <c r="E20" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="172" t="inlineStr"/>
-      <c r="G20" s="172" t="inlineStr"/>
-      <c r="H20" s="172" t="inlineStr"/>
-      <c r="I20" s="172" t="inlineStr"/>
-    </row>
-    <row r="21" ht="17" customHeight="1" s="143">
-      <c r="A21" s="165" t="n">
+      <c r="E21" s="172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="172" t="inlineStr"/>
+      <c r="G21" s="172" t="inlineStr"/>
+      <c r="H21" s="172" t="inlineStr"/>
+      <c r="I21" s="172" t="inlineStr"/>
+    </row>
+    <row r="22" ht="17" customHeight="1" s="143">
+      <c r="A22" s="165" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="166" t="inlineStr">
+      <c r="B22" s="166" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="C21" s="167" t="n">
+      <c r="C22" s="167" t="n">
         <v>16</v>
       </c>
-      <c r="D21" s="168" t="n">
+      <c r="D22" s="168" t="n">
         <v>16</v>
       </c>
-      <c r="E21" s="168" t="inlineStr"/>
-      <c r="F21" s="168" t="inlineStr"/>
-      <c r="G21" s="168" t="inlineStr"/>
-      <c r="H21" s="168" t="inlineStr"/>
-      <c r="I21" s="168" t="inlineStr"/>
-    </row>
-    <row r="22" ht="17" customHeight="1" s="143">
-      <c r="A22" s="169" t="n">
+      <c r="E22" s="168" t="inlineStr"/>
+      <c r="F22" s="168" t="inlineStr"/>
+      <c r="G22" s="168" t="inlineStr"/>
+      <c r="H22" s="168" t="inlineStr"/>
+      <c r="I22" s="168" t="inlineStr"/>
+    </row>
+    <row r="23" ht="17" customHeight="1" s="143">
+      <c r="A23" s="169" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="170" t="inlineStr">
+      <c r="B23" s="170" t="inlineStr">
         <is>
           <t>Russland</t>
         </is>
       </c>
-      <c r="C22" s="171" t="n">
+      <c r="C23" s="171" t="n">
         <v>15</v>
       </c>
-      <c r="D22" s="172" t="n">
+      <c r="D23" s="172" t="n">
         <v>15</v>
       </c>
-      <c r="E22" s="172" t="inlineStr"/>
-      <c r="F22" s="172" t="inlineStr"/>
-      <c r="G22" s="172" t="inlineStr"/>
-      <c r="H22" s="172" t="inlineStr"/>
-      <c r="I22" s="172" t="inlineStr"/>
-    </row>
-    <row r="23" ht="17" customHeight="1" s="143">
-      <c r="A23" s="165" t="n">
+      <c r="E23" s="172" t="inlineStr"/>
+      <c r="F23" s="172" t="inlineStr"/>
+      <c r="G23" s="172" t="inlineStr"/>
+      <c r="H23" s="172" t="inlineStr"/>
+      <c r="I23" s="172" t="inlineStr"/>
+    </row>
+    <row r="24" ht="17" customHeight="1" s="143">
+      <c r="A24" s="165" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="166" t="inlineStr">
+      <c r="B24" s="166" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="C23" s="167" t="n">
+      <c r="C24" s="167" t="n">
         <v>14</v>
       </c>
-      <c r="D23" s="168" t="n">
+      <c r="D24" s="168" t="n">
         <v>14</v>
       </c>
-      <c r="E23" s="168" t="inlineStr"/>
-      <c r="F23" s="168" t="inlineStr"/>
-      <c r="G23" s="168" t="inlineStr"/>
-      <c r="H23" s="168" t="inlineStr"/>
-      <c r="I23" s="168" t="inlineStr"/>
-    </row>
-    <row r="24" ht="17" customHeight="1" s="143">
-      <c r="A24" s="169" t="n">
+      <c r="E24" s="168" t="inlineStr"/>
+      <c r="F24" s="168" t="inlineStr"/>
+      <c r="G24" s="168" t="inlineStr"/>
+      <c r="H24" s="168" t="inlineStr"/>
+      <c r="I24" s="168" t="inlineStr"/>
+    </row>
+    <row r="25" ht="17" customHeight="1" s="143">
+      <c r="A25" s="169" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="170" t="inlineStr">
+      <c r="B25" s="170" t="inlineStr">
         <is>
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="C24" s="171" t="n">
+      <c r="C25" s="171" t="n">
         <v>14</v>
       </c>
-      <c r="D24" s="172" t="n">
+      <c r="D25" s="172" t="n">
         <v>14</v>
       </c>
-      <c r="E24" s="172" t="inlineStr"/>
-      <c r="F24" s="172" t="inlineStr"/>
-      <c r="G24" s="172" t="inlineStr"/>
-      <c r="H24" s="172" t="inlineStr"/>
-      <c r="I24" s="172" t="inlineStr"/>
-    </row>
-    <row r="25" ht="17" customHeight="1" s="143">
-      <c r="A25" s="165" t="n">
+      <c r="E25" s="172" t="inlineStr"/>
+      <c r="F25" s="172" t="inlineStr"/>
+      <c r="G25" s="172" t="inlineStr"/>
+      <c r="H25" s="172" t="inlineStr"/>
+      <c r="I25" s="172" t="inlineStr"/>
+    </row>
+    <row r="26" ht="17" customHeight="1" s="143">
+      <c r="A26" s="165" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="166" t="inlineStr">
+      <c r="B26" s="166" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="C25" s="167" t="n">
+      <c r="C26" s="167" t="n">
         <v>13</v>
       </c>
-      <c r="D25" s="168" t="n">
+      <c r="D26" s="168" t="n">
         <v>10</v>
       </c>
-      <c r="E25" s="168" t="n">
+      <c r="E26" s="168" t="n">
         <v>3</v>
       </c>
-      <c r="F25" s="168" t="inlineStr"/>
-      <c r="G25" s="168" t="inlineStr"/>
-      <c r="H25" s="168" t="inlineStr"/>
-      <c r="I25" s="168" t="inlineStr"/>
-    </row>
-    <row r="26" ht="17" customHeight="1" s="143">
-      <c r="A26" s="169" t="n">
+      <c r="F26" s="168" t="inlineStr"/>
+      <c r="G26" s="168" t="inlineStr"/>
+      <c r="H26" s="168" t="inlineStr"/>
+      <c r="I26" s="168" t="inlineStr"/>
+    </row>
+    <row r="27" ht="17" customHeight="1" s="143">
+      <c r="A27" s="169" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="170" t="inlineStr">
+      <c r="B27" s="170" t="inlineStr">
         <is>
           <t>Hellas</t>
         </is>
       </c>
-      <c r="C26" s="171" t="n">
+      <c r="C27" s="171" t="n">
         <v>12</v>
       </c>
-      <c r="D26" s="172" t="n">
+      <c r="D27" s="172" t="n">
         <v>12</v>
       </c>
-      <c r="E26" s="172" t="inlineStr"/>
-      <c r="F26" s="172" t="inlineStr"/>
-      <c r="G26" s="172" t="inlineStr"/>
-      <c r="H26" s="172" t="inlineStr"/>
-      <c r="I26" s="172" t="inlineStr"/>
-    </row>
-    <row r="27" ht="17" customHeight="1" s="143">
-      <c r="A27" s="165" t="n">
+      <c r="E27" s="172" t="inlineStr"/>
+      <c r="F27" s="172" t="inlineStr"/>
+      <c r="G27" s="172" t="inlineStr"/>
+      <c r="H27" s="172" t="inlineStr"/>
+      <c r="I27" s="172" t="inlineStr"/>
+    </row>
+    <row r="28" ht="17" customHeight="1" s="143">
+      <c r="A28" s="165" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="166" t="inlineStr">
+      <c r="B28" s="166" t="inlineStr">
         <is>
           <t>Danmark</t>
         </is>
       </c>
-      <c r="C27" s="167" t="n">
+      <c r="C28" s="167" t="n">
         <v>12</v>
       </c>
-      <c r="D27" s="168" t="n">
+      <c r="D28" s="168" t="n">
         <v>12</v>
       </c>
-      <c r="E27" s="168" t="inlineStr"/>
-      <c r="F27" s="168" t="inlineStr"/>
-      <c r="G27" s="168" t="inlineStr"/>
-      <c r="H27" s="168" t="inlineStr"/>
-      <c r="I27" s="168" t="inlineStr"/>
-    </row>
-    <row r="28" ht="17" customHeight="1" s="143">
-      <c r="A28" s="169" t="n">
+      <c r="E28" s="168" t="inlineStr"/>
+      <c r="F28" s="168" t="inlineStr"/>
+      <c r="G28" s="168" t="inlineStr"/>
+      <c r="H28" s="168" t="inlineStr"/>
+      <c r="I28" s="168" t="inlineStr"/>
+    </row>
+    <row r="29" ht="17" customHeight="1" s="143">
+      <c r="A29" s="169" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="170" t="inlineStr">
+      <c r="B29" s="170" t="inlineStr">
         <is>
           <t>Sveits</t>
         </is>
       </c>
-      <c r="C28" s="171" t="n">
+      <c r="C29" s="171" t="n">
         <v>12</v>
       </c>
-      <c r="D28" s="172" t="n">
+      <c r="D29" s="172" t="n">
         <v>11</v>
       </c>
-      <c r="E28" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="172" t="inlineStr"/>
-      <c r="G28" s="172" t="inlineStr"/>
-      <c r="H28" s="172" t="inlineStr"/>
-      <c r="I28" s="172" t="inlineStr"/>
-    </row>
-    <row r="29" ht="17" customHeight="1" s="143">
-      <c r="A29" s="165" t="n">
+      <c r="E29" s="172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="172" t="inlineStr"/>
+      <c r="G29" s="172" t="inlineStr"/>
+      <c r="H29" s="172" t="inlineStr"/>
+      <c r="I29" s="172" t="inlineStr"/>
+    </row>
+    <row r="30" ht="17" customHeight="1" s="143">
+      <c r="A30" s="165" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="166" t="inlineStr">
+      <c r="B30" s="166" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="C29" s="167" t="n">
+      <c r="C30" s="167" t="n">
         <v>12</v>
       </c>
-      <c r="D29" s="168" t="n">
+      <c r="D30" s="168" t="n">
         <v>12</v>
       </c>
-      <c r="E29" s="168" t="inlineStr"/>
-      <c r="F29" s="168" t="inlineStr"/>
-      <c r="G29" s="168" t="inlineStr"/>
-      <c r="H29" s="168" t="inlineStr"/>
-      <c r="I29" s="168" t="inlineStr"/>
-    </row>
-    <row r="30" ht="17" customHeight="1" s="143">
-      <c r="A30" s="169" t="n">
+      <c r="E30" s="168" t="inlineStr"/>
+      <c r="F30" s="168" t="inlineStr"/>
+      <c r="G30" s="168" t="inlineStr"/>
+      <c r="H30" s="168" t="inlineStr"/>
+      <c r="I30" s="168" t="inlineStr"/>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="143">
+      <c r="A31" s="169" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="170" t="inlineStr">
+      <c r="B31" s="170" t="inlineStr">
         <is>
           <t>Kypros</t>
         </is>
       </c>
-      <c r="C30" s="171" t="n">
+      <c r="C31" s="171" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="172" t="n">
+      <c r="D31" s="172" t="n">
         <v>10</v>
       </c>
-      <c r="E30" s="172" t="inlineStr"/>
-      <c r="F30" s="172" t="inlineStr"/>
-      <c r="G30" s="172" t="inlineStr"/>
-      <c r="H30" s="172" t="inlineStr"/>
-      <c r="I30" s="172" t="inlineStr"/>
-    </row>
-    <row r="31" ht="17" customHeight="1" s="143">
-      <c r="A31" s="165" t="n">
+      <c r="E31" s="172" t="inlineStr"/>
+      <c r="F31" s="172" t="inlineStr"/>
+      <c r="G31" s="172" t="inlineStr"/>
+      <c r="H31" s="172" t="inlineStr"/>
+      <c r="I31" s="172" t="inlineStr"/>
+    </row>
+    <row r="32" ht="17" customHeight="1" s="143">
+      <c r="A32" s="165" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="166" t="inlineStr">
+      <c r="B32" s="166" t="inlineStr">
         <is>
           <t>Sør-Korea</t>
         </is>
       </c>
-      <c r="C31" s="167" t="n">
+      <c r="C32" s="167" t="n">
         <v>9</v>
       </c>
-      <c r="D31" s="168" t="n">
+      <c r="D32" s="168" t="n">
         <v>9</v>
       </c>
-      <c r="E31" s="168" t="inlineStr"/>
-      <c r="F31" s="168" t="inlineStr"/>
-      <c r="G31" s="168" t="inlineStr"/>
-      <c r="H31" s="168" t="inlineStr"/>
-      <c r="I31" s="168" t="inlineStr"/>
-    </row>
-    <row r="32" ht="17" customHeight="1" s="143">
-      <c r="A32" s="169" t="n">
+      <c r="E32" s="168" t="inlineStr"/>
+      <c r="F32" s="168" t="inlineStr"/>
+      <c r="G32" s="168" t="inlineStr"/>
+      <c r="H32" s="168" t="inlineStr"/>
+      <c r="I32" s="168" t="inlineStr"/>
+    </row>
+    <row r="33" ht="17" customHeight="1" s="143">
+      <c r="A33" s="169" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="170" t="inlineStr">
+      <c r="B33" s="170" t="inlineStr">
         <is>
           <t>Ny-Zealand</t>
         </is>
       </c>
-      <c r="C32" s="171" t="n">
+      <c r="C33" s="171" t="n">
         <v>9</v>
       </c>
-      <c r="D32" s="172" t="n">
+      <c r="D33" s="172" t="n">
         <v>9</v>
       </c>
-      <c r="E32" s="172" t="inlineStr"/>
-      <c r="F32" s="172" t="inlineStr"/>
-      <c r="G32" s="172" t="inlineStr"/>
-      <c r="H32" s="172" t="inlineStr"/>
-      <c r="I32" s="172" t="inlineStr"/>
-    </row>
-    <row r="33" ht="17" customHeight="1" s="143">
-      <c r="A33" s="165" t="n">
+      <c r="E33" s="172" t="inlineStr"/>
+      <c r="F33" s="172" t="inlineStr"/>
+      <c r="G33" s="172" t="inlineStr"/>
+      <c r="H33" s="172" t="inlineStr"/>
+      <c r="I33" s="172" t="inlineStr"/>
+    </row>
+    <row r="34" ht="17" customHeight="1" s="143">
+      <c r="A34" s="165" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="166" t="inlineStr">
+      <c r="B34" s="166" t="inlineStr">
         <is>
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="C33" s="167" t="n">
+      <c r="C34" s="167" t="n">
         <v>8</v>
       </c>
-      <c r="D33" s="168" t="n">
+      <c r="D34" s="168" t="n">
         <v>8</v>
       </c>
-      <c r="E33" s="168" t="inlineStr"/>
-      <c r="F33" s="168" t="inlineStr"/>
-      <c r="G33" s="168" t="inlineStr"/>
-      <c r="H33" s="168" t="inlineStr"/>
-      <c r="I33" s="168" t="inlineStr"/>
-    </row>
-    <row r="34" ht="17" customHeight="1" s="143">
-      <c r="A34" s="169" t="n">
+      <c r="E34" s="168" t="inlineStr"/>
+      <c r="F34" s="168" t="inlineStr"/>
+      <c r="G34" s="168" t="inlineStr"/>
+      <c r="H34" s="168" t="inlineStr"/>
+      <c r="I34" s="168" t="inlineStr"/>
+    </row>
+    <row r="35" ht="17" customHeight="1" s="143">
+      <c r="A35" s="169" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="170" t="inlineStr">
+      <c r="B35" s="170" t="inlineStr">
         <is>
           <t>Norge</t>
         </is>
       </c>
-      <c r="C34" s="171" t="n">
+      <c r="C35" s="171" t="n">
         <v>7</v>
       </c>
-      <c r="D34" s="172" t="n">
+      <c r="D35" s="172" t="n">
         <v>7</v>
       </c>
-      <c r="E34" s="172" t="inlineStr"/>
-      <c r="F34" s="172" t="inlineStr"/>
-      <c r="G34" s="172" t="inlineStr"/>
-      <c r="H34" s="172" t="inlineStr"/>
-      <c r="I34" s="172" t="inlineStr"/>
-    </row>
-    <row r="35" ht="17" customHeight="1" s="143">
-      <c r="A35" s="165" t="n">
+      <c r="E35" s="172" t="inlineStr"/>
+      <c r="F35" s="172" t="inlineStr"/>
+      <c r="G35" s="172" t="inlineStr"/>
+      <c r="H35" s="172" t="inlineStr"/>
+      <c r="I35" s="172" t="inlineStr"/>
+    </row>
+    <row r="36" ht="17" customHeight="1" s="143">
+      <c r="A36" s="165" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="166" t="inlineStr">
+      <c r="B36" s="166" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="C35" s="167" t="n">
+      <c r="C36" s="167" t="n">
         <v>7</v>
       </c>
-      <c r="D35" s="168" t="n">
+      <c r="D36" s="168" t="n">
         <v>6</v>
       </c>
-      <c r="E35" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="168" t="inlineStr"/>
-      <c r="G35" s="168" t="inlineStr"/>
-      <c r="H35" s="168" t="inlineStr"/>
-      <c r="I35" s="168" t="inlineStr"/>
-    </row>
-    <row r="36" ht="17" customHeight="1" s="143">
-      <c r="A36" s="169" t="n">
+      <c r="E36" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="168" t="inlineStr"/>
+      <c r="G36" s="168" t="inlineStr"/>
+      <c r="H36" s="168" t="inlineStr"/>
+      <c r="I36" s="168" t="inlineStr"/>
+    </row>
+    <row r="37" ht="17" customHeight="1" s="143">
+      <c r="A37" s="169" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="170" t="inlineStr">
+      <c r="B37" s="170" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="C36" s="171" t="n">
+      <c r="C37" s="171" t="n">
         <v>7</v>
       </c>
-      <c r="D36" s="172" t="n">
+      <c r="D37" s="172" t="n">
         <v>7</v>
       </c>
-      <c r="E36" s="172" t="inlineStr"/>
-      <c r="F36" s="172" t="inlineStr"/>
-      <c r="G36" s="172" t="inlineStr"/>
-      <c r="H36" s="172" t="inlineStr"/>
-      <c r="I36" s="172" t="inlineStr"/>
-    </row>
-    <row r="37" ht="17" customHeight="1" s="143">
-      <c r="A37" s="165" t="n">
+      <c r="E37" s="172" t="inlineStr"/>
+      <c r="F37" s="172" t="inlineStr"/>
+      <c r="G37" s="172" t="inlineStr"/>
+      <c r="H37" s="172" t="inlineStr"/>
+      <c r="I37" s="172" t="inlineStr"/>
+    </row>
+    <row r="38" ht="17" customHeight="1" s="143">
+      <c r="A38" s="165" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="166" t="inlineStr">
+      <c r="B38" s="166" t="inlineStr">
         <is>
           <t>Polen</t>
         </is>
       </c>
-      <c r="C37" s="167" t="n">
+      <c r="C38" s="167" t="n">
         <v>7</v>
       </c>
-      <c r="D37" s="168" t="n">
+      <c r="D38" s="168" t="n">
         <v>7</v>
       </c>
-      <c r="E37" s="168" t="inlineStr"/>
-      <c r="F37" s="168" t="inlineStr"/>
-      <c r="G37" s="168" t="inlineStr"/>
-      <c r="H37" s="168" t="inlineStr"/>
-      <c r="I37" s="168" t="inlineStr"/>
-    </row>
-    <row r="38" ht="17" customHeight="1" s="143">
-      <c r="A38" s="169" t="n">
+      <c r="E38" s="168" t="inlineStr"/>
+      <c r="F38" s="168" t="inlineStr"/>
+      <c r="G38" s="168" t="inlineStr"/>
+      <c r="H38" s="168" t="inlineStr"/>
+      <c r="I38" s="168" t="inlineStr"/>
+    </row>
+    <row r="39" ht="17" customHeight="1" s="143">
+      <c r="A39" s="169" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="170" t="inlineStr">
+      <c r="B39" s="170" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="C38" s="171" t="n">
+      <c r="C39" s="171" t="n">
         <v>7</v>
       </c>
-      <c r="D38" s="172" t="n">
+      <c r="D39" s="172" t="n">
         <v>7</v>
       </c>
-      <c r="E38" s="172" t="inlineStr"/>
-      <c r="F38" s="172" t="inlineStr"/>
-      <c r="G38" s="172" t="inlineStr"/>
-      <c r="H38" s="172" t="inlineStr"/>
-      <c r="I38" s="172" t="inlineStr"/>
-    </row>
-    <row r="39" ht="17" customHeight="1" s="143">
-      <c r="A39" s="165" t="n">
+      <c r="E39" s="172" t="inlineStr"/>
+      <c r="F39" s="172" t="inlineStr"/>
+      <c r="G39" s="172" t="inlineStr"/>
+      <c r="H39" s="172" t="inlineStr"/>
+      <c r="I39" s="172" t="inlineStr"/>
+    </row>
+    <row r="40" ht="17" customHeight="1" s="143">
+      <c r="A40" s="165" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="166" t="inlineStr">
+      <c r="B40" s="166" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
-      <c r="C39" s="167" t="n">
+      <c r="C40" s="167" t="n">
         <v>6</v>
       </c>
-      <c r="D39" s="168" t="n">
+      <c r="D40" s="168" t="n">
         <v>6</v>
       </c>
-      <c r="E39" s="168" t="inlineStr"/>
-      <c r="F39" s="168" t="inlineStr"/>
-      <c r="G39" s="168" t="inlineStr"/>
-      <c r="H39" s="168" t="inlineStr"/>
-      <c r="I39" s="168" t="inlineStr"/>
-    </row>
-    <row r="40" ht="17" customHeight="1" s="143">
-      <c r="A40" s="169" t="n">
+      <c r="E40" s="168" t="inlineStr"/>
+      <c r="F40" s="168" t="inlineStr"/>
+      <c r="G40" s="168" t="inlineStr"/>
+      <c r="H40" s="168" t="inlineStr"/>
+      <c r="I40" s="168" t="inlineStr"/>
+    </row>
+    <row r="41" ht="17" customHeight="1" s="143">
+      <c r="A41" s="169" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="170" t="inlineStr">
+      <c r="B41" s="170" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="C40" s="171" t="n">
+      <c r="C41" s="171" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="172" t="n">
+      <c r="D41" s="172" t="n">
         <v>6</v>
       </c>
-      <c r="E40" s="172" t="inlineStr"/>
-      <c r="F40" s="172" t="inlineStr"/>
-      <c r="G40" s="172" t="inlineStr"/>
-      <c r="H40" s="172" t="inlineStr"/>
-      <c r="I40" s="172" t="inlineStr"/>
-    </row>
-    <row r="41" ht="17" customHeight="1" s="143">
-      <c r="A41" s="165" t="n">
+      <c r="E41" s="172" t="inlineStr"/>
+      <c r="F41" s="172" t="inlineStr"/>
+      <c r="G41" s="172" t="inlineStr"/>
+      <c r="H41" s="172" t="inlineStr"/>
+      <c r="I41" s="172" t="inlineStr"/>
+    </row>
+    <row r="42" ht="17" customHeight="1" s="143">
+      <c r="A42" s="165" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="166" t="inlineStr">
+      <c r="B42" s="166" t="inlineStr">
         <is>
           <t>Israel</t>
         </is>
       </c>
-      <c r="C41" s="167" t="n">
+      <c r="C42" s="167" t="n">
         <v>4</v>
       </c>
-      <c r="D41" s="168" t="n">
+      <c r="D42" s="168" t="n">
         <v>4</v>
       </c>
-      <c r="E41" s="168" t="inlineStr"/>
-      <c r="F41" s="168" t="inlineStr"/>
-      <c r="G41" s="168" t="inlineStr"/>
-      <c r="H41" s="168" t="inlineStr"/>
-      <c r="I41" s="168" t="inlineStr"/>
-    </row>
-    <row r="42" ht="17" customHeight="1" s="143">
-      <c r="A42" s="169" t="n">
+      <c r="E42" s="168" t="inlineStr"/>
+      <c r="F42" s="168" t="inlineStr"/>
+      <c r="G42" s="168" t="inlineStr"/>
+      <c r="H42" s="168" t="inlineStr"/>
+      <c r="I42" s="168" t="inlineStr"/>
+    </row>
+    <row r="43" ht="17" customHeight="1" s="143">
+      <c r="A43" s="169" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="170" t="inlineStr">
+      <c r="B43" s="170" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="C42" s="171" t="n">
+      <c r="C43" s="171" t="n">
         <v>4</v>
       </c>
-      <c r="D42" s="172" t="n">
+      <c r="D43" s="172" t="n">
         <v>4</v>
       </c>
-      <c r="E42" s="172" t="inlineStr"/>
-      <c r="F42" s="172" t="inlineStr"/>
-      <c r="G42" s="172" t="inlineStr"/>
-      <c r="H42" s="172" t="inlineStr"/>
-      <c r="I42" s="172" t="inlineStr"/>
-    </row>
-    <row r="43" ht="17" customHeight="1" s="143">
-      <c r="A43" s="165" t="n">
+      <c r="E43" s="172" t="inlineStr"/>
+      <c r="F43" s="172" t="inlineStr"/>
+      <c r="G43" s="172" t="inlineStr"/>
+      <c r="H43" s="172" t="inlineStr"/>
+      <c r="I43" s="172" t="inlineStr"/>
+    </row>
+    <row r="44" ht="17" customHeight="1" s="143">
+      <c r="A44" s="165" t="n">
         <v>40</v>
       </c>
-      <c r="B43" s="166" t="inlineStr">
+      <c r="B44" s="166" t="inlineStr">
         <is>
           <t>Sverige</t>
         </is>
       </c>
-      <c r="C43" s="167" t="n">
+      <c r="C44" s="167" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="168" t="n">
+      <c r="D44" s="168" t="n">
         <v>3</v>
       </c>
-      <c r="E43" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="168" t="inlineStr"/>
-      <c r="G43" s="168" t="inlineStr"/>
-      <c r="H43" s="168" t="inlineStr"/>
-      <c r="I43" s="168" t="inlineStr"/>
-    </row>
-    <row r="44" ht="17" customHeight="1" s="143">
-      <c r="A44" s="169" t="n">
+      <c r="E44" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="168" t="inlineStr"/>
+      <c r="G44" s="168" t="inlineStr"/>
+      <c r="H44" s="168" t="inlineStr"/>
+      <c r="I44" s="168" t="inlineStr"/>
+    </row>
+    <row r="45" ht="17" customHeight="1" s="143">
+      <c r="A45" s="169" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="170" t="inlineStr">
+      <c r="B45" s="170" t="inlineStr">
         <is>
           <t>Aserbajdsjan</t>
         </is>
       </c>
-      <c r="C44" s="171" t="n">
+      <c r="C45" s="171" t="n">
         <v>4</v>
       </c>
-      <c r="D44" s="172" t="n">
+      <c r="D45" s="172" t="n">
         <v>4</v>
       </c>
-      <c r="E44" s="172" t="inlineStr"/>
-      <c r="F44" s="172" t="inlineStr"/>
-      <c r="G44" s="172" t="inlineStr"/>
-      <c r="H44" s="172" t="inlineStr"/>
-      <c r="I44" s="172" t="inlineStr"/>
-    </row>
-    <row r="45" ht="17" customHeight="1" s="143">
-      <c r="A45" s="165" t="n">
+      <c r="E45" s="172" t="inlineStr"/>
+      <c r="F45" s="172" t="inlineStr"/>
+      <c r="G45" s="172" t="inlineStr"/>
+      <c r="H45" s="172" t="inlineStr"/>
+      <c r="I45" s="172" t="inlineStr"/>
+    </row>
+    <row r="46" ht="17" customHeight="1" s="143">
+      <c r="A46" s="165" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="166" t="inlineStr">
+      <c r="B46" s="166" t="inlineStr">
         <is>
           <t>Chile</t>
         </is>
       </c>
-      <c r="C45" s="167" t="n">
+      <c r="C46" s="167" t="n">
         <v>4</v>
       </c>
-      <c r="D45" s="168" t="n">
+      <c r="D46" s="168" t="n">
         <v>4</v>
       </c>
-      <c r="E45" s="168" t="inlineStr"/>
-      <c r="F45" s="168" t="inlineStr"/>
-      <c r="G45" s="168" t="inlineStr"/>
-      <c r="H45" s="168" t="inlineStr"/>
-      <c r="I45" s="168" t="inlineStr"/>
-    </row>
-    <row r="46" ht="17" customHeight="1" s="143">
-      <c r="A46" s="169" t="n">
+      <c r="E46" s="168" t="inlineStr"/>
+      <c r="F46" s="168" t="inlineStr"/>
+      <c r="G46" s="168" t="inlineStr"/>
+      <c r="H46" s="168" t="inlineStr"/>
+      <c r="I46" s="168" t="inlineStr"/>
+    </row>
+    <row r="47" ht="17" customHeight="1" s="143">
+      <c r="A47" s="169" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="170" t="inlineStr">
+      <c r="B47" s="170" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="C46" s="171" t="n">
+      <c r="C47" s="171" t="n">
         <v>3</v>
       </c>
-      <c r="D46" s="172" t="n">
+      <c r="D47" s="172" t="n">
         <v>3</v>
       </c>
-      <c r="E46" s="172" t="inlineStr"/>
-      <c r="F46" s="172" t="inlineStr"/>
-      <c r="G46" s="172" t="inlineStr"/>
-      <c r="H46" s="172" t="inlineStr"/>
-      <c r="I46" s="172" t="inlineStr"/>
-    </row>
-    <row r="47" ht="17" customHeight="1" s="143">
-      <c r="A47" s="165" t="n">
+      <c r="E47" s="172" t="inlineStr"/>
+      <c r="F47" s="172" t="inlineStr"/>
+      <c r="G47" s="172" t="inlineStr"/>
+      <c r="H47" s="172" t="inlineStr"/>
+      <c r="I47" s="172" t="inlineStr"/>
+    </row>
+    <row r="48" ht="17" customHeight="1" s="143">
+      <c r="A48" s="165" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="166" t="inlineStr">
+      <c r="B48" s="166" t="inlineStr">
         <is>
           <t>Ungarn</t>
         </is>
       </c>
-      <c r="C47" s="167" t="n">
+      <c r="C48" s="167" t="n">
         <v>3</v>
       </c>
-      <c r="D47" s="168" t="n">
+      <c r="D48" s="168" t="n">
         <v>3</v>
       </c>
-      <c r="E47" s="168" t="inlineStr"/>
-      <c r="F47" s="168" t="inlineStr"/>
-      <c r="G47" s="168" t="inlineStr"/>
-      <c r="H47" s="168" t="inlineStr"/>
-      <c r="I47" s="168" t="inlineStr"/>
-    </row>
-    <row r="48" ht="17" customHeight="1" s="143">
-      <c r="A48" s="169" t="n">
+      <c r="E48" s="168" t="inlineStr"/>
+      <c r="F48" s="168" t="inlineStr"/>
+      <c r="G48" s="168" t="inlineStr"/>
+      <c r="H48" s="168" t="inlineStr"/>
+      <c r="I48" s="168" t="inlineStr"/>
+    </row>
+    <row r="49" ht="17" customHeight="1" s="143">
+      <c r="A49" s="169" t="n">
         <v>45</v>
       </c>
-      <c r="B48" s="170" t="inlineStr">
+      <c r="B49" s="170" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="C48" s="171" t="n">
+      <c r="C49" s="171" t="n">
         <v>3</v>
       </c>
-      <c r="D48" s="172" t="n">
+      <c r="D49" s="172" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="172" t="inlineStr"/>
-      <c r="F48" s="172" t="inlineStr"/>
-      <c r="G48" s="172" t="inlineStr"/>
-      <c r="H48" s="172" t="inlineStr"/>
-      <c r="I48" s="172" t="inlineStr"/>
-    </row>
-    <row r="49" ht="17" customHeight="1" s="143">
-      <c r="A49" s="165" t="n">
+      <c r="E49" s="172" t="inlineStr"/>
+      <c r="F49" s="172" t="inlineStr"/>
+      <c r="G49" s="172" t="inlineStr"/>
+      <c r="H49" s="172" t="inlineStr"/>
+      <c r="I49" s="172" t="inlineStr"/>
+    </row>
+    <row r="50" ht="17" customHeight="1" s="143">
+      <c r="A50" s="165" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="166" t="inlineStr">
+      <c r="B50" s="166" t="inlineStr">
         <is>
           <t>Algerie</t>
         </is>
       </c>
-      <c r="C49" s="167" t="n">
+      <c r="C50" s="167" t="n">
         <v>3</v>
       </c>
-      <c r="D49" s="168" t="n">
+      <c r="D50" s="168" t="n">
         <v>3</v>
       </c>
-      <c r="E49" s="168" t="inlineStr"/>
-      <c r="F49" s="168" t="inlineStr"/>
-      <c r="G49" s="168" t="inlineStr"/>
-      <c r="H49" s="168" t="inlineStr"/>
-      <c r="I49" s="168" t="inlineStr"/>
-    </row>
-    <row r="50" ht="17" customHeight="1" s="143">
-      <c r="A50" s="169" t="n">
+      <c r="E50" s="168" t="inlineStr"/>
+      <c r="F50" s="168" t="inlineStr"/>
+      <c r="G50" s="168" t="inlineStr"/>
+      <c r="H50" s="168" t="inlineStr"/>
+      <c r="I50" s="168" t="inlineStr"/>
+    </row>
+    <row r="51" ht="17" customHeight="1" s="143">
+      <c r="A51" s="169" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="170" t="inlineStr">
+      <c r="B51" s="170" t="inlineStr">
         <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="C50" s="171" t="n">
+      <c r="C51" s="171" t="n">
         <v>2</v>
       </c>
-      <c r="D50" s="172" t="n">
+      <c r="D51" s="172" t="n">
         <v>2</v>
       </c>
-      <c r="E50" s="172" t="inlineStr"/>
-      <c r="F50" s="172" t="inlineStr"/>
-      <c r="G50" s="172" t="inlineStr"/>
-      <c r="H50" s="172" t="inlineStr"/>
-      <c r="I50" s="172" t="inlineStr"/>
-    </row>
-    <row r="51" ht="17" customHeight="1" s="143">
-      <c r="A51" s="165" t="n">
+      <c r="E51" s="172" t="inlineStr"/>
+      <c r="F51" s="172" t="inlineStr"/>
+      <c r="G51" s="172" t="inlineStr"/>
+      <c r="H51" s="172" t="inlineStr"/>
+      <c r="I51" s="172" t="inlineStr"/>
+    </row>
+    <row r="52" ht="17" customHeight="1" s="143">
+      <c r="A52" s="165" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="166" t="inlineStr">
+      <c r="B52" s="166" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="C51" s="167" t="n">
+      <c r="C52" s="167" t="n">
         <v>2</v>
       </c>
-      <c r="D51" s="168" t="n">
+      <c r="D52" s="168" t="n">
         <v>2</v>
       </c>
-      <c r="E51" s="168" t="inlineStr"/>
-      <c r="F51" s="168" t="inlineStr"/>
-      <c r="G51" s="168" t="inlineStr"/>
-      <c r="H51" s="168" t="inlineStr"/>
-      <c r="I51" s="168" t="inlineStr"/>
-    </row>
-    <row r="52" ht="17" customHeight="1" s="143">
-      <c r="A52" s="169" t="n">
+      <c r="E52" s="168" t="inlineStr"/>
+      <c r="F52" s="168" t="inlineStr"/>
+      <c r="G52" s="168" t="inlineStr"/>
+      <c r="H52" s="168" t="inlineStr"/>
+      <c r="I52" s="168" t="inlineStr"/>
+    </row>
+    <row r="53" ht="17" customHeight="1" s="143">
+      <c r="A53" s="169" t="n">
         <v>49</v>
       </c>
-      <c r="B52" s="170" t="inlineStr">
+      <c r="B53" s="170" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="C52" s="171" t="n">
+      <c r="C53" s="171" t="n">
         <v>2</v>
       </c>
-      <c r="D52" s="172" t="n">
+      <c r="D53" s="172" t="n">
         <v>2</v>
       </c>
-      <c r="E52" s="172" t="inlineStr"/>
-      <c r="F52" s="172" t="inlineStr"/>
-      <c r="G52" s="172" t="inlineStr"/>
-      <c r="H52" s="172" t="inlineStr"/>
-      <c r="I52" s="172" t="inlineStr"/>
-    </row>
-    <row r="53" ht="17" customHeight="1" s="143">
-      <c r="A53" s="165" t="n">
+      <c r="E53" s="172" t="inlineStr"/>
+      <c r="F53" s="172" t="inlineStr"/>
+      <c r="G53" s="172" t="inlineStr"/>
+      <c r="H53" s="172" t="inlineStr"/>
+      <c r="I53" s="172" t="inlineStr"/>
+    </row>
+    <row r="54" ht="17" customHeight="1" s="143">
+      <c r="A54" s="165" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="166" t="inlineStr">
+      <c r="B54" s="166" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="C53" s="167" t="n">
+      <c r="C54" s="167" t="n">
         <v>2</v>
       </c>
-      <c r="D53" s="168" t="n">
+      <c r="D54" s="168" t="n">
         <v>2</v>
       </c>
-      <c r="E53" s="168" t="inlineStr"/>
-      <c r="F53" s="168" t="inlineStr"/>
-      <c r="G53" s="168" t="inlineStr"/>
-      <c r="H53" s="168" t="inlineStr"/>
-      <c r="I53" s="168" t="inlineStr"/>
-    </row>
-    <row r="54" ht="17" customHeight="1" s="143">
-      <c r="A54" s="169" t="n">
+      <c r="E54" s="168" t="inlineStr"/>
+      <c r="F54" s="168" t="inlineStr"/>
+      <c r="G54" s="168" t="inlineStr"/>
+      <c r="H54" s="168" t="inlineStr"/>
+      <c r="I54" s="168" t="inlineStr"/>
+    </row>
+    <row r="55" ht="17" customHeight="1" s="143">
+      <c r="A55" s="169" t="n">
         <v>49</v>
       </c>
-      <c r="B54" s="170" t="inlineStr">
+      <c r="B55" s="170" t="inlineStr">
         <is>
           <t>Irland</t>
         </is>
       </c>
-      <c r="C54" s="171" t="n">
+      <c r="C55" s="171" t="n">
         <v>2</v>
       </c>
-      <c r="D54" s="172" t="n">
+      <c r="D55" s="172" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="172" t="inlineStr"/>
-      <c r="F54" s="172" t="inlineStr"/>
-      <c r="G54" s="172" t="inlineStr"/>
-      <c r="H54" s="172" t="inlineStr"/>
-      <c r="I54" s="172" t="inlineStr"/>
-    </row>
-    <row r="55" ht="17" customHeight="1" s="143">
-      <c r="A55" s="165" t="n">
+      <c r="E55" s="172" t="inlineStr"/>
+      <c r="F55" s="172" t="inlineStr"/>
+      <c r="G55" s="172" t="inlineStr"/>
+      <c r="H55" s="172" t="inlineStr"/>
+      <c r="I55" s="172" t="inlineStr"/>
+    </row>
+    <row r="56" ht="17" customHeight="1" s="143">
+      <c r="A56" s="165" t="n">
         <v>49</v>
       </c>
-      <c r="B55" s="166" t="inlineStr">
+      <c r="B56" s="166" t="inlineStr">
         <is>
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="C55" s="167" t="n">
+      <c r="C56" s="167" t="n">
         <v>2</v>
       </c>
-      <c r="D55" s="168" t="n">
+      <c r="D56" s="168" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="168" t="inlineStr"/>
-      <c r="F55" s="168" t="inlineStr"/>
-      <c r="G55" s="168" t="inlineStr"/>
-      <c r="H55" s="168" t="inlineStr"/>
-      <c r="I55" s="168" t="inlineStr"/>
-    </row>
-    <row r="56" ht="17" customHeight="1" s="143">
-      <c r="A56" s="169" t="n">
+      <c r="E56" s="168" t="inlineStr"/>
+      <c r="F56" s="168" t="inlineStr"/>
+      <c r="G56" s="168" t="inlineStr"/>
+      <c r="H56" s="168" t="inlineStr"/>
+      <c r="I56" s="168" t="inlineStr"/>
+    </row>
+    <row r="57" ht="17" customHeight="1" s="143">
+      <c r="A57" s="169" t="n">
         <v>49</v>
       </c>
-      <c r="B56" s="170" t="inlineStr">
+      <c r="B57" s="170" t="inlineStr">
         <is>
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="C56" s="171" t="n">
+      <c r="C57" s="171" t="n">
         <v>2</v>
       </c>
-      <c r="D56" s="172" t="n">
+      <c r="D57" s="172" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="172" t="inlineStr"/>
-      <c r="F56" s="172" t="inlineStr"/>
-      <c r="G56" s="172" t="inlineStr"/>
-      <c r="H56" s="172" t="inlineStr"/>
-      <c r="I56" s="172" t="inlineStr"/>
-    </row>
-    <row r="57" ht="17" customHeight="1" s="143">
-      <c r="A57" s="165" t="n">
+      <c r="E57" s="172" t="inlineStr"/>
+      <c r="F57" s="172" t="inlineStr"/>
+      <c r="G57" s="172" t="inlineStr"/>
+      <c r="H57" s="172" t="inlineStr"/>
+      <c r="I57" s="172" t="inlineStr"/>
+    </row>
+    <row r="58" ht="17" customHeight="1" s="143">
+      <c r="A58" s="165" t="n">
         <v>49</v>
       </c>
-      <c r="B57" s="166" t="inlineStr">
+      <c r="B58" s="166" t="inlineStr">
         <is>
           <t>Venezuela</t>
         </is>
       </c>
-      <c r="C57" s="167" t="n">
+      <c r="C58" s="167" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="168" t="n">
+      <c r="D58" s="168" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="168" t="inlineStr"/>
-      <c r="F57" s="168" t="inlineStr"/>
-      <c r="G57" s="168" t="inlineStr"/>
-      <c r="H57" s="168" t="inlineStr"/>
-      <c r="I57" s="168" t="inlineStr"/>
-    </row>
-    <row r="58" ht="17" customHeight="1" s="143">
-      <c r="A58" s="169" t="n">
+      <c r="E58" s="168" t="inlineStr"/>
+      <c r="F58" s="168" t="inlineStr"/>
+      <c r="G58" s="168" t="inlineStr"/>
+      <c r="H58" s="168" t="inlineStr"/>
+      <c r="I58" s="168" t="inlineStr"/>
+    </row>
+    <row r="59" ht="17" customHeight="1" s="143">
+      <c r="A59" s="169" t="n">
         <v>49</v>
       </c>
-      <c r="B58" s="170" t="inlineStr">
+      <c r="B59" s="170" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="C58" s="171" t="n">
+      <c r="C59" s="171" t="n">
         <v>2</v>
       </c>
-      <c r="D58" s="172" t="n">
+      <c r="D59" s="172" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="172" t="inlineStr"/>
-      <c r="F58" s="172" t="inlineStr"/>
-      <c r="G58" s="172" t="inlineStr"/>
-      <c r="H58" s="172" t="inlineStr"/>
-      <c r="I58" s="172" t="inlineStr"/>
-    </row>
-    <row r="59" ht="17" customHeight="1" s="143">
-      <c r="A59" s="165" t="n">
+      <c r="E59" s="172" t="inlineStr"/>
+      <c r="F59" s="172" t="inlineStr"/>
+      <c r="G59" s="172" t="inlineStr"/>
+      <c r="H59" s="172" t="inlineStr"/>
+      <c r="I59" s="172" t="inlineStr"/>
+    </row>
+    <row r="60" ht="17" customHeight="1" s="143">
+      <c r="A60" s="165" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="166" t="inlineStr">
+      <c r="B60" s="166" t="inlineStr">
         <is>
           <t>Bosnia og Hercegovina</t>
         </is>
       </c>
-      <c r="C59" s="167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="168" t="inlineStr"/>
-      <c r="F59" s="168" t="inlineStr"/>
-      <c r="G59" s="168" t="inlineStr"/>
-      <c r="H59" s="168" t="inlineStr"/>
-      <c r="I59" s="168" t="inlineStr"/>
-    </row>
-    <row r="60" ht="17" customHeight="1" s="143">
-      <c r="A60" s="169" t="n">
+      <c r="C60" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="168" t="inlineStr"/>
+      <c r="F60" s="168" t="inlineStr"/>
+      <c r="G60" s="168" t="inlineStr"/>
+      <c r="H60" s="168" t="inlineStr"/>
+      <c r="I60" s="168" t="inlineStr"/>
+    </row>
+    <row r="61" ht="17" customHeight="1" s="143">
+      <c r="A61" s="169" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="170" t="inlineStr">
+      <c r="B61" s="170" t="inlineStr">
         <is>
           <t>Kasakhstan</t>
         </is>
       </c>
-      <c r="C60" s="171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="172" t="inlineStr"/>
-      <c r="F60" s="172" t="inlineStr"/>
-      <c r="G60" s="172" t="inlineStr"/>
-      <c r="H60" s="172" t="inlineStr"/>
-      <c r="I60" s="172" t="inlineStr"/>
-    </row>
-    <row r="61" ht="17" customHeight="1" s="143">
-      <c r="A61" s="165" t="n">
+      <c r="C61" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="172" t="inlineStr"/>
+      <c r="F61" s="172" t="inlineStr"/>
+      <c r="G61" s="172" t="inlineStr"/>
+      <c r="H61" s="172" t="inlineStr"/>
+      <c r="I61" s="172" t="inlineStr"/>
+    </row>
+    <row r="62" ht="17" customHeight="1" s="143">
+      <c r="A62" s="165" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="166" t="inlineStr">
+      <c r="B62" s="166" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="C61" s="167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="168" t="inlineStr"/>
-      <c r="F61" s="168" t="inlineStr"/>
-      <c r="G61" s="168" t="inlineStr"/>
-      <c r="H61" s="168" t="inlineStr"/>
-      <c r="I61" s="168" t="inlineStr"/>
-    </row>
-    <row r="62" ht="17" customHeight="1" s="143">
-      <c r="A62" s="169" t="n">
+      <c r="C62" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="168" t="inlineStr"/>
+      <c r="F62" s="168" t="inlineStr"/>
+      <c r="G62" s="168" t="inlineStr"/>
+      <c r="H62" s="168" t="inlineStr"/>
+      <c r="I62" s="168" t="inlineStr"/>
+    </row>
+    <row r="63" ht="17" customHeight="1" s="143">
+      <c r="A63" s="169" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="170" t="inlineStr">
+      <c r="B63" s="170" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="C62" s="171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="172" t="inlineStr"/>
-      <c r="F62" s="172" t="inlineStr"/>
-      <c r="G62" s="172" t="inlineStr"/>
-      <c r="H62" s="172" t="inlineStr"/>
-      <c r="I62" s="172" t="inlineStr"/>
-    </row>
-    <row r="63" ht="17" customHeight="1" s="143">
-      <c r="A63" s="165" t="n">
+      <c r="C63" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="172" t="inlineStr"/>
+      <c r="F63" s="172" t="inlineStr"/>
+      <c r="G63" s="172" t="inlineStr"/>
+      <c r="H63" s="172" t="inlineStr"/>
+      <c r="I63" s="172" t="inlineStr"/>
+    </row>
+    <row r="64" ht="17" customHeight="1" s="143">
+      <c r="A64" s="165" t="n">
         <v>58</v>
       </c>
-      <c r="B63" s="166" t="inlineStr">
+      <c r="B64" s="166" t="inlineStr">
         <is>
           <t>Indonesia</t>
         </is>
       </c>
-      <c r="C63" s="167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D63" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="168" t="inlineStr"/>
-      <c r="F63" s="168" t="inlineStr"/>
-      <c r="G63" s="168" t="inlineStr"/>
-      <c r="H63" s="168" t="inlineStr"/>
-      <c r="I63" s="168" t="inlineStr"/>
-    </row>
-    <row r="64" ht="17" customHeight="1" s="143">
-      <c r="A64" s="169" t="n">
+      <c r="C64" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="168" t="inlineStr"/>
+      <c r="F64" s="168" t="inlineStr"/>
+      <c r="G64" s="168" t="inlineStr"/>
+      <c r="H64" s="168" t="inlineStr"/>
+      <c r="I64" s="168" t="inlineStr"/>
+    </row>
+    <row r="65" ht="17" customHeight="1" s="143">
+      <c r="A65" s="169" t="n">
         <v>58</v>
       </c>
-      <c r="B64" s="170" t="inlineStr">
+      <c r="B65" s="170" t="inlineStr">
         <is>
           <t>Serbia</t>
         </is>
       </c>
-      <c r="C64" s="171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="172" t="inlineStr"/>
-      <c r="F64" s="172" t="inlineStr"/>
-      <c r="G64" s="172" t="inlineStr"/>
-      <c r="H64" s="172" t="inlineStr"/>
-      <c r="I64" s="172" t="inlineStr"/>
-    </row>
-    <row r="65" ht="17" customHeight="1" s="143">
-      <c r="A65" s="165" t="n">
+      <c r="C65" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="172" t="inlineStr"/>
+      <c r="F65" s="172" t="inlineStr"/>
+      <c r="G65" s="172" t="inlineStr"/>
+      <c r="H65" s="172" t="inlineStr"/>
+      <c r="I65" s="172" t="inlineStr"/>
+    </row>
+    <row r="66" ht="17" customHeight="1" s="143">
+      <c r="A66" s="165" t="n">
         <v>58</v>
       </c>
-      <c r="B65" s="166" t="inlineStr">
+      <c r="B66" s="166" t="inlineStr">
         <is>
           <t>Armenia</t>
         </is>
       </c>
-      <c r="C65" s="167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="168" t="inlineStr"/>
-      <c r="F65" s="168" t="inlineStr"/>
-      <c r="G65" s="168" t="inlineStr"/>
-      <c r="H65" s="168" t="inlineStr"/>
-      <c r="I65" s="168" t="inlineStr"/>
-    </row>
-    <row r="66" ht="17" customHeight="1" s="143">
-      <c r="A66" s="169" t="n">
+      <c r="C66" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="168" t="inlineStr"/>
+      <c r="F66" s="168" t="inlineStr"/>
+      <c r="G66" s="168" t="inlineStr"/>
+      <c r="H66" s="168" t="inlineStr"/>
+      <c r="I66" s="168" t="inlineStr"/>
+    </row>
+    <row r="67" ht="17" customHeight="1" s="143">
+      <c r="A67" s="169" t="n">
         <v>58</v>
       </c>
-      <c r="B66" s="170" t="inlineStr">
+      <c r="B67" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="C66" s="171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D66" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="172" t="inlineStr"/>
-      <c r="F66" s="172" t="inlineStr"/>
-      <c r="G66" s="172" t="inlineStr"/>
-      <c r="H66" s="172" t="inlineStr"/>
-      <c r="I66" s="172" t="inlineStr"/>
-    </row>
-    <row r="67" ht="17" customHeight="1" s="143">
-      <c r="A67" s="165" t="n">
+      <c r="C67" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="172" t="inlineStr"/>
+      <c r="F67" s="172" t="inlineStr"/>
+      <c r="G67" s="172" t="inlineStr"/>
+      <c r="H67" s="172" t="inlineStr"/>
+      <c r="I67" s="172" t="inlineStr"/>
+    </row>
+    <row r="68" ht="17" customHeight="1" s="143">
+      <c r="A68" s="165" t="n">
         <v>58</v>
       </c>
-      <c r="B67" s="166" t="inlineStr">
+      <c r="B68" s="166" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C67" s="167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="168" t="inlineStr"/>
-      <c r="F67" s="168" t="inlineStr"/>
-      <c r="G67" s="168" t="inlineStr"/>
-      <c r="H67" s="168" t="inlineStr"/>
-      <c r="I67" s="168" t="inlineStr"/>
-    </row>
-    <row r="68" ht="17" customHeight="1" s="143">
-      <c r="A68" s="169" t="n">
+      <c r="C68" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="168" t="inlineStr"/>
+      <c r="F68" s="168" t="inlineStr"/>
+      <c r="G68" s="168" t="inlineStr"/>
+      <c r="H68" s="168" t="inlineStr"/>
+      <c r="I68" s="168" t="inlineStr"/>
+    </row>
+    <row r="69" ht="17" customHeight="1" s="143">
+      <c r="A69" s="169" t="n">
         <v>58</v>
       </c>
-      <c r="B68" s="170" t="inlineStr">
+      <c r="B69" s="170" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="C68" s="171" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="172" t="inlineStr"/>
-      <c r="F68" s="172" t="inlineStr"/>
-      <c r="G68" s="172" t="inlineStr"/>
-      <c r="H68" s="172" t="inlineStr"/>
-      <c r="I68" s="172" t="inlineStr"/>
-    </row>
-    <row r="69" ht="17" customHeight="1" s="143">
-      <c r="A69" s="165" t="n">
+      <c r="C69" s="171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="172" t="inlineStr"/>
+      <c r="F69" s="172" t="inlineStr"/>
+      <c r="G69" s="172" t="inlineStr"/>
+      <c r="H69" s="172" t="inlineStr"/>
+      <c r="I69" s="172" t="inlineStr"/>
+    </row>
+    <row r="70" ht="17" customHeight="1" s="143">
+      <c r="A70" s="165" t="n">
         <v>58</v>
       </c>
-      <c r="B69" s="166" t="inlineStr">
+      <c r="B70" s="166" t="inlineStr">
         <is>
           <t>Honduras</t>
         </is>
       </c>
-      <c r="C69" s="167" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="168" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="168" t="inlineStr"/>
-      <c r="F69" s="168" t="inlineStr"/>
-      <c r="G69" s="168" t="inlineStr"/>
-      <c r="H69" s="168" t="inlineStr"/>
-      <c r="I69" s="168" t="inlineStr"/>
+      <c r="C70" s="167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="168" t="inlineStr"/>
+      <c r="F70" s="168" t="inlineStr"/>
+      <c r="G70" s="168" t="inlineStr"/>
+      <c r="H70" s="168" t="inlineStr"/>
+      <c r="I70" s="168" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A2:I2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -28,13 +28,13 @@
     <sheet name="Klubber" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="Alder" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Nivå 2 og lavere" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Spillere etter klubbland" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Spillere etter klubbland" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Nivå 2 og lavere" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Klubber'!$A$2:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Nivå 2 og lavere'!$A$2:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'Nivå 2 og lavere'!$A$2:$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -817,7 +817,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="188">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1340,6 +1340,36 @@
     <xf numFmtId="0" fontId="45" fillId="44" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="51" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="51" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="52" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="52" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="53" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="53" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="54" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="54" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="51" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="52" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="53" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="55" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="54" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -50065,1943 +50095,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" style="143" min="1" max="1"/>
-    <col width="26" customWidth="1" style="143" min="2" max="2"/>
-    <col width="16" customWidth="1" style="143" min="3" max="3"/>
-    <col width="22" customWidth="1" style="143" min="4" max="4"/>
-    <col width="30" customWidth="1" style="143" min="5" max="5"/>
-    <col width="22" customWidth="1" style="143" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" s="143">
-      <c r="A1" s="150" t="inlineStr">
-        <is>
-          <t>VM 2026 — Spillere på nivå 2 og lavere   61 spillere</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" s="143">
-      <c r="A2" s="187" t="inlineStr">
-        <is>
-          <t>Nivå</t>
-        </is>
-      </c>
-      <c r="B2" s="187" t="inlineStr">
-        <is>
-          <t>Klubb</t>
-        </is>
-      </c>
-      <c r="C2" s="187" t="inlineStr">
-        <is>
-          <t>Land</t>
-        </is>
-      </c>
-      <c r="D2" s="187" t="inlineStr">
-        <is>
-          <t>Liga</t>
-        </is>
-      </c>
-      <c r="E2" s="187" t="inlineStr">
-        <is>
-          <t>Spiller</t>
-        </is>
-      </c>
-      <c r="F2" s="187" t="inlineStr">
-        <is>
-          <t>Nasjonallag</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="175" t="inlineStr">
-        <is>
-          <t>Charlton Athletic</t>
-        </is>
-      </c>
-      <c r="C3" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D3" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E3" s="175" t="inlineStr">
-        <is>
-          <t>Lyndon Dykes</t>
-        </is>
-      </c>
-      <c r="F3" s="175" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="175" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="C4" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D4" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E4" s="175" t="inlineStr">
-        <is>
-          <t>Brandon Thomas-Asante</t>
-        </is>
-      </c>
-      <c r="F4" s="175" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="175" t="inlineStr">
-        <is>
-          <t>Coventry City</t>
-        </is>
-      </c>
-      <c r="C5" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D5" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E5" s="175" t="inlineStr">
-        <is>
-          <t>Haji Wright</t>
-        </is>
-      </c>
-      <c r="F5" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="175" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="C6" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D6" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E6" s="175" t="inlineStr">
-        <is>
-          <t>Jacob Widell Zetterström</t>
-        </is>
-      </c>
-      <c r="F6" s="175" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="175" t="inlineStr">
-        <is>
-          <t>Derby County</t>
-        </is>
-      </c>
-      <c r="C7" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D7" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E7" s="175" t="inlineStr">
-        <is>
-          <t>Sondre Langås</t>
-        </is>
-      </c>
-      <c r="F7" s="175" t="inlineStr">
-        <is>
-          <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="175" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C8" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D8" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E8" s="175" t="inlineStr">
-        <is>
-          <t>Amir Hadžiahmetović</t>
-        </is>
-      </c>
-      <c r="F8" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="175" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C9" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D9" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E9" s="175" t="inlineStr">
-        <is>
-          <t>Ivor Pandur</t>
-        </is>
-      </c>
-      <c r="F9" s="175" t="inlineStr">
-        <is>
-          <t>Kroatia</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="175" t="inlineStr">
-        <is>
-          <t>Hull City</t>
-        </is>
-      </c>
-      <c r="C10" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D10" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E10" s="175" t="inlineStr">
-        <is>
-          <t>Liam Miller</t>
-        </is>
-      </c>
-      <c r="F10" s="175" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="175" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="C11" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D11" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E11" s="175" t="inlineStr">
-        <is>
-          <t>Alfie Jones</t>
-        </is>
-      </c>
-      <c r="F11" s="175" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="175" t="inlineStr">
-        <is>
-          <t>Middlesbrough</t>
-        </is>
-      </c>
-      <c r="C12" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D12" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E12" s="175" t="inlineStr">
-        <is>
-          <t>Sontje Hansen</t>
-        </is>
-      </c>
-      <c r="F12" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="175" t="inlineStr">
-        <is>
-          <t>Millwall FC</t>
-        </is>
-      </c>
-      <c r="C13" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D13" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E13" s="175" t="inlineStr">
-        <is>
-          <t>Max Crocombe</t>
-        </is>
-      </c>
-      <c r="F13" s="175" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C14" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D14" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E14" s="175" t="inlineStr">
-        <is>
-          <t>Ali Ahmed</t>
-        </is>
-      </c>
-      <c r="F14" s="175" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C15" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D15" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E15" s="175" t="inlineStr">
-        <is>
-          <t>José Córdoba</t>
-        </is>
-      </c>
-      <c r="F15" s="175" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C16" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D16" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E16" s="175" t="inlineStr">
-        <is>
-          <t>Kenny McLean</t>
-        </is>
-      </c>
-      <c r="F16" s="175" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="175" t="inlineStr">
-        <is>
-          <t>Norwich City</t>
-        </is>
-      </c>
-      <c r="C17" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D17" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E17" s="175" t="inlineStr">
-        <is>
-          <t>Toure</t>
-        </is>
-      </c>
-      <c r="F17" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="175" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="C18" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D18" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E18" s="175" t="inlineStr">
-        <is>
-          <t>Gustavo Caballero</t>
-        </is>
-      </c>
-      <c r="F18" s="175" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="175" t="inlineStr">
-        <is>
-          <t>Sheffield United</t>
-        </is>
-      </c>
-      <c r="C19" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D19" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E19" s="175" t="inlineStr">
-        <is>
-          <t>Tahith Chong</t>
-        </is>
-      </c>
-      <c r="F19" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" s="175" t="inlineStr">
-        <is>
-          <t>Stoke City</t>
-        </is>
-      </c>
-      <c r="C20" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D20" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E20" s="175" t="inlineStr">
-        <is>
-          <t>Viktor Johansson</t>
-        </is>
-      </c>
-      <c r="F20" s="175" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="175" t="inlineStr">
-        <is>
-          <t>Swansea</t>
-        </is>
-      </c>
-      <c r="C21" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D21" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E21" s="175" t="inlineStr">
-        <is>
-          <t>Eom Jisung</t>
-        </is>
-      </c>
-      <c r="F21" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="175" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="C22" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D22" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E22" s="175" t="inlineStr">
-        <is>
-          <t>Burgess</t>
-        </is>
-      </c>
-      <c r="F22" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="175" t="inlineStr">
-        <is>
-          <t>Swansea City</t>
-        </is>
-      </c>
-      <c r="C23" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D23" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E23" s="175" t="inlineStr">
-        <is>
-          <t>Marko Stamenić</t>
-        </is>
-      </c>
-      <c r="F23" s="175" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="175" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C24" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D24" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E24" s="175" t="inlineStr">
-        <is>
-          <t>Edo Kayembe</t>
-        </is>
-      </c>
-      <c r="F24" s="175" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="175" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C25" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D25" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E25" s="175" t="inlineStr">
-        <is>
-          <t>Egil Selvik</t>
-        </is>
-      </c>
-      <c r="F25" s="175" t="inlineStr">
-        <is>
-          <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" s="175" t="inlineStr">
-        <is>
-          <t>Watford</t>
-        </is>
-      </c>
-      <c r="C26" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D26" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E26" s="175" t="inlineStr">
-        <is>
-          <t>Irankunda</t>
-        </is>
-      </c>
-      <c r="F26" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" s="175" t="inlineStr">
-        <is>
-          <t>Wrexham</t>
-        </is>
-      </c>
-      <c r="C27" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D27" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E27" s="175" t="inlineStr">
-        <is>
-          <t>Dom Hyam</t>
-        </is>
-      </c>
-      <c r="F27" s="175" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" s="175" t="inlineStr">
-        <is>
-          <t>Wrexham AFC</t>
-        </is>
-      </c>
-      <c r="C28" s="175" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D28" s="175" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="E28" s="175" t="inlineStr">
-        <is>
-          <t>Liberato Cacace</t>
-        </is>
-      </c>
-      <c r="F28" s="175" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="175" t="inlineStr">
-        <is>
-          <t>AS Nancy-Lorraine</t>
-        </is>
-      </c>
-      <c r="C29" s="175" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D29" s="175" t="inlineStr">
-        <is>
-          <t>Ligue 2</t>
-        </is>
-      </c>
-      <c r="E29" s="175" t="inlineStr">
-        <is>
-          <t>Martin Experience</t>
-        </is>
-      </c>
-      <c r="F29" s="175" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="175" t="inlineStr">
-        <is>
-          <t>SC Bastia</t>
-        </is>
-      </c>
-      <c r="C30" s="175" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D30" s="175" t="inlineStr">
-        <is>
-          <t>Ligue 2</t>
-        </is>
-      </c>
-      <c r="E30" s="175" t="inlineStr">
-        <is>
-          <t>Johnny Placide</t>
-        </is>
-      </c>
-      <c r="F30" s="175" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B31" s="175" t="inlineStr">
-        <is>
-          <t>Frosinone</t>
-        </is>
-      </c>
-      <c r="C31" s="175" t="inlineStr">
-        <is>
-          <t>Italia</t>
-        </is>
-      </c>
-      <c r="D31" s="175" t="inlineStr">
-        <is>
-          <t>Serie B</t>
-        </is>
-      </c>
-      <c r="E31" s="175" t="inlineStr">
-        <is>
-          <t>Farès Ghedjemis</t>
-        </is>
-      </c>
-      <c r="F31" s="175" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="175" t="inlineStr">
-        <is>
-          <t>UC Sampdoria</t>
-        </is>
-      </c>
-      <c r="C32" s="175" t="inlineStr">
-        <is>
-          <t>Italia</t>
-        </is>
-      </c>
-      <c r="D32" s="175" t="inlineStr">
-        <is>
-          <t>Serie B</t>
-        </is>
-      </c>
-      <c r="E32" s="175" t="inlineStr">
-        <is>
-          <t>Dennis Hadžikadunić</t>
-        </is>
-      </c>
-      <c r="F32" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="175" t="inlineStr">
-        <is>
-          <t>Albirex Niigata</t>
-        </is>
-      </c>
-      <c r="C33" s="175" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D33" s="175" t="inlineStr">
-        <is>
-          <t>J2 League</t>
-        </is>
-      </c>
-      <c r="E33" s="175" t="inlineStr">
-        <is>
-          <t>Geria</t>
-        </is>
-      </c>
-      <c r="F33" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B34" s="175" t="inlineStr">
-        <is>
-          <t>FC Den Bosch</t>
-        </is>
-      </c>
-      <c r="C34" s="175" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D34" s="175" t="inlineStr">
-        <is>
-          <t>Eerste Divisie</t>
-        </is>
-      </c>
-      <c r="E34" s="175" t="inlineStr">
-        <is>
-          <t>Kevin Felida</t>
-        </is>
-      </c>
-      <c r="F34" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="175" t="inlineStr">
-        <is>
-          <t>VVV-Venlo</t>
-        </is>
-      </c>
-      <c r="C35" s="175" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D35" s="175" t="inlineStr">
-        <is>
-          <t>Eerste Divisie</t>
-        </is>
-      </c>
-      <c r="E35" s="175" t="inlineStr">
-        <is>
-          <t>Trevor Doornbusch</t>
-        </is>
-      </c>
-      <c r="F35" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B36" s="175" t="inlineStr">
-        <is>
-          <t>Chaves</t>
-        </is>
-      </c>
-      <c r="C36" s="175" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D36" s="175" t="inlineStr">
-        <is>
-          <t>Liga Portugal 2</t>
-        </is>
-      </c>
-      <c r="E36" s="175" t="inlineStr">
-        <is>
-          <t>Josimar Dias "Vozinha"</t>
-        </is>
-      </c>
-      <c r="F36" s="175" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" s="175" t="inlineStr">
-        <is>
-          <t>Torreense</t>
-        </is>
-      </c>
-      <c r="C37" s="175" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D37" s="175" t="inlineStr">
-        <is>
-          <t>Liga Portugal 2</t>
-        </is>
-      </c>
-      <c r="E37" s="175" t="inlineStr">
-        <is>
-          <t>Ianique Tavares "Stopira"</t>
-        </is>
-      </c>
-      <c r="F37" s="175" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" s="175" t="inlineStr">
-        <is>
-          <t>Castellón</t>
-        </is>
-      </c>
-      <c r="C38" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D38" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E38" s="175" t="inlineStr">
-        <is>
-          <t>Brian Cipenga</t>
-        </is>
-      </c>
-      <c r="F38" s="175" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B39" s="175" t="inlineStr">
-        <is>
-          <t>Castellón</t>
-        </is>
-      </c>
-      <c r="C39" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D39" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E39" s="175" t="inlineStr">
-        <is>
-          <t>Mabil</t>
-        </is>
-      </c>
-      <c r="F39" s="175" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" s="175" t="inlineStr">
-        <is>
-          <t>Cultural Leonesa</t>
-        </is>
-      </c>
-      <c r="C40" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D40" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E40" s="175" t="inlineStr">
-        <is>
-          <t>Homam Al-Amin</t>
-        </is>
-      </c>
-      <c r="F40" s="175" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B41" s="175" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C41" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D41" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E41" s="175" t="inlineStr">
-        <is>
-          <t>Federico Viñas</t>
-        </is>
-      </c>
-      <c r="F41" s="175" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B42" s="175" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C42" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D42" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E42" s="175" t="inlineStr">
-        <is>
-          <t>Haissem Hassan</t>
-        </is>
-      </c>
-      <c r="F42" s="175" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" s="175" t="inlineStr">
-        <is>
-          <t>Real Oviedo</t>
-        </is>
-      </c>
-      <c r="C43" s="175" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D43" s="175" t="inlineStr">
-        <is>
-          <t>Segunda División</t>
-        </is>
-      </c>
-      <c r="E43" s="175" t="inlineStr">
-        <is>
-          <t>Kwasi Sibo</t>
-        </is>
-      </c>
-      <c r="F43" s="175" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" s="175" t="inlineStr">
-        <is>
-          <t>Stade Nyonnais</t>
-        </is>
-      </c>
-      <c r="C44" s="175" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D44" s="175" t="inlineStr">
-        <is>
-          <t>Challenge League</t>
-        </is>
-      </c>
-      <c r="E44" s="175" t="inlineStr">
-        <is>
-          <t>Melvin Mastil</t>
-        </is>
-      </c>
-      <c r="F44" s="175" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="175" t="inlineStr">
-        <is>
-          <t>IFK Norrköping</t>
-        </is>
-      </c>
-      <c r="C45" s="175" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D45" s="175" t="inlineStr">
-        <is>
-          <t>Superettan</t>
-        </is>
-      </c>
-      <c r="E45" s="175" t="inlineStr">
-        <is>
-          <t>Moutaz Neffati</t>
-        </is>
-      </c>
-      <c r="F45" s="175" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B46" s="175" t="inlineStr">
-        <is>
-          <t>Siwelele FC</t>
-        </is>
-      </c>
-      <c r="C46" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D46" s="175" t="inlineStr">
-        <is>
-          <t>National First Division</t>
-        </is>
-      </c>
-      <c r="E46" s="175" t="inlineStr">
-        <is>
-          <t>Ricardo Goss</t>
-        </is>
-      </c>
-      <c r="F46" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" s="175" t="inlineStr">
-        <is>
-          <t>Iğdır</t>
-        </is>
-      </c>
-      <c r="C47" s="175" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D47" s="175" t="inlineStr">
-        <is>
-          <t>TFF 1. Lig</t>
-        </is>
-      </c>
-      <c r="E47" s="175" t="inlineStr">
-        <is>
-          <t>Leandro Bacuna</t>
-        </is>
-      </c>
-      <c r="F47" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B48" s="175" t="inlineStr">
-        <is>
-          <t>Iğdır</t>
-        </is>
-      </c>
-      <c r="C48" s="175" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D48" s="175" t="inlineStr">
-        <is>
-          <t>TFF 1. Lig</t>
-        </is>
-      </c>
-      <c r="E48" s="175" t="inlineStr">
-        <is>
-          <t>Ryan Mendes</t>
-        </is>
-      </c>
-      <c r="F48" s="175" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B49" s="175" t="inlineStr">
-        <is>
-          <t>Fortuna Düsseldorf</t>
-        </is>
-      </c>
-      <c r="C49" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D49" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E49" s="175" t="inlineStr">
-        <is>
-          <t>Cedric Itten</t>
-        </is>
-      </c>
-      <c r="F49" s="175" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" s="175" t="inlineStr">
-        <is>
-          <t>Hannover 96</t>
-        </is>
-      </c>
-      <c r="C50" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D50" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E50" s="175" t="inlineStr">
-        <is>
-          <t>Ime Okon</t>
-        </is>
-      </c>
-      <c r="F50" s="175" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B51" s="175" t="inlineStr">
-        <is>
-          <t>Hannover 96</t>
-        </is>
-      </c>
-      <c r="C51" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D51" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E51" s="175" t="inlineStr">
-        <is>
-          <t>​Elias Saad</t>
-        </is>
-      </c>
-      <c r="F51" s="175" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B52" s="175" t="inlineStr">
-        <is>
-          <t>Karlsruher SC</t>
-        </is>
-      </c>
-      <c r="C52" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D52" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E52" s="175" t="inlineStr">
-        <is>
-          <t>Dženis Burnić</t>
-        </is>
-      </c>
-      <c r="F52" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B53" s="175" t="inlineStr">
-        <is>
-          <t>Schalke 04</t>
-        </is>
-      </c>
-      <c r="C53" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D53" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E53" s="175" t="inlineStr">
-        <is>
-          <t>Edin Džeko</t>
-        </is>
-      </c>
-      <c r="F53" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B54" s="175" t="inlineStr">
-        <is>
-          <t>Schalke 04</t>
-        </is>
-      </c>
-      <c r="C54" s="175" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D54" s="175" t="inlineStr">
-        <is>
-          <t>2. Bundesliga</t>
-        </is>
-      </c>
-      <c r="E54" s="175" t="inlineStr">
-        <is>
-          <t>Nikola Katić</t>
-        </is>
-      </c>
-      <c r="F54" s="175" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B55" s="175" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive FC</t>
-        </is>
-      </c>
-      <c r="C55" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D55" s="175" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E55" s="175" t="inlineStr">
-        <is>
-          <t>Carl-Fred Sainthe</t>
-        </is>
-      </c>
-      <c r="F55" s="175" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B56" s="175" t="inlineStr">
-        <is>
-          <t>Miami FC</t>
-        </is>
-      </c>
-      <c r="C56" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D56" s="175" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E56" s="175" t="inlineStr">
-        <is>
-          <t>Eloy Room</t>
-        </is>
-      </c>
-      <c r="F56" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="B57" s="175" t="inlineStr">
-        <is>
-          <t>Miami FC</t>
-        </is>
-      </c>
-      <c r="C57" s="175" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D57" s="175" t="inlineStr">
-        <is>
-          <t>USL Championship</t>
-        </is>
-      </c>
-      <c r="E57" s="175" t="inlineStr">
-        <is>
-          <t>Jürgen Locadia</t>
-        </is>
-      </c>
-      <c r="F57" s="175" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B58" s="177" t="inlineStr">
-        <is>
-          <t>Port Vale</t>
-        </is>
-      </c>
-      <c r="C58" s="177" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D58" s="177" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E58" s="177" t="inlineStr">
-        <is>
-          <t>Ben Waine</t>
-        </is>
-      </c>
-      <c r="F58" s="177" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B59" s="177" t="inlineStr">
-        <is>
-          <t>Rotherham United</t>
-        </is>
-      </c>
-      <c r="C59" s="177" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D59" s="177" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E59" s="177" t="inlineStr">
-        <is>
-          <t>Ar’Jany Martha</t>
-        </is>
-      </c>
-      <c r="F59" s="177" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B60" s="177" t="inlineStr">
-        <is>
-          <t>FC Sochaux</t>
-        </is>
-      </c>
-      <c r="C60" s="177" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="D60" s="177" t="inlineStr">
-        <is>
-          <t>National</t>
-        </is>
-      </c>
-      <c r="E60" s="177" t="inlineStr">
-        <is>
-          <t>Alexandre Pierre</t>
-        </is>
-      </c>
-      <c r="F60" s="177" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="B61" s="177" t="inlineStr">
-        <is>
-          <t>BSC Young Boys II</t>
-        </is>
-      </c>
-      <c r="C61" s="177" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D61" s="177" t="inlineStr">
-        <is>
-          <t>Promotion League</t>
-        </is>
-      </c>
-      <c r="E61" s="177" t="inlineStr">
-        <is>
-          <t>Keeto Thermoncy</t>
-        </is>
-      </c>
-      <c r="F61" s="177" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="178" t="n">
-        <v>4</v>
-      </c>
-      <c r="B62" s="179" t="inlineStr">
-        <is>
-          <t>FC Cosmos Koblenz</t>
-        </is>
-      </c>
-      <c r="C62" s="179" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D62" s="179" t="inlineStr">
-        <is>
-          <t>Regionalliga</t>
-        </is>
-      </c>
-      <c r="E62" s="179" t="inlineStr">
-        <is>
-          <t>Josué Duverger</t>
-        </is>
-      </c>
-      <c r="F62" s="179" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="180" t="n">
-        <v>6</v>
-      </c>
-      <c r="B63" s="181" t="inlineStr">
-        <is>
-          <t>Braintree Town</t>
-        </is>
-      </c>
-      <c r="C63" s="181" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D63" s="181" t="inlineStr">
-        <is>
-          <t>National League South</t>
-        </is>
-      </c>
-      <c r="E63" s="181" t="inlineStr">
-        <is>
-          <t>Tommy Smith</t>
-        </is>
-      </c>
-      <c r="F63" s="181" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t>Fargeforklaring:</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="182" t="inlineStr">
-        <is>
-          <t>Nivå 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="183" t="inlineStr">
-        <is>
-          <t>Nivå 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="184" t="inlineStr">
-        <is>
-          <t>Nivå 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="185" t="inlineStr">
-        <is>
-          <t>Nivå 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="186" t="inlineStr">
-        <is>
-          <t>Nivå 6</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:F2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -53544,6 +51637,1943 @@
   <autoFilter ref="A2:I2"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="143" min="1" max="1"/>
+    <col width="26" customWidth="1" style="143" min="2" max="2"/>
+    <col width="16" customWidth="1" style="143" min="3" max="3"/>
+    <col width="22" customWidth="1" style="143" min="4" max="4"/>
+    <col width="30" customWidth="1" style="143" min="5" max="5"/>
+    <col width="22" customWidth="1" style="143" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="143">
+      <c r="A1" s="150" t="inlineStr">
+        <is>
+          <t>VM 2026 — Spillere på nivå 2 og lavere   61 spillere</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="143">
+      <c r="A2" s="151" t="inlineStr">
+        <is>
+          <t>Nivå</t>
+        </is>
+      </c>
+      <c r="B2" s="151" t="inlineStr">
+        <is>
+          <t>Klubb</t>
+        </is>
+      </c>
+      <c r="C2" s="151" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D2" s="151" t="inlineStr">
+        <is>
+          <t>Liga</t>
+        </is>
+      </c>
+      <c r="E2" s="151" t="inlineStr">
+        <is>
+          <t>Spiller</t>
+        </is>
+      </c>
+      <c r="F2" s="151" t="inlineStr">
+        <is>
+          <t>Nasjonallag</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1" s="143">
+      <c r="A3" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="189" t="inlineStr">
+        <is>
+          <t>Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="C3" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D3" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E3" s="189" t="inlineStr">
+        <is>
+          <t>Lyndon Dykes</t>
+        </is>
+      </c>
+      <c r="F3" s="189" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1" s="143">
+      <c r="A4" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="189" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="C4" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D4" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E4" s="189" t="inlineStr">
+        <is>
+          <t>Brandon Thomas-Asante</t>
+        </is>
+      </c>
+      <c r="F4" s="189" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1" s="143">
+      <c r="A5" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="189" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="C5" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D5" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E5" s="189" t="inlineStr">
+        <is>
+          <t>Haji Wright</t>
+        </is>
+      </c>
+      <c r="F5" s="189" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1" s="143">
+      <c r="A6" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="189" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="C6" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D6" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E6" s="189" t="inlineStr">
+        <is>
+          <t>Jacob Widell Zetterström</t>
+        </is>
+      </c>
+      <c r="F6" s="189" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1" s="143">
+      <c r="A7" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="189" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="C7" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D7" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E7" s="189" t="inlineStr">
+        <is>
+          <t>Sondre Langås</t>
+        </is>
+      </c>
+      <c r="F7" s="189" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1" s="143">
+      <c r="A8" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="189" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C8" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D8" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E8" s="189" t="inlineStr">
+        <is>
+          <t>Amir Hadžiahmetović</t>
+        </is>
+      </c>
+      <c r="F8" s="189" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1" s="143">
+      <c r="A9" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="189" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C9" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D9" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E9" s="189" t="inlineStr">
+        <is>
+          <t>Ivor Pandur</t>
+        </is>
+      </c>
+      <c r="F9" s="189" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1" s="143">
+      <c r="A10" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="189" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C10" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D10" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E10" s="189" t="inlineStr">
+        <is>
+          <t>Liam Miller</t>
+        </is>
+      </c>
+      <c r="F10" s="189" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1" s="143">
+      <c r="A11" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="189" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C11" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D11" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E11" s="189" t="inlineStr">
+        <is>
+          <t>Alfie Jones</t>
+        </is>
+      </c>
+      <c r="F11" s="189" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1" s="143">
+      <c r="A12" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="189" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C12" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D12" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E12" s="189" t="inlineStr">
+        <is>
+          <t>Sontje Hansen</t>
+        </is>
+      </c>
+      <c r="F12" s="189" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1" s="143">
+      <c r="A13" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="189" t="inlineStr">
+        <is>
+          <t>Millwall FC</t>
+        </is>
+      </c>
+      <c r="C13" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D13" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E13" s="189" t="inlineStr">
+        <is>
+          <t>Max Crocombe</t>
+        </is>
+      </c>
+      <c r="F13" s="189" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1" s="143">
+      <c r="A14" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="189" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C14" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D14" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E14" s="189" t="inlineStr">
+        <is>
+          <t>Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="F14" s="189" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1" s="143">
+      <c r="A15" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="189" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C15" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D15" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E15" s="189" t="inlineStr">
+        <is>
+          <t>José Córdoba</t>
+        </is>
+      </c>
+      <c r="F15" s="189" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1" s="143">
+      <c r="A16" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="189" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C16" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D16" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E16" s="189" t="inlineStr">
+        <is>
+          <t>Kenny McLean</t>
+        </is>
+      </c>
+      <c r="F16" s="189" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1" s="143">
+      <c r="A17" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="189" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C17" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D17" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E17" s="189" t="inlineStr">
+        <is>
+          <t>Toure</t>
+        </is>
+      </c>
+      <c r="F17" s="189" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1" s="143">
+      <c r="A18" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="189" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="C18" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D18" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E18" s="189" t="inlineStr">
+        <is>
+          <t>Gustavo Caballero</t>
+        </is>
+      </c>
+      <c r="F18" s="189" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1" s="143">
+      <c r="A19" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="189" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="C19" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D19" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E19" s="189" t="inlineStr">
+        <is>
+          <t>Tahith Chong</t>
+        </is>
+      </c>
+      <c r="F19" s="189" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1" s="143">
+      <c r="A20" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="189" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="C20" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D20" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E20" s="189" t="inlineStr">
+        <is>
+          <t>Viktor Johansson</t>
+        </is>
+      </c>
+      <c r="F20" s="189" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1" s="143">
+      <c r="A21" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="189" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="C21" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D21" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E21" s="189" t="inlineStr">
+        <is>
+          <t>Eom Jisung</t>
+        </is>
+      </c>
+      <c r="F21" s="189" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1" s="143">
+      <c r="A22" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="189" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="C22" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D22" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E22" s="189" t="inlineStr">
+        <is>
+          <t>Burgess</t>
+        </is>
+      </c>
+      <c r="F22" s="189" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1" s="143">
+      <c r="A23" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="189" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="C23" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D23" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E23" s="189" t="inlineStr">
+        <is>
+          <t>Marko Stamenić</t>
+        </is>
+      </c>
+      <c r="F23" s="189" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1" s="143">
+      <c r="A24" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="189" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C24" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D24" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E24" s="189" t="inlineStr">
+        <is>
+          <t>Edo Kayembe</t>
+        </is>
+      </c>
+      <c r="F24" s="189" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1" s="143">
+      <c r="A25" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="189" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C25" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D25" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E25" s="189" t="inlineStr">
+        <is>
+          <t>Egil Selvik</t>
+        </is>
+      </c>
+      <c r="F25" s="189" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1" s="143">
+      <c r="A26" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" s="189" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C26" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D26" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E26" s="189" t="inlineStr">
+        <is>
+          <t>Irankunda</t>
+        </is>
+      </c>
+      <c r="F26" s="189" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1" s="143">
+      <c r="A27" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="189" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="C27" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D27" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E27" s="189" t="inlineStr">
+        <is>
+          <t>Dom Hyam</t>
+        </is>
+      </c>
+      <c r="F27" s="189" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1" s="143">
+      <c r="A28" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="189" t="inlineStr">
+        <is>
+          <t>Wrexham AFC</t>
+        </is>
+      </c>
+      <c r="C28" s="189" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D28" s="189" t="inlineStr">
+        <is>
+          <t>Championship</t>
+        </is>
+      </c>
+      <c r="E28" s="189" t="inlineStr">
+        <is>
+          <t>Liberato Cacace</t>
+        </is>
+      </c>
+      <c r="F28" s="189" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1" s="143">
+      <c r="A29" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" s="189" t="inlineStr">
+        <is>
+          <t>AS Nancy-Lorraine</t>
+        </is>
+      </c>
+      <c r="C29" s="189" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D29" s="189" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="E29" s="189" t="inlineStr">
+        <is>
+          <t>Martin Experience</t>
+        </is>
+      </c>
+      <c r="F29" s="189" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1" s="143">
+      <c r="A30" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="189" t="inlineStr">
+        <is>
+          <t>SC Bastia</t>
+        </is>
+      </c>
+      <c r="C30" s="189" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D30" s="189" t="inlineStr">
+        <is>
+          <t>Ligue 2</t>
+        </is>
+      </c>
+      <c r="E30" s="189" t="inlineStr">
+        <is>
+          <t>Johnny Placide</t>
+        </is>
+      </c>
+      <c r="F30" s="189" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1" s="143">
+      <c r="A31" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="189" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="C31" s="189" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D31" s="189" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="E31" s="189" t="inlineStr">
+        <is>
+          <t>Farès Ghedjemis</t>
+        </is>
+      </c>
+      <c r="F31" s="189" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1" s="143">
+      <c r="A32" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="189" t="inlineStr">
+        <is>
+          <t>UC Sampdoria</t>
+        </is>
+      </c>
+      <c r="C32" s="189" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D32" s="189" t="inlineStr">
+        <is>
+          <t>Serie B</t>
+        </is>
+      </c>
+      <c r="E32" s="189" t="inlineStr">
+        <is>
+          <t>Dennis Hadžikadunić</t>
+        </is>
+      </c>
+      <c r="F32" s="189" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1" s="143">
+      <c r="A33" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="189" t="inlineStr">
+        <is>
+          <t>Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="C33" s="189" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D33" s="189" t="inlineStr">
+        <is>
+          <t>J2 League</t>
+        </is>
+      </c>
+      <c r="E33" s="189" t="inlineStr">
+        <is>
+          <t>Geria</t>
+        </is>
+      </c>
+      <c r="F33" s="189" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1" s="143">
+      <c r="A34" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="189" t="inlineStr">
+        <is>
+          <t>FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="C34" s="189" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D34" s="189" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="E34" s="189" t="inlineStr">
+        <is>
+          <t>Kevin Felida</t>
+        </is>
+      </c>
+      <c r="F34" s="189" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1" s="143">
+      <c r="A35" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="189" t="inlineStr">
+        <is>
+          <t>VVV-Venlo</t>
+        </is>
+      </c>
+      <c r="C35" s="189" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D35" s="189" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="E35" s="189" t="inlineStr">
+        <is>
+          <t>Trevor Doornbusch</t>
+        </is>
+      </c>
+      <c r="F35" s="189" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1" s="143">
+      <c r="A36" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="189" t="inlineStr">
+        <is>
+          <t>Chaves</t>
+        </is>
+      </c>
+      <c r="C36" s="189" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D36" s="189" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2</t>
+        </is>
+      </c>
+      <c r="E36" s="189" t="inlineStr">
+        <is>
+          <t>Josimar Dias "Vozinha"</t>
+        </is>
+      </c>
+      <c r="F36" s="189" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1" s="143">
+      <c r="A37" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" s="189" t="inlineStr">
+        <is>
+          <t>Torreense</t>
+        </is>
+      </c>
+      <c r="C37" s="189" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D37" s="189" t="inlineStr">
+        <is>
+          <t>Liga Portugal 2</t>
+        </is>
+      </c>
+      <c r="E37" s="189" t="inlineStr">
+        <is>
+          <t>Ianique Tavares "Stopira"</t>
+        </is>
+      </c>
+      <c r="F37" s="189" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1" s="143">
+      <c r="A38" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" s="189" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C38" s="189" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D38" s="189" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E38" s="189" t="inlineStr">
+        <is>
+          <t>Brian Cipenga</t>
+        </is>
+      </c>
+      <c r="F38" s="189" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1" s="143">
+      <c r="A39" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" s="189" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C39" s="189" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D39" s="189" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E39" s="189" t="inlineStr">
+        <is>
+          <t>Mabil</t>
+        </is>
+      </c>
+      <c r="F39" s="189" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1" s="143">
+      <c r="A40" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="189" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa</t>
+        </is>
+      </c>
+      <c r="C40" s="189" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D40" s="189" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E40" s="189" t="inlineStr">
+        <is>
+          <t>Homam Al-Amin</t>
+        </is>
+      </c>
+      <c r="F40" s="189" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1" s="143">
+      <c r="A41" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" s="189" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C41" s="189" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D41" s="189" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E41" s="189" t="inlineStr">
+        <is>
+          <t>Federico Viñas</t>
+        </is>
+      </c>
+      <c r="F41" s="189" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1" s="143">
+      <c r="A42" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="189" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C42" s="189" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D42" s="189" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E42" s="189" t="inlineStr">
+        <is>
+          <t>Haissem Hassan</t>
+        </is>
+      </c>
+      <c r="F42" s="189" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1" s="143">
+      <c r="A43" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="189" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C43" s="189" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D43" s="189" t="inlineStr">
+        <is>
+          <t>Segunda División</t>
+        </is>
+      </c>
+      <c r="E43" s="189" t="inlineStr">
+        <is>
+          <t>Kwasi Sibo</t>
+        </is>
+      </c>
+      <c r="F43" s="189" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1" s="143">
+      <c r="A44" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="189" t="inlineStr">
+        <is>
+          <t>Stade Nyonnais</t>
+        </is>
+      </c>
+      <c r="C44" s="189" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D44" s="189" t="inlineStr">
+        <is>
+          <t>Challenge League</t>
+        </is>
+      </c>
+      <c r="E44" s="189" t="inlineStr">
+        <is>
+          <t>Melvin Mastil</t>
+        </is>
+      </c>
+      <c r="F44" s="189" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1" s="143">
+      <c r="A45" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="189" t="inlineStr">
+        <is>
+          <t>IFK Norrköping</t>
+        </is>
+      </c>
+      <c r="C45" s="189" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D45" s="189" t="inlineStr">
+        <is>
+          <t>Superettan</t>
+        </is>
+      </c>
+      <c r="E45" s="189" t="inlineStr">
+        <is>
+          <t>Moutaz Neffati</t>
+        </is>
+      </c>
+      <c r="F45" s="189" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1" s="143">
+      <c r="A46" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" s="189" t="inlineStr">
+        <is>
+          <t>Siwelele FC</t>
+        </is>
+      </c>
+      <c r="C46" s="189" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D46" s="189" t="inlineStr">
+        <is>
+          <t>National First Division</t>
+        </is>
+      </c>
+      <c r="E46" s="189" t="inlineStr">
+        <is>
+          <t>Ricardo Goss</t>
+        </is>
+      </c>
+      <c r="F46" s="189" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1" s="143">
+      <c r="A47" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B47" s="189" t="inlineStr">
+        <is>
+          <t>Iğdır</t>
+        </is>
+      </c>
+      <c r="C47" s="189" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D47" s="189" t="inlineStr">
+        <is>
+          <t>TFF 1. Lig</t>
+        </is>
+      </c>
+      <c r="E47" s="189" t="inlineStr">
+        <is>
+          <t>Leandro Bacuna</t>
+        </is>
+      </c>
+      <c r="F47" s="189" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1" s="143">
+      <c r="A48" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B48" s="189" t="inlineStr">
+        <is>
+          <t>Iğdır</t>
+        </is>
+      </c>
+      <c r="C48" s="189" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D48" s="189" t="inlineStr">
+        <is>
+          <t>TFF 1. Lig</t>
+        </is>
+      </c>
+      <c r="E48" s="189" t="inlineStr">
+        <is>
+          <t>Ryan Mendes</t>
+        </is>
+      </c>
+      <c r="F48" s="189" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1" s="143">
+      <c r="A49" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" s="189" t="inlineStr">
+        <is>
+          <t>Fortuna Düsseldorf</t>
+        </is>
+      </c>
+      <c r="C49" s="189" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D49" s="189" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E49" s="189" t="inlineStr">
+        <is>
+          <t>Cedric Itten</t>
+        </is>
+      </c>
+      <c r="F49" s="189" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1" s="143">
+      <c r="A50" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" s="189" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="C50" s="189" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D50" s="189" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E50" s="189" t="inlineStr">
+        <is>
+          <t>Ime Okon</t>
+        </is>
+      </c>
+      <c r="F50" s="189" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1" s="143">
+      <c r="A51" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B51" s="189" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="C51" s="189" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D51" s="189" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E51" s="189" t="inlineStr">
+        <is>
+          <t>​Elias Saad</t>
+        </is>
+      </c>
+      <c r="F51" s="189" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1" s="143">
+      <c r="A52" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B52" s="189" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="C52" s="189" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D52" s="189" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E52" s="189" t="inlineStr">
+        <is>
+          <t>Dženis Burnić</t>
+        </is>
+      </c>
+      <c r="F52" s="189" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1" s="143">
+      <c r="A53" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" s="189" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="C53" s="189" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D53" s="189" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E53" s="189" t="inlineStr">
+        <is>
+          <t>Edin Džeko</t>
+        </is>
+      </c>
+      <c r="F53" s="189" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1" s="143">
+      <c r="A54" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B54" s="189" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="C54" s="189" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D54" s="189" t="inlineStr">
+        <is>
+          <t>2. Bundesliga</t>
+        </is>
+      </c>
+      <c r="E54" s="189" t="inlineStr">
+        <is>
+          <t>Nikola Katić</t>
+        </is>
+      </c>
+      <c r="F54" s="189" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1" s="143">
+      <c r="A55" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B55" s="189" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="C55" s="189" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D55" s="189" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E55" s="189" t="inlineStr">
+        <is>
+          <t>Carl-Fred Sainthe</t>
+        </is>
+      </c>
+      <c r="F55" s="189" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1" s="143">
+      <c r="A56" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="189" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C56" s="189" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D56" s="189" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E56" s="189" t="inlineStr">
+        <is>
+          <t>Eloy Room</t>
+        </is>
+      </c>
+      <c r="F56" s="189" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1" s="143">
+      <c r="A57" s="188" t="n">
+        <v>2</v>
+      </c>
+      <c r="B57" s="189" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C57" s="189" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D57" s="189" t="inlineStr">
+        <is>
+          <t>USL Championship</t>
+        </is>
+      </c>
+      <c r="E57" s="189" t="inlineStr">
+        <is>
+          <t>Jürgen Locadia</t>
+        </is>
+      </c>
+      <c r="F57" s="189" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="17" customHeight="1" s="143">
+      <c r="A58" s="190" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" s="191" t="inlineStr">
+        <is>
+          <t>Port Vale</t>
+        </is>
+      </c>
+      <c r="C58" s="191" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D58" s="191" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="E58" s="191" t="inlineStr">
+        <is>
+          <t>Ben Waine</t>
+        </is>
+      </c>
+      <c r="F58" s="191" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1" s="143">
+      <c r="A59" s="190" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" s="191" t="inlineStr">
+        <is>
+          <t>Rotherham United</t>
+        </is>
+      </c>
+      <c r="C59" s="191" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D59" s="191" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="E59" s="191" t="inlineStr">
+        <is>
+          <t>Ar’Jany Martha</t>
+        </is>
+      </c>
+      <c r="F59" s="191" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="17" customHeight="1" s="143">
+      <c r="A60" s="190" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="191" t="inlineStr">
+        <is>
+          <t>FC Sochaux</t>
+        </is>
+      </c>
+      <c r="C60" s="191" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D60" s="191" t="inlineStr">
+        <is>
+          <t>National</t>
+        </is>
+      </c>
+      <c r="E60" s="191" t="inlineStr">
+        <is>
+          <t>Alexandre Pierre</t>
+        </is>
+      </c>
+      <c r="F60" s="191" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1" s="143">
+      <c r="A61" s="190" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" s="191" t="inlineStr">
+        <is>
+          <t>BSC Young Boys II</t>
+        </is>
+      </c>
+      <c r="C61" s="191" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D61" s="191" t="inlineStr">
+        <is>
+          <t>Promotion League</t>
+        </is>
+      </c>
+      <c r="E61" s="191" t="inlineStr">
+        <is>
+          <t>Keeto Thermoncy</t>
+        </is>
+      </c>
+      <c r="F61" s="191" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1" s="143">
+      <c r="A62" s="192" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" s="193" t="inlineStr">
+        <is>
+          <t>FC Cosmos Koblenz</t>
+        </is>
+      </c>
+      <c r="C62" s="193" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D62" s="193" t="inlineStr">
+        <is>
+          <t>Regionalliga</t>
+        </is>
+      </c>
+      <c r="E62" s="193" t="inlineStr">
+        <is>
+          <t>Josué Duverger</t>
+        </is>
+      </c>
+      <c r="F62" s="193" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1" s="143">
+      <c r="A63" s="194" t="n">
+        <v>6</v>
+      </c>
+      <c r="B63" s="195" t="inlineStr">
+        <is>
+          <t>Braintree Town</t>
+        </is>
+      </c>
+      <c r="C63" s="195" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D63" s="195" t="inlineStr">
+        <is>
+          <t>National League South</t>
+        </is>
+      </c>
+      <c r="E63" s="195" t="inlineStr">
+        <is>
+          <t>Tommy Smith</t>
+        </is>
+      </c>
+      <c r="F63" s="195" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="196" t="inlineStr">
+        <is>
+          <t>Fargeforklaring:</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="197" t="inlineStr">
+        <is>
+          <t>Nivå 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="198" t="inlineStr">
+        <is>
+          <t>Nivå 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="199" t="inlineStr">
+        <is>
+          <t>Nivå 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="200" t="inlineStr">
+        <is>
+          <t>Nivå 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="201" t="inlineStr">
+        <is>
+          <t>Nivå 6</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:F2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -33863,7 +33863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="143" min="1" max="1"/>
@@ -33986,44 +33986,44 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C4" s="232" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="D4" s="233" t="n">
-        <v>16</v>
+      <c r="C4" s="238" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D4" s="234" t="n">
+        <v>8</v>
       </c>
       <c r="E4" s="233" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="234" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" s="235" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" s="236" t="inlineStr">
         <is>
-          <t>2–0</t>
+          <t>1–0</t>
         </is>
       </c>
       <c r="I4" s="237" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J4" s="234" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K4" s="234" t="n">
         <v>2</v>
       </c>
       <c r="L4" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="M4" s="238" t="n">
-        <v>0.39</v>
+        <v>8</v>
+      </c>
+      <c r="M4" s="232" t="n">
+        <v>0.57</v>
       </c>
       <c r="N4" s="231" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
     </row>
@@ -34031,95 +34031,99 @@
       <c r="A5" s="239" t="inlineStr"/>
       <c r="B5" s="240" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Tsjekkia</t>
         </is>
       </c>
       <c r="C5" s="238" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="D5" s="241" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="241" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="244" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I5" s="245" t="n">
         <v>8</v>
       </c>
-      <c r="E5" s="242" t="n">
+      <c r="J5" s="241" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="G5" s="243" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="244" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I5" s="245" t="n">
-        <v>3</v>
-      </c>
-      <c r="J5" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" s="241" t="n">
+      <c r="K5" s="242" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" s="242" t="n">
+        <v>17</v>
+      </c>
+      <c r="M5" s="232" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N5" s="240" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="143">
+      <c r="A6" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="B6" s="231" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C6" s="247" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D6" s="233" t="n">
+        <v>31</v>
+      </c>
+      <c r="E6" s="233" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="G6" s="235" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="236" t="inlineStr">
+        <is>
+          <t>6–0</t>
+        </is>
+      </c>
+      <c r="I6" s="237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="241" t="n">
-        <v>8</v>
-      </c>
-      <c r="M5" s="232" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N5" s="240" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="143">
-      <c r="A6" s="246" t="inlineStr"/>
-      <c r="B6" s="231" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="C6" s="232" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D6" s="233" t="n">
-        <v>15</v>
-      </c>
-      <c r="E6" s="233" t="n">
-        <v>7</v>
-      </c>
-      <c r="F6" s="234" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" s="235" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="236" t="inlineStr">
-        <is>
-          <t>2–1</t>
-        </is>
-      </c>
-      <c r="I6" s="237" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" s="234" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" s="234" t="n">
-        <v>8</v>
-      </c>
       <c r="M6" s="238" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="N6" s="231" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
+          <t>Qatar</t>
         </is>
       </c>
     </row>
@@ -34127,99 +34131,99 @@
       <c r="A7" s="239" t="inlineStr"/>
       <c r="B7" s="240" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
-        </is>
-      </c>
-      <c r="C7" s="238" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D7" s="241" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" s="241" t="n">
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="C7" s="232" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D7" s="242" t="n">
+        <v>13</v>
+      </c>
+      <c r="E7" s="242" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="241" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="241" t="n">
-        <v>6</v>
-      </c>
       <c r="G7" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="244" t="inlineStr">
+        <is>
+          <t>4–1</t>
+        </is>
+      </c>
+      <c r="I7" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="241" t="n">
         <v>3</v>
       </c>
-      <c r="H7" s="244" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I7" s="245" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="241" t="n">
+      <c r="L7" s="241" t="n">
         <v>4</v>
       </c>
-      <c r="K7" s="242" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="242" t="n">
-        <v>17</v>
-      </c>
-      <c r="M7" s="232" t="n">
-        <v>0.61</v>
+      <c r="M7" s="238" t="n">
+        <v>0.38</v>
       </c>
       <c r="N7" s="240" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="143">
       <c r="A8" s="230" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="B8" s="231" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="C8" s="232" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="D8" s="233" t="n">
-        <v>13</v>
-      </c>
-      <c r="E8" s="234" t="n">
-        <v>3</v>
+        <v>9</v>
+      </c>
+      <c r="E8" s="233" t="n">
+        <v>5</v>
       </c>
       <c r="F8" s="234" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="235" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H8" s="236" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I8" s="237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="234" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" s="233" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="234" t="n">
         <v>4</v>
       </c>
       <c r="L8" s="234" t="n">
         <v>8</v>
       </c>
       <c r="M8" s="238" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="N8" s="231" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Haiti</t>
         </is>
       </c>
     </row>
@@ -34227,95 +34231,99 @@
       <c r="A9" s="239" t="inlineStr"/>
       <c r="B9" s="240" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C9" s="247" t="n">
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="C9" s="238" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D9" s="241" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="244" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I9" s="245" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="241" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" s="242" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="242" t="n">
+        <v>12</v>
+      </c>
+      <c r="M9" s="232" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N9" s="240" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="143">
+      <c r="A10" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="B10" s="231" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="C10" s="247" t="n">
         <v>0.78</v>
       </c>
-      <c r="D9" s="242" t="n">
-        <v>31</v>
-      </c>
-      <c r="E9" s="242" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="241" t="n">
-        <v>8</v>
-      </c>
-      <c r="G9" s="243" t="n">
-        <v>13</v>
-      </c>
-      <c r="H9" s="244" t="inlineStr">
-        <is>
-          <t>6–0</t>
-        </is>
-      </c>
-      <c r="I9" s="245" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="241" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="241" t="n">
+      <c r="D10" s="233" t="n">
+        <v>33</v>
+      </c>
+      <c r="E10" s="233" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" s="234" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" s="235" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" s="236" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I10" s="237" t="n">
         <v>2</v>
       </c>
-      <c r="M9" s="238" t="n">
+      <c r="J10" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="234" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" s="238" t="n">
         <v>0.22</v>
       </c>
-      <c r="N9" s="240" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="143">
-      <c r="A10" s="246" t="inlineStr"/>
-      <c r="B10" s="231" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C10" s="238" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D10" s="234" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="236" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I10" s="237" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" s="233" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="233" t="n">
-        <v>27</v>
-      </c>
-      <c r="M10" s="247" t="n">
-        <v>0.7</v>
-      </c>
       <c r="N10" s="231" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -34323,199 +34331,199 @@
       <c r="A11" s="239" t="inlineStr"/>
       <c r="B11" s="240" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C11" s="232" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="D11" s="242" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E11" s="242" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="241" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="244" t="inlineStr">
+        <is>
+          <t>3–0</t>
+        </is>
+      </c>
+      <c r="I11" s="245" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="241" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" s="238" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N11" s="240" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="143">
+      <c r="A12" s="246" t="inlineStr"/>
+      <c r="B12" s="231" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C12" s="232" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D12" s="233" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="243" t="n">
+      <c r="E12" s="234" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="244" t="inlineStr">
-        <is>
-          <t>4–1</t>
-        </is>
-      </c>
-      <c r="I11" s="245" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="241" t="n">
+      <c r="F12" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="235" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="236" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I12" s="237" t="n">
         <v>0</v>
-      </c>
-      <c r="K11" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="238" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N11" s="240" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="143">
-      <c r="A12" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe C</t>
-        </is>
-      </c>
-      <c r="B12" s="231" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="C12" s="248" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D12" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" s="233" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="235" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="236" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I12" s="237" t="n">
-        <v>6</v>
       </c>
       <c r="J12" s="234" t="n">
         <v>3</v>
       </c>
       <c r="K12" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" s="234" t="n">
+        <v>5</v>
+      </c>
+      <c r="M12" s="238" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N12" s="231" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="143">
+      <c r="A13" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="B13" s="240" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="C13" s="248" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D13" s="242" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="242" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="241" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="244" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="I13" s="245" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="241" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="233" t="n">
-        <v>13</v>
-      </c>
-      <c r="M12" s="248" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N12" s="231" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" s="143">
-      <c r="A13" s="239" t="inlineStr"/>
-      <c r="B13" s="240" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C13" s="248" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="242" t="n">
-        <v>13</v>
-      </c>
-      <c r="E13" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="241" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="243" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="244" t="inlineStr">
-        <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="I13" s="245" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="241" t="n">
-        <v>3</v>
-      </c>
       <c r="K13" s="241" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L13" s="241" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M13" s="248" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="N13" s="240" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Ecuador</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="143">
       <c r="A14" s="230" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="B14" s="231" t="inlineStr">
         <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="C14" s="238" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D14" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="E14" s="234" t="n">
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C14" s="232" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D14" s="233" t="n">
+        <v>14</v>
+      </c>
+      <c r="E14" s="233" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="234" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="236" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I14" s="237" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="F14" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="235" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="236" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I14" s="237" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" s="234" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" s="233" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" s="233" t="n">
-        <v>28</v>
-      </c>
-      <c r="M14" s="232" t="n">
-        <v>0.63</v>
+      <c r="L14" s="234" t="n">
+        <v>9</v>
+      </c>
+      <c r="M14" s="238" t="n">
+        <v>0.44</v>
       </c>
       <c r="N14" s="231" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Egypt</t>
         </is>
       </c>
     </row>
@@ -34523,199 +34531,203 @@
       <c r="A15" s="239" t="inlineStr"/>
       <c r="B15" s="240" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C15" s="232" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D15" s="242" t="n">
-        <v>17</v>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C15" s="248" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="D15" s="241" t="n">
+        <v>10</v>
       </c>
       <c r="E15" s="242" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" s="241" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="244" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I15" s="245" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="241" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="243" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" s="244" t="inlineStr">
-        <is>
-          <t>4–1</t>
-        </is>
-      </c>
-      <c r="I15" s="245" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="241" t="n">
-        <v>2</v>
-      </c>
       <c r="K15" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="L15" s="241" t="n">
-        <v>8</v>
-      </c>
-      <c r="M15" s="238" t="n">
-        <v>0.37</v>
+        <v>3</v>
+      </c>
+      <c r="L15" s="242" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" s="248" t="n">
+        <v>0.52</v>
       </c>
       <c r="N15" s="240" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="143">
       <c r="A16" s="230" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="B16" s="231" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="C16" s="248" t="n">
-        <v>0.49</v>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C16" s="247" t="n">
+        <v>0.74</v>
       </c>
       <c r="D16" s="233" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E16" s="233" t="n">
+        <v>6</v>
+      </c>
+      <c r="F16" s="234" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" s="235" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="236" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I16" s="237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" s="234" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="234" t="n">
-        <v>9</v>
-      </c>
-      <c r="G16" s="235" t="n">
+      <c r="M16" s="238" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N16" s="231" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="143">
+      <c r="A17" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="B17" s="240" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C17" s="238" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D17" s="241" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="241" t="n">
         <v>3</v>
       </c>
-      <c r="H16" s="236" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I16" s="237" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" s="234" t="n">
-        <v>10</v>
-      </c>
-      <c r="M16" s="248" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N16" s="231" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" s="143">
-      <c r="A17" s="239" t="inlineStr"/>
-      <c r="B17" s="240" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="C17" s="247" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D17" s="242" t="n">
-        <v>26</v>
-      </c>
-      <c r="E17" s="242" t="n">
-        <v>11</v>
-      </c>
       <c r="F17" s="241" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G17" s="243" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H17" s="244" t="inlineStr">
         <is>
-          <t>7–1</t>
+          <t>1–3</t>
         </is>
       </c>
       <c r="I17" s="245" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J17" s="241" t="n">
         <v>5</v>
       </c>
-      <c r="K17" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="241" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="238" t="n">
-        <v>0.35</v>
+      <c r="K17" s="242" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" s="242" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" s="247" t="n">
+        <v>0.67</v>
       </c>
       <c r="N17" s="240" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Colombia</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="143">
       <c r="A18" s="230" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="B18" s="231" t="inlineStr">
         <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="C18" s="232" t="n">
-        <v>0.6</v>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C18" s="247" t="n">
+        <v>0.65</v>
       </c>
       <c r="D18" s="233" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E18" s="233" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="234" t="n">
+        <v>9</v>
+      </c>
+      <c r="G18" s="235" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="236" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I18" s="237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="234" t="n">
         <v>7</v>
       </c>
-      <c r="F18" s="234" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="236" t="inlineStr">
-        <is>
-          <t>2–2</t>
-        </is>
-      </c>
-      <c r="I18" s="237" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="234" t="n">
-        <v>5</v>
-      </c>
-      <c r="K18" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="L18" s="234" t="n">
-        <v>8</v>
-      </c>
       <c r="M18" s="238" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="N18" s="231" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Kroatia</t>
         </is>
       </c>
     </row>
@@ -34723,679 +34735,79 @@
       <c r="A19" s="239" t="inlineStr"/>
       <c r="B19" s="240" t="inlineStr">
         <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="C19" s="248" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D19" s="242" t="n">
-        <v>13</v>
-      </c>
-      <c r="E19" s="242" t="n">
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C19" s="238" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D19" s="241" t="n">
         <v>8</v>
       </c>
+      <c r="E19" s="241" t="n">
+        <v>3</v>
+      </c>
       <c r="F19" s="241" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G19" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="244" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I19" s="245" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="244" t="inlineStr">
-        <is>
-          <t>5–1</t>
-        </is>
-      </c>
-      <c r="I19" s="245" t="n">
-        <v>1</v>
-      </c>
       <c r="J19" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="K19" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="241" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="248" t="n">
-        <v>0.51</v>
+      <c r="K19" s="242" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="242" t="n">
+        <v>11</v>
+      </c>
+      <c r="M19" s="232" t="n">
+        <v>0.63</v>
       </c>
       <c r="N19" s="240" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" s="143">
-      <c r="A20" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe G</t>
-        </is>
-      </c>
-      <c r="B20" s="231" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C20" s="248" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D20" s="233" t="n">
-        <v>15</v>
-      </c>
-      <c r="E20" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="234" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="235" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="236" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I20" s="237" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="233" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" s="234" t="n">
-        <v>14</v>
-      </c>
-      <c r="M20" s="248" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="N20" s="231" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1" s="143">
-      <c r="A21" s="239" t="inlineStr"/>
-      <c r="B21" s="240" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="C21" s="248" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D21" s="242" t="n">
-        <v>17</v>
-      </c>
-      <c r="E21" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" s="241" t="n">
-        <v>8</v>
-      </c>
-      <c r="G21" s="243" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="244" t="inlineStr">
-        <is>
-          <t>2–2</t>
-        </is>
-      </c>
-      <c r="I21" s="245" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="242" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="241" t="n">
-        <v>13</v>
-      </c>
-      <c r="M21" s="248" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N21" s="240" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="14" customHeight="1" s="143">
+      <c r="A21" s="227" t="inlineStr">
+        <is>
+          <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="143">
-      <c r="A22" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe H</t>
-        </is>
-      </c>
-      <c r="B22" s="231" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="C22" s="238" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D22" s="234" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="235" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="236" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I22" s="237" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="K22" s="233" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="233" t="n">
-        <v>27</v>
-      </c>
-      <c r="M22" s="247" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N22" s="231" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="143">
-      <c r="A23" s="239" t="inlineStr"/>
-      <c r="B23" s="240" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C23" s="247" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D23" s="242" t="n">
-        <v>23</v>
-      </c>
-      <c r="E23" s="242" t="n">
-        <v>8</v>
-      </c>
-      <c r="F23" s="241" t="n">
-        <v>9</v>
-      </c>
-      <c r="G23" s="243" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" s="244" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I23" s="245" t="n">
-        <v>2</v>
-      </c>
-      <c r="J23" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" s="241" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" s="241" t="n">
-        <v>6</v>
-      </c>
-      <c r="M23" s="238" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N23" s="240" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="143">
-      <c r="A24" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe I</t>
-        </is>
-      </c>
-      <c r="B24" s="231" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C24" s="248" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D24" s="233" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" s="233" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="235" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="236" t="inlineStr">
-        <is>
-          <t>3–1</t>
-        </is>
-      </c>
-      <c r="I24" s="237" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" s="234" t="n">
-        <v>6</v>
-      </c>
-      <c r="M24" s="248" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N24" s="231" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1" s="143">
-      <c r="A25" s="239" t="inlineStr"/>
-      <c r="B25" s="240" t="inlineStr">
-        <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C25" s="238" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D25" s="241" t="n">
-        <v>11</v>
-      </c>
-      <c r="E25" s="241" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="241" t="n">
-        <v>8</v>
-      </c>
-      <c r="G25" s="243" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="244" t="inlineStr">
-        <is>
-          <t>1–4</t>
-        </is>
-      </c>
-      <c r="I25" s="245" t="n">
-        <v>2</v>
-      </c>
-      <c r="J25" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="K25" s="242" t="n">
-        <v>6</v>
-      </c>
-      <c r="L25" s="242" t="n">
-        <v>12</v>
-      </c>
-      <c r="M25" s="232" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N25" s="240" t="inlineStr">
-        <is>
-          <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1" s="143">
-      <c r="A26" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe J</t>
-        </is>
-      </c>
-      <c r="B26" s="231" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="C26" s="248" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D26" s="233" t="n">
-        <v>9</v>
-      </c>
-      <c r="E26" s="233" t="n">
-        <v>6</v>
-      </c>
-      <c r="F26" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" s="235" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="236" t="inlineStr">
-        <is>
-          <t>3–0</t>
-        </is>
-      </c>
-      <c r="I26" s="237" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="K26" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="234" t="n">
-        <v>6</v>
-      </c>
-      <c r="M26" s="248" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N26" s="231" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="143">
-      <c r="A27" s="239" t="inlineStr"/>
-      <c r="B27" s="240" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C27" s="232" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D27" s="241" t="n">
-        <v>9</v>
-      </c>
-      <c r="E27" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" s="243" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="244" t="inlineStr">
-        <is>
-          <t>3–1</t>
-        </is>
-      </c>
-      <c r="I27" s="245" t="n">
-        <v>3</v>
-      </c>
-      <c r="J27" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="K27" s="242" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="242" t="n">
-        <v>11</v>
-      </c>
-      <c r="M27" s="238" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N27" s="240" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="143">
-      <c r="A28" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe K</t>
-        </is>
-      </c>
-      <c r="B28" s="231" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C28" s="247" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D28" s="233" t="n">
-        <v>9</v>
-      </c>
-      <c r="E28" s="233" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="234" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" s="235" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="236" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I28" s="237" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="M28" s="238" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N28" s="231" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1" s="143">
-      <c r="A29" s="239" t="inlineStr"/>
-      <c r="B29" s="240" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C29" s="238" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D29" s="241" t="n">
-        <v>7</v>
-      </c>
-      <c r="E29" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="F29" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="243" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="244" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="I29" s="245" t="n">
-        <v>4</v>
-      </c>
-      <c r="J29" s="241" t="n">
-        <v>5</v>
-      </c>
-      <c r="K29" s="242" t="n">
-        <v>6</v>
-      </c>
-      <c r="L29" s="242" t="n">
-        <v>15</v>
-      </c>
-      <c r="M29" s="247" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="N29" s="240" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1" s="143">
-      <c r="A30" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe L</t>
-        </is>
-      </c>
-      <c r="B30" s="231" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C30" s="248" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D30" s="233" t="n">
-        <v>20</v>
-      </c>
-      <c r="E30" s="233" t="n">
-        <v>12</v>
-      </c>
-      <c r="F30" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" s="235" t="n">
-        <v>5</v>
-      </c>
-      <c r="H30" s="236" t="inlineStr">
-        <is>
-          <t>4–2</t>
-        </is>
-      </c>
-      <c r="I30" s="237" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="234" t="n">
-        <v>3</v>
-      </c>
-      <c r="K30" s="234" t="n">
-        <v>5</v>
-      </c>
-      <c r="L30" s="234" t="n">
-        <v>11</v>
-      </c>
-      <c r="M30" s="248" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N30" s="231" t="inlineStr">
-        <is>
-          <t>Kroatia</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1" s="143">
-      <c r="A31" s="239" t="inlineStr"/>
-      <c r="B31" s="240" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C31" s="238" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D31" s="241" t="n">
-        <v>8</v>
-      </c>
-      <c r="E31" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="F31" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="243" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="244" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I31" s="245" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="241" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" s="242" t="n">
-        <v>4</v>
-      </c>
-      <c r="L31" s="242" t="n">
-        <v>11</v>
-      </c>
-      <c r="M31" s="232" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N31" s="240" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="14" customHeight="1" s="143">
-      <c r="A33" s="227" t="inlineStr">
-        <is>
-          <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1" s="143">
-      <c r="A34" s="219" t="inlineStr">
+      <c r="A22" s="219" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B34" s="226" t="inlineStr">
+      <c r="B22" s="226" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C34" s="225" t="inlineStr">
+      <c r="C22" s="225" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D34" s="222" t="inlineStr">
+      <c r="D22" s="222" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E34" s="249" t="inlineStr">
+      <c r="E22" s="249" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -35404,7 +34816,7 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A33:N33"/>
+    <mergeCell ref="A21:N21"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -39096,7 +39096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="143" min="1" max="1"/>
@@ -39219,44 +39219,44 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C4" s="238" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D4" s="234" t="n">
-        <v>8</v>
+      <c r="C4" s="232" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="D4" s="233" t="n">
+        <v>16</v>
       </c>
       <c r="E4" s="233" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="234" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G4" s="235" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H4" s="236" t="inlineStr">
         <is>
-          <t>1–0</t>
+          <t>2–0</t>
         </is>
       </c>
       <c r="I4" s="237" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="234" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" s="234" t="n">
         <v>2</v>
       </c>
       <c r="L4" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="M4" s="232" t="n">
-        <v>0.57</v>
+        <v>3</v>
+      </c>
+      <c r="M4" s="238" t="n">
+        <v>0.39</v>
       </c>
       <c r="N4" s="231" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
     </row>
@@ -39264,99 +39264,95 @@
       <c r="A5" s="239" t="inlineStr"/>
       <c r="B5" s="240" t="inlineStr">
         <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C5" s="238" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D5" s="241" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" s="242" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="244" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I5" s="245" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" s="241" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" s="232" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N5" s="240" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="143">
+      <c r="A6" s="246" t="inlineStr"/>
+      <c r="B6" s="231" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="C6" s="232" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D6" s="233" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="233" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="234" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="236" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="I6" s="237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" s="238" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N6" s="231" t="inlineStr">
+        <is>
           <t>Tsjekkia</t>
-        </is>
-      </c>
-      <c r="C5" s="238" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D5" s="241" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="241" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" s="243" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="244" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I5" s="245" t="n">
-        <v>8</v>
-      </c>
-      <c r="J5" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" s="242" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" s="242" t="n">
-        <v>17</v>
-      </c>
-      <c r="M5" s="232" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N5" s="240" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" s="143">
-      <c r="A6" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe B</t>
-        </is>
-      </c>
-      <c r="B6" s="231" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C6" s="247" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D6" s="233" t="n">
-        <v>31</v>
-      </c>
-      <c r="E6" s="233" t="n">
-        <v>10</v>
-      </c>
-      <c r="F6" s="234" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="235" t="n">
-        <v>13</v>
-      </c>
-      <c r="H6" s="236" t="inlineStr">
-        <is>
-          <t>6–0</t>
-        </is>
-      </c>
-      <c r="I6" s="237" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="234" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" s="238" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N6" s="231" t="inlineStr">
-        <is>
-          <t>Qatar</t>
         </is>
       </c>
     </row>
@@ -39364,99 +39360,99 @@
       <c r="A7" s="239" t="inlineStr"/>
       <c r="B7" s="240" t="inlineStr">
         <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="C7" s="232" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D7" s="242" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" s="242" t="n">
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="C7" s="238" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D7" s="241" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="241" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" s="243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="244" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I7" s="245" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" s="243" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="244" t="inlineStr">
-        <is>
-          <t>4–1</t>
-        </is>
-      </c>
-      <c r="I7" s="245" t="n">
-        <v>1</v>
-      </c>
       <c r="J7" s="241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="241" t="n">
         <v>4</v>
       </c>
-      <c r="M7" s="238" t="n">
-        <v>0.38</v>
+      <c r="K7" s="242" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" s="242" t="n">
+        <v>17</v>
+      </c>
+      <c r="M7" s="232" t="n">
+        <v>0.61</v>
       </c>
       <c r="N7" s="240" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="143">
       <c r="A8" s="230" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="B8" s="231" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C8" s="232" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="D8" s="233" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" s="233" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="234" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="234" t="n">
-        <v>2</v>
-      </c>
       <c r="G8" s="235" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H8" s="236" t="inlineStr">
         <is>
-          <t>3–0</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I8" s="237" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="233" t="n">
         <v>4</v>
       </c>
       <c r="L8" s="234" t="n">
         <v>8</v>
       </c>
       <c r="M8" s="238" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="N8" s="231" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
     </row>
@@ -39464,99 +39460,95 @@
       <c r="A9" s="239" t="inlineStr"/>
       <c r="B9" s="240" t="inlineStr">
         <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="C9" s="238" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D9" s="241" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" s="241" t="n">
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C9" s="247" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D9" s="242" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" s="242" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="241" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" s="243" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" s="244" t="inlineStr">
+        <is>
+          <t>6–0</t>
+        </is>
+      </c>
+      <c r="I9" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="241" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="241" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="241" t="n">
+      <c r="L9" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" s="238" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N9" s="240" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="143">
+      <c r="A10" s="246" t="inlineStr"/>
+      <c r="B10" s="231" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C10" s="238" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="234" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="234" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="243" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="244" t="inlineStr">
-        <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="I9" s="245" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" s="241" t="n">
-        <v>5</v>
-      </c>
-      <c r="K9" s="242" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" s="242" t="n">
-        <v>12</v>
-      </c>
-      <c r="M9" s="232" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N9" s="240" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" s="143">
-      <c r="A10" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe D</t>
-        </is>
-      </c>
-      <c r="B10" s="231" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="C10" s="247" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D10" s="233" t="n">
-        <v>33</v>
-      </c>
-      <c r="E10" s="233" t="n">
-        <v>6</v>
-      </c>
       <c r="F10" s="234" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G10" s="235" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H10" s="236" t="inlineStr">
         <is>
-          <t>0–1</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I10" s="237" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J10" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" s="234" t="n">
-        <v>6</v>
-      </c>
-      <c r="M10" s="238" t="n">
-        <v>0.22</v>
+        <v>8</v>
+      </c>
+      <c r="K10" s="233" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="233" t="n">
+        <v>27</v>
+      </c>
+      <c r="M10" s="247" t="n">
+        <v>0.7</v>
       </c>
       <c r="N10" s="231" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Sveits</t>
         </is>
       </c>
     </row>
@@ -39564,179 +39556,175 @@
       <c r="A11" s="239" t="inlineStr"/>
       <c r="B11" s="240" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sveits</t>
         </is>
       </c>
       <c r="C11" s="232" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="D11" s="242" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E11" s="242" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="241" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G11" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="244" t="inlineStr">
+        <is>
+          <t>4–1</t>
+        </is>
+      </c>
+      <c r="I11" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="241" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="244" t="inlineStr">
-        <is>
-          <t>3–0</t>
-        </is>
-      </c>
-      <c r="I11" s="245" t="n">
+      <c r="L11" s="241" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" s="238" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N11" s="240" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="143">
+      <c r="A12" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
+      <c r="B12" s="231" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C12" s="248" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D12" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" s="233" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="235" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" s="241" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="241" t="n">
+      <c r="H12" s="236" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I12" s="237" t="n">
         <v>6</v>
-      </c>
-      <c r="M11" s="238" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="N11" s="240" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" s="143">
-      <c r="A12" s="246" t="inlineStr"/>
-      <c r="B12" s="231" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C12" s="232" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D12" s="233" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="235" t="n">
-        <v>5</v>
-      </c>
-      <c r="H12" s="236" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I12" s="237" t="n">
-        <v>0</v>
       </c>
       <c r="J12" s="234" t="n">
         <v>3</v>
       </c>
       <c r="K12" s="234" t="n">
-        <v>2</v>
-      </c>
-      <c r="L12" s="234" t="n">
-        <v>5</v>
-      </c>
-      <c r="M12" s="238" t="n">
-        <v>0.37</v>
+        <v>4</v>
+      </c>
+      <c r="L12" s="233" t="n">
+        <v>13</v>
+      </c>
+      <c r="M12" s="248" t="n">
+        <v>0.46</v>
       </c>
       <c r="N12" s="231" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="143">
-      <c r="A13" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe E</t>
-        </is>
-      </c>
+      <c r="A13" s="239" t="inlineStr"/>
       <c r="B13" s="240" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="C13" s="248" t="n">
-        <v>0.49</v>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C13" s="232" t="n">
+        <v>0.57</v>
       </c>
       <c r="D13" s="242" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E13" s="242" t="n">
         <v>5</v>
       </c>
       <c r="F13" s="241" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G13" s="243" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="244" t="inlineStr">
         <is>
-          <t>2–1</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I13" s="245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" s="241" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K13" s="241" t="n">
         <v>4</v>
       </c>
       <c r="L13" s="241" t="n">
-        <v>11</v>
-      </c>
-      <c r="M13" s="248" t="n">
-        <v>0.51</v>
+        <v>8</v>
+      </c>
+      <c r="M13" s="238" t="n">
+        <v>0.43</v>
       </c>
       <c r="N13" s="240" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Haiti</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="143">
-      <c r="A14" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe G</t>
-        </is>
-      </c>
+      <c r="A14" s="246" t="inlineStr"/>
       <c r="B14" s="231" t="inlineStr">
         <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C14" s="232" t="n">
-        <v>0.5600000000000001</v>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C14" s="248" t="n">
+        <v>0.5</v>
       </c>
       <c r="D14" s="233" t="n">
-        <v>14</v>
-      </c>
-      <c r="E14" s="233" t="n">
-        <v>5</v>
+        <v>13</v>
+      </c>
+      <c r="E14" s="234" t="n">
+        <v>3</v>
       </c>
       <c r="F14" s="234" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" s="235" t="n">
         <v>3</v>
       </c>
       <c r="H14" s="236" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>0–1</t>
         </is>
       </c>
       <c r="I14" s="237" t="n">
@@ -39746,17 +39734,17 @@
         <v>3</v>
       </c>
       <c r="K14" s="234" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L14" s="234" t="n">
-        <v>9</v>
-      </c>
-      <c r="M14" s="238" t="n">
-        <v>0.44</v>
+        <v>8</v>
+      </c>
+      <c r="M14" s="248" t="n">
+        <v>0.5</v>
       </c>
       <c r="N14" s="231" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Skottland</t>
         </is>
       </c>
     </row>
@@ -39764,203 +39752,195 @@
       <c r="A15" s="239" t="inlineStr"/>
       <c r="B15" s="240" t="inlineStr">
         <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="C15" s="248" t="n">
-        <v>0.48</v>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="C15" s="238" t="n">
+        <v>0.4</v>
       </c>
       <c r="D15" s="241" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="242" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="243" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="244" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I15" s="245" t="n">
         <v>4</v>
-      </c>
-      <c r="F15" s="241" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="243" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="244" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I15" s="245" t="n">
-        <v>3</v>
       </c>
       <c r="J15" s="241" t="n">
         <v>5</v>
       </c>
-      <c r="K15" s="241" t="n">
+      <c r="K15" s="242" t="n">
         <v>3</v>
       </c>
       <c r="L15" s="242" t="n">
-        <v>11</v>
-      </c>
-      <c r="M15" s="248" t="n">
-        <v>0.52</v>
+        <v>12</v>
+      </c>
+      <c r="M15" s="232" t="n">
+        <v>0.6</v>
       </c>
       <c r="N15" s="240" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="143">
       <c r="A16" s="230" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="B16" s="231" t="inlineStr">
         <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C16" s="247" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D16" s="233" t="n">
-        <v>24</v>
-      </c>
-      <c r="E16" s="233" t="n">
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C16" s="238" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D16" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="236" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I16" s="237" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" s="234" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="233" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="233" t="n">
+        <v>28</v>
+      </c>
+      <c r="M16" s="232" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N16" s="231" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="143">
+      <c r="A17" s="239" t="inlineStr"/>
+      <c r="B17" s="240" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="C17" s="247" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D17" s="242" t="n">
+        <v>33</v>
+      </c>
+      <c r="E17" s="242" t="n">
         <v>6</v>
       </c>
-      <c r="F16" s="234" t="n">
+      <c r="F17" s="241" t="n">
+        <v>15</v>
+      </c>
+      <c r="G17" s="243" t="n">
         <v>12</v>
       </c>
-      <c r="G16" s="235" t="n">
+      <c r="H17" s="244" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I17" s="245" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" s="241" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="236" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I16" s="237" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="234" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" s="234" t="n">
+      <c r="M17" s="238" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N17" s="240" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="143">
+      <c r="A18" s="246" t="inlineStr"/>
+      <c r="B18" s="231" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C18" s="232" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D18" s="233" t="n">
+        <v>17</v>
+      </c>
+      <c r="E18" s="233" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="234" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="235" t="n">
+        <v>6</v>
+      </c>
+      <c r="H18" s="236" t="inlineStr">
+        <is>
+          <t>4–1</t>
+        </is>
+      </c>
+      <c r="I18" s="237" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="234" t="n">
         <v>2</v>
-      </c>
-      <c r="L16" s="234" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" s="238" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N16" s="231" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1" s="143">
-      <c r="A17" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe K</t>
-        </is>
-      </c>
-      <c r="B17" s="240" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C17" s="238" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D17" s="241" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="241" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="241" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="243" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="244" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="I17" s="245" t="n">
-        <v>4</v>
-      </c>
-      <c r="J17" s="241" t="n">
-        <v>5</v>
-      </c>
-      <c r="K17" s="242" t="n">
-        <v>6</v>
-      </c>
-      <c r="L17" s="242" t="n">
-        <v>15</v>
-      </c>
-      <c r="M17" s="247" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="N17" s="240" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1" s="143">
-      <c r="A18" s="230" t="inlineStr">
-        <is>
-          <t>Gruppe L</t>
-        </is>
-      </c>
-      <c r="B18" s="231" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C18" s="247" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D18" s="233" t="n">
-        <v>22</v>
-      </c>
-      <c r="E18" s="233" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" s="234" t="n">
-        <v>9</v>
-      </c>
-      <c r="G18" s="235" t="n">
-        <v>5</v>
-      </c>
-      <c r="H18" s="236" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I18" s="237" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="234" t="n">
-        <v>4</v>
       </c>
       <c r="K18" s="234" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="234" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M18" s="238" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="N18" s="231" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -39968,79 +39948,879 @@
       <c r="A19" s="239" t="inlineStr"/>
       <c r="B19" s="240" t="inlineStr">
         <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C19" s="232" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D19" s="242" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="243" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="244" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I19" s="245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="241" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="238" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N19" s="240" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="143">
+      <c r="A20" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="B20" s="231" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="C20" s="248" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D20" s="233" t="n">
+        <v>16</v>
+      </c>
+      <c r="E20" s="233" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="234" t="n">
+        <v>9</v>
+      </c>
+      <c r="G20" s="235" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="236" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I20" s="237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="K20" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="234" t="n">
+        <v>10</v>
+      </c>
+      <c r="M20" s="248" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N20" s="231" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="143">
+      <c r="A21" s="239" t="inlineStr"/>
+      <c r="B21" s="240" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C21" s="247" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D21" s="242" t="n">
+        <v>26</v>
+      </c>
+      <c r="E21" s="242" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" s="241" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="243" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="244" t="inlineStr">
+        <is>
+          <t>7–1</t>
+        </is>
+      </c>
+      <c r="I21" s="245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="241" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" s="241" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" s="238" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N21" s="240" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="143">
+      <c r="A22" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="B22" s="231" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C22" s="232" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="233" t="n">
+        <v>11</v>
+      </c>
+      <c r="E22" s="233" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="236" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I22" s="237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="234" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="M22" s="238" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N22" s="231" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="143">
+      <c r="A23" s="239" t="inlineStr"/>
+      <c r="B23" s="240" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="C23" s="248" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D23" s="242" t="n">
+        <v>13</v>
+      </c>
+      <c r="E23" s="242" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="244" t="inlineStr">
+        <is>
+          <t>5–1</t>
+        </is>
+      </c>
+      <c r="I23" s="245" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="241" t="n">
+        <v>5</v>
+      </c>
+      <c r="M23" s="248" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N23" s="240" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="143">
+      <c r="A24" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="B24" s="231" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C24" s="248" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D24" s="233" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="234" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" s="235" t="n">
+        <v>5</v>
+      </c>
+      <c r="H24" s="236" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I24" s="237" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="233" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="234" t="n">
+        <v>14</v>
+      </c>
+      <c r="M24" s="248" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N24" s="231" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="143">
+      <c r="A25" s="239" t="inlineStr"/>
+      <c r="B25" s="240" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C25" s="248" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D25" s="242" t="n">
+        <v>17</v>
+      </c>
+      <c r="E25" s="241" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="241" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="243" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="244" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I25" s="245" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="242" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="241" t="n">
+        <v>13</v>
+      </c>
+      <c r="M25" s="248" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N25" s="240" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="143">
+      <c r="A26" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="B26" s="231" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C26" s="238" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D26" s="234" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="236" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I26" s="237" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="K26" s="233" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="233" t="n">
+        <v>27</v>
+      </c>
+      <c r="M26" s="247" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N26" s="231" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="143">
+      <c r="A27" s="239" t="inlineStr"/>
+      <c r="B27" s="240" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C27" s="247" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D27" s="242" t="n">
+        <v>23</v>
+      </c>
+      <c r="E27" s="242" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="241" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="243" t="n">
+        <v>6</v>
+      </c>
+      <c r="H27" s="244" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I27" s="245" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="K27" s="241" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="241" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" s="238" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N27" s="240" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="143">
+      <c r="A28" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
+      <c r="B28" s="231" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C28" s="248" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D28" s="233" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28" s="233" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" s="234" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="236" t="inlineStr">
+        <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="I28" s="237" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="L28" s="234" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" s="248" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N28" s="231" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="143">
+      <c r="A29" s="239" t="inlineStr"/>
+      <c r="B29" s="240" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C29" s="238" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D29" s="241" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" s="241" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="241" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="244" t="inlineStr">
+        <is>
+          <t>1–4</t>
+        </is>
+      </c>
+      <c r="I29" s="245" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="241" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" s="242" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" s="242" t="n">
+        <v>12</v>
+      </c>
+      <c r="M29" s="232" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N29" s="240" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="143">
+      <c r="A30" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="B30" s="231" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C30" s="248" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D30" s="233" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" s="233" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="236" t="inlineStr">
+        <is>
+          <t>3–0</t>
+        </is>
+      </c>
+      <c r="I30" s="237" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="234" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" s="248" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N30" s="231" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="143">
+      <c r="A31" s="239" t="inlineStr"/>
+      <c r="B31" s="240" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C31" s="232" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D31" s="241" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="241" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="244" t="inlineStr">
+        <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="I31" s="245" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="241" t="n">
+        <v>4</v>
+      </c>
+      <c r="K31" s="242" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" s="242" t="n">
+        <v>11</v>
+      </c>
+      <c r="M31" s="238" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N31" s="240" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="143">
+      <c r="A32" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="B32" s="231" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C32" s="247" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D32" s="233" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="233" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="234" t="n">
+        <v>4</v>
+      </c>
+      <c r="G32" s="235" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="236" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I32" s="237" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" s="234" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="234" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" s="238" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N32" s="231" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="143">
+      <c r="A33" s="239" t="inlineStr"/>
+      <c r="B33" s="240" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C33" s="238" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D33" s="241" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="241" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="241" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="243" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="244" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I33" s="245" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" s="241" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="242" t="n">
+        <v>6</v>
+      </c>
+      <c r="L33" s="242" t="n">
+        <v>15</v>
+      </c>
+      <c r="M33" s="247" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N33" s="240" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="143">
+      <c r="A34" s="230" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="B34" s="231" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C34" s="248" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D34" s="233" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" s="233" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="235" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="236" t="inlineStr">
+        <is>
+          <t>4–2</t>
+        </is>
+      </c>
+      <c r="I34" s="237" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="234" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="234" t="n">
+        <v>5</v>
+      </c>
+      <c r="L34" s="234" t="n">
+        <v>11</v>
+      </c>
+      <c r="M34" s="248" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N34" s="231" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="143">
+      <c r="A35" s="239" t="inlineStr"/>
+      <c r="B35" s="240" t="inlineStr">
+        <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C19" s="238" t="n">
+      <c r="C35" s="238" t="n">
         <v>0.37</v>
       </c>
-      <c r="D19" s="241" t="n">
+      <c r="D35" s="241" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="241" t="n">
+      <c r="E35" s="241" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="241" t="n">
+      <c r="F35" s="241" t="n">
         <v>4</v>
       </c>
-      <c r="G19" s="243" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="244" t="inlineStr">
+      <c r="G35" s="243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="244" t="inlineStr">
         <is>
           <t>1–0</t>
         </is>
       </c>
-      <c r="I19" s="245" t="n">
+      <c r="I35" s="245" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="241" t="n">
+      <c r="J35" s="241" t="n">
         <v>5</v>
       </c>
-      <c r="K19" s="242" t="n">
+      <c r="K35" s="242" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="242" t="n">
+      <c r="L35" s="242" t="n">
         <v>11</v>
       </c>
-      <c r="M19" s="232" t="n">
+      <c r="M35" s="232" t="n">
         <v>0.63</v>
       </c>
-      <c r="N19" s="240" t="inlineStr">
+      <c r="N35" s="240" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1" s="143">
-      <c r="A21" s="227" t="inlineStr">
+    <row r="37" ht="14" customHeight="1" s="143">
+      <c r="A37" s="227" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1" s="143">
-      <c r="A22" s="219" t="inlineStr">
+    <row r="38" ht="18" customHeight="1" s="143">
+      <c r="A38" s="219" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B22" s="226" t="inlineStr">
+      <c r="B38" s="226" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C22" s="225" t="inlineStr">
+      <c r="C38" s="225" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D22" s="222" t="inlineStr">
+      <c r="D38" s="222" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E22" s="249" t="inlineStr">
+      <c r="E38" s="249" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -40049,7 +40829,7 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A21:N21"/>
+    <mergeCell ref="A37:N37"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1039,7 +1039,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="256">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1744,6 +1744,9 @@
     <xf numFmtId="0" fontId="67" fillId="49" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="61" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -38620,7 +38623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="143" min="1" max="1"/>
@@ -38810,12 +38813,10 @@
       <c r="H7" s="211" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="211" t="n">
-        <v>2</v>
-      </c>
+      <c r="I7" s="210" t="n"/>
       <c r="J7" s="210" t="n"/>
-      <c r="K7" s="216" t="n">
-        <v>7</v>
+      <c r="K7" s="212" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" s="143">
@@ -38944,7 +38945,7 @@
     <row r="13" ht="16" customHeight="1" s="143">
       <c r="A13" s="209" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>45+</t>
         </is>
       </c>
       <c r="B13" s="218" t="inlineStr">
@@ -39001,82 +39002,173 @@
     <row r="14" ht="20" customHeight="1" s="143">
       <c r="A14" s="209" t="inlineStr">
         <is>
+          <t>HT</t>
+        </is>
+      </c>
+      <c r="B14" s="210" t="n"/>
+      <c r="C14" s="210" t="n"/>
+      <c r="D14" s="211" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="210" t="n"/>
+      <c r="F14" s="256" t="n">
+        <v>4</v>
+      </c>
+      <c r="G14" s="210" t="n"/>
+      <c r="H14" s="210" t="n"/>
+      <c r="I14" s="210" t="n"/>
+      <c r="J14" s="210" t="n"/>
+      <c r="K14" s="210" t="n"/>
+    </row>
+    <row r="15" ht="8" customHeight="1" s="143">
+      <c r="A15" s="217" t="n"/>
+      <c r="B15" s="217" t="n"/>
+      <c r="C15" s="217" t="n"/>
+      <c r="D15" s="217" t="n"/>
+      <c r="E15" s="217" t="n"/>
+      <c r="F15" s="217" t="n"/>
+      <c r="G15" s="217" t="n"/>
+      <c r="H15" s="217" t="n"/>
+      <c r="I15" s="217" t="n"/>
+      <c r="J15" s="217" t="n"/>
+      <c r="K15" s="217" t="n"/>
+    </row>
+    <row r="16" ht="16" customHeight="1" s="143">
+      <c r="A16" s="209" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B16" s="218" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="C16" s="218" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="D16" s="218" t="inlineStr">
+        <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="E16" s="218" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="F16" s="218" t="inlineStr">
+        <is>
+          <t>+5</t>
+        </is>
+      </c>
+      <c r="G16" s="218" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+      <c r="H16" s="218" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="I16" s="218" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="J16" s="218" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="K16" s="218" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="143">
+      <c r="A17" s="209" t="inlineStr">
+        <is>
           <t>90+</t>
         </is>
       </c>
-      <c r="B14" s="210" t="n"/>
-      <c r="C14" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="211" t="n">
+      <c r="B17" s="210" t="n"/>
+      <c r="C17" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="211" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="212" t="n">
+      <c r="G17" s="212" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="213" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" s="210" t="n"/>
-    </row>
-    <row r="16" ht="14" customHeight="1" s="143">
-      <c r="A16" s="219" t="inlineStr">
+      <c r="H17" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="213" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="210" t="n"/>
+    </row>
+    <row r="19" ht="14" customHeight="1" s="143">
+      <c r="A19" s="219" t="inlineStr">
         <is>
           <t>Fargeskala:</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1" s="143">
-      <c r="B17" s="220" t="inlineStr">
+    <row r="20" ht="18" customHeight="1" s="143">
+      <c r="B20" s="220" t="inlineStr">
         <is>
           <t>0 mål</t>
         </is>
       </c>
-      <c r="C17" s="221" t="inlineStr">
+      <c r="C20" s="221" t="inlineStr">
         <is>
           <t>1 mål</t>
         </is>
       </c>
-      <c r="D17" s="222" t="inlineStr">
+      <c r="D20" s="222" t="inlineStr">
         <is>
           <t>2 mål</t>
         </is>
       </c>
-      <c r="E17" s="223" t="inlineStr">
+      <c r="E20" s="223" t="inlineStr">
         <is>
           <t>3 mål</t>
         </is>
       </c>
-      <c r="F17" s="224" t="inlineStr">
+      <c r="F20" s="224" t="inlineStr">
         <is>
           <t>4 mål</t>
         </is>
       </c>
-      <c r="G17" s="225" t="inlineStr">
+      <c r="G20" s="225" t="inlineStr">
         <is>
           <t>5 mål</t>
         </is>
       </c>
-      <c r="H17" s="226" t="inlineStr">
+      <c r="H20" s="226" t="inlineStr">
         <is>
           <t>6+ mål</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="14" customHeight="1" s="143">
-      <c r="A19" s="227" t="inlineStr">
+    <row r="22" ht="14" customHeight="1" s="143">
+      <c r="A22" s="227" t="inlineStr">
         <is>
           <t>| Tykk strek markerer halvtidspausen (mellom minutt 45 og 46)</t>
         </is>
@@ -58982,9 +59074,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assists" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Assists" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Alder" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -809,13 +809,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -834,7 +834,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -858,12 +858,12 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -877,7 +877,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -890,8 +889,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -905,7 +904,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -915,7 +913,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -930,9 +928,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Assists" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Alder" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assists" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -809,13 +809,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -834,7 +834,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -858,12 +858,12 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -877,6 +877,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -889,8 +890,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -904,6 +905,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -913,7 +915,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -928,9 +930,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -57278,7 +57280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -58182,47 +58184,47 @@
       </c>
       <c r="B20" s="66" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="C20" s="83" t="n">
-        <v>0.49</v>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C20" s="82" t="n">
+        <v>0.75</v>
       </c>
       <c r="D20" s="68" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E20" s="68" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="G20" s="70" t="n">
-        <v>3</v>
-      </c>
       <c r="H20" s="71" t="inlineStr">
         <is>
-          <t>1–0</t>
+          <t>0–0</t>
         </is>
       </c>
       <c r="I20" s="72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" s="69" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K20" s="69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="M20" s="83" t="n">
-        <v>0.51</v>
+      <c r="M20" s="73" t="n">
+        <v>0.25</v>
       </c>
       <c r="N20" s="66" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -58230,79 +58232,75 @@
       <c r="A21" s="74" t="inlineStr"/>
       <c r="B21" s="75" t="inlineStr">
         <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="C21" s="83" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D21" s="77" t="n">
+        <v>16</v>
+      </c>
+      <c r="E21" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="76" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="79" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I21" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="76" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M21" s="83" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N21" s="75" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="81" t="inlineStr"/>
+      <c r="B22" s="66" t="inlineStr">
+        <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="C21" s="82" t="n">
+      <c r="C22" s="82" t="n">
         <v>0.65</v>
       </c>
-      <c r="D21" s="77" t="n">
+      <c r="D22" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="E21" s="77" t="n">
+      <c r="E22" s="68" t="n">
         <v>11</v>
       </c>
-      <c r="F21" s="76" t="n">
+      <c r="F22" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="G21" s="78" t="n">
+      <c r="G22" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="H21" s="79" t="inlineStr">
+      <c r="H22" s="71" t="inlineStr">
         <is>
           <t>7–1</t>
-        </is>
-      </c>
-      <c r="I21" s="80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="76" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="76" t="n">
-        <v>7</v>
-      </c>
-      <c r="M21" s="73" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="N21" s="75" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="65" t="inlineStr">
-        <is>
-          <t>Gruppe F</t>
-        </is>
-      </c>
-      <c r="B22" s="66" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="C22" s="67" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D22" s="68" t="n">
-        <v>11</v>
-      </c>
-      <c r="E22" s="68" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="71" t="inlineStr">
-        <is>
-          <t>2–2</t>
         </is>
       </c>
       <c r="I22" s="72" t="n">
@@ -58312,17 +58310,17 @@
         <v>5</v>
       </c>
       <c r="K22" s="69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L22" s="69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M22" s="73" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="N22" s="66" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -58330,147 +58328,147 @@
       <c r="A23" s="74" t="inlineStr"/>
       <c r="B23" s="75" t="inlineStr">
         <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D23" s="77" t="n">
+        <v>16</v>
+      </c>
+      <c r="E23" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="79" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="I23" s="80" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="76" t="n">
+        <v>9</v>
+      </c>
+      <c r="M23" s="83" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N23" s="75" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="65" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="B24" s="66" t="inlineStr">
+        <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="C23" s="83" t="n">
+      <c r="C24" s="67" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D24" s="68" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" s="68" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I24" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="M24" s="73" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N24" s="66" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="74" t="inlineStr"/>
+      <c r="B25" s="75" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C25" s="83" t="n">
         <v>0.52</v>
       </c>
-      <c r="D23" s="76" t="n">
+      <c r="D25" s="76" t="n">
         <v>12</v>
       </c>
-      <c r="E23" s="76" t="n">
+      <c r="E25" s="76" t="n">
         <v>7</v>
       </c>
-      <c r="F23" s="76" t="n">
+      <c r="F25" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="78" t="n">
+      <c r="G25" s="78" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="79" t="inlineStr">
+      <c r="H25" s="79" t="inlineStr">
         <is>
           <t>5–1</t>
         </is>
       </c>
-      <c r="I23" s="80" t="n">
+      <c r="I25" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="76" t="n">
+      <c r="J25" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="K23" s="77" t="n">
+      <c r="K25" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="L23" s="77" t="n">
+      <c r="L25" s="77" t="n">
         <v>20</v>
       </c>
-      <c r="M23" s="83" t="n">
+      <c r="M25" s="83" t="n">
         <v>0.48</v>
       </c>
-      <c r="N23" s="75" t="inlineStr">
+      <c r="N25" s="75" t="inlineStr">
         <is>
           <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="81" t="inlineStr"/>
-      <c r="B24" s="66" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="C24" s="83" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D24" s="68" t="n">
-        <v>13</v>
-      </c>
-      <c r="E24" s="68" t="n">
-        <v>8</v>
-      </c>
-      <c r="F24" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>5–1</t>
-        </is>
-      </c>
-      <c r="I24" s="72" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" s="69" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" s="83" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="N24" s="66" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="65" t="inlineStr">
-        <is>
-          <t>Gruppe G</t>
-        </is>
-      </c>
-      <c r="B25" s="75" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C25" s="83" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D25" s="77" t="n">
-        <v>15</v>
-      </c>
-      <c r="E25" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="76" t="n">
-        <v>7</v>
-      </c>
-      <c r="G25" s="78" t="n">
-        <v>5</v>
-      </c>
-      <c r="H25" s="79" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I25" s="80" t="n">
-        <v>8</v>
-      </c>
-      <c r="J25" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" s="76" t="n">
-        <v>14</v>
-      </c>
-      <c r="M25" s="83" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="N25" s="75" t="inlineStr">
-        <is>
-          <t>Egypt</t>
         </is>
       </c>
     </row>
@@ -58478,75 +58476,75 @@
       <c r="A26" s="81" t="inlineStr"/>
       <c r="B26" s="66" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C26" s="83" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="D26" s="68" t="n">
-        <v>17</v>
-      </c>
-      <c r="E26" s="69" t="n">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="E26" s="68" t="n">
+        <v>8</v>
       </c>
       <c r="F26" s="69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G26" s="70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H26" s="71" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>5–1</t>
         </is>
       </c>
       <c r="I26" s="72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J26" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="K26" s="68" t="n">
-        <v>8</v>
+      <c r="K26" s="69" t="n">
+        <v>2</v>
       </c>
       <c r="L26" s="69" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M26" s="83" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="N26" s="66" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tunisia</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="65" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="B27" s="75" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="C27" s="73" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D27" s="76" t="n">
-        <v>7</v>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C27" s="83" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D27" s="77" t="n">
+        <v>15</v>
       </c>
       <c r="E27" s="76" t="n">
         <v>3</v>
       </c>
       <c r="F27" s="76" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G27" s="78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H27" s="79" t="inlineStr">
         <is>
@@ -58554,23 +58552,23 @@
         </is>
       </c>
       <c r="I27" s="80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J27" s="76" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K27" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="L27" s="77" t="n">
-        <v>27</v>
-      </c>
-      <c r="M27" s="82" t="n">
-        <v>0.65</v>
+        <v>4</v>
+      </c>
+      <c r="L27" s="76" t="n">
+        <v>14</v>
+      </c>
+      <c r="M27" s="83" t="n">
+        <v>0.47</v>
       </c>
       <c r="N27" s="75" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Egypt</t>
         </is>
       </c>
     </row>
@@ -58578,99 +58576,99 @@
       <c r="A28" s="81" t="inlineStr"/>
       <c r="B28" s="66" t="inlineStr">
         <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C28" s="82" t="n">
-        <v>0.74</v>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C28" s="83" t="n">
+        <v>0.47</v>
       </c>
       <c r="D28" s="68" t="n">
-        <v>23</v>
-      </c>
-      <c r="E28" s="68" t="n">
+        <v>17</v>
+      </c>
+      <c r="E28" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="F28" s="69" t="n">
-        <v>9</v>
-      </c>
       <c r="G28" s="70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H28" s="71" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>2–2</t>
         </is>
       </c>
       <c r="I28" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="K28" s="69" t="n">
-        <v>1</v>
+      <c r="K28" s="68" t="n">
+        <v>8</v>
       </c>
       <c r="L28" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="M28" s="73" t="n">
-        <v>0.26</v>
+        <v>13</v>
+      </c>
+      <c r="M28" s="83" t="n">
+        <v>0.53</v>
       </c>
       <c r="N28" s="66" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="65" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="B29" s="75" t="inlineStr">
         <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C29" s="83" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D29" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E29" s="77" t="n">
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C29" s="73" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D29" s="76" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="79" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I29" s="80" t="n">
         <v>9</v>
       </c>
-      <c r="F29" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="79" t="inlineStr">
-        <is>
-          <t>3–1</t>
-        </is>
-      </c>
-      <c r="I29" s="80" t="n">
-        <v>1</v>
-      </c>
       <c r="J29" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" s="76" t="n">
-        <v>6</v>
-      </c>
-      <c r="M29" s="83" t="n">
-        <v>0.46</v>
+        <v>8</v>
+      </c>
+      <c r="K29" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" s="77" t="n">
+        <v>27</v>
+      </c>
+      <c r="M29" s="82" t="n">
+        <v>0.65</v>
       </c>
       <c r="N29" s="75" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
     </row>
@@ -58678,99 +58676,99 @@
       <c r="A30" s="81" t="inlineStr"/>
       <c r="B30" s="66" t="inlineStr">
         <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C30" s="73" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D30" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="E30" s="69" t="n">
-        <v>1</v>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C30" s="82" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D30" s="68" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" s="68" t="n">
+        <v>8</v>
       </c>
       <c r="F30" s="69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30" s="70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H30" s="71" t="inlineStr">
         <is>
-          <t>1–4</t>
+          <t>0–0</t>
         </is>
       </c>
       <c r="I30" s="72" t="n">
         <v>2</v>
       </c>
       <c r="J30" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="K30" s="68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="L30" s="68" t="n">
-        <v>12</v>
-      </c>
-      <c r="M30" s="67" t="n">
-        <v>0.63</v>
+      <c r="M30" s="73" t="n">
+        <v>0.26</v>
       </c>
       <c r="N30" s="66" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="65" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="B31" s="75" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C31" s="83" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="D31" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="E31" s="77" t="n">
-        <v>6</v>
-      </c>
       <c r="F31" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="79" t="inlineStr">
+        <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="I31" s="80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="76" t="n">
         <v>3</v>
-      </c>
-      <c r="G31" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="79" t="inlineStr">
-        <is>
-          <t>3–0</t>
-        </is>
-      </c>
-      <c r="I31" s="80" t="n">
-        <v>3</v>
-      </c>
-      <c r="J31" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="76" t="n">
-        <v>0</v>
       </c>
       <c r="L31" s="76" t="n">
         <v>6</v>
       </c>
       <c r="M31" s="83" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="N31" s="75" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
@@ -58778,79 +58776,79 @@
       <c r="A32" s="81" t="inlineStr"/>
       <c r="B32" s="66" t="inlineStr">
         <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C32" s="67" t="n">
-        <v>0.62</v>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C32" s="73" t="n">
+        <v>0.37</v>
       </c>
       <c r="D32" s="69" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E32" s="69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" s="69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G32" s="70" t="n">
         <v>2</v>
       </c>
       <c r="H32" s="71" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>1–4</t>
         </is>
       </c>
       <c r="I32" s="72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" s="69" t="n">
         <v>4</v>
       </c>
       <c r="K32" s="68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L32" s="68" t="n">
-        <v>11</v>
-      </c>
-      <c r="M32" s="73" t="n">
-        <v>0.38</v>
+        <v>12</v>
+      </c>
+      <c r="M32" s="67" t="n">
+        <v>0.63</v>
       </c>
       <c r="N32" s="66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Norge</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="65" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="B33" s="75" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C33" s="82" t="n">
-        <v>0.75</v>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C33" s="83" t="n">
+        <v>0.47</v>
       </c>
       <c r="D33" s="77" t="n">
         <v>9</v>
       </c>
       <c r="E33" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="F33" s="76" t="n">
-        <v>4</v>
-      </c>
       <c r="G33" s="78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" s="79" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I33" s="80" t="n">
@@ -58860,17 +58858,17 @@
         <v>3</v>
       </c>
       <c r="K33" s="76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="76" t="n">
-        <v>8</v>
-      </c>
-      <c r="M33" s="73" t="n">
-        <v>0.25</v>
+        <v>6</v>
+      </c>
+      <c r="M33" s="83" t="n">
+        <v>0.53</v>
       </c>
       <c r="N33" s="75" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -58878,79 +58876,79 @@
       <c r="A34" s="81" t="inlineStr"/>
       <c r="B34" s="66" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C34" s="73" t="n">
-        <v>0.33</v>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C34" s="67" t="n">
+        <v>0.62</v>
       </c>
       <c r="D34" s="69" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E34" s="69" t="n">
         <v>3</v>
       </c>
       <c r="F34" s="69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" s="70" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="71" t="inlineStr">
         <is>
-          <t>1–3</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I34" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="J34" s="69" t="n">
-        <v>5</v>
-      </c>
       <c r="K34" s="68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L34" s="68" t="n">
-        <v>15</v>
-      </c>
-      <c r="M34" s="82" t="n">
-        <v>0.67</v>
+        <v>11</v>
+      </c>
+      <c r="M34" s="73" t="n">
+        <v>0.38</v>
       </c>
       <c r="N34" s="66" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Jordan</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="65" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="B35" s="75" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C35" s="83" t="n">
-        <v>0.54</v>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C35" s="82" t="n">
+        <v>0.75</v>
       </c>
       <c r="D35" s="77" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E35" s="77" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F35" s="76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H35" s="79" t="inlineStr">
         <is>
-          <t>4–2</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I35" s="80" t="n">
@@ -58960,17 +58958,17 @@
         <v>3</v>
       </c>
       <c r="K35" s="76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L35" s="76" t="n">
-        <v>11</v>
-      </c>
-      <c r="M35" s="83" t="n">
-        <v>0.46</v>
+        <v>8</v>
+      </c>
+      <c r="M35" s="73" t="n">
+        <v>0.25</v>
       </c>
       <c r="N35" s="75" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -58978,79 +58976,179 @@
       <c r="A36" s="81" t="inlineStr"/>
       <c r="B36" s="66" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Usbekistan</t>
         </is>
       </c>
       <c r="C36" s="73" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="D36" s="69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" s="69" t="n">
         <v>3</v>
       </c>
       <c r="F36" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="71" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I36" s="72" t="n">
         <v>4</v>
-      </c>
-      <c r="G36" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="71" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I36" s="72" t="n">
-        <v>2</v>
       </c>
       <c r="J36" s="69" t="n">
         <v>5</v>
       </c>
       <c r="K36" s="68" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" s="68" t="n">
+        <v>15</v>
+      </c>
+      <c r="M36" s="82" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N36" s="66" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="65" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="B37" s="75" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C37" s="83" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D37" s="77" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="79" t="inlineStr">
+        <is>
+          <t>4–2</t>
+        </is>
+      </c>
+      <c r="I37" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" s="76" t="n">
+        <v>11</v>
+      </c>
+      <c r="M37" s="83" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N37" s="75" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="81" t="inlineStr"/>
+      <c r="B38" s="66" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C38" s="73" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D38" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="L36" s="68" t="n">
+      <c r="G38" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="71" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I38" s="72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" s="68" t="n">
+        <v>4</v>
+      </c>
+      <c r="L38" s="68" t="n">
         <v>11</v>
       </c>
-      <c r="M36" s="67" t="n">
+      <c r="M38" s="67" t="n">
         <v>0.63</v>
       </c>
-      <c r="N36" s="66" t="inlineStr">
+      <c r="N38" s="66" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="62" t="inlineStr">
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="62" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="54" t="inlineStr">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="54" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B39" s="61" t="inlineStr">
+      <c r="B41" s="61" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C39" s="60" t="inlineStr">
+      <c r="C41" s="60" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D39" s="57" t="inlineStr">
+      <c r="D41" s="57" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E39" s="84" t="inlineStr">
+      <c r="E41" s="84" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -59058,8 +59156,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A40:N40"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A38:N38"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assists" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Assists" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Alder" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -809,13 +809,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -834,7 +834,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -858,12 +858,12 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -877,7 +877,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -890,8 +889,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -905,7 +904,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -915,7 +913,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -930,9 +928,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -57280,7 +57278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -58521,423 +58519,419 @@
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="65" t="inlineStr">
-        <is>
-          <t>Gruppe G</t>
-        </is>
-      </c>
+      <c r="A27" s="74" t="inlineStr"/>
       <c r="B27" s="75" t="inlineStr">
         <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C27" s="83" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D27" s="77" t="n">
-        <v>15</v>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C27" s="73" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D27" s="76" t="n">
+        <v>3</v>
       </c>
       <c r="E27" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="79" t="inlineStr">
+        <is>
+          <t>0–4</t>
+        </is>
+      </c>
+      <c r="I27" s="80" t="n">
         <v>3</v>
-      </c>
-      <c r="F27" s="76" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" s="78" t="n">
-        <v>5</v>
-      </c>
-      <c r="H27" s="79" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I27" s="80" t="n">
-        <v>8</v>
       </c>
       <c r="J27" s="76" t="n">
         <v>2</v>
       </c>
       <c r="K27" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" s="76" t="n">
-        <v>14</v>
-      </c>
-      <c r="M27" s="83" t="n">
-        <v>0.47</v>
+        <v>5</v>
+      </c>
+      <c r="L27" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" s="67" t="n">
+        <v>0.57</v>
       </c>
       <c r="N27" s="75" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="81" t="inlineStr"/>
+      <c r="A28" s="65" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
       <c r="B28" s="66" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="C28" s="83" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="D28" s="68" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E28" s="69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="70" t="n">
         <v>5</v>
       </c>
       <c r="H28" s="71" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I28" s="72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J28" s="69" t="n">
         <v>2</v>
       </c>
       <c r="K28" s="68" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="69" t="n">
+        <v>14</v>
+      </c>
+      <c r="M28" s="83" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N28" s="66" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="74" t="inlineStr"/>
+      <c r="B29" s="75" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C29" s="83" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D29" s="77" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="69" t="n">
+      <c r="G29" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" s="79" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I29" s="80" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="76" t="n">
         <v>13</v>
       </c>
-      <c r="M28" s="83" t="n">
+      <c r="M29" s="83" t="n">
         <v>0.53</v>
       </c>
-      <c r="N28" s="66" t="inlineStr">
+      <c r="N29" s="75" t="inlineStr">
         <is>
           <t>New Zealand</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="65" t="inlineStr">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="65" t="inlineStr">
         <is>
           <t>Gruppe H</t>
         </is>
       </c>
-      <c r="B29" s="75" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>Saudi-Arabia</t>
         </is>
       </c>
-      <c r="C29" s="73" t="n">
+      <c r="C30" s="73" t="n">
         <v>0.35</v>
       </c>
-      <c r="D29" s="76" t="n">
+      <c r="D30" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="E29" s="76" t="n">
+      <c r="E30" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="76" t="n">
+      <c r="F30" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="78" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="79" t="inlineStr">
+      <c r="G30" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="71" t="inlineStr">
         <is>
           <t>1–1</t>
         </is>
       </c>
-      <c r="I29" s="80" t="n">
+      <c r="I30" s="72" t="n">
         <v>9</v>
       </c>
-      <c r="J29" s="76" t="n">
+      <c r="J30" s="69" t="n">
         <v>8</v>
       </c>
-      <c r="K29" s="77" t="n">
+      <c r="K30" s="68" t="n">
         <v>10</v>
       </c>
-      <c r="L29" s="77" t="n">
+      <c r="L30" s="68" t="n">
         <v>27</v>
       </c>
-      <c r="M29" s="82" t="n">
+      <c r="M30" s="82" t="n">
         <v>0.65</v>
       </c>
-      <c r="N29" s="75" t="inlineStr">
+      <c r="N30" s="66" t="inlineStr">
         <is>
           <t>Uruguay</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="81" t="inlineStr"/>
-      <c r="B30" s="66" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="74" t="inlineStr"/>
+      <c r="B31" s="75" t="inlineStr">
         <is>
           <t>Spania</t>
         </is>
       </c>
-      <c r="C30" s="82" t="n">
+      <c r="C31" s="82" t="n">
         <v>0.74</v>
       </c>
-      <c r="D30" s="68" t="n">
+      <c r="D31" s="77" t="n">
         <v>23</v>
       </c>
-      <c r="E30" s="68" t="n">
+      <c r="E31" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="69" t="n">
+      <c r="F31" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="G30" s="70" t="n">
+      <c r="G31" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="H30" s="71" t="inlineStr">
+      <c r="H31" s="79" t="inlineStr">
         <is>
           <t>0–0</t>
         </is>
       </c>
-      <c r="I30" s="72" t="n">
+      <c r="I31" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="69" t="n">
+      <c r="J31" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="M30" s="73" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N30" s="66" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="65" t="inlineStr">
-        <is>
-          <t>Gruppe I</t>
-        </is>
-      </c>
-      <c r="B31" s="75" t="inlineStr">
-        <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C31" s="83" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D31" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E31" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="F31" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="78" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="79" t="inlineStr">
-        <is>
-          <t>3–1</t>
-        </is>
-      </c>
-      <c r="I31" s="80" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="76" t="n">
-        <v>2</v>
-      </c>
       <c r="K31" s="76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L31" s="76" t="n">
         <v>6</v>
       </c>
-      <c r="M31" s="83" t="n">
-        <v>0.46</v>
+      <c r="M31" s="73" t="n">
+        <v>0.26</v>
       </c>
       <c r="N31" s="75" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="81" t="inlineStr"/>
+      <c r="A32" s="65" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
       <c r="B32" s="66" t="inlineStr">
         <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C32" s="73" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D32" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="E32" s="69" t="n">
-        <v>1</v>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C32" s="83" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D32" s="68" t="n">
+        <v>12</v>
+      </c>
+      <c r="E32" s="68" t="n">
+        <v>9</v>
       </c>
       <c r="F32" s="69" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G32" s="70" t="n">
         <v>2</v>
       </c>
       <c r="H32" s="71" t="inlineStr">
         <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="I32" s="72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" s="83" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N32" s="66" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="74" t="inlineStr"/>
+      <c r="B33" s="75" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C33" s="73" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D33" s="76" t="n">
+        <v>11</v>
+      </c>
+      <c r="E33" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="76" t="n">
+        <v>8</v>
+      </c>
+      <c r="G33" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="79" t="inlineStr">
+        <is>
           <t>1–4</t>
         </is>
       </c>
-      <c r="I32" s="72" t="n">
+      <c r="I33" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="J32" s="69" t="n">
+      <c r="J33" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="68" t="n">
+      <c r="K33" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="L32" s="68" t="n">
+      <c r="L33" s="77" t="n">
         <v>12</v>
       </c>
-      <c r="M32" s="67" t="n">
+      <c r="M33" s="67" t="n">
         <v>0.63</v>
       </c>
-      <c r="N32" s="66" t="inlineStr">
+      <c r="N33" s="75" t="inlineStr">
         <is>
           <t>Norge</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="65" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="65" t="inlineStr">
         <is>
           <t>Gruppe J</t>
         </is>
       </c>
-      <c r="B33" s="75" t="inlineStr">
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="C33" s="83" t="n">
+      <c r="C34" s="83" t="n">
         <v>0.47</v>
       </c>
-      <c r="D33" s="77" t="n">
+      <c r="D34" s="68" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="77" t="n">
+      <c r="E34" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="F33" s="76" t="n">
+      <c r="F34" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="G33" s="78" t="n">
+      <c r="G34" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="79" t="inlineStr">
+      <c r="H34" s="71" t="inlineStr">
         <is>
           <t>3–0</t>
-        </is>
-      </c>
-      <c r="I33" s="80" t="n">
-        <v>3</v>
-      </c>
-      <c r="J33" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" s="76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="76" t="n">
-        <v>6</v>
-      </c>
-      <c r="M33" s="83" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N33" s="75" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="81" t="inlineStr"/>
-      <c r="B34" s="66" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C34" s="67" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D34" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="E34" s="69" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="G34" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="71" t="inlineStr">
-        <is>
-          <t>3–1</t>
         </is>
       </c>
       <c r="I34" s="72" t="n">
         <v>3</v>
       </c>
       <c r="J34" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="K34" s="68" t="n">
-        <v>4</v>
-      </c>
-      <c r="L34" s="68" t="n">
-        <v>11</v>
-      </c>
-      <c r="M34" s="73" t="n">
-        <v>0.38</v>
+        <v>3</v>
+      </c>
+      <c r="K34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="M34" s="83" t="n">
+        <v>0.53</v>
       </c>
       <c r="N34" s="66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="65" t="inlineStr">
-        <is>
-          <t>Gruppe K</t>
-        </is>
-      </c>
+      <c r="A35" s="74" t="inlineStr"/>
       <c r="B35" s="75" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C35" s="82" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D35" s="77" t="n">
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C35" s="67" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D35" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="E35" s="77" t="n">
+      <c r="E35" s="76" t="n">
         <v>3</v>
       </c>
       <c r="F35" s="76" t="n">
@@ -58948,207 +58942,259 @@
       </c>
       <c r="H35" s="79" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I35" s="80" t="n">
         <v>3</v>
       </c>
       <c r="J35" s="76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K35" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="77" t="n">
+        <v>11</v>
+      </c>
+      <c r="M35" s="73" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N35" s="75" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="65" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="B36" s="66" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C36" s="82" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D36" s="68" t="n">
+        <v>9</v>
+      </c>
+      <c r="E36" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="K35" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="L35" s="76" t="n">
-        <v>8</v>
-      </c>
-      <c r="M35" s="73" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N35" s="75" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="81" t="inlineStr"/>
-      <c r="B36" s="66" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C36" s="73" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D36" s="69" t="n">
-        <v>7</v>
-      </c>
-      <c r="E36" s="69" t="n">
-        <v>3</v>
-      </c>
       <c r="F36" s="69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G36" s="70" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="71" t="inlineStr">
         <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I36" s="72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="69" t="n">
+        <v>3</v>
+      </c>
+      <c r="K36" s="69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" s="73" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N36" s="66" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="74" t="inlineStr"/>
+      <c r="B37" s="75" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C37" s="73" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D37" s="76" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="79" t="inlineStr">
+        <is>
           <t>1–3</t>
         </is>
       </c>
-      <c r="I36" s="72" t="n">
+      <c r="I37" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="J36" s="69" t="n">
+      <c r="J37" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="K36" s="68" t="n">
+      <c r="K37" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="L36" s="68" t="n">
+      <c r="L37" s="77" t="n">
         <v>15</v>
       </c>
-      <c r="M36" s="82" t="n">
+      <c r="M37" s="82" t="n">
         <v>0.67</v>
       </c>
-      <c r="N36" s="66" t="inlineStr">
+      <c r="N37" s="75" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="65" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="65" t="inlineStr">
         <is>
           <t>Gruppe L</t>
         </is>
       </c>
-      <c r="B37" s="75" t="inlineStr">
+      <c r="B38" s="66" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="C37" s="83" t="n">
+      <c r="C38" s="83" t="n">
         <v>0.54</v>
       </c>
-      <c r="D37" s="77" t="n">
+      <c r="D38" s="68" t="n">
         <v>20</v>
       </c>
-      <c r="E37" s="77" t="n">
+      <c r="E38" s="68" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="76" t="n">
+      <c r="F38" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="G37" s="78" t="n">
+      <c r="G38" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="79" t="inlineStr">
+      <c r="H38" s="71" t="inlineStr">
         <is>
           <t>4–2</t>
         </is>
       </c>
-      <c r="I37" s="80" t="n">
+      <c r="I38" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="J37" s="76" t="n">
+      <c r="J38" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="K37" s="76" t="n">
+      <c r="K38" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="L37" s="76" t="n">
+      <c r="L38" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="M37" s="83" t="n">
+      <c r="M38" s="83" t="n">
         <v>0.46</v>
       </c>
-      <c r="N37" s="75" t="inlineStr">
+      <c r="N38" s="66" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="81" t="inlineStr"/>
-      <c r="B38" s="66" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="74" t="inlineStr"/>
+      <c r="B39" s="75" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C38" s="73" t="n">
+      <c r="C39" s="73" t="n">
         <v>0.37</v>
       </c>
-      <c r="D38" s="69" t="n">
+      <c r="D39" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="E38" s="69" t="n">
+      <c r="E39" s="76" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="69" t="n">
+      <c r="F39" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="G38" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="71" t="inlineStr">
+      <c r="G39" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="79" t="inlineStr">
         <is>
           <t>1–0</t>
         </is>
       </c>
-      <c r="I38" s="72" t="n">
+      <c r="I39" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="69" t="n">
+      <c r="J39" s="76" t="n">
         <v>5</v>
       </c>
-      <c r="K38" s="68" t="n">
+      <c r="K39" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="L38" s="68" t="n">
+      <c r="L39" s="77" t="n">
         <v>11</v>
       </c>
-      <c r="M38" s="67" t="n">
+      <c r="M39" s="67" t="n">
         <v>0.63</v>
       </c>
-      <c r="N38" s="66" t="inlineStr">
+      <c r="N39" s="75" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="62" t="inlineStr">
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="62" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="54" t="inlineStr">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="54" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B41" s="61" t="inlineStr">
+      <c r="B42" s="61" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C41" s="60" t="inlineStr">
+      <c r="C42" s="60" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D41" s="57" t="inlineStr">
+      <c r="D42" s="57" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E41" s="84" t="inlineStr">
+      <c r="E42" s="84" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -59156,8 +59202,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A40:N40"/>
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A41:N41"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -46609,7 +46609,7 @@
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>VM 2026 — Rene nullere</t>
+          <t>VM 2026 — Clean sheet</t>
         </is>
       </c>
     </row>
@@ -46636,7 +46636,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Rene nullere</t>
+          <t>Clean sheet</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Assists" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Alder" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assists" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -809,13 +809,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -834,7 +834,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -858,12 +858,12 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -877,6 +877,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -889,8 +890,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -904,6 +905,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -913,7 +915,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -928,9 +930,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,42 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="32-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assists" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Toppscorere" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Assists" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Alder" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Lagstatistikk" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Scoringstidspunkt" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Heatmap" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Ballbesittelse" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -809,13 +809,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -834,7 +834,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -858,12 +858,12 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -877,7 +877,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -890,8 +889,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -905,7 +904,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -915,7 +913,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -930,9 +928,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -17627,7 +17625,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>VM 2026 — 32-delsfinale</t>
+          <t>VM 2026 — 16-delsfinale</t>
         </is>
       </c>
     </row>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="7" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Alder" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -1385,13 +1385,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1410,7 +1410,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1438,8 +1438,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1465,8 +1465,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1489,7 +1489,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1504,9 +1504,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1814,473 +1814,474 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe A — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>11.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>11.06 21:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>2 – 0</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Sør-Afrika</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>80 824</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Mexico City Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Wilton Sampaio</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>11.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>11.06 04:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Sør-Korea</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>2 – 1</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Tsjekkia</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>44 985</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>Guadalajara Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Amin Mohamed</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
+        <is>
+          <t>18.06 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>Tsjekkia</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
         <is>
           <t>1 – 1</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="109" t="inlineStr">
         <is>
           <t>Sør-Afrika</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="108" t="inlineStr">
         <is>
           <t>67 442</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="109" t="inlineStr">
         <is>
           <t>Atlanta Stadium</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="109" t="inlineStr">
         <is>
           <t>Tori Penso</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
+        <is>
+          <t>18.06 03:00</t>
+        </is>
+      </c>
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>1 – 0</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="109" t="inlineStr">
         <is>
           <t>Sør-Korea</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="108" t="inlineStr">
         <is>
           <t>45 522</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <t>Guadalajara Stadium</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="109" t="inlineStr">
         <is>
           <t>Gustavo Tejera</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>24.06 03:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Tsjekkia</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>24.06 03:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Sør-Afrika</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Sør-Korea</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe A — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Mexico</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Sør-Korea</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Tsjekkia</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="D14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="114" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Sør-Afrika</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="D15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5949,441 +5950,450 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe J — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>16.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>16.06 03:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>3 – 0</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Algerie</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>69 045</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Kansas City Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Szymon Marciniak</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>17.06 06:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>3 – 1</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>68 527</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>San Francisco Bay Area Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Dahane Beida</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="114" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>22.06</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="114" t="inlineStr">
+        <is>
+          <t>22.06 19:00</t>
+        </is>
+      </c>
+      <c r="C5" s="115" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="116" t="inlineStr">
+        <is>
+          <t>– – –</t>
+        </is>
+      </c>
+      <c r="E5" s="115" t="inlineStr">
         <is>
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="F5" s="114" t="inlineStr"/>
+      <c r="G5" s="115" t="inlineStr"/>
+      <c r="H5" s="115" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="111" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>22.06</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
+        <is>
+          <t>22.06 05:00</t>
+        </is>
+      </c>
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="D6" s="113" t="inlineStr">
+        <is>
+          <t>– – –</t>
+        </is>
+      </c>
+      <c r="E6" s="112" t="inlineStr">
         <is>
           <t>Algerie</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="F6" s="111" t="inlineStr"/>
+      <c r="G6" s="112" t="inlineStr"/>
+      <c r="H6" s="112" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>27.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>27.06 04:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>27.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>27.06 04:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Algerie</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe J — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+      <c r="B12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
+      <c r="B13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="119" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Jordan</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="114" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Algerie</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="n">
+      <c r="B15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10020,441 +10030,442 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe K — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>17.06 19:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>1 – 1</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>DR Kongo</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>68 777</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Houston Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Abdulrahman Aljassim</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>17.06 04:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>1 – 3</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>80 824</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>Mexico City Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Anthony Taylor</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="114" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="114" t="inlineStr">
+        <is>
+          <t>23.06 19:00</t>
+        </is>
+      </c>
+      <c r="C5" s="115" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="116" t="inlineStr"/>
+      <c r="E5" s="115" t="inlineStr">
         <is>
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="F5" s="114" t="inlineStr"/>
+      <c r="G5" s="115" t="inlineStr"/>
+      <c r="H5" s="115" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="111" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
+        <is>
+          <t>23.06 04:00</t>
+        </is>
+      </c>
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="D6" s="113" t="inlineStr"/>
+      <c r="E6" s="112" t="inlineStr">
         <is>
           <t>DR Kongo</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="F6" s="111" t="inlineStr"/>
+      <c r="G6" s="112" t="inlineStr"/>
+      <c r="H6" s="112" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>27.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>27.06 01:30</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>27.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>27.06 01:30</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>DR Kongo</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe K — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+      <c r="B12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>3</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="G12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>DR Kongo</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="F13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="n">
+      <c r="D14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="F14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="n">
+      <c r="B15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="E15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14109,441 +14120,442 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe L — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>17.06 22:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>4 – 2</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>70 389</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Dallas Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Clement Turpin</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>17.06 01:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>1 – 0</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>42 942</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>Toronto Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Glenn Nyberg</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="114" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="114" t="inlineStr">
+        <is>
+          <t>23.06 22:00</t>
+        </is>
+      </c>
+      <c r="C5" s="115" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="116" t="inlineStr"/>
+      <c r="E5" s="115" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="F5" s="114" t="inlineStr"/>
+      <c r="G5" s="115" t="inlineStr"/>
+      <c r="H5" s="115" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="111" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>23.06</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
+        <is>
+          <t>23.06 01:00</t>
+        </is>
+      </c>
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="D6" s="113" t="inlineStr"/>
+      <c r="E6" s="112" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="F6" s="111" t="inlineStr"/>
+      <c r="G6" s="112" t="inlineStr"/>
+      <c r="H6" s="112" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>27.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>27.06 23:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>27.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>27.06 23:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe L — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+      <c r="B12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
+      <c r="B13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="16" t="n">
+      <c r="F13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="n">
+      <c r="B15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
+      <c r="E15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -29854,473 +29866,474 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe B — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>12.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>12.06 21:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>1 – 1</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Bosnia-Hercegovina</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>43 002</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Toronto Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Facundo Tello</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>13.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>13.06 21:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>1 – 1</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Sveits</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>67 966</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>San Francisco Bay Area Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Said Martinez</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
+        <is>
+          <t>18.06 21:00</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>Sveits</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
         <is>
           <t>4 – 1</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="109" t="inlineStr">
         <is>
           <t>Bosnia-Hercegovina</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="108" t="inlineStr">
         <is>
           <t>70 026</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="109" t="inlineStr">
         <is>
           <t>Los Angeles Stadium</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="109" t="inlineStr">
         <is>
           <t>Joao Pinheiro</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>18.06</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
+        <is>
+          <t>18.06 00:00</t>
+        </is>
+      </c>
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>6 – 0</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="109" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="108" t="inlineStr">
         <is>
           <t>52 497</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <t>BC Place Vancouver</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="109" t="inlineStr">
         <is>
           <t>Cristian Garay</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>24.06 21:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Sveits</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>24.06 21:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Bosnia-Hercegovina</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe B — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="C12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="G12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Sveits</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16" t="n">
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="119" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Bosnia-Hercegovina</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="D14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="114" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="D15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="111" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -55985,473 +55998,474 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe C — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>13.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>13.06 00:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>1 – 1</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>80 663</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>New York/New Jersey Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Slavko Vincic</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>13.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>13.06 03:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>0 – 1</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Skottland</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>64 146</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>Boston Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Mustapha Ghorbal</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
+        <is>
+          <t>19.06 00:00</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>Skottland</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
         <is>
           <t>0 – 1</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="109" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="108" t="inlineStr">
         <is>
           <t>64 146</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="109" t="inlineStr">
         <is>
           <t>Boston Stadium</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="109" t="inlineStr">
         <is>
           <t>Ilgiz Tantashev</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
+        <is>
+          <t>19.06 02:30</t>
+        </is>
+      </c>
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>3 – 0</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="109" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="108" t="inlineStr">
         <is>
           <t>68 324</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <t>Philadelphia Stadium</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="109" t="inlineStr">
         <is>
           <t>Alejandro Hernandez</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>24.06 00:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Skottland</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>24.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>24.06 00:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe C — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="C12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="G12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16" t="n">
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Skottland</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Haiti</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -60112,473 +60126,474 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe D — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>12.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>12.06 03:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>4 – 1</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>70 492</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Los Angeles Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Danny Makkelie</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>14.06 06:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>2 – 0</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>52 497</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>BC Place Vancouver</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Jesus Valenzuela</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
+        <is>
+          <t>19.06 21:00</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
         <is>
           <t>2 – 0</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="109" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="108" t="inlineStr">
         <is>
           <t>66 925</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="109" t="inlineStr">
         <is>
           <t>Seattle Stadium</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="109" t="inlineStr">
         <is>
           <t>Felix Zwayer</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
+        <is>
+          <t>19.06 05:00</t>
+        </is>
+      </c>
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>0 – 1</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="109" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="108" t="inlineStr">
         <is>
           <t>68 827</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <t>San Francisco Bay Area Stadium</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="109" t="inlineStr">
         <is>
           <t>Ivan Barton</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>25.06 04:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>25.06 04:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe D — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="G12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="114" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G15" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -64257,473 +64272,474 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe E — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>14.06 19:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>7 – 1</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>68 021</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Houston Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Jalal Jayed</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>14.06 01:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Elfenbenskysten</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>1 – 0</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>68 274</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>Philadelphia Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Francois Letexier</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>20.06</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
+        <is>
+          <t>20.06 22:00</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
         <is>
           <t>2 – 1</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="109" t="inlineStr">
         <is>
           <t>Elfenbenskysten</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="108" t="inlineStr">
         <is>
           <t>43 036</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="109" t="inlineStr">
         <is>
           <t>Toronto Stadium</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="109" t="inlineStr">
         <is>
           <t>Juan Gabriel Benitez</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>20.06</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
+        <is>
+          <t>20.06 02:00</t>
+        </is>
+      </c>
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>0 – 0</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="109" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="108" t="inlineStr">
         <is>
           <t>68 598</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <t>Kansas City Stadium</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="109" t="inlineStr">
         <is>
           <t>Ma Ning</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>25.06 22:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>25.06 22:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Elfenbenskysten</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe E — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Elfenbenskysten</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="D14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="G14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="D15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="111" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>1</v>
       </c>
     </row>
@@ -68396,473 +68412,474 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe F — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>14.06 22:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>2 – 2</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>69 285</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>Dallas Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Ismail Elfath</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>14.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>14.06 04:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Sverige</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>5 – 1</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>50 987</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>Monterrey Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Yael Falcon Perez</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
-        <is>
-          <t>20.06</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
+        <is>
+          <t>20.06 19:00</t>
+        </is>
+      </c>
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
         <is>
           <t>5 – 1</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="109" t="inlineStr">
         <is>
           <t>Sverige</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="108" t="inlineStr">
         <is>
           <t>68 777</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="109" t="inlineStr">
         <is>
           <t>Houston Stadium</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="109" t="inlineStr">
         <is>
           <t>Michael Oliver</t>
         </is>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="B6" s="108" t="inlineStr">
+        <is>
+          <t>21.06 06:00</t>
+        </is>
+      </c>
+      <c r="C6" s="109" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="110" t="inlineStr">
         <is>
           <t>0 – 4</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="109" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="108" t="inlineStr">
         <is>
           <t>51 243</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="109" t="inlineStr">
         <is>
           <t>Monterrey Stadium</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="109" t="inlineStr">
         <is>
           <t>Istvan Kovacs</t>
         </is>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>25.06 01:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>25.06 01:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Sverige</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe F — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="108" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="C12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="108" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16" t="n">
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="119" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="119" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Sverige</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="C14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
         <v>6</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="114" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E15" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="F15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="111" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72575,7 +72592,7 @@
       </c>
       <c r="B2" s="106" t="inlineStr">
         <is>
-          <t>Dato</t>
+          <t>Dato og kl.slett</t>
         </is>
       </c>
       <c r="C2" s="107" t="inlineStr">
@@ -72617,7 +72634,7 @@
       </c>
       <c r="B3" s="108" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.06 21:00</t>
         </is>
       </c>
       <c r="C3" s="109" t="inlineStr">
@@ -72659,7 +72676,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.06 03:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -72701,7 +72718,7 @@
       </c>
       <c r="B5" s="108" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>21.06 21:00</t>
         </is>
       </c>
       <c r="C5" s="109" t="inlineStr">
@@ -72743,7 +72760,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>21.06 03:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -72785,7 +72802,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.06 05:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -72811,7 +72828,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.06 05:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -76713,7 +76730,7 @@
       </c>
       <c r="B2" s="106" t="inlineStr">
         <is>
-          <t>Dato</t>
+          <t>Dato og kl.slett</t>
         </is>
       </c>
       <c r="C2" s="107" t="inlineStr">
@@ -76755,7 +76772,7 @@
       </c>
       <c r="B3" s="108" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.06 18:00</t>
         </is>
       </c>
       <c r="C3" s="109" t="inlineStr">
@@ -76797,7 +76814,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>15.06</t>
+          <t>15.06 00:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -76839,7 +76856,7 @@
       </c>
       <c r="B5" s="108" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>21.06 18:00</t>
         </is>
       </c>
       <c r="C5" s="109" t="inlineStr">
@@ -76881,7 +76898,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>21.06</t>
+          <t>21.06 00:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -76923,7 +76940,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.06 02:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -76949,7 +76966,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>26.06 02:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -80815,441 +80832,450 @@
     <col width="22" customWidth="1" style="98" min="5" max="5"/>
     <col width="12" customWidth="1" style="98" min="6" max="6"/>
     <col width="20" customWidth="1" style="98" min="7" max="8"/>
+    <col width="20" customWidth="1" style="98" min="8" max="8"/>
     <col width="6" customWidth="1" style="98" min="9" max="10"/>
     <col width="6" customWidth="1" style="98" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="98">
-      <c r="A1" s="99" t="inlineStr">
+      <c r="A1" s="105" t="inlineStr">
         <is>
           <t>Gruppe I — Kamper</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="98">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="106" t="inlineStr">
         <is>
           <t>Runde</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="106" t="inlineStr">
+        <is>
+          <t>Dato og kl.slett</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
         <is>
           <t>Hjemmelag</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="106" t="inlineStr">
         <is>
           <t>Resultat</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="107" t="inlineStr">
         <is>
           <t>Bortelag</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="106" t="inlineStr">
         <is>
           <t>Tilskuere</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="107" t="inlineStr">
         <is>
           <t>Stadion</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="107" t="inlineStr">
         <is>
           <t>Dommer</t>
         </is>
       </c>
     </row>
     <row r="3" ht="17" customHeight="1" s="98">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>16.06</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="B3" s="108" t="inlineStr">
+        <is>
+          <t>16.06 21:00</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
         <is>
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="110" t="inlineStr">
         <is>
           <t>3 – 1</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="109" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="108" t="inlineStr">
         <is>
           <t>80 545</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="109" t="inlineStr">
         <is>
           <t>New York/New Jersey Stadium</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="109" t="inlineStr">
         <is>
           <t>Alireza Faghani</t>
         </is>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="108" t="inlineStr">
         <is>
           <t>Runde 1</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>16.06</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="B4" s="108" t="inlineStr">
+        <is>
+          <t>16.06 00:00</t>
+        </is>
+      </c>
+      <c r="C4" s="109" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="110" t="inlineStr">
         <is>
           <t>1 – 4</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="109" t="inlineStr">
         <is>
           <t>Norge</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="108" t="inlineStr">
         <is>
           <t>63 106</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="109" t="inlineStr">
         <is>
           <t>Boston Stadium</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="109" t="inlineStr">
         <is>
           <t>Pierre Atcho</t>
         </is>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="114" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>22.06</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="114" t="inlineStr">
+        <is>
+          <t>22.06 23:00</t>
+        </is>
+      </c>
+      <c r="C5" s="115" t="inlineStr">
         <is>
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="116" t="inlineStr">
+        <is>
+          <t>– – –</t>
+        </is>
+      </c>
+      <c r="E5" s="115" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
+      <c r="F5" s="114" t="inlineStr"/>
+      <c r="G5" s="115" t="inlineStr"/>
+      <c r="H5" s="115" t="inlineStr"/>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="111" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>22.06</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
+        <is>
+          <t>22.06 02:00</t>
+        </is>
+      </c>
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>Norge</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="D6" s="113" t="inlineStr">
+        <is>
+          <t>– – –</t>
+        </is>
+      </c>
+      <c r="E6" s="112" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="F6" s="111" t="inlineStr"/>
+      <c r="G6" s="112" t="inlineStr"/>
+      <c r="H6" s="112" t="inlineStr"/>
     </row>
     <row r="7" ht="17" customHeight="1" s="98">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="114" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>26.06</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="114" t="inlineStr">
+        <is>
+          <t>26.06 21:00</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
         <is>
           <t>Norge</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="116" t="inlineStr"/>
+      <c r="E7" s="115" t="inlineStr">
         <is>
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="F7" s="114" t="inlineStr"/>
+      <c r="G7" s="115" t="inlineStr"/>
+      <c r="H7" s="115" t="inlineStr"/>
     </row>
     <row r="8" ht="17" customHeight="1" s="98">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="111" t="inlineStr">
         <is>
           <t>Runde 3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>26.06</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
+        <is>
+          <t>26.06 21:00</t>
+        </is>
+      </c>
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="D8" s="113" t="inlineStr"/>
+      <c r="E8" s="112" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="F8" s="111" t="inlineStr"/>
+      <c r="G8" s="112" t="inlineStr"/>
+      <c r="H8" s="112" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n"/>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="n"/>
-      <c r="I9" s="14" t="n"/>
+      <c r="A9" s="117" t="n"/>
+      <c r="B9" s="117" t="n"/>
+      <c r="C9" s="117" t="n"/>
+      <c r="D9" s="117" t="n"/>
+      <c r="E9" s="117" t="n"/>
+      <c r="F9" s="117" t="n"/>
+      <c r="G9" s="117" t="n"/>
+      <c r="H9" s="117" t="n"/>
+      <c r="I9" s="117" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1" s="98">
-      <c r="A10" s="99" t="inlineStr">
+      <c r="A10" s="105" t="inlineStr">
         <is>
           <t>Gruppe I — Tabell</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" s="98">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="106" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="106" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="106" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E11" s="106" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F11" s="106" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G11" s="106" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H11" s="106" t="inlineStr">
         <is>
           <t>MD</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I11" s="106" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="98">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="109" t="inlineStr">
         <is>
           <t>Norge</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9" t="n">
+      <c r="B12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="108" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="108" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="G12" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="108" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="110" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="118" t="inlineStr">
         <is>
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="16" t="n">
+      <c r="B13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="119" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="119" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="119" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="120" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" s="98">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="115" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="B14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="114" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="E14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="114" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="114" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I14" s="121" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" s="98">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="112" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="n">
+      <c r="B15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="111" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="n">
+      <c r="E15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="111" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="I15" s="8" t="n">
+      <c r="I15" s="122" t="n">
         <v>0</v>
       </c>
     </row>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>11.06 04:00</t>
+          <t>12.06 04:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>18.06 03:00</t>
+          <t>19.06 03:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>24.06 03:00</t>
+          <t>25.06 03:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>24.06 03:00</t>
+          <t>25.06 03:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="B3" s="108" t="inlineStr">
         <is>
-          <t>16.06 03:00</t>
+          <t>17.06 03:00</t>
         </is>
       </c>
       <c r="C3" s="109" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="B6" s="111" t="inlineStr">
         <is>
-          <t>22.06 05:00</t>
+          <t>23.06 05:00</t>
         </is>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -6134,11 +6134,7 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="D6" s="113" t="inlineStr">
-        <is>
-          <t>– – –</t>
-        </is>
-      </c>
+      <c r="D6" s="113" t="inlineStr"/>
       <c r="E6" s="112" t="inlineStr">
         <is>
           <t>Algerie</t>
@@ -6156,7 +6152,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>27.06 04:00</t>
+          <t>28.06 04:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -6182,7 +6178,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>27.06 04:00</t>
+          <t>28.06 04:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -10134,7 +10130,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>17.06 04:00</t>
+          <t>18.06 04:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -10202,7 +10198,7 @@
       </c>
       <c r="B6" s="111" t="inlineStr">
         <is>
-          <t>23.06 04:00</t>
+          <t>24.06 04:00</t>
         </is>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -10228,7 +10224,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>27.06 01:30</t>
+          <t>28.06 01:30</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -10254,7 +10250,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>27.06 01:30</t>
+          <t>28.06 01:30</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -14224,7 +14220,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>17.06 01:00</t>
+          <t>18.06 01:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -14292,7 +14288,7 @@
       </c>
       <c r="B6" s="111" t="inlineStr">
         <is>
-          <t>23.06 01:00</t>
+          <t>24.06 01:00</t>
         </is>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -30054,7 +30050,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>18.06 00:00</t>
+          <t>19.06 00:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -56060,7 +56056,7 @@
       </c>
       <c r="B3" s="108" t="inlineStr">
         <is>
-          <t>13.06 00:00</t>
+          <t>14.06 00:00</t>
         </is>
       </c>
       <c r="C3" s="109" t="inlineStr">
@@ -56102,7 +56098,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>13.06 03:00</t>
+          <t>14.06 03:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -56144,7 +56140,7 @@
       </c>
       <c r="B5" s="108" t="inlineStr">
         <is>
-          <t>19.06 00:00</t>
+          <t>20.06 00:00</t>
         </is>
       </c>
       <c r="C5" s="109" t="inlineStr">
@@ -56186,7 +56182,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>19.06 02:30</t>
+          <t>20.06 02:30</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -56228,7 +56224,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>24.06 00:00</t>
+          <t>25.06 00:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -56254,7 +56250,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>24.06 00:00</t>
+          <t>25.06 00:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -60188,7 +60184,7 @@
       </c>
       <c r="B3" s="108" t="inlineStr">
         <is>
-          <t>12.06 03:00</t>
+          <t>13.06 03:00</t>
         </is>
       </c>
       <c r="C3" s="109" t="inlineStr">
@@ -60314,7 +60310,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>19.06 05:00</t>
+          <t>20.06 05:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -60356,7 +60352,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>25.06 04:00</t>
+          <t>26.06 04:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -60382,7 +60378,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>25.06 04:00</t>
+          <t>26.06 04:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -64376,7 +64372,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>14.06 01:00</t>
+          <t>15.06 01:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -64460,7 +64456,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>20.06 02:00</t>
+          <t>21.06 02:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -68516,7 +68512,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>14.06 04:00</t>
+          <t>15.06 04:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -68642,7 +68638,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>25.06 01:00</t>
+          <t>26.06 01:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -68668,7 +68664,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>25.06 01:00</t>
+          <t>26.06 01:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -72676,7 +72672,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>15.06 03:00</t>
+          <t>16.06 03:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -72760,7 +72756,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>21.06 03:00</t>
+          <t>22.06 03:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -72802,7 +72798,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>26.06 05:00</t>
+          <t>27.06 05:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -72828,7 +72824,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>26.06 05:00</t>
+          <t>27.06 05:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -76814,7 +76810,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>15.06 00:00</t>
+          <t>16.06 00:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -76898,7 +76894,7 @@
       </c>
       <c r="B6" s="108" t="inlineStr">
         <is>
-          <t>21.06 00:00</t>
+          <t>22.06 00:00</t>
         </is>
       </c>
       <c r="C6" s="109" t="inlineStr">
@@ -76940,7 +76936,7 @@
       </c>
       <c r="B7" s="114" t="inlineStr">
         <is>
-          <t>26.06 02:00</t>
+          <t>27.06 02:00</t>
         </is>
       </c>
       <c r="C7" s="115" t="inlineStr">
@@ -76966,7 +76962,7 @@
       </c>
       <c r="B8" s="111" t="inlineStr">
         <is>
-          <t>26.06 02:00</t>
+          <t>27.06 02:00</t>
         </is>
       </c>
       <c r="C8" s="112" t="inlineStr">
@@ -80936,7 +80932,7 @@
       </c>
       <c r="B4" s="108" t="inlineStr">
         <is>
-          <t>16.06 00:00</t>
+          <t>17.06 00:00</t>
         </is>
       </c>
       <c r="C4" s="109" t="inlineStr">
@@ -81008,7 +81004,7 @@
       </c>
       <c r="B6" s="111" t="inlineStr">
         <is>
-          <t>22.06 02:00</t>
+          <t>23.06 02:00</t>
         </is>
       </c>
       <c r="C6" s="112" t="inlineStr">
@@ -81016,11 +81012,7 @@
           <t>Norge</t>
         </is>
       </c>
-      <c r="D6" s="113" t="inlineStr">
-        <is>
-          <t>– – –</t>
-        </is>
-      </c>
+      <c r="D6" s="113" t="inlineStr"/>
       <c r="E6" s="112" t="inlineStr">
         <is>
           <t>Senegal</t>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,40 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="7" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Alder" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -1385,13 +1385,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1410,7 +1410,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1438,8 +1438,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1465,8 +1465,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1489,7 +1489,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1504,9 +1504,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -46940,7 +46940,7 @@
       </c>
       <c r="F56" s="132" t="inlineStr">
         <is>
-          <t>18.06</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="G56" s="132" t="n">
@@ -46973,7 +46973,7 @@
       </c>
       <c r="F57" s="132" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>15.06</t>
         </is>
       </c>
       <c r="G57" s="132" t="n">
@@ -47105,7 +47105,7 @@
       </c>
       <c r="F61" s="113" t="inlineStr">
         <is>
-          <t>12.06</t>
+          <t>13.06</t>
         </is>
       </c>
       <c r="G61" s="113" t="n">
@@ -47138,7 +47138,7 @@
       </c>
       <c r="F62" s="116" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="G62" s="116" t="n">
@@ -49257,35 +49257,35 @@
     </row>
     <row r="138" ht="16" customHeight="1" s="98">
       <c r="A138" s="114" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B138" s="115" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="C138" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D138" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F138" s="116" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>14,0</t>
         </is>
       </c>
       <c r="G138" s="116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H138" s="116" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -49295,23 +49295,23 @@
       </c>
       <c r="B139" s="112" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C139" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D139" s="113" t="n">
         <v>1</v>
       </c>
       <c r="E139" s="113" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F139" s="113" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>13,0</t>
         </is>
       </c>
       <c r="G139" s="113" t="n">
@@ -49319,7 +49319,7 @@
       </c>
       <c r="H139" s="113" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>62%</t>
         </is>
       </c>
     </row>
@@ -49329,46 +49329,46 @@
       </c>
       <c r="B140" s="115" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="C140" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D140" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" s="116" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F140" s="116" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="G140" s="116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H140" s="116" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1" s="98">
       <c r="A141" s="111" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B141" s="112" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C141" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D141" s="113" t="n">
@@ -49383,26 +49383,26 @@
         </is>
       </c>
       <c r="G141" s="113" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H141" s="113" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>73%</t>
         </is>
       </c>
     </row>
     <row r="142" ht="16" customHeight="1" s="98">
       <c r="A142" s="114" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B142" s="115" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C142" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D142" s="116" t="n">
@@ -49417,26 +49417,26 @@
         </is>
       </c>
       <c r="G142" s="116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H142" s="116" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>45%</t>
         </is>
       </c>
     </row>
     <row r="143" ht="16" customHeight="1" s="98">
       <c r="A143" s="111" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B143" s="112" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C143" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D143" s="113" t="n">
@@ -49451,21 +49451,21 @@
         </is>
       </c>
       <c r="G143" s="113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H143" s="113" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
     <row r="144" ht="16" customHeight="1" s="98">
       <c r="A144" s="114" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B144" s="115" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C144" s="116" t="inlineStr">
@@ -49477,79 +49477,79 @@
         <v>1</v>
       </c>
       <c r="E144" s="116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F144" s="116" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>11,0</t>
         </is>
       </c>
       <c r="G144" s="116" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H144" s="116" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
     <row r="145" ht="16" customHeight="1" s="98">
       <c r="A145" s="111" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B145" s="112" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="C145" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D145" s="113" t="n">
         <v>1</v>
       </c>
       <c r="E145" s="113" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F145" s="113" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>11,0</t>
         </is>
       </c>
       <c r="G145" s="113" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H145" s="113" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>9%</t>
         </is>
       </c>
     </row>
     <row r="146" ht="16" customHeight="1" s="98">
       <c r="A146" s="114" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B146" s="115" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Kroatia</t>
         </is>
       </c>
       <c r="C146" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D146" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E146" s="116" t="n">
         <v>10</v>
       </c>
       <c r="F146" s="116" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="G146" s="116" t="n">
@@ -49563,35 +49563,35 @@
     </row>
     <row r="147" ht="16" customHeight="1" s="98">
       <c r="A147" s="111" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B147" s="112" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
       <c r="C147" s="113" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D147" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="113" t="n">
         <v>10</v>
       </c>
       <c r="F147" s="113" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G147" s="113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H147" s="113" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -35,6 +35,7 @@
     <sheet name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Stadionoversikt" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -50,7 +51,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="55">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -346,8 +347,24 @@
       <color rgb="006B7A99"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F5132"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00856404"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001A3C6B"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="50">
     <fill>
       <patternFill/>
     </fill>
@@ -569,6 +586,31 @@
         <fgColor rgb="000E4D5C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00006847"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D9E75"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C7F0DF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F5132"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -779,7 +821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -1308,6 +1350,73 @@
     <xf numFmtId="0" fontId="28" fillId="27" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="45" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="30" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="30" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="46" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="30" fillId="29" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="29" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="47" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="48" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="49" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="34" fillId="33" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="49" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="46" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="47" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="33" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -49057,31 +49166,31 @@
       </c>
       <c r="B132" s="115" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C132" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D132" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" s="116" t="n">
         <v>18</v>
       </c>
       <c r="F132" s="116" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>18,0</t>
         </is>
       </c>
       <c r="G132" s="116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H132" s="116" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>44%</t>
         </is>
       </c>
     </row>
@@ -49091,12 +49200,12 @@
       </c>
       <c r="B133" s="112" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
       <c r="C133" s="113" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D133" s="113" t="n">
@@ -49121,35 +49230,35 @@
     </row>
     <row r="134" ht="16" customHeight="1" s="98">
       <c r="A134" s="114" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B134" s="115" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C134" s="116" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D134" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E134" s="116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F134" s="116" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="G134" s="116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H134" s="116" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>28%</t>
         </is>
       </c>
     </row>
@@ -49159,133 +49268,133 @@
       </c>
       <c r="B135" s="112" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C135" s="113" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D135" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F135" s="113" t="inlineStr">
         <is>
-          <t>15,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G135" s="113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H135" s="113" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
     <row r="136" ht="16" customHeight="1" s="98">
       <c r="A136" s="114" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B136" s="115" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="C136" s="116" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D136" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" s="116" t="n">
         <v>15</v>
       </c>
       <c r="F136" s="116" t="inlineStr">
         <is>
-          <t>7,5</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="G136" s="116" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H136" s="116" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1" s="98">
       <c r="A137" s="111" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B137" s="112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C137" s="113" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D137" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E137" s="113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F137" s="113" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="G137" s="113" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H137" s="113" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
     <row r="138" ht="16" customHeight="1" s="98">
       <c r="A138" s="114" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B138" s="115" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C138" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D138" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F138" s="116" t="inlineStr">
         <is>
-          <t>14,0</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="G138" s="116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H138" s="116" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>13%</t>
         </is>
       </c>
     </row>
@@ -49295,37 +49404,37 @@
       </c>
       <c r="B139" s="112" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C139" s="113" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D139" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" s="113" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F139" s="113" t="inlineStr">
         <is>
-          <t>13,0</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="G139" s="113" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H139" s="113" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1" s="98">
       <c r="A140" s="114" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B140" s="115" t="inlineStr">
         <is>
@@ -49431,12 +49540,12 @@
       </c>
       <c r="B143" s="112" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C143" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D143" s="113" t="n">
@@ -49465,12 +49574,12 @@
       </c>
       <c r="B144" s="115" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C144" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D144" s="116" t="n">
@@ -49485,11 +49594,11 @@
         </is>
       </c>
       <c r="G144" s="116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H144" s="116" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -60101,6 +60210,2173 @@
     <mergeCell ref="A104:D104"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A46:D46"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="98" min="1" max="1"/>
+    <col width="9" customWidth="1" style="98" min="2" max="2"/>
+    <col width="20" customWidth="1" style="98" min="3" max="3"/>
+    <col width="7" customWidth="1" style="98" min="4" max="4"/>
+    <col width="20" customWidth="1" style="98" min="5" max="5"/>
+    <col width="24" customWidth="1" style="98" min="6" max="6"/>
+    <col width="24" customWidth="1" style="98" min="7" max="7"/>
+    <col width="9" customWidth="1" style="98" min="8" max="8"/>
+    <col width="12" customWidth="1" style="98" min="9" max="9"/>
+    <col width="11" customWidth="1" style="98" min="10" max="10"/>
+    <col width="9" customWidth="1" style="98" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="98">
+      <c r="A1" s="105" t="inlineStr">
+        <is>
+          <t>Tilskuere og arenaer — VM 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1" s="98">
+      <c r="A2" s="168" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="B2" s="168" t="inlineStr">
+        <is>
+          <t>Gruppe</t>
+        </is>
+      </c>
+      <c r="C2" s="107" t="inlineStr">
+        <is>
+          <t>Hjemmelag</t>
+        </is>
+      </c>
+      <c r="D2" s="168" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E2" s="107" t="inlineStr">
+        <is>
+          <t>Bortelag</t>
+        </is>
+      </c>
+      <c r="F2" s="107" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="G2" s="107" t="inlineStr">
+        <is>
+          <t>By</t>
+        </is>
+      </c>
+      <c r="H2" s="106" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="I2" s="190" t="inlineStr">
+        <is>
+          <t>Tilskuere</t>
+        </is>
+      </c>
+      <c r="J2" s="190" t="inlineStr">
+        <is>
+          <t>Kapasitet</t>
+        </is>
+      </c>
+      <c r="K2" s="106" t="inlineStr">
+        <is>
+          <t>Belegg %</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="98">
+      <c r="A3" s="173" t="inlineStr">
+        <is>
+          <t>11.06</t>
+        </is>
+      </c>
+      <c r="B3" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
+      <c r="C3" s="192" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D3" s="172" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="E3" s="193" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="F3" s="192" t="inlineStr">
+        <is>
+          <t>Estadio Azteca</t>
+        </is>
+      </c>
+      <c r="G3" s="194" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="H3" s="195" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I3" s="196" t="n">
+        <v>80824</v>
+      </c>
+      <c r="J3" s="197" t="n">
+        <v>87523</v>
+      </c>
+      <c r="K3" s="198" t="n">
+        <v>0.9234601190544199</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="98">
+      <c r="A4" s="180" t="inlineStr">
+        <is>
+          <t>12.06</t>
+        </is>
+      </c>
+      <c r="B4" s="182" t="inlineStr"/>
+      <c r="C4" s="199" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D4" s="181" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="E4" s="200" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="F4" s="199" t="inlineStr">
+        <is>
+          <t>Estadio Akron</t>
+        </is>
+      </c>
+      <c r="G4" s="201" t="inlineStr">
+        <is>
+          <t>Zapopan / Guadalajara</t>
+        </is>
+      </c>
+      <c r="H4" s="195" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I4" s="202" t="n">
+        <v>44985</v>
+      </c>
+      <c r="J4" s="203" t="n">
+        <v>49850</v>
+      </c>
+      <c r="K4" s="204" t="n">
+        <v>0.902407221664995</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="98">
+      <c r="A5" s="173" t="inlineStr">
+        <is>
+          <t>12.06</t>
+        </is>
+      </c>
+      <c r="B5" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="C5" s="192" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D5" s="172" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="E5" s="193" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="F5" s="192" t="inlineStr">
+        <is>
+          <t>BMO Field</t>
+        </is>
+      </c>
+      <c r="G5" s="194" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="H5" s="205" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I5" s="196" t="n">
+        <v>43002</v>
+      </c>
+      <c r="J5" s="197" t="n">
+        <v>45736</v>
+      </c>
+      <c r="K5" s="198" t="n">
+        <v>0.9402221444813713</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="98">
+      <c r="A6" s="180" t="inlineStr">
+        <is>
+          <t>13.06</t>
+        </is>
+      </c>
+      <c r="B6" s="182" t="inlineStr"/>
+      <c r="C6" s="199" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D6" s="181" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="E6" s="200" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="F6" s="199" t="inlineStr">
+        <is>
+          <t>Levi's Stadium</t>
+        </is>
+      </c>
+      <c r="G6" s="201" t="inlineStr">
+        <is>
+          <t>Santa Clara / SF Bay Area</t>
+        </is>
+      </c>
+      <c r="H6" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I6" s="202" t="n">
+        <v>67966</v>
+      </c>
+      <c r="J6" s="203" t="n">
+        <v>68500</v>
+      </c>
+      <c r="K6" s="206" t="n">
+        <v>0.9922043795620438</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="98">
+      <c r="A7" s="173" t="inlineStr">
+        <is>
+          <t>13.06</t>
+        </is>
+      </c>
+      <c r="B7" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="C7" s="192" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D7" s="172" t="inlineStr">
+        <is>
+          <t>4–1</t>
+        </is>
+      </c>
+      <c r="E7" s="193" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F7" s="192" t="inlineStr">
+        <is>
+          <t>SoFi Stadium</t>
+        </is>
+      </c>
+      <c r="G7" s="194" t="inlineStr">
+        <is>
+          <t>Inglewood / Los Angeles</t>
+        </is>
+      </c>
+      <c r="H7" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I7" s="196" t="n">
+        <v>70492</v>
+      </c>
+      <c r="J7" s="197" t="n">
+        <v>70240</v>
+      </c>
+      <c r="K7" s="206" t="n">
+        <v>1.003587699316629</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="98">
+      <c r="A8" s="180" t="inlineStr">
+        <is>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="B8" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
+      <c r="C8" s="199" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D8" s="181" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="E8" s="200" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="F8" s="199" t="inlineStr">
+        <is>
+          <t>MetLife Stadium</t>
+        </is>
+      </c>
+      <c r="G8" s="201" t="inlineStr">
+        <is>
+          <t>East Rutherford, NJ</t>
+        </is>
+      </c>
+      <c r="H8" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I8" s="202" t="n">
+        <v>80663</v>
+      </c>
+      <c r="J8" s="203" t="n">
+        <v>82500</v>
+      </c>
+      <c r="K8" s="206" t="n">
+        <v>0.9777333333333335</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="98">
+      <c r="A9" s="173" t="inlineStr">
+        <is>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="B9" s="174" t="inlineStr"/>
+      <c r="C9" s="192" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D9" s="172" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="E9" s="193" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="F9" s="192" t="inlineStr">
+        <is>
+          <t>Gillette Stadium</t>
+        </is>
+      </c>
+      <c r="G9" s="194" t="inlineStr">
+        <is>
+          <t>Foxborough / Boston</t>
+        </is>
+      </c>
+      <c r="H9" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I9" s="196" t="n">
+        <v>64146</v>
+      </c>
+      <c r="J9" s="197" t="n">
+        <v>65878</v>
+      </c>
+      <c r="K9" s="206" t="n">
+        <v>0.9737089772002793</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="98">
+      <c r="A10" s="180" t="inlineStr">
+        <is>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="B10" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="C10" s="199" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D10" s="181" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="E10" s="200" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="F10" s="199" t="inlineStr">
+        <is>
+          <t>BC Place</t>
+        </is>
+      </c>
+      <c r="G10" s="201" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="H10" s="205" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I10" s="202" t="n">
+        <v>52497</v>
+      </c>
+      <c r="J10" s="203" t="n">
+        <v>54500</v>
+      </c>
+      <c r="K10" s="198" t="n">
+        <v>0.9632477064220184</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="98">
+      <c r="A11" s="173" t="inlineStr">
+        <is>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="B11" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="C11" s="192" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D11" s="172" t="inlineStr">
+        <is>
+          <t>7–1</t>
+        </is>
+      </c>
+      <c r="E11" s="193" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="F11" s="192" t="inlineStr">
+        <is>
+          <t>NRG Stadium</t>
+        </is>
+      </c>
+      <c r="G11" s="194" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="H11" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I11" s="196" t="n">
+        <v>68021</v>
+      </c>
+      <c r="J11" s="197" t="n">
+        <v>72220</v>
+      </c>
+      <c r="K11" s="198" t="n">
+        <v>0.9418582110218776</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="98">
+      <c r="A12" s="180" t="inlineStr">
+        <is>
+          <t>14.06</t>
+        </is>
+      </c>
+      <c r="B12" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="C12" s="199" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D12" s="181" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="E12" s="200" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F12" s="199" t="inlineStr">
+        <is>
+          <t>AT&amp;T Stadium</t>
+        </is>
+      </c>
+      <c r="G12" s="201" t="inlineStr">
+        <is>
+          <t>Arlington / Dallas</t>
+        </is>
+      </c>
+      <c r="H12" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I12" s="202" t="n">
+        <v>69285</v>
+      </c>
+      <c r="J12" s="203" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K12" s="207" t="n">
+        <v>0.8660624999999998</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="98">
+      <c r="A13" s="173" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="B13" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="C13" s="192" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="D13" s="172" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="E13" s="193" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="F13" s="192" t="inlineStr">
+        <is>
+          <t>Lincoln Financial Field</t>
+        </is>
+      </c>
+      <c r="G13" s="194" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="H13" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I13" s="196" t="n">
+        <v>68274</v>
+      </c>
+      <c r="J13" s="197" t="n">
+        <v>69796</v>
+      </c>
+      <c r="K13" s="206" t="n">
+        <v>0.9781935927560319</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="98">
+      <c r="A14" s="180" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="B14" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="C14" s="199" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D14" s="181" t="inlineStr">
+        <is>
+          <t>5–1</t>
+        </is>
+      </c>
+      <c r="E14" s="200" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="F14" s="199" t="inlineStr">
+        <is>
+          <t>Estadio BBVA</t>
+        </is>
+      </c>
+      <c r="G14" s="201" t="inlineStr">
+        <is>
+          <t>San Nicolás / Monterrey</t>
+        </is>
+      </c>
+      <c r="H14" s="195" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I14" s="202" t="n">
+        <v>50987</v>
+      </c>
+      <c r="J14" s="203" t="n">
+        <v>53464</v>
+      </c>
+      <c r="K14" s="198" t="n">
+        <v>0.9536697590902289</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="98">
+      <c r="A15" s="173" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="B15" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="C15" s="192" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D15" s="172" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="E15" s="193" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F15" s="192" t="inlineStr">
+        <is>
+          <t>Lumen Field</t>
+        </is>
+      </c>
+      <c r="G15" s="194" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="H15" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I15" s="196" t="n">
+        <v>66775</v>
+      </c>
+      <c r="J15" s="197" t="n">
+        <v>68740</v>
+      </c>
+      <c r="K15" s="206" t="n">
+        <v>0.9714140238580157</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="98">
+      <c r="A16" s="180" t="inlineStr">
+        <is>
+          <t>15.06</t>
+        </is>
+      </c>
+      <c r="B16" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="C16" s="199" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D16" s="181" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="E16" s="200" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+      <c r="F16" s="199" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium</t>
+        </is>
+      </c>
+      <c r="G16" s="201" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H16" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I16" s="202" t="n">
+        <v>67640</v>
+      </c>
+      <c r="J16" s="203" t="n">
+        <v>71000</v>
+      </c>
+      <c r="K16" s="198" t="n">
+        <v>0.9526760563380282</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="98">
+      <c r="A17" s="173" t="inlineStr">
+        <is>
+          <t>16.06</t>
+        </is>
+      </c>
+      <c r="B17" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="C17" s="192" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="D17" s="172" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="E17" s="193" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="F17" s="192" t="inlineStr">
+        <is>
+          <t>SoFi Stadium</t>
+        </is>
+      </c>
+      <c r="G17" s="194" t="inlineStr">
+        <is>
+          <t>Inglewood / Los Angeles</t>
+        </is>
+      </c>
+      <c r="H17" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I17" s="196" t="n">
+        <v>70108</v>
+      </c>
+      <c r="J17" s="197" t="n">
+        <v>70240</v>
+      </c>
+      <c r="K17" s="206" t="n">
+        <v>0.998120728929385</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="98">
+      <c r="A18" s="180" t="inlineStr">
+        <is>
+          <t>16.06</t>
+        </is>
+      </c>
+      <c r="B18" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="C18" s="199" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D18" s="181" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="E18" s="200" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="F18" s="199" t="inlineStr">
+        <is>
+          <t>Hard Rock Stadium</t>
+        </is>
+      </c>
+      <c r="G18" s="201" t="inlineStr">
+        <is>
+          <t>Miami Gardens / Miami</t>
+        </is>
+      </c>
+      <c r="H18" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I18" s="202" t="n">
+        <v>62764</v>
+      </c>
+      <c r="J18" s="203" t="n">
+        <v>64767</v>
+      </c>
+      <c r="K18" s="198" t="n">
+        <v>0.9690737566970834</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="98">
+      <c r="A19" s="173" t="inlineStr">
+        <is>
+          <t>16.06</t>
+        </is>
+      </c>
+      <c r="B19" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
+      <c r="C19" s="192" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D19" s="172" t="inlineStr">
+        <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="E19" s="193" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="F19" s="192" t="inlineStr">
+        <is>
+          <t>MetLife Stadium</t>
+        </is>
+      </c>
+      <c r="G19" s="194" t="inlineStr">
+        <is>
+          <t>East Rutherford, NJ</t>
+        </is>
+      </c>
+      <c r="H19" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I19" s="196" t="n">
+        <v>80545</v>
+      </c>
+      <c r="J19" s="197" t="n">
+        <v>82500</v>
+      </c>
+      <c r="K19" s="206" t="n">
+        <v>0.9763030303030305</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="98">
+      <c r="A20" s="180" t="inlineStr">
+        <is>
+          <t>17.06</t>
+        </is>
+      </c>
+      <c r="B20" s="182" t="inlineStr"/>
+      <c r="C20" s="199" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D20" s="181" t="inlineStr">
+        <is>
+          <t>1–4</t>
+        </is>
+      </c>
+      <c r="E20" s="200" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="F20" s="199" t="inlineStr">
+        <is>
+          <t>Gillette Stadium</t>
+        </is>
+      </c>
+      <c r="G20" s="201" t="inlineStr">
+        <is>
+          <t>Foxborough / Boston</t>
+        </is>
+      </c>
+      <c r="H20" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I20" s="202" t="n">
+        <v>63106</v>
+      </c>
+      <c r="J20" s="203" t="n">
+        <v>65878</v>
+      </c>
+      <c r="K20" s="198" t="n">
+        <v>0.9579222198609549</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="98">
+      <c r="A21" s="173" t="inlineStr">
+        <is>
+          <t>17.06</t>
+        </is>
+      </c>
+      <c r="B21" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="C21" s="192" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D21" s="172" t="inlineStr">
+        <is>
+          <t>3–0</t>
+        </is>
+      </c>
+      <c r="E21" s="193" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+      <c r="F21" s="192" t="inlineStr">
+        <is>
+          <t>Arrowhead Stadium</t>
+        </is>
+      </c>
+      <c r="G21" s="194" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="H21" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I21" s="196" t="n">
+        <v>69045</v>
+      </c>
+      <c r="J21" s="197" t="n">
+        <v>76416</v>
+      </c>
+      <c r="K21" s="204" t="n">
+        <v>0.9035411432160804</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="98">
+      <c r="A22" s="180" t="inlineStr">
+        <is>
+          <t>17.06</t>
+        </is>
+      </c>
+      <c r="B22" s="182" t="inlineStr"/>
+      <c r="C22" s="199" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="D22" s="181" t="inlineStr">
+        <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="E22" s="200" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="F22" s="199" t="inlineStr">
+        <is>
+          <t>Levi's Stadium</t>
+        </is>
+      </c>
+      <c r="G22" s="201" t="inlineStr">
+        <is>
+          <t>Santa Clara / SF Bay Area</t>
+        </is>
+      </c>
+      <c r="H22" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I22" s="202" t="n">
+        <v>68527</v>
+      </c>
+      <c r="J22" s="203" t="n">
+        <v>68500</v>
+      </c>
+      <c r="K22" s="206" t="n">
+        <v>1.000394160583942</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="98">
+      <c r="A23" s="173" t="inlineStr">
+        <is>
+          <t>17.06</t>
+        </is>
+      </c>
+      <c r="B23" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="C23" s="192" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D23" s="172" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="E23" s="193" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+      <c r="F23" s="192" t="inlineStr">
+        <is>
+          <t>NRG Stadium</t>
+        </is>
+      </c>
+      <c r="G23" s="194" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="H23" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I23" s="196" t="n">
+        <v>68777</v>
+      </c>
+      <c r="J23" s="197" t="n">
+        <v>72220</v>
+      </c>
+      <c r="K23" s="198" t="n">
+        <v>0.9523262254223206</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="98">
+      <c r="A24" s="180" t="inlineStr">
+        <is>
+          <t>17.06</t>
+        </is>
+      </c>
+      <c r="B24" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="C24" s="199" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D24" s="181" t="inlineStr">
+        <is>
+          <t>4–2</t>
+        </is>
+      </c>
+      <c r="E24" s="200" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+      <c r="F24" s="199" t="inlineStr">
+        <is>
+          <t>AT&amp;T Stadium</t>
+        </is>
+      </c>
+      <c r="G24" s="201" t="inlineStr">
+        <is>
+          <t>Arlington / Dallas</t>
+        </is>
+      </c>
+      <c r="H24" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I24" s="202" t="n">
+        <v>70389</v>
+      </c>
+      <c r="J24" s="203" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K24" s="204" t="n">
+        <v>0.8798625</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="98">
+      <c r="A25" s="173" t="inlineStr">
+        <is>
+          <t>18.06</t>
+        </is>
+      </c>
+      <c r="B25" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
+      <c r="C25" s="192" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="D25" s="172" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="E25" s="193" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="F25" s="192" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium</t>
+        </is>
+      </c>
+      <c r="G25" s="194" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H25" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I25" s="196" t="n">
+        <v>67442</v>
+      </c>
+      <c r="J25" s="197" t="n">
+        <v>71000</v>
+      </c>
+      <c r="K25" s="198" t="n">
+        <v>0.9498873239436619</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="98">
+      <c r="A26" s="180" t="inlineStr">
+        <is>
+          <t>18.06</t>
+        </is>
+      </c>
+      <c r="B26" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="C26" s="199" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D26" s="181" t="inlineStr">
+        <is>
+          <t>4–1</t>
+        </is>
+      </c>
+      <c r="E26" s="200" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="F26" s="199" t="inlineStr">
+        <is>
+          <t>SoFi Stadium</t>
+        </is>
+      </c>
+      <c r="G26" s="201" t="inlineStr">
+        <is>
+          <t>Inglewood / Los Angeles</t>
+        </is>
+      </c>
+      <c r="H26" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I26" s="202" t="n">
+        <v>70026</v>
+      </c>
+      <c r="J26" s="203" t="n">
+        <v>70240</v>
+      </c>
+      <c r="K26" s="206" t="n">
+        <v>0.9969533029612756</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="98">
+      <c r="A27" s="173" t="inlineStr">
+        <is>
+          <t>18.06</t>
+        </is>
+      </c>
+      <c r="B27" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="C27" s="192" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D27" s="172" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="E27" s="193" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="F27" s="192" t="inlineStr">
+        <is>
+          <t>Estadio Azteca</t>
+        </is>
+      </c>
+      <c r="G27" s="194" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="H27" s="195" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I27" s="196" t="n">
+        <v>80824</v>
+      </c>
+      <c r="J27" s="197" t="n">
+        <v>87523</v>
+      </c>
+      <c r="K27" s="198" t="n">
+        <v>0.9234601190544199</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="98">
+      <c r="A28" s="180" t="inlineStr">
+        <is>
+          <t>18.06</t>
+        </is>
+      </c>
+      <c r="B28" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="C28" s="199" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D28" s="181" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="E28" s="200" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="F28" s="199" t="inlineStr">
+        <is>
+          <t>BMO Field</t>
+        </is>
+      </c>
+      <c r="G28" s="201" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="H28" s="205" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I28" s="202" t="n">
+        <v>42942</v>
+      </c>
+      <c r="J28" s="203" t="n">
+        <v>45736</v>
+      </c>
+      <c r="K28" s="198" t="n">
+        <v>0.9389102676228791</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="98">
+      <c r="A29" s="173" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="B29" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
+      <c r="C29" s="192" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D29" s="172" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="E29" s="193" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="F29" s="192" t="inlineStr">
+        <is>
+          <t>Estadio Akron</t>
+        </is>
+      </c>
+      <c r="G29" s="194" t="inlineStr">
+        <is>
+          <t>Zapopan / Guadalajara</t>
+        </is>
+      </c>
+      <c r="H29" s="195" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I29" s="196" t="n">
+        <v>45522</v>
+      </c>
+      <c r="J29" s="197" t="n">
+        <v>49850</v>
+      </c>
+      <c r="K29" s="204" t="n">
+        <v>0.9131795386158476</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="98">
+      <c r="A30" s="180" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="B30" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="C30" s="199" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D30" s="181" t="inlineStr">
+        <is>
+          <t>6–0</t>
+        </is>
+      </c>
+      <c r="E30" s="200" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="F30" s="199" t="inlineStr">
+        <is>
+          <t>BC Place</t>
+        </is>
+      </c>
+      <c r="G30" s="201" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="H30" s="205" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I30" s="202" t="n">
+        <v>52497</v>
+      </c>
+      <c r="J30" s="203" t="n">
+        <v>54500</v>
+      </c>
+      <c r="K30" s="198" t="n">
+        <v>0.9632477064220184</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="98">
+      <c r="A31" s="173" t="inlineStr">
+        <is>
+          <t>19.06</t>
+        </is>
+      </c>
+      <c r="B31" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="C31" s="192" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D31" s="172" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="E31" s="193" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="F31" s="192" t="inlineStr">
+        <is>
+          <t>Lumen Field</t>
+        </is>
+      </c>
+      <c r="G31" s="194" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="H31" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I31" s="196" t="n">
+        <v>66925</v>
+      </c>
+      <c r="J31" s="197" t="n">
+        <v>68740</v>
+      </c>
+      <c r="K31" s="206" t="n">
+        <v>0.9735961594413733</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="98">
+      <c r="A32" s="180" t="inlineStr">
+        <is>
+          <t>20.06</t>
+        </is>
+      </c>
+      <c r="B32" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
+      <c r="C32" s="199" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D32" s="181" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="E32" s="200" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="F32" s="199" t="inlineStr">
+        <is>
+          <t>Gillette Stadium</t>
+        </is>
+      </c>
+      <c r="G32" s="201" t="inlineStr">
+        <is>
+          <t>Foxborough / Boston</t>
+        </is>
+      </c>
+      <c r="H32" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I32" s="202" t="n">
+        <v>64146</v>
+      </c>
+      <c r="J32" s="203" t="n">
+        <v>65878</v>
+      </c>
+      <c r="K32" s="206" t="n">
+        <v>0.9737089772002793</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="98">
+      <c r="A33" s="173" t="inlineStr">
+        <is>
+          <t>20.06</t>
+        </is>
+      </c>
+      <c r="B33" s="174" t="inlineStr"/>
+      <c r="C33" s="192" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D33" s="172" t="inlineStr">
+        <is>
+          <t>3–0</t>
+        </is>
+      </c>
+      <c r="E33" s="193" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="F33" s="192" t="inlineStr">
+        <is>
+          <t>Lincoln Financial Field</t>
+        </is>
+      </c>
+      <c r="G33" s="194" t="inlineStr">
+        <is>
+          <t>Philadelphia</t>
+        </is>
+      </c>
+      <c r="H33" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I33" s="196" t="n">
+        <v>68324</v>
+      </c>
+      <c r="J33" s="197" t="n">
+        <v>69796</v>
+      </c>
+      <c r="K33" s="206" t="n">
+        <v>0.9789099661871741</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="98">
+      <c r="A34" s="180" t="inlineStr">
+        <is>
+          <t>20.06</t>
+        </is>
+      </c>
+      <c r="B34" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="C34" s="199" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D34" s="181" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="E34" s="200" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F34" s="199" t="inlineStr">
+        <is>
+          <t>Levi's Stadium</t>
+        </is>
+      </c>
+      <c r="G34" s="201" t="inlineStr">
+        <is>
+          <t>Santa Clara / SF Bay Area</t>
+        </is>
+      </c>
+      <c r="H34" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I34" s="202" t="n">
+        <v>68827</v>
+      </c>
+      <c r="J34" s="203" t="n">
+        <v>68500</v>
+      </c>
+      <c r="K34" s="206" t="n">
+        <v>1.004773722627737</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="98">
+      <c r="A35" s="173" t="inlineStr">
+        <is>
+          <t>20.06</t>
+        </is>
+      </c>
+      <c r="B35" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="C35" s="192" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D35" s="172" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="E35" s="193" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="F35" s="192" t="inlineStr">
+        <is>
+          <t>BMO Field</t>
+        </is>
+      </c>
+      <c r="G35" s="194" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="H35" s="205" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I35" s="196" t="n">
+        <v>43036</v>
+      </c>
+      <c r="J35" s="197" t="n">
+        <v>45736</v>
+      </c>
+      <c r="K35" s="198" t="n">
+        <v>0.9409655413678503</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="98">
+      <c r="A36" s="180" t="inlineStr">
+        <is>
+          <t>20.06</t>
+        </is>
+      </c>
+      <c r="B36" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="C36" s="199" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D36" s="181" t="inlineStr">
+        <is>
+          <t>5–1</t>
+        </is>
+      </c>
+      <c r="E36" s="200" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="F36" s="199" t="inlineStr">
+        <is>
+          <t>NRG Stadium</t>
+        </is>
+      </c>
+      <c r="G36" s="201" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="H36" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I36" s="202" t="n">
+        <v>68777</v>
+      </c>
+      <c r="J36" s="203" t="n">
+        <v>72220</v>
+      </c>
+      <c r="K36" s="198" t="n">
+        <v>0.9523262254223206</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="98">
+      <c r="A37" s="173" t="inlineStr">
+        <is>
+          <t>21.06</t>
+        </is>
+      </c>
+      <c r="B37" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="C37" s="192" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D37" s="172" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="E37" s="193" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="F37" s="192" t="inlineStr">
+        <is>
+          <t>Arrowhead Stadium</t>
+        </is>
+      </c>
+      <c r="G37" s="194" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="H37" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I37" s="196" t="n">
+        <v>68598</v>
+      </c>
+      <c r="J37" s="197" t="n">
+        <v>76416</v>
+      </c>
+      <c r="K37" s="204" t="n">
+        <v>0.8976915829145728</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="98">
+      <c r="A38" s="180" t="inlineStr">
+        <is>
+          <t>21.06</t>
+        </is>
+      </c>
+      <c r="B38" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="C38" s="199" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D38" s="181" t="inlineStr">
+        <is>
+          <t>0–4</t>
+        </is>
+      </c>
+      <c r="E38" s="200" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="F38" s="199" t="inlineStr">
+        <is>
+          <t>Estadio BBVA</t>
+        </is>
+      </c>
+      <c r="G38" s="201" t="inlineStr">
+        <is>
+          <t>San Nicolás / Monterrey</t>
+        </is>
+      </c>
+      <c r="H38" s="195" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="I38" s="202" t="n">
+        <v>51243</v>
+      </c>
+      <c r="J38" s="203" t="n">
+        <v>53464</v>
+      </c>
+      <c r="K38" s="198" t="n">
+        <v>0.9584580278318121</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="98">
+      <c r="A39" s="173" t="inlineStr">
+        <is>
+          <t>21.06</t>
+        </is>
+      </c>
+      <c r="B39" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="C39" s="192" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D39" s="172" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="E39" s="193" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="F39" s="192" t="inlineStr">
+        <is>
+          <t>SoFi Stadium</t>
+        </is>
+      </c>
+      <c r="G39" s="194" t="inlineStr">
+        <is>
+          <t>Inglewood / Los Angeles</t>
+        </is>
+      </c>
+      <c r="H39" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I39" s="196" t="n">
+        <v>70317</v>
+      </c>
+      <c r="J39" s="197" t="n">
+        <v>70240</v>
+      </c>
+      <c r="K39" s="206" t="n">
+        <v>1.001096241457859</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="98">
+      <c r="A40" s="180" t="inlineStr">
+        <is>
+          <t>21.06</t>
+        </is>
+      </c>
+      <c r="B40" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="C40" s="199" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D40" s="181" t="inlineStr">
+        <is>
+          <t>4–0</t>
+        </is>
+      </c>
+      <c r="E40" s="200" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="F40" s="199" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Stadium</t>
+        </is>
+      </c>
+      <c r="G40" s="201" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="H40" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I40" s="202" t="n">
+        <v>68239</v>
+      </c>
+      <c r="J40" s="203" t="n">
+        <v>71000</v>
+      </c>
+      <c r="K40" s="198" t="n">
+        <v>0.961112676056338</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="98">
+      <c r="A41" s="173" t="inlineStr">
+        <is>
+          <t>22.06</t>
+        </is>
+      </c>
+      <c r="B41" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="C41" s="192" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D41" s="172" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="E41" s="193" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="F41" s="192" t="inlineStr">
+        <is>
+          <t>BC Place</t>
+        </is>
+      </c>
+      <c r="G41" s="194" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="H41" s="205" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="I41" s="196" t="n">
+        <v>52497</v>
+      </c>
+      <c r="J41" s="197" t="n">
+        <v>54500</v>
+      </c>
+      <c r="K41" s="198" t="n">
+        <v>0.9632477064220184</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="98">
+      <c r="A42" s="180" t="inlineStr">
+        <is>
+          <t>22.06</t>
+        </is>
+      </c>
+      <c r="B42" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="C42" s="199" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="D42" s="181" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="E42" s="200" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+      <c r="F42" s="199" t="inlineStr">
+        <is>
+          <t>Hard Rock Stadium</t>
+        </is>
+      </c>
+      <c r="G42" s="201" t="inlineStr">
+        <is>
+          <t>Miami Gardens / Miami</t>
+        </is>
+      </c>
+      <c r="H42" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I42" s="202" t="n">
+        <v>64003</v>
+      </c>
+      <c r="J42" s="203" t="n">
+        <v>64767</v>
+      </c>
+      <c r="K42" s="206" t="n">
+        <v>0.9882038692544043</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="98">
+      <c r="A44" s="158" t="inlineStr">
+        <is>
+          <t>Belegg:</t>
+        </is>
+      </c>
+      <c r="B44" s="208" t="inlineStr">
+        <is>
+          <t>≥97% (praktisk utsolgt)</t>
+        </is>
+      </c>
+      <c r="C44" s="209" t="inlineStr">
+        <is>
+          <t>92–96%</t>
+        </is>
+      </c>
+      <c r="D44" s="210" t="inlineStr">
+        <is>
+          <t>87–91%</t>
+        </is>
+      </c>
+      <c r="E44" s="211" t="inlineStr">
+        <is>
+          <t>&lt;87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="14" customHeight="1" s="98">
+      <c r="A45" s="166" t="inlineStr">
+        <is>
+          <t>Kapasitetstall: offisielle arenakapasiteter (ikke FIFA-sertifisert VM-kapasitet som kan avvike noe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="98">
+      <c r="A47" s="212" t="inlineStr">
+        <is>
+          <t>Totalt tilskuere: 2 563 003</t>
+        </is>
+      </c>
+      <c r="C47" s="212" t="inlineStr">
+        <is>
+          <t>Snitt belegg: 95.6%</t>
+        </is>
+      </c>
+      <c r="E47" s="212" t="inlineStr">
+        <is>
+          <t>Høyest: 80 824 (Mexico – Sør-Afrika)</t>
+        </is>
+      </c>
+      <c r="H47" s="212" t="inlineStr">
+        <is>
+          <t>Lavest: 42 942 (Ghana – Panama)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="7" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Alder" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Stadionoversikt" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -1494,13 +1494,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1519,7 +1519,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1547,8 +1547,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1574,8 +1574,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1598,7 +1598,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1613,9 +1613,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -60224,14 +60224,14 @@
   <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" style="98" min="1" max="1"/>
+    <col width="7" customWidth="1" style="98" min="1" max="1"/>
     <col width="9" customWidth="1" style="98" min="2" max="2"/>
     <col width="20" customWidth="1" style="98" min="3" max="3"/>
     <col width="7" customWidth="1" style="98" min="4" max="4"/>
-    <col width="20" customWidth="1" style="98" min="5" max="5"/>
+    <col width="16" customWidth="1" style="98" min="5" max="5"/>
     <col width="24" customWidth="1" style="98" min="6" max="6"/>
     <col width="24" customWidth="1" style="98" min="7" max="7"/>
-    <col width="9" customWidth="1" style="98" min="8" max="8"/>
+    <col width="7" customWidth="1" style="98" min="8" max="8"/>
     <col width="12" customWidth="1" style="98" min="9" max="9"/>
     <col width="11" customWidth="1" style="98" min="10" max="10"/>
     <col width="9" customWidth="1" style="98" min="11" max="11"/>
@@ -60358,7 +60358,11 @@
           <t>12.06</t>
         </is>
       </c>
-      <c r="B4" s="182" t="inlineStr"/>
+      <c r="B4" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
       <c r="C4" s="199" t="inlineStr">
         <is>
           <t>Sør-Korea</t>
@@ -60456,7 +60460,11 @@
           <t>13.06</t>
         </is>
       </c>
-      <c r="B6" s="182" t="inlineStr"/>
+      <c r="B6" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
       <c r="C6" s="199" t="inlineStr">
         <is>
           <t>Qatar</t>
@@ -60605,7 +60613,11 @@
           <t>14.06</t>
         </is>
       </c>
-      <c r="B9" s="174" t="inlineStr"/>
+      <c r="B9" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
       <c r="C9" s="192" t="inlineStr">
         <is>
           <t>Haiti</t>
@@ -61162,7 +61174,11 @@
           <t>17.06</t>
         </is>
       </c>
-      <c r="B20" s="182" t="inlineStr"/>
+      <c r="B20" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
       <c r="C20" s="199" t="inlineStr">
         <is>
           <t>Irak</t>
@@ -61260,7 +61276,11 @@
           <t>17.06</t>
         </is>
       </c>
-      <c r="B22" s="182" t="inlineStr"/>
+      <c r="B22" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
       <c r="C22" s="199" t="inlineStr">
         <is>
           <t>Østerrike</t>
@@ -61817,7 +61837,11 @@
           <t>20.06</t>
         </is>
       </c>
-      <c r="B33" s="174" t="inlineStr"/>
+      <c r="B33" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
       <c r="C33" s="192" t="inlineStr">
         <is>
           <t>Brasil</t>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="7" activeTab="12" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Klubber" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Aldersfordeling" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Nivå 2 og lavere" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Kort" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Scorere og assists" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Alder" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Lagstatistikk" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Scoringstidspunkt" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Heatmap" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Ballbesittelse" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Stadionoversikt" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'Klubber'!$A$2:$E$2</definedName>
@@ -1494,13 +1494,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -1519,7 +1519,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1547,8 +1547,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1574,8 +1574,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1598,7 +1598,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1613,9 +1613,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -6198,34 +6198,46 @@
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="114" t="inlineStr">
+      <c r="A5" s="108" t="inlineStr">
         <is>
           <t>Runde 2</t>
         </is>
       </c>
-      <c r="B5" s="114" t="inlineStr">
+      <c r="B5" s="108" t="inlineStr">
         <is>
           <t>22.06 19:00</t>
         </is>
       </c>
-      <c r="C5" s="115" t="inlineStr">
+      <c r="C5" s="109" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="D5" s="116" t="inlineStr">
-        <is>
-          <t>– – –</t>
-        </is>
-      </c>
-      <c r="E5" s="115" t="inlineStr">
+      <c r="D5" s="110" t="inlineStr">
+        <is>
+          <t>2 – 0</t>
+        </is>
+      </c>
+      <c r="E5" s="109" t="inlineStr">
         <is>
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="F5" s="114" t="inlineStr"/>
-      <c r="G5" s="115" t="inlineStr"/>
-      <c r="H5" s="115" t="inlineStr"/>
+      <c r="F5" s="108" t="inlineStr">
+        <is>
+          <t>70 649</t>
+        </is>
+      </c>
+      <c r="G5" s="109" t="inlineStr">
+        <is>
+          <t>Dallas Stadium</t>
+        </is>
+      </c>
+      <c r="H5" s="109" t="inlineStr">
+        <is>
+          <t>Amin Mohamed</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
       <c r="A6" s="111" t="inlineStr">
@@ -6377,10 +6389,10 @@
         </is>
       </c>
       <c r="B12" s="108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" s="108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="108" t="n">
         <v>0</v>
@@ -6389,18 +6401,18 @@
         <v>0</v>
       </c>
       <c r="F12" s="108" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G12" s="108" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="108" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="I12" s="110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" s="98">
@@ -6410,7 +6422,7 @@
         </is>
       </c>
       <c r="B13" s="119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="119" t="n">
         <v>1</v>
@@ -6419,17 +6431,17 @@
         <v>0</v>
       </c>
       <c r="E13" s="119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="119" t="n">
         <v>3</v>
       </c>
       <c r="G13" s="119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="119" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="120" t="n">
@@ -6658,8 +6670,8 @@
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
-      <c r="J21" s="140" t="n">
-        <v>0</v>
+      <c r="J21" s="137" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="98">
@@ -6720,10 +6732,12 @@
       </c>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
-      <c r="H23" s="3" t="n"/>
+      <c r="H23" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I23" s="3" t="n"/>
-      <c r="J23" s="140" t="n">
-        <v>0</v>
+      <c r="J23" s="137" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1" s="98">
@@ -6755,7 +6769,7 @@
       <c r="H24" s="6" t="n"/>
       <c r="I24" s="6" t="n"/>
       <c r="J24" s="138" t="n">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1" s="98">
@@ -6789,7 +6803,7 @@
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="137" t="n">
-        <v>99</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1" s="98">
@@ -6853,7 +6867,7 @@
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="137" t="n">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1" s="98">
@@ -6881,13 +6895,13 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="6" t="n"/>
       <c r="I28" s="6" t="n"/>
       <c r="J28" s="138" t="n">
-        <v>83</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1" s="98">
@@ -6983,7 +6997,7 @@
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
       <c r="J31" s="137" t="n">
-        <v>83</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1" s="98">
@@ -7049,7 +7063,7 @@
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="137" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1" s="98">
@@ -7081,7 +7095,7 @@
       <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="n"/>
       <c r="J34" s="138" t="n">
-        <v>59</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1" s="98">
@@ -7177,7 +7191,7 @@
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="137" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1" s="98">
@@ -7209,7 +7223,7 @@
       <c r="H38" s="6" t="n"/>
       <c r="I38" s="6" t="n"/>
       <c r="J38" s="138" t="n">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1" s="98">
@@ -7273,7 +7287,7 @@
       <c r="H40" s="6" t="n"/>
       <c r="I40" s="6" t="n"/>
       <c r="J40" s="138" t="n">
-        <v>59</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1" s="98">
@@ -7305,7 +7319,7 @@
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="137" t="n">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1" s="98">
@@ -7337,7 +7351,7 @@
       <c r="H42" s="6" t="n"/>
       <c r="I42" s="6" t="n"/>
       <c r="J42" s="138" t="n">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1" s="98">
@@ -7365,11 +7379,15 @@
         </is>
       </c>
       <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="3" t="n"/>
+      <c r="G43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I43" s="3" t="n"/>
       <c r="J43" s="137" t="n">
-        <v>99</v>
+        <v>187</v>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1" s="98">
@@ -7401,7 +7419,7 @@
       <c r="H44" s="6" t="n"/>
       <c r="I44" s="6" t="n"/>
       <c r="J44" s="138" t="n">
-        <v>50</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" ht="24" customHeight="1" s="98">
@@ -8393,7 +8411,7 @@
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
       <c r="J77" s="137" t="n">
-        <v>106</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" ht="16" customHeight="1" s="98">
@@ -8457,7 +8475,7 @@
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="J79" s="137" t="n">
-        <v>44</v>
+        <v>148</v>
       </c>
     </row>
     <row r="80" ht="16" customHeight="1" s="98">
@@ -8491,7 +8509,7 @@
       <c r="H80" s="6" t="n"/>
       <c r="I80" s="6" t="n"/>
       <c r="J80" s="138" t="n">
-        <v>62</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1" s="98">
@@ -8520,10 +8538,12 @@
       </c>
       <c r="F81" s="5" t="n"/>
       <c r="G81" s="5" t="n"/>
-      <c r="H81" s="3" t="n"/>
+      <c r="H81" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="I81" s="3" t="n"/>
       <c r="J81" s="137" t="n">
-        <v>106</v>
+        <v>180</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1" s="98">
@@ -8555,7 +8575,7 @@
       <c r="H82" s="6" t="n"/>
       <c r="I82" s="6" t="n"/>
       <c r="J82" s="138" t="n">
-        <v>106</v>
+        <v>211</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1" s="98">
@@ -8589,7 +8609,7 @@
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
       <c r="J83" s="137" t="n">
-        <v>57</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1" s="98">
@@ -8621,7 +8641,7 @@
       <c r="H84" s="6" t="n"/>
       <c r="I84" s="6" t="n"/>
       <c r="J84" s="138" t="n">
-        <v>62</v>
+        <v>136</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1" s="98">
@@ -8655,7 +8675,7 @@
       </c>
       <c r="I85" s="3" t="n"/>
       <c r="J85" s="137" t="n">
-        <v>106</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1" s="98">
@@ -8718,8 +8738,8 @@
       <c r="G87" s="5" t="n"/>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
-      <c r="J87" s="140" t="n">
-        <v>0</v>
+      <c r="J87" s="137" t="n">
+        <v>91</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1" s="98">
@@ -8782,8 +8802,8 @@
       <c r="G89" s="5" t="n"/>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
-      <c r="J89" s="140" t="n">
-        <v>0</v>
+      <c r="J89" s="137" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1" s="98">
@@ -8911,7 +8931,7 @@
       <c r="H93" s="3" t="n"/>
       <c r="I93" s="3" t="n"/>
       <c r="J93" s="137" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1" s="98">
@@ -8943,7 +8963,7 @@
       <c r="H94" s="6" t="n"/>
       <c r="I94" s="6" t="n"/>
       <c r="J94" s="138" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1" s="98">
@@ -9004,10 +9024,12 @@
       </c>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
-      <c r="H96" s="6" t="n"/>
+      <c r="H96" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="I96" s="6" t="n"/>
       <c r="J96" s="138" t="n">
-        <v>106</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1" s="98">
@@ -9041,7 +9063,7 @@
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
       <c r="J97" s="137" t="n">
-        <v>86</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1" s="98">
@@ -9072,8 +9094,8 @@
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="6" t="n"/>
       <c r="I98" s="6" t="n"/>
-      <c r="J98" s="139" t="n">
-        <v>0</v>
+      <c r="J98" s="138" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1" s="98">
@@ -9104,8 +9126,8 @@
       <c r="G99" s="5" t="n"/>
       <c r="H99" s="3" t="n"/>
       <c r="I99" s="3" t="n"/>
-      <c r="J99" s="140" t="n">
-        <v>0</v>
+      <c r="J99" s="137" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="100" ht="16" customHeight="1" s="98">
@@ -9137,7 +9159,7 @@
       <c r="H100" s="6" t="n"/>
       <c r="I100" s="6" t="n"/>
       <c r="J100" s="138" t="n">
-        <v>44</v>
+        <v>118</v>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="98">
@@ -39832,7 +39854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="98" min="1" max="1"/>
@@ -39845,7 +39867,7 @@
     <row r="1" ht="28" customHeight="1" s="98">
       <c r="A1" s="105" t="inlineStr">
         <is>
-          <t>VM 2026 — Kort  (102 spillere)</t>
+          <t>VM 2026 — Kort  (106 spillere)</t>
         </is>
       </c>
     </row>
@@ -40682,12 +40704,12 @@
       </c>
       <c r="B45" s="115" t="inlineStr">
         <is>
-          <t>Findlay Curtis</t>
+          <t>Facundo Medina</t>
         </is>
       </c>
       <c r="C45" s="116" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D45" s="128" t="n">
@@ -40701,12 +40723,12 @@
       </c>
       <c r="B46" s="112" t="inlineStr">
         <is>
-          <t>Folarin Balogun</t>
+          <t>Findlay Curtis</t>
         </is>
       </c>
       <c r="C46" s="113" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="D46" s="128" t="n">
@@ -40720,12 +40742,12 @@
       </c>
       <c r="B47" s="115" t="inlineStr">
         <is>
-          <t>Franck Kessie</t>
+          <t>Folarin Balogun</t>
         </is>
       </c>
       <c r="C47" s="116" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D47" s="128" t="n">
@@ -40739,12 +40761,12 @@
       </c>
       <c r="B48" s="112" t="inlineStr">
         <is>
-          <t>Frantzdy Pierrot</t>
+          <t>Franck Kessie</t>
         </is>
       </c>
       <c r="C48" s="113" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="D48" s="128" t="n">
@@ -40758,12 +40780,12 @@
       </c>
       <c r="B49" s="115" t="inlineStr">
         <is>
-          <t>Gabriel Gudmundsson</t>
+          <t>Frantzdy Pierrot</t>
         </is>
       </c>
       <c r="C49" s="116" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="D49" s="128" t="n">
@@ -40777,12 +40799,12 @@
       </c>
       <c r="B50" s="112" t="inlineStr">
         <is>
-          <t>Gervane Kastaneer</t>
+          <t>Gabriel Gudmundsson</t>
         </is>
       </c>
       <c r="C50" s="113" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="D50" s="128" t="n">
@@ -40796,12 +40818,12 @@
       </c>
       <c r="B51" s="115" t="inlineStr">
         <is>
-          <t>Guela Doue</t>
+          <t>Gervane Kastaneer</t>
         </is>
       </c>
       <c r="C51" s="116" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D51" s="128" t="n">
@@ -40815,12 +40837,12 @@
       </c>
       <c r="B52" s="112" t="inlineStr">
         <is>
-          <t>Harry Souttar</t>
+          <t>Guela Doue</t>
         </is>
       </c>
       <c r="C52" s="113" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="D52" s="128" t="n">
@@ -40834,12 +40856,12 @@
       </c>
       <c r="B53" s="115" t="inlineStr">
         <is>
-          <t>Issa Diop</t>
+          <t>Harry Souttar</t>
         </is>
       </c>
       <c r="C53" s="116" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D53" s="128" t="n">
@@ -40853,12 +40875,12 @@
       </c>
       <c r="B54" s="112" t="inlineStr">
         <is>
-          <t>Jackson Porozo</t>
+          <t>Issa Diop</t>
         </is>
       </c>
       <c r="C54" s="113" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="D54" s="128" t="n">
@@ -40872,12 +40894,12 @@
       </c>
       <c r="B55" s="115" t="inlineStr">
         <is>
-          <t>Jacob Italiano</t>
+          <t>Jackson Porozo</t>
         </is>
       </c>
       <c r="C55" s="116" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D55" s="128" t="n">
@@ -40891,12 +40913,12 @@
       </c>
       <c r="B56" s="112" t="inlineStr">
         <is>
-          <t>Jassem Gaber</t>
+          <t>Jacob Italiano</t>
         </is>
       </c>
       <c r="C56" s="113" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D56" s="128" t="n">
@@ -40910,12 +40932,12 @@
       </c>
       <c r="B57" s="115" t="inlineStr">
         <is>
-          <t>Jean-Ricner Bellegarde</t>
+          <t>Jassem Gaber</t>
         </is>
       </c>
       <c r="C57" s="116" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D57" s="128" t="n">
@@ -40929,12 +40951,12 @@
       </c>
       <c r="B58" s="112" t="inlineStr">
         <is>
-          <t>Johan Mojica</t>
+          <t>Jean-Ricner Bellegarde</t>
         </is>
       </c>
       <c r="C58" s="113" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="D58" s="128" t="n">
@@ -40948,12 +40970,12 @@
       </c>
       <c r="B59" s="115" t="inlineStr">
         <is>
-          <t>Jordan Bos</t>
+          <t>Johan Mojica</t>
         </is>
       </c>
       <c r="C59" s="116" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D59" s="128" t="n">
@@ -40967,12 +40989,12 @@
       </c>
       <c r="B60" s="112" t="inlineStr">
         <is>
-          <t>Jordy Alcivar</t>
+          <t>Jordan Bos</t>
         </is>
       </c>
       <c r="C60" s="113" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D60" s="128" t="n">
@@ -40986,12 +41008,12 @@
       </c>
       <c r="B61" s="115" t="inlineStr">
         <is>
-          <t>Jovo Lukic</t>
+          <t>Jordy Alcivar</t>
         </is>
       </c>
       <c r="C61" s="116" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D61" s="128" t="n">
@@ -41005,12 +41027,12 @@
       </c>
       <c r="B62" s="112" t="inlineStr">
         <is>
-          <t>Juan Jose Caceres</t>
+          <t>Jovo Lukic</t>
         </is>
       </c>
       <c r="C62" s="113" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="D62" s="128" t="n">
@@ -41024,12 +41046,12 @@
       </c>
       <c r="B63" s="115" t="inlineStr">
         <is>
-          <t>Juninho Bacuna</t>
+          <t>Juan Jose Caceres</t>
         </is>
       </c>
       <c r="C63" s="116" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D63" s="128" t="n">
@@ -41043,12 +41065,12 @@
       </c>
       <c r="B64" s="112" t="inlineStr">
         <is>
-          <t>Junior Alonso</t>
+          <t>Juninho Bacuna</t>
         </is>
       </c>
       <c r="C64" s="113" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D64" s="128" t="n">
@@ -41062,12 +41084,12 @@
       </c>
       <c r="B65" s="115" t="inlineStr">
         <is>
-          <t>Jurien Gaari</t>
+          <t>Junior Alonso</t>
         </is>
       </c>
       <c r="C65" s="116" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D65" s="128" t="n">
@@ -41081,12 +41103,12 @@
       </c>
       <c r="B66" s="112" t="inlineStr">
         <is>
-          <t>Kenny Mclean</t>
+          <t>Jurien Gaari</t>
         </is>
       </c>
       <c r="C66" s="113" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D66" s="128" t="n">
@@ -41100,12 +41122,12 @@
       </c>
       <c r="B67" s="115" t="inlineStr">
         <is>
-          <t>Ladislav Krejci</t>
+          <t>Kenny Mclean</t>
         </is>
       </c>
       <c r="C67" s="116" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="D67" s="128" t="n">
@@ -41119,12 +41141,12 @@
       </c>
       <c r="B68" s="112" t="inlineStr">
         <is>
-          <t>Leandro Bacuna</t>
+          <t>Konrad Laimer</t>
         </is>
       </c>
       <c r="C68" s="113" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="D68" s="128" t="n">
@@ -41138,12 +41160,12 @@
       </c>
       <c r="B69" s="115" t="inlineStr">
         <is>
-          <t>Lee Gihyuk</t>
+          <t>Ladislav Krejci</t>
         </is>
       </c>
       <c r="C69" s="116" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Tsjekkia</t>
         </is>
       </c>
       <c r="D69" s="128" t="n">
@@ -41157,12 +41179,12 @@
       </c>
       <c r="B70" s="112" t="inlineStr">
         <is>
-          <t>Lee Kangin</t>
+          <t>Leandro Bacuna</t>
         </is>
       </c>
       <c r="C70" s="113" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D70" s="128" t="n">
@@ -41176,12 +41198,12 @@
       </c>
       <c r="B71" s="115" t="inlineStr">
         <is>
-          <t>Livano Comenencia</t>
+          <t>Leandro Paredes</t>
         </is>
       </c>
       <c r="C71" s="116" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D71" s="128" t="n">
@@ -41195,12 +41217,12 @@
       </c>
       <c r="B72" s="112" t="inlineStr">
         <is>
-          <t>Luc De Fougerolles</t>
+          <t>Lee Gihyuk</t>
         </is>
       </c>
       <c r="C72" s="113" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="D72" s="128" t="n">
@@ -41214,12 +41236,12 @@
       </c>
       <c r="B73" s="115" t="inlineStr">
         <is>
-          <t>Lucas Bergvall</t>
+          <t>Lee Kangin</t>
         </is>
       </c>
       <c r="C73" s="116" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="D73" s="128" t="n">
@@ -41233,12 +41255,12 @@
       </c>
       <c r="B74" s="112" t="inlineStr">
         <is>
-          <t>Mahmoud Abunada</t>
+          <t>Livano Comenencia</t>
         </is>
       </c>
       <c r="C74" s="113" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D74" s="128" t="n">
@@ -41252,12 +41274,12 @@
       </c>
       <c r="B75" s="115" t="inlineStr">
         <is>
-          <t>Marawan Attia</t>
+          <t>Luc De Fougerolles</t>
         </is>
       </c>
       <c r="C75" s="116" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D75" s="128" t="n">
@@ -41271,12 +41293,12 @@
       </c>
       <c r="B76" s="112" t="inlineStr">
         <is>
-          <t>Marcel Sabitzer</t>
+          <t>Lucas Bergvall</t>
         </is>
       </c>
       <c r="C76" s="113" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="D76" s="128" t="n">
@@ -41290,12 +41312,12 @@
       </c>
       <c r="B77" s="115" t="inlineStr">
         <is>
-          <t>Mathias Olivera</t>
+          <t>Mahmoud Abunada</t>
         </is>
       </c>
       <c r="C77" s="116" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="D77" s="128" t="n">
@@ -41309,12 +41331,12 @@
       </c>
       <c r="B78" s="112" t="inlineStr">
         <is>
-          <t>Matias Galarza</t>
+          <t>Marawan Attia</t>
         </is>
       </c>
       <c r="C78" s="113" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D78" s="128" t="n">
@@ -41328,12 +41350,12 @@
       </c>
       <c r="B79" s="115" t="inlineStr">
         <is>
-          <t>Maxim De Cuyper</t>
+          <t>Marcel Sabitzer</t>
         </is>
       </c>
       <c r="C79" s="116" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="D79" s="128" t="n">
@@ -41347,12 +41369,12 @@
       </c>
       <c r="B80" s="112" t="inlineStr">
         <is>
-          <t>Memphis Depay</t>
+          <t>Mathias Olivera</t>
         </is>
       </c>
       <c r="C80" s="113" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D80" s="128" t="n">
@@ -41366,12 +41388,12 @@
       </c>
       <c r="B81" s="115" t="inlineStr">
         <is>
-          <t>Micky Van De Ven</t>
+          <t>Matias Galarza</t>
         </is>
       </c>
       <c r="C81" s="116" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D81" s="128" t="n">
@@ -41385,12 +41407,12 @@
       </c>
       <c r="B82" s="112" t="inlineStr">
         <is>
-          <t>Mohamed Kanno</t>
+          <t>Maxim De Cuyper</t>
         </is>
       </c>
       <c r="C82" s="113" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="D82" s="128" t="n">
@@ -41404,12 +41426,12 @@
       </c>
       <c r="B83" s="115" t="inlineStr">
         <is>
-          <t>Mohanad Lashin</t>
+          <t>Memphis Depay</t>
         </is>
       </c>
       <c r="C83" s="116" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="D83" s="128" t="n">
@@ -41423,12 +41445,12 @@
       </c>
       <c r="B84" s="112" t="inlineStr">
         <is>
-          <t>Nelson Semedo</t>
+          <t>Micky Van De Ven</t>
         </is>
       </c>
       <c r="C84" s="113" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="D84" s="128" t="n">
@@ -41442,12 +41464,12 @@
       </c>
       <c r="B85" s="115" t="inlineStr">
         <is>
-          <t>Nico Elvedi</t>
+          <t>Mohamed Kanno</t>
         </is>
       </c>
       <c r="C85" s="116" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
       <c r="D85" s="128" t="n">
@@ -41461,12 +41483,12 @@
       </c>
       <c r="B86" s="112" t="inlineStr">
         <is>
-          <t>Nikola Katic</t>
+          <t>Mohanad Lashin</t>
         </is>
       </c>
       <c r="C86" s="113" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D86" s="128" t="n">
@@ -41480,12 +41502,12 @@
       </c>
       <c r="B87" s="115" t="inlineStr">
         <is>
-          <t>Nkosinathi Sibisi</t>
+          <t>Nelson Semedo</t>
         </is>
       </c>
       <c r="C87" s="116" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D87" s="128" t="n">
@@ -41499,12 +41521,12 @@
       </c>
       <c r="B88" s="112" t="inlineStr">
         <is>
-          <t>Paik Seungho</t>
+          <t>Nico Elvedi</t>
         </is>
       </c>
       <c r="C88" s="113" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Sveits</t>
         </is>
       </c>
       <c r="D88" s="128" t="n">
@@ -41518,12 +41540,12 @@
       </c>
       <c r="B89" s="115" t="inlineStr">
         <is>
-          <t>Pedri</t>
+          <t>Nikola Katic</t>
         </is>
       </c>
       <c r="C89" s="116" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="D89" s="128" t="n">
@@ -41537,12 +41559,12 @@
       </c>
       <c r="B90" s="112" t="inlineStr">
         <is>
-          <t>Rani Khedira</t>
+          <t>Nkosinathi Sibisi</t>
         </is>
       </c>
       <c r="C90" s="113" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
       <c r="D90" s="128" t="n">
@@ -41556,12 +41578,12 @@
       </c>
       <c r="B91" s="115" t="inlineStr">
         <is>
-          <t>Rodrigo Bentancur</t>
+          <t>Paik Seungho</t>
         </is>
       </c>
       <c r="C91" s="116" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="D91" s="128" t="n">
@@ -41575,12 +41597,12 @@
       </c>
       <c r="B92" s="112" t="inlineStr">
         <is>
-          <t>Roger Ibanez</t>
+          <t>Pedri</t>
         </is>
       </c>
       <c r="C92" s="113" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Spania</t>
         </is>
       </c>
       <c r="D92" s="128" t="n">
@@ -41594,12 +41616,12 @@
       </c>
       <c r="B93" s="115" t="inlineStr">
         <is>
-          <t>Romelu Lukaku</t>
+          <t>Rani Khedira</t>
         </is>
       </c>
       <c r="C93" s="116" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D93" s="128" t="n">
@@ -41613,12 +41635,12 @@
       </c>
       <c r="B94" s="112" t="inlineStr">
         <is>
-          <t>Saeid Ezatolahi</t>
+          <t>Rodrigo Bentancur</t>
         </is>
       </c>
       <c r="C94" s="113" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D94" s="128" t="n">
@@ -41632,12 +41654,12 @@
       </c>
       <c r="B95" s="115" t="inlineStr">
         <is>
-          <t>Salem Aldawsari</t>
+          <t>Roger Ibanez</t>
         </is>
       </c>
       <c r="C95" s="116" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D95" s="128" t="n">
@@ -41651,12 +41673,12 @@
       </c>
       <c r="B96" s="112" t="inlineStr">
         <is>
-          <t>Sarpreet Singh</t>
+          <t>Romelu Lukaku</t>
         </is>
       </c>
       <c r="C96" s="113" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="D96" s="128" t="n">
@@ -41670,12 +41692,12 @@
       </c>
       <c r="B97" s="115" t="inlineStr">
         <is>
-          <t>Seko Fofana</t>
+          <t>Saeid Ezatolahi</t>
         </is>
       </c>
       <c r="C97" s="116" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="D97" s="128" t="n">
@@ -41689,12 +41711,12 @@
       </c>
       <c r="B98" s="112" t="inlineStr">
         <is>
-          <t>Thalente Mbatha</t>
+          <t>Salem Aldawsari</t>
         </is>
       </c>
       <c r="C98" s="113" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
       <c r="D98" s="128" t="n">
@@ -41708,12 +41730,12 @@
       </c>
       <c r="B99" s="115" t="inlineStr">
         <is>
-          <t>Timothy Castagne</t>
+          <t>Sarpreet Singh</t>
         </is>
       </c>
       <c r="C99" s="116" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D99" s="128" t="n">
@@ -41727,12 +41749,12 @@
       </c>
       <c r="B100" s="112" t="inlineStr">
         <is>
-          <t>Tomas Araujo</t>
+          <t>Seko Fofana</t>
         </is>
       </c>
       <c r="C100" s="113" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="D100" s="128" t="n">
@@ -41746,12 +41768,12 @@
       </c>
       <c r="B101" s="115" t="inlineStr">
         <is>
-          <t>Tyler Adams</t>
+          <t>Stefan Posch</t>
         </is>
       </c>
       <c r="C101" s="116" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="D101" s="128" t="n">
@@ -41765,12 +41787,12 @@
       </c>
       <c r="B102" s="112" t="inlineStr">
         <is>
-          <t>Yasin Ayari</t>
+          <t>Thalente Mbatha</t>
         </is>
       </c>
       <c r="C102" s="113" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
       <c r="D102" s="128" t="n">
@@ -41784,12 +41806,12 @@
       </c>
       <c r="B103" s="115" t="inlineStr">
         <is>
-          <t>Yunus Akgun</t>
+          <t>Timothy Castagne</t>
         </is>
       </c>
       <c r="C103" s="116" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="D103" s="128" t="n">
@@ -41803,18 +41825,94 @@
       </c>
       <c r="B104" s="112" t="inlineStr">
         <is>
+          <t>Tomas Araujo</t>
+        </is>
+      </c>
+      <c r="C104" s="113" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D104" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="113" t="n"/>
+    </row>
+    <row r="105" ht="17" customHeight="1" s="98">
+      <c r="A105" s="114" t="n">
+        <v>11</v>
+      </c>
+      <c r="B105" s="115" t="inlineStr">
+        <is>
+          <t>Tyler Adams</t>
+        </is>
+      </c>
+      <c r="C105" s="116" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D105" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="116" t="n"/>
+    </row>
+    <row r="106" ht="17" customHeight="1" s="98">
+      <c r="A106" s="111" t="n">
+        <v>11</v>
+      </c>
+      <c r="B106" s="112" t="inlineStr">
+        <is>
+          <t>Yasin Ayari</t>
+        </is>
+      </c>
+      <c r="C106" s="113" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D106" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="113" t="n"/>
+    </row>
+    <row r="107" ht="17" customHeight="1" s="98">
+      <c r="A107" s="114" t="n">
+        <v>11</v>
+      </c>
+      <c r="B107" s="115" t="inlineStr">
+        <is>
+          <t>Yunus Akgun</t>
+        </is>
+      </c>
+      <c r="C107" s="116" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D107" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="116" t="n"/>
+    </row>
+    <row r="108" ht="17" customHeight="1" s="98">
+      <c r="A108" s="111" t="n">
+        <v>11</v>
+      </c>
+      <c r="B108" s="112" t="inlineStr">
+        <is>
           <t>Zaid Tahseen</t>
         </is>
       </c>
-      <c r="C104" s="113" t="inlineStr">
+      <c r="C108" s="113" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="D104" s="128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="113" t="n"/>
+      <c r="D108" s="128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="113" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -41830,7 +41928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="98" min="1" max="1"/>
@@ -41843,7 +41941,7 @@
     <row r="1" ht="28" customHeight="1" s="98">
       <c r="A1" s="105" t="inlineStr">
         <is>
-          <t>VM 2026 — Scorere og assists   113 mål · 79 assists</t>
+          <t>VM 2026 — Scorere og assists   115 mål · 80 assists</t>
         </is>
       </c>
     </row>
@@ -41880,58 +41978,58 @@
       </c>
       <c r="B3" s="126" t="inlineStr">
         <is>
+          <t>Lionel Messi</t>
+        </is>
+      </c>
+      <c r="C3" s="126" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D3" s="127" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" s="127" t="n"/>
+    </row>
+    <row r="4" ht="17" customHeight="1" s="98">
+      <c r="A4" s="130" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="131" t="inlineStr">
+        <is>
           <t>Deniz Undav</t>
         </is>
       </c>
-      <c r="C3" s="126" t="inlineStr">
+      <c r="C4" s="131" t="inlineStr">
         <is>
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="D3" s="127" t="n">
+      <c r="D4" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="E3" s="127" t="n">
+      <c r="E4" s="132" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="17" customHeight="1" s="98">
-      <c r="A4" s="125" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="126" t="inlineStr">
+    <row r="5" ht="17" customHeight="1" s="98">
+      <c r="A5" s="130" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="131" t="inlineStr">
         <is>
           <t>Jonathan David</t>
         </is>
       </c>
-      <c r="C4" s="126" t="inlineStr">
+      <c r="C5" s="131" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="D4" s="127" t="n">
+      <c r="D5" s="132" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="127" t="n"/>
-    </row>
-    <row r="5" ht="17" customHeight="1" s="98">
-      <c r="A5" s="125" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="126" t="inlineStr">
-        <is>
-          <t>Lionel Messi</t>
-        </is>
-      </c>
-      <c r="C5" s="126" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D5" s="127" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="127" t="n"/>
+      <c r="E5" s="132" t="n"/>
     </row>
     <row r="6" ht="17" customHeight="1" s="98">
       <c r="A6" s="111" t="n">
@@ -43955,12 +44053,12 @@
       </c>
       <c r="B110" s="112" t="inlineStr">
         <is>
-          <t>Florian Wirtz</t>
+          <t>Facundo Medina</t>
         </is>
       </c>
       <c r="C110" s="112" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D110" s="113" t="n"/>
@@ -43974,12 +44072,12 @@
       </c>
       <c r="B111" s="115" t="inlineStr">
         <is>
-          <t>Gustavo Puerta</t>
+          <t>Florian Wirtz</t>
         </is>
       </c>
       <c r="C111" s="115" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="D111" s="116" t="n"/>
@@ -43993,12 +44091,12 @@
       </c>
       <c r="B112" s="112" t="inlineStr">
         <is>
-          <t>Hannibal Mejbri</t>
+          <t>Gustavo Puerta</t>
         </is>
       </c>
       <c r="C112" s="112" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D112" s="113" t="n"/>
@@ -44012,12 +44110,12 @@
       </c>
       <c r="B113" s="115" t="inlineStr">
         <is>
-          <t>Iliman Ndiaye</t>
+          <t>Hannibal Mejbri</t>
         </is>
       </c>
       <c r="C113" s="115" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D113" s="116" t="n"/>
@@ -44031,12 +44129,12 @@
       </c>
       <c r="B114" s="112" t="inlineStr">
         <is>
-          <t>Ivan Perišić</t>
+          <t>Iliman Ndiaye</t>
         </is>
       </c>
       <c r="C114" s="112" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D114" s="113" t="n"/>
@@ -44050,12 +44148,12 @@
       </c>
       <c r="B115" s="115" t="inlineStr">
         <is>
-          <t>Kaishu Sano</t>
+          <t>Ivan Perišić</t>
         </is>
       </c>
       <c r="C115" s="115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Kroatia</t>
         </is>
       </c>
       <c r="D115" s="116" t="n"/>
@@ -44069,7 +44167,7 @@
       </c>
       <c r="B116" s="112" t="inlineStr">
         <is>
-          <t>Ko Itakura</t>
+          <t>Kaishu Sano</t>
         </is>
       </c>
       <c r="C116" s="112" t="inlineStr">
@@ -44088,7 +44186,7 @@
       </c>
       <c r="B117" s="115" t="inlineStr">
         <is>
-          <t>Koki Ogawa</t>
+          <t>Ko Itakura</t>
         </is>
       </c>
       <c r="C117" s="115" t="inlineStr">
@@ -44107,12 +44205,12 @@
       </c>
       <c r="B118" s="112" t="inlineStr">
         <is>
-          <t>Lee Kang-in</t>
+          <t>Koki Ogawa</t>
         </is>
       </c>
       <c r="C118" s="112" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D118" s="113" t="n"/>
@@ -44126,12 +44224,12 @@
       </c>
       <c r="B119" s="115" t="inlineStr">
         <is>
-          <t>Lucas Bergvall</t>
+          <t>Lee Kang-in</t>
         </is>
       </c>
       <c r="C119" s="115" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="D119" s="116" t="n"/>
@@ -44145,12 +44243,12 @@
       </c>
       <c r="B120" s="112" t="inlineStr">
         <is>
-          <t>Lucas Paquetá</t>
+          <t>Lucas Bergvall</t>
         </is>
       </c>
       <c r="C120" s="112" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="D120" s="113" t="n"/>
@@ -44164,12 +44262,12 @@
       </c>
       <c r="B121" s="115" t="inlineStr">
         <is>
-          <t>Malik Tillman</t>
+          <t>Lucas Paquetá</t>
         </is>
       </c>
       <c r="C121" s="115" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D121" s="116" t="n"/>
@@ -44183,12 +44281,12 @@
       </c>
       <c r="B122" s="112" t="inlineStr">
         <is>
-          <t>Martin Ødegaard</t>
+          <t>Malik Tillman</t>
         </is>
       </c>
       <c r="C122" s="112" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D122" s="113" t="n"/>
@@ -44202,12 +44300,12 @@
       </c>
       <c r="B123" s="115" t="inlineStr">
         <is>
-          <t>Memphis Depay</t>
+          <t>Martin Ødegaard</t>
         </is>
       </c>
       <c r="C123" s="115" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="D123" s="116" t="n"/>
@@ -44221,12 +44319,12 @@
       </c>
       <c r="B124" s="112" t="inlineStr">
         <is>
-          <t>Michael Olise</t>
+          <t>Memphis Depay</t>
         </is>
       </c>
       <c r="C124" s="112" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="D124" s="113" t="n"/>
@@ -44240,12 +44338,12 @@
       </c>
       <c r="B125" s="115" t="inlineStr">
         <is>
-          <t>Mohamed Hany</t>
+          <t>Michael Olise</t>
         </is>
       </c>
       <c r="C125" s="115" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="D125" s="116" t="n"/>
@@ -44259,12 +44357,12 @@
       </c>
       <c r="B126" s="112" t="inlineStr">
         <is>
-          <t>Nadiem Amiri</t>
+          <t>Mohamed Hany</t>
         </is>
       </c>
       <c r="C126" s="112" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D126" s="113" t="n"/>
@@ -44278,12 +44376,12 @@
       </c>
       <c r="B127" s="115" t="inlineStr">
         <is>
-          <t>Nicolás González</t>
+          <t>Nadiem Amiri</t>
         </is>
       </c>
       <c r="C127" s="115" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="D127" s="116" t="n"/>
@@ -44297,12 +44395,12 @@
       </c>
       <c r="B128" s="112" t="inlineStr">
         <is>
-          <t>Paul Okon-Engstler</t>
+          <t>Nicolás González</t>
         </is>
       </c>
       <c r="C128" s="112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D128" s="113" t="n"/>
@@ -44316,12 +44414,12 @@
       </c>
       <c r="B129" s="115" t="inlineStr">
         <is>
-          <t>Pedro Neto</t>
+          <t>Paul Okon-Engstler</t>
         </is>
       </c>
       <c r="C129" s="115" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="D129" s="116" t="n"/>
@@ -44335,12 +44433,12 @@
       </c>
       <c r="B130" s="112" t="inlineStr">
         <is>
-          <t>Petar Sučić</t>
+          <t>Pedro Neto</t>
         </is>
       </c>
       <c r="C130" s="112" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D130" s="113" t="n"/>
@@ -44354,12 +44452,12 @@
       </c>
       <c r="B131" s="115" t="inlineStr">
         <is>
-          <t>Promise David</t>
+          <t>Petar Sučić</t>
         </is>
       </c>
       <c r="C131" s="115" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Kroatia</t>
         </is>
       </c>
       <c r="D131" s="116" t="n"/>
@@ -44373,12 +44471,12 @@
       </c>
       <c r="B132" s="112" t="inlineStr">
         <is>
-          <t>Roberto Alvarado</t>
+          <t>Promise David</t>
         </is>
       </c>
       <c r="C132" s="112" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D132" s="113" t="n"/>
@@ -44392,12 +44490,12 @@
       </c>
       <c r="B133" s="115" t="inlineStr">
         <is>
-          <t>Rodrigo De Paul</t>
+          <t>Roberto Alvarado</t>
         </is>
       </c>
       <c r="C133" s="115" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D133" s="116" t="n"/>
@@ -44411,12 +44509,12 @@
       </c>
       <c r="B134" s="112" t="inlineStr">
         <is>
-          <t>Sead Kolašinac</t>
+          <t>Rodrigo De Paul</t>
         </is>
       </c>
       <c r="C134" s="112" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D134" s="113" t="n"/>
@@ -44430,12 +44528,12 @@
       </c>
       <c r="B135" s="115" t="inlineStr">
         <is>
-          <t>Takefusa Kubo</t>
+          <t>Sead Kolašinac</t>
         </is>
       </c>
       <c r="C135" s="115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="D135" s="116" t="n"/>
@@ -44449,12 +44547,12 @@
       </c>
       <c r="B136" s="112" t="inlineStr">
         <is>
-          <t>Tim Payne</t>
+          <t>Takefusa Kubo</t>
         </is>
       </c>
       <c r="C136" s="112" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D136" s="113" t="n"/>
@@ -44468,12 +44566,12 @@
       </c>
       <c r="B137" s="115" t="inlineStr">
         <is>
-          <t>Vladimír Coufal</t>
+          <t>Tim Payne</t>
         </is>
       </c>
       <c r="C137" s="115" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D137" s="116" t="n"/>
@@ -44487,12 +44585,12 @@
       </c>
       <c r="B138" s="112" t="inlineStr">
         <is>
-          <t>Wilfried Singo</t>
+          <t>Vladimír Coufal</t>
         </is>
       </c>
       <c r="C138" s="112" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>Tsjekkia</t>
         </is>
       </c>
       <c r="D138" s="113" t="n"/>
@@ -44506,16 +44604,35 @@
       </c>
       <c r="B139" s="115" t="inlineStr">
         <is>
-          <t>Xaver Schlager</t>
+          <t>Wilfried Singo</t>
         </is>
       </c>
       <c r="C139" s="115" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="D139" s="116" t="n"/>
       <c r="E139" s="116" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" ht="17" customHeight="1" s="98">
+      <c r="A140" s="111" t="n">
+        <v>89</v>
+      </c>
+      <c r="B140" s="112" t="inlineStr">
+        <is>
+          <t>Xaver Schlager</t>
+        </is>
+      </c>
+      <c r="C140" s="112" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="D140" s="113" t="n"/>
+      <c r="E140" s="113" t="n">
         <v>1</v>
       </c>
     </row>
@@ -45245,7 +45362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H257"/>
+  <dimension ref="A1:H258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="98" min="1" max="1"/>
@@ -45261,14 +45378,14 @@
     <row r="1" ht="26" customHeight="1" s="98">
       <c r="A1" s="105" t="inlineStr">
         <is>
-          <t>VM 2026 — Mål per kamp   121 mål totalt</t>
+          <t>VM 2026 — Mål per kamp   123 mål totalt</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="98">
       <c r="A2" s="141" t="inlineStr">
         <is>
-          <t>Spillermål: 107     Straffer: 6     Selvmål: 8</t>
+          <t>Spillermål: 109     Straffer: 6     Selvmål: 8</t>
         </is>
       </c>
     </row>
@@ -45554,50 +45671,50 @@
     </row>
     <row r="11" ht="16" customHeight="1" s="98">
       <c r="A11" s="111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="112" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C11" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D11" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="113" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>2,50</t>
         </is>
       </c>
       <c r="G11" s="113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="113" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>0,00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1" s="98">
       <c r="A12" s="114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" s="115" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C12" s="116" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D12" s="116" t="n">
@@ -45612,60 +45729,60 @@
         </is>
       </c>
       <c r="G12" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="116" t="inlineStr">
         <is>
-          <t>2,00</t>
+          <t>1,00</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1" s="98">
       <c r="A13" s="111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="112" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C13" s="113" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D13" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="113" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="113" t="inlineStr">
         <is>
+          <t>4,00</t>
+        </is>
+      </c>
+      <c r="G13" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="113" t="inlineStr">
+        <is>
           <t>2,00</t>
-        </is>
-      </c>
-      <c r="G13" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="113" t="inlineStr">
-        <is>
-          <t>0,50</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1" s="98">
       <c r="A14" s="114" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" s="115" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="C14" s="116" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D14" s="116" t="n">
@@ -45680,26 +45797,26 @@
         </is>
       </c>
       <c r="G14" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="116" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>0,50</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1" s="98">
       <c r="A15" s="111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15" s="112" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C15" s="113" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D15" s="113" t="n">
@@ -45714,60 +45831,60 @@
         </is>
       </c>
       <c r="G15" s="113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" s="113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1,00</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1" s="98">
       <c r="A16" s="114" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B16" s="115" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Spania</t>
         </is>
       </c>
       <c r="C16" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D16" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="116" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>2,00</t>
         </is>
       </c>
       <c r="G16" s="116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" s="116" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>0,00</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1" s="98">
       <c r="A17" s="111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="112" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C17" s="113" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D17" s="113" t="n">
@@ -45782,26 +45899,26 @@
         </is>
       </c>
       <c r="G17" s="113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="113" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>1,00</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1" s="98">
       <c r="A18" s="114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="115" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C18" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D18" s="116" t="n">
@@ -45826,50 +45943,50 @@
     </row>
     <row r="19" ht="16" customHeight="1" s="98">
       <c r="A19" s="111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="112" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C19" s="113" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D19" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="113" t="n">
         <v>3</v>
       </c>
       <c r="F19" s="113" t="inlineStr">
         <is>
-          <t>3,00</t>
+          <t>1,50</t>
         </is>
       </c>
       <c r="G19" s="113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" s="113" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>0,00</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1" s="98">
       <c r="A20" s="114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="115" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C20" s="116" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D20" s="116" t="n">
@@ -45884,26 +46001,26 @@
         </is>
       </c>
       <c r="G20" s="116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H20" s="116" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>2,50</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1" s="98">
       <c r="A21" s="111" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B21" s="112" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C21" s="113" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D21" s="113" t="n">
@@ -45918,26 +46035,26 @@
         </is>
       </c>
       <c r="G21" s="113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H21" s="113" t="inlineStr">
         <is>
-          <t>2,50</t>
+          <t>1,50</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1" s="98">
       <c r="A22" s="114" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B22" s="115" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="C22" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D22" s="116" t="n">
@@ -47412,416 +47529,416 @@
       </c>
     </row>
     <row r="70" ht="16" customHeight="1" s="98">
-      <c r="A70" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B70" s="134" t="inlineStr">
+      <c r="A70" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="126" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C70" s="127" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="D70" s="127" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="127" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="127" t="inlineStr">
+        <is>
+          <t>2/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1" s="98">
+      <c r="A71" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" s="112" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="C70" s="135" t="inlineStr">
+      <c r="C71" s="113" t="inlineStr">
         <is>
           <t>Gruppe B</t>
         </is>
       </c>
-      <c r="D70" s="135" t="n">
+      <c r="D71" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" s="135" t="inlineStr">
+      <c r="E71" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="113" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1" s="98">
-      <c r="A71" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" s="134" t="inlineStr">
+    <row r="72" ht="16" customHeight="1" s="98">
+      <c r="A72" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" s="115" t="inlineStr">
         <is>
           <t>Brasil</t>
         </is>
       </c>
-      <c r="C71" s="135" t="inlineStr">
+      <c r="C72" s="116" t="inlineStr">
         <is>
           <t>Gruppe C</t>
         </is>
       </c>
-      <c r="D71" s="135" t="n">
+      <c r="D72" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="E71" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="135" t="inlineStr">
+      <c r="E72" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="116" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1" s="98">
-      <c r="A72" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B72" s="134" t="inlineStr">
+    <row r="73" ht="16" customHeight="1" s="98">
+      <c r="A73" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" s="112" t="inlineStr">
         <is>
           <t>Marokko</t>
         </is>
       </c>
-      <c r="C72" s="135" t="inlineStr">
+      <c r="C73" s="113" t="inlineStr">
         <is>
           <t>Gruppe C</t>
         </is>
       </c>
-      <c r="D72" s="135" t="n">
+      <c r="D73" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="E72" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" s="135" t="inlineStr">
+      <c r="E73" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="113" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1" s="98">
-      <c r="A73" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" s="134" t="inlineStr">
+    <row r="74" ht="16" customHeight="1" s="98">
+      <c r="A74" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" s="115" t="inlineStr">
         <is>
           <t>Skottland</t>
         </is>
       </c>
-      <c r="C73" s="135" t="inlineStr">
+      <c r="C74" s="116" t="inlineStr">
         <is>
           <t>Gruppe C</t>
         </is>
       </c>
-      <c r="D73" s="135" t="n">
+      <c r="D74" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="E73" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" s="135" t="inlineStr">
+      <c r="E74" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="116" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1" s="98">
-      <c r="A74" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B74" s="134" t="inlineStr">
+    <row r="75" ht="16" customHeight="1" s="98">
+      <c r="A75" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" s="112" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="C74" s="135" t="inlineStr">
+      <c r="C75" s="113" t="inlineStr">
         <is>
           <t>Gruppe D</t>
         </is>
       </c>
-      <c r="D74" s="135" t="n">
+      <c r="D75" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="E74" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="135" t="inlineStr">
+      <c r="E75" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="113" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="16" customHeight="1" s="98">
-      <c r="A75" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B75" s="134" t="inlineStr">
+    <row r="76" ht="16" customHeight="1" s="98">
+      <c r="A76" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" s="115" t="inlineStr">
         <is>
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="C75" s="135" t="inlineStr">
+      <c r="C76" s="116" t="inlineStr">
         <is>
           <t>Gruppe D</t>
         </is>
       </c>
-      <c r="D75" s="135" t="n">
+      <c r="D76" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="E75" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="135" t="inlineStr">
+      <c r="E76" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="116" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="16" customHeight="1" s="98">
-      <c r="A76" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B76" s="134" t="inlineStr">
+    <row r="77" ht="16" customHeight="1" s="98">
+      <c r="A77" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" s="112" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="C76" s="135" t="inlineStr">
+      <c r="C77" s="113" t="inlineStr">
         <is>
           <t>Gruppe D</t>
         </is>
       </c>
-      <c r="D76" s="135" t="n">
+      <c r="D77" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="E76" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" s="135" t="inlineStr">
+      <c r="E77" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="113" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16" customHeight="1" s="98">
-      <c r="A77" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B77" s="134" t="inlineStr">
+    <row r="78" ht="16" customHeight="1" s="98">
+      <c r="A78" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" s="115" t="inlineStr">
         <is>
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="C77" s="135" t="inlineStr">
+      <c r="C78" s="116" t="inlineStr">
         <is>
           <t>Gruppe E</t>
         </is>
       </c>
-      <c r="D77" s="135" t="n">
+      <c r="D78" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="135" t="inlineStr">
+      <c r="E78" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="116" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1" s="98">
-      <c r="A78" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B78" s="134" t="inlineStr">
+    <row r="79" ht="16" customHeight="1" s="98">
+      <c r="A79" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" s="112" t="inlineStr">
         <is>
           <t>Elfenbenskysten</t>
         </is>
       </c>
-      <c r="C78" s="135" t="inlineStr">
+      <c r="C79" s="113" t="inlineStr">
         <is>
           <t>Gruppe E</t>
         </is>
       </c>
-      <c r="D78" s="135" t="n">
+      <c r="D79" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" s="135" t="inlineStr">
+      <c r="E79" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="113" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="16" customHeight="1" s="98">
-      <c r="A79" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B79" s="134" t="inlineStr">
+    <row r="80" ht="16" customHeight="1" s="98">
+      <c r="A80" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" s="115" t="inlineStr">
         <is>
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="C79" s="135" t="inlineStr">
+      <c r="C80" s="116" t="inlineStr">
         <is>
           <t>Gruppe E</t>
         </is>
       </c>
-      <c r="D79" s="135" t="n">
+      <c r="D80" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="135" t="inlineStr">
+      <c r="E80" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="116" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1" s="98">
-      <c r="A80" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B80" s="134" t="inlineStr">
+    <row r="81" ht="16" customHeight="1" s="98">
+      <c r="A81" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" s="112" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="C80" s="135" t="inlineStr">
+      <c r="C81" s="113" t="inlineStr">
         <is>
           <t>Gruppe F</t>
         </is>
       </c>
-      <c r="D80" s="135" t="n">
+      <c r="D81" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" s="135" t="inlineStr">
+      <c r="E81" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="113" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1" s="98">
-      <c r="A81" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B81" s="134" t="inlineStr">
+    <row r="82" ht="16" customHeight="1" s="98">
+      <c r="A82" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" s="115" t="inlineStr">
         <is>
           <t>Belgia</t>
         </is>
       </c>
-      <c r="C81" s="135" t="inlineStr">
+      <c r="C82" s="116" t="inlineStr">
         <is>
           <t>Gruppe G</t>
         </is>
       </c>
-      <c r="D81" s="135" t="n">
+      <c r="D82" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="E81" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F81" s="135" t="inlineStr">
+      <c r="E82" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="116" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="16" customHeight="1" s="98">
-      <c r="A82" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B82" s="134" t="inlineStr">
+    <row r="83" ht="16" customHeight="1" s="98">
+      <c r="A83" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" s="112" t="inlineStr">
         <is>
           <t>Iran</t>
         </is>
       </c>
-      <c r="C82" s="135" t="inlineStr">
+      <c r="C83" s="113" t="inlineStr">
         <is>
           <t>Gruppe G</t>
         </is>
       </c>
-      <c r="D82" s="135" t="n">
+      <c r="D83" s="113" t="n">
         <v>2</v>
       </c>
-      <c r="E82" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F82" s="135" t="inlineStr">
+      <c r="E83" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="113" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="16" customHeight="1" s="98">
-      <c r="A83" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B83" s="134" t="inlineStr">
+    <row r="84" ht="16" customHeight="1" s="98">
+      <c r="A84" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="B84" s="115" t="inlineStr">
         <is>
           <t>Kapp Verde</t>
         </is>
       </c>
-      <c r="C83" s="135" t="inlineStr">
+      <c r="C84" s="116" t="inlineStr">
         <is>
           <t>Gruppe H</t>
         </is>
       </c>
-      <c r="D83" s="135" t="n">
+      <c r="D84" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="E83" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" s="135" t="inlineStr">
+      <c r="E84" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="116" t="inlineStr">
         <is>
           <t>1/2</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="16" customHeight="1" s="98">
-      <c r="A84" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" s="134" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="C84" s="135" t="inlineStr">
-        <is>
-          <t>Gruppe J</t>
-        </is>
-      </c>
-      <c r="D84" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" s="135" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-    </row>
     <row r="85" ht="16" customHeight="1" s="98">
-      <c r="A85" s="133" t="n">
-        <v>3</v>
-      </c>
-      <c r="B85" s="134" t="inlineStr">
+      <c r="A85" s="111" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" s="112" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C85" s="135" t="inlineStr">
+      <c r="C85" s="113" t="inlineStr">
         <is>
           <t>Gruppe L</t>
         </is>
       </c>
-      <c r="D85" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="135" t="n">
-        <v>1</v>
-      </c>
-      <c r="F85" s="135" t="inlineStr">
+      <c r="D85" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="113" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
@@ -48016,511 +48133,506 @@
         </is>
       </c>
     </row>
-    <row r="95" ht="26" customHeight="1" s="98">
-      <c r="A95" s="105" t="inlineStr">
+    <row r="94" ht="16" customHeight="1" s="98">
+      <c r="A94" s="130" t="n">
+        <v>2</v>
+      </c>
+      <c r="B94" s="131" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C94" s="132" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="D94" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="132" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1" s="98">
+      <c r="A96" s="105" t="inlineStr">
         <is>
           <t>VM 2026 — Selvmål</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="18" customHeight="1" s="98">
-      <c r="A96" s="106" t="inlineStr">
+    <row r="97" ht="18" customHeight="1" s="98">
+      <c r="A97" s="106" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B96" s="107" t="inlineStr">
+      <c r="B97" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="C96" s="106" t="inlineStr">
+      <c r="C97" s="106" t="inlineStr">
         <is>
           <t>Gruppe</t>
         </is>
       </c>
-      <c r="D96" s="107" t="inlineStr">
+      <c r="D97" s="107" t="inlineStr">
         <is>
           <t>Spiller</t>
         </is>
       </c>
-      <c r="E96" s="107" t="inlineStr">
+      <c r="E97" s="107" t="inlineStr">
         <is>
           <t>Kamp</t>
         </is>
       </c>
-      <c r="F96" s="106" t="inlineStr">
+      <c r="F97" s="106" t="inlineStr">
         <is>
           <t>Minutt</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="16" customHeight="1" s="98">
-      <c r="A97" s="125" t="n">
-        <v>1</v>
-      </c>
-      <c r="B97" s="126" t="inlineStr">
+    <row r="98" ht="16" customHeight="1" s="98">
+      <c r="A98" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="B98" s="126" t="inlineStr">
         <is>
           <t>Australia</t>
         </is>
       </c>
-      <c r="C97" s="127" t="inlineStr">
+      <c r="C98" s="127" t="inlineStr">
         <is>
           <t>Gruppe D</t>
         </is>
       </c>
-      <c r="D97" s="126" t="inlineStr">
+      <c r="D98" s="126" t="inlineStr">
         <is>
           <t>Cameron BURGESS</t>
         </is>
       </c>
-      <c r="E97" s="126" t="inlineStr">
+      <c r="E98" s="126" t="inlineStr">
         <is>
           <t>USA – Australia</t>
         </is>
       </c>
-      <c r="F97" s="127" t="inlineStr">
+      <c r="F98" s="127" t="inlineStr">
         <is>
           <t>11''</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="16" customHeight="1" s="98">
-      <c r="A98" s="130" t="n">
+    <row r="99" ht="16" customHeight="1" s="98">
+      <c r="A99" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="B98" s="131" t="inlineStr">
+      <c r="B99" s="131" t="inlineStr">
         <is>
           <t>Egypt</t>
         </is>
       </c>
-      <c r="C98" s="132" t="inlineStr">
+      <c r="C99" s="132" t="inlineStr">
         <is>
           <t>Gruppe G</t>
         </is>
       </c>
-      <c r="D98" s="131" t="inlineStr">
+      <c r="D99" s="131" t="inlineStr">
         <is>
           <t>MOHAMED HANY</t>
         </is>
       </c>
-      <c r="E98" s="131" t="inlineStr">
+      <c r="E99" s="131" t="inlineStr">
         <is>
           <t>Belgia – Egypt</t>
         </is>
       </c>
-      <c r="F98" s="132" t="inlineStr">
+      <c r="F99" s="132" t="inlineStr">
         <is>
           <t>66''</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="16" customHeight="1" s="98">
-      <c r="A99" s="133" t="n">
+    <row r="100" ht="16" customHeight="1" s="98">
+      <c r="A100" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="B99" s="134" t="inlineStr">
+      <c r="B100" s="134" t="inlineStr">
         <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="C99" s="135" t="inlineStr">
+      <c r="C100" s="135" t="inlineStr">
         <is>
           <t>Gruppe I</t>
         </is>
       </c>
-      <c r="D99" s="134" t="inlineStr">
+      <c r="D100" s="134" t="inlineStr">
         <is>
           <t>AYMEN HUSSEIN</t>
         </is>
       </c>
-      <c r="E99" s="134" t="inlineStr">
+      <c r="E100" s="134" t="inlineStr">
         <is>
           <t>Irak – Norge</t>
         </is>
       </c>
-      <c r="F99" s="135" t="inlineStr">
+      <c r="F100" s="135" t="inlineStr">
         <is>
           <t>90'+6''</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1" s="98">
-      <c r="A100" s="114" t="n">
-        <v>4</v>
-      </c>
-      <c r="B100" s="115" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="C100" s="116" t="inlineStr">
-        <is>
-          <t>Gruppe J</t>
-        </is>
-      </c>
-      <c r="D100" s="115" t="inlineStr">
-        <is>
-          <t>YAZAN ALARAB</t>
-        </is>
-      </c>
-      <c r="E100" s="115" t="inlineStr">
-        <is>
-          <t>Østerrike – Jordan</t>
-        </is>
-      </c>
-      <c r="F100" s="116" t="inlineStr">
-        <is>
-          <t>76''</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1" s="98">
       <c r="A101" s="111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B101" s="112" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C101" s="113" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D101" s="112" t="inlineStr">
         <is>
-          <t>Damian BOBADILLA</t>
+          <t>YAZAN ALARAB</t>
         </is>
       </c>
       <c r="E101" s="112" t="inlineStr">
         <is>
-          <t>USA – Paraguay</t>
+          <t>Østerrike – Jordan</t>
         </is>
       </c>
       <c r="F101" s="113" t="inlineStr">
         <is>
-          <t>7''</t>
+          <t>76''</t>
         </is>
       </c>
     </row>
     <row r="102" ht="16" customHeight="1" s="98">
       <c r="A102" s="114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B102" s="115" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C102" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D102" s="115" t="inlineStr">
         <is>
-          <t>MOHAMED MANAI</t>
+          <t>Damian BOBADILLA</t>
         </is>
       </c>
       <c r="E102" s="115" t="inlineStr">
         <is>
-          <t>Canada – Qatar</t>
+          <t>USA – Paraguay</t>
         </is>
       </c>
       <c r="F102" s="116" t="inlineStr">
         <is>
-          <t>75''</t>
+          <t>7''</t>
         </is>
       </c>
     </row>
     <row r="103" ht="16" customHeight="1" s="98">
       <c r="A103" s="111" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B103" s="112" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C103" s="113" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D103" s="112" t="inlineStr">
         <is>
-          <t>HASSAN ALTAMBAKTI</t>
+          <t>MOHAMED MANAI</t>
         </is>
       </c>
       <c r="E103" s="112" t="inlineStr">
         <is>
-          <t>Spania – Saudi-Arabia</t>
+          <t>Canada – Qatar</t>
         </is>
       </c>
       <c r="F103" s="113" t="inlineStr">
         <is>
-          <t>49''</t>
+          <t>75''</t>
         </is>
       </c>
     </row>
     <row r="104" ht="16" customHeight="1" s="98">
       <c r="A104" s="114" t="n">
+        <v>7</v>
+      </c>
+      <c r="B104" s="115" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C104" s="116" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="D104" s="115" t="inlineStr">
+        <is>
+          <t>HASSAN ALTAMBAKTI</t>
+        </is>
+      </c>
+      <c r="E104" s="115" t="inlineStr">
+        <is>
+          <t>Spania – Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="F104" s="116" t="inlineStr">
+        <is>
+          <t>49''</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1" s="98">
+      <c r="A105" s="111" t="n">
         <v>8</v>
       </c>
-      <c r="B104" s="115" t="inlineStr">
+      <c r="B105" s="112" t="inlineStr">
         <is>
           <t>Sveits</t>
         </is>
       </c>
-      <c r="C104" s="116" t="inlineStr">
+      <c r="C105" s="113" t="inlineStr">
         <is>
           <t>Gruppe B</t>
         </is>
       </c>
-      <c r="D104" s="115" t="inlineStr">
+      <c r="D105" s="112" t="inlineStr">
         <is>
           <t>Miro MUHEIM</t>
         </is>
       </c>
-      <c r="E104" s="115" t="inlineStr">
+      <c r="E105" s="112" t="inlineStr">
         <is>
           <t>Qatar – Sveits</t>
         </is>
       </c>
-      <c r="F104" s="116" t="inlineStr">
+      <c r="F105" s="113" t="inlineStr">
         <is>
           <t>90'+4''</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="26" customHeight="1" s="98">
-      <c r="A106" s="105" t="inlineStr">
+    <row r="107" ht="26" customHeight="1" s="98">
+      <c r="A107" s="105" t="inlineStr">
         <is>
           <t>VM 2026 — Skudd per lag</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="18" customHeight="1" s="98">
-      <c r="A107" s="106" t="inlineStr">
+    <row r="108" ht="18" customHeight="1" s="98">
+      <c r="A108" s="106" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B107" s="107" t="inlineStr">
+      <c r="B108" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="C107" s="106" t="inlineStr">
+      <c r="C108" s="106" t="inlineStr">
         <is>
           <t>Gruppe</t>
         </is>
       </c>
-      <c r="D107" s="106" t="inlineStr">
+      <c r="D108" s="106" t="inlineStr">
         <is>
           <t>Kamper</t>
         </is>
       </c>
-      <c r="E107" s="106" t="inlineStr">
+      <c r="E108" s="106" t="inlineStr">
         <is>
           <t>Skudd</t>
         </is>
       </c>
-      <c r="F107" s="106" t="inlineStr">
+      <c r="F108" s="106" t="inlineStr">
         <is>
           <t>Skudd/kamp</t>
         </is>
       </c>
-      <c r="G107" s="106" t="inlineStr">
+      <c r="G108" s="106" t="inlineStr">
         <is>
           <t>På mål</t>
         </is>
       </c>
-      <c r="H107" s="106" t="inlineStr">
+      <c r="H108" s="106" t="inlineStr">
         <is>
           <t>Treff%</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="16" customHeight="1" s="98">
-      <c r="A108" s="125" t="n">
-        <v>1</v>
-      </c>
-      <c r="B108" s="126" t="inlineStr">
+    <row r="109" ht="16" customHeight="1" s="98">
+      <c r="A109" s="125" t="n">
+        <v>1</v>
+      </c>
+      <c r="B109" s="126" t="inlineStr">
         <is>
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="C108" s="127" t="inlineStr">
+      <c r="C109" s="127" t="inlineStr">
         <is>
           <t>Gruppe D</t>
         </is>
       </c>
-      <c r="D108" s="127" t="n">
+      <c r="D109" s="127" t="n">
         <v>2</v>
       </c>
-      <c r="E108" s="127" t="n">
+      <c r="E109" s="127" t="n">
         <v>62</v>
       </c>
-      <c r="F108" s="127" t="inlineStr">
+      <c r="F109" s="127" t="inlineStr">
         <is>
           <t>31,0</t>
         </is>
       </c>
-      <c r="G108" s="127" t="n">
+      <c r="G109" s="127" t="n">
         <v>12</v>
       </c>
-      <c r="H108" s="127" t="inlineStr">
+      <c r="H109" s="127" t="inlineStr">
         <is>
           <t>19%</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1" s="98">
-      <c r="A109" s="130" t="n">
+    <row r="110" ht="16" customHeight="1" s="98">
+      <c r="A110" s="130" t="n">
         <v>2</v>
       </c>
-      <c r="B109" s="131" t="inlineStr">
+      <c r="B110" s="131" t="inlineStr">
         <is>
           <t>Spania</t>
         </is>
       </c>
-      <c r="C109" s="132" t="inlineStr">
+      <c r="C110" s="132" t="inlineStr">
         <is>
           <t>Gruppe H</t>
         </is>
       </c>
-      <c r="D109" s="132" t="n">
+      <c r="D110" s="132" t="n">
         <v>2</v>
       </c>
-      <c r="E109" s="132" t="n">
+      <c r="E110" s="132" t="n">
         <v>49</v>
       </c>
-      <c r="F109" s="132" t="inlineStr">
+      <c r="F110" s="132" t="inlineStr">
         <is>
           <t>24,5</t>
         </is>
       </c>
-      <c r="G109" s="132" t="n">
+      <c r="G110" s="132" t="n">
         <v>15</v>
       </c>
-      <c r="H109" s="132" t="inlineStr">
+      <c r="H110" s="132" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="16" customHeight="1" s="98">
-      <c r="A110" s="133" t="n">
+    <row r="111" ht="16" customHeight="1" s="98">
+      <c r="A111" s="133" t="n">
         <v>3</v>
       </c>
-      <c r="B110" s="134" t="inlineStr">
+      <c r="B111" s="134" t="inlineStr">
         <is>
           <t>Canada</t>
         </is>
       </c>
-      <c r="C110" s="135" t="inlineStr">
+      <c r="C111" s="135" t="inlineStr">
         <is>
           <t>Gruppe B</t>
         </is>
       </c>
-      <c r="D110" s="135" t="n">
+      <c r="D111" s="135" t="n">
         <v>2</v>
       </c>
-      <c r="E110" s="135" t="n">
+      <c r="E111" s="135" t="n">
         <v>46</v>
       </c>
-      <c r="F110" s="135" t="inlineStr">
+      <c r="F111" s="135" t="inlineStr">
         <is>
           <t>23,0</t>
         </is>
       </c>
-      <c r="G110" s="135" t="n">
+      <c r="G111" s="135" t="n">
         <v>15</v>
       </c>
-      <c r="H110" s="135" t="inlineStr">
+      <c r="H111" s="135" t="inlineStr">
         <is>
           <t>33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1" s="98">
-      <c r="A111" s="111" t="n">
-        <v>4</v>
-      </c>
-      <c r="B111" s="112" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="C111" s="113" t="inlineStr">
-        <is>
-          <t>Gruppe H</t>
-        </is>
-      </c>
-      <c r="D111" s="113" t="n">
-        <v>2</v>
-      </c>
-      <c r="E111" s="113" t="n">
-        <v>44</v>
-      </c>
-      <c r="F111" s="113" t="inlineStr">
-        <is>
-          <t>22,0</t>
-        </is>
-      </c>
-      <c r="G111" s="113" t="n">
-        <v>12</v>
-      </c>
-      <c r="H111" s="113" t="inlineStr">
-        <is>
-          <t>27%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1" s="98">
       <c r="A112" s="114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B112" s="115" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C112" s="116" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D112" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E112" s="116" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F112" s="116" t="inlineStr">
         <is>
-          <t>21,0</t>
+          <t>22,0</t>
         </is>
       </c>
       <c r="G112" s="116" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="H112" s="116" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1" s="98">
       <c r="A113" s="111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B113" s="112" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="C113" s="113" t="inlineStr">
@@ -48532,19 +48644,19 @@
         <v>2</v>
       </c>
       <c r="E113" s="113" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F113" s="113" t="inlineStr">
         <is>
-          <t>19,5</t>
+          <t>21,0</t>
         </is>
       </c>
       <c r="G113" s="113" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H113" s="113" t="inlineStr">
         <is>
-          <t>41%</t>
+          <t>45%</t>
         </is>
       </c>
     </row>
@@ -48554,12 +48666,12 @@
       </c>
       <c r="B114" s="115" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C114" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D114" s="116" t="n">
@@ -48574,55 +48686,55 @@
         </is>
       </c>
       <c r="G114" s="116" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H114" s="116" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>41%</t>
         </is>
       </c>
     </row>
     <row r="115" ht="16" customHeight="1" s="98">
       <c r="A115" s="111" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B115" s="112" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>Sveits</t>
         </is>
       </c>
       <c r="C115" s="113" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D115" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E115" s="113" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F115" s="113" t="inlineStr">
         <is>
-          <t>19,0</t>
+          <t>19,5</t>
         </is>
       </c>
       <c r="G115" s="113" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H115" s="113" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
     <row r="116" ht="16" customHeight="1" s="98">
       <c r="A116" s="114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B116" s="115" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="C116" s="116" t="inlineStr">
@@ -48634,87 +48746,87 @@
         <v>2</v>
       </c>
       <c r="E116" s="116" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F116" s="116" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>19,0</t>
         </is>
       </c>
       <c r="G116" s="116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H116" s="116" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
     <row r="117" ht="16" customHeight="1" s="98">
       <c r="A117" s="111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B117" s="112" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C117" s="113" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D117" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E117" s="113" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F117" s="113" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="G117" s="113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H117" s="113" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
     <row r="118" ht="16" customHeight="1" s="98">
       <c r="A118" s="114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B118" s="115" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C118" s="116" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D118" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E118" s="116" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F118" s="116" t="inlineStr">
         <is>
-          <t>13,0</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="G118" s="116" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H118" s="116" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>52%</t>
         </is>
       </c>
     </row>
@@ -48724,12 +48836,12 @@
       </c>
       <c r="B119" s="112" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C119" s="113" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D119" s="113" t="n">
@@ -48744,79 +48856,79 @@
         </is>
       </c>
       <c r="G119" s="113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H119" s="113" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
     <row r="120" ht="16" customHeight="1" s="98">
       <c r="A120" s="114" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B120" s="115" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="C120" s="116" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D120" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E120" s="116" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F120" s="116" t="inlineStr">
         <is>
-          <t>12,5</t>
+          <t>13,0</t>
         </is>
       </c>
       <c r="G120" s="116" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H120" s="116" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1" s="98">
       <c r="A121" s="111" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B121" s="112" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C121" s="113" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D121" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E121" s="113" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F121" s="113" t="inlineStr">
         <is>
-          <t>12,0</t>
+          <t>12,5</t>
         </is>
       </c>
       <c r="G121" s="113" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H121" s="113" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>52%</t>
         </is>
       </c>
     </row>
@@ -48826,7 +48938,7 @@
       </c>
       <c r="B122" s="115" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="C122" s="116" t="inlineStr">
@@ -48860,12 +48972,12 @@
       </c>
       <c r="B123" s="112" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C123" s="113" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D123" s="113" t="n">
@@ -48880,11 +48992,11 @@
         </is>
       </c>
       <c r="G123" s="113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H123" s="113" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>
@@ -48894,12 +49006,12 @@
       </c>
       <c r="B124" s="115" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C124" s="116" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D124" s="116" t="n">
@@ -48914,45 +49026,45 @@
         </is>
       </c>
       <c r="G124" s="116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H124" s="116" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
     <row r="125" ht="16" customHeight="1" s="98">
       <c r="A125" s="111" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B125" s="112" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="C125" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D125" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" s="113" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F125" s="113" t="inlineStr">
         <is>
-          <t>22,0</t>
+          <t>12,0</t>
         </is>
       </c>
       <c r="G125" s="113" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H125" s="113" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -48962,12 +49074,12 @@
       </c>
       <c r="B126" s="115" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C126" s="116" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D126" s="116" t="n">
@@ -48982,79 +49094,79 @@
         </is>
       </c>
       <c r="G126" s="116" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H126" s="116" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="127" ht="16" customHeight="1" s="98">
       <c r="A127" s="111" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B127" s="112" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C127" s="113" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D127" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" s="113" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F127" s="113" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>22,0</t>
         </is>
       </c>
       <c r="G127" s="113" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H127" s="113" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
     <row r="128" ht="16" customHeight="1" s="98">
       <c r="A128" s="114" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B128" s="115" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C128" s="116" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D128" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E128" s="116" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F128" s="116" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>11,0</t>
         </is>
       </c>
       <c r="G128" s="116" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H128" s="116" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>23%</t>
         </is>
       </c>
     </row>
@@ -49064,7 +49176,7 @@
       </c>
       <c r="B129" s="112" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Tsjekkia</t>
         </is>
       </c>
       <c r="C129" s="113" t="inlineStr">
@@ -49076,79 +49188,79 @@
         <v>2</v>
       </c>
       <c r="E129" s="113" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F129" s="113" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>10,5</t>
         </is>
       </c>
       <c r="G129" s="113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H129" s="113" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>
     <row r="130" ht="16" customHeight="1" s="98">
       <c r="A130" s="114" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B130" s="115" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="C130" s="116" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D130" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E130" s="116" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F130" s="116" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="G130" s="116" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H130" s="116" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>65%</t>
         </is>
       </c>
     </row>
     <row r="131" ht="16" customHeight="1" s="98">
       <c r="A131" s="111" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B131" s="112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
       <c r="C131" s="113" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D131" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E131" s="113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F131" s="113" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="G131" s="113" t="n">
@@ -49156,90 +49268,90 @@
       </c>
       <c r="H131" s="113" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1" s="98">
       <c r="A132" s="114" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B132" s="115" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="C132" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D132" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" s="116" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F132" s="116" t="inlineStr">
         <is>
-          <t>18,0</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="G132" s="116" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H132" s="116" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>47%</t>
         </is>
       </c>
     </row>
     <row r="133" ht="16" customHeight="1" s="98">
       <c r="A133" s="111" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B133" s="112" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C133" s="113" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D133" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E133" s="113" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F133" s="113" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="G133" s="113" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H133" s="113" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>32%</t>
         </is>
       </c>
     </row>
     <row r="134" ht="16" customHeight="1" s="98">
       <c r="A134" s="114" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B134" s="115" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
       <c r="C134" s="116" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D134" s="116" t="n">
@@ -49264,41 +49376,41 @@
     </row>
     <row r="135" ht="16" customHeight="1" s="98">
       <c r="A135" s="111" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B135" s="112" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C135" s="113" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D135" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E135" s="113" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F135" s="113" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="G135" s="113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H135" s="113" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>28%</t>
         </is>
       </c>
     </row>
     <row r="136" ht="16" customHeight="1" s="98">
       <c r="A136" s="114" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B136" s="115" t="inlineStr">
         <is>
@@ -49311,14 +49423,14 @@
         </is>
       </c>
       <c r="D136" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" s="116" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F136" s="116" t="inlineStr">
         <is>
-          <t>15,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G136" s="116" t="n">
@@ -49326,135 +49438,135 @@
       </c>
       <c r="H136" s="116" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1" s="98">
       <c r="A137" s="111" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B137" s="112" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C137" s="113" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D137" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" s="113" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F137" s="113" t="inlineStr">
         <is>
-          <t>15,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G137" s="113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H137" s="113" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
     <row r="138" ht="16" customHeight="1" s="98">
       <c r="A138" s="114" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B138" s="115" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C138" s="116" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D138" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138" s="116" t="n">
         <v>15</v>
       </c>
       <c r="F138" s="116" t="inlineStr">
         <is>
-          <t>7,5</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="G138" s="116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H138" s="116" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
     <row r="139" ht="16" customHeight="1" s="98">
       <c r="A139" s="111" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B139" s="112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C139" s="113" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D139" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E139" s="113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F139" s="113" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="G139" s="113" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H139" s="113" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>13%</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1" s="98">
       <c r="A140" s="114" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B140" s="115" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C140" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D140" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E140" s="116" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F140" s="116" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="G140" s="116" t="n">
@@ -49462,41 +49574,41 @@
       </c>
       <c r="H140" s="116" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
     <row r="141" ht="16" customHeight="1" s="98">
       <c r="A141" s="111" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B141" s="112" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="C141" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D141" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" s="113" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F141" s="113" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="G141" s="113" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H141" s="113" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -49506,7 +49618,7 @@
       </c>
       <c r="B142" s="115" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C142" s="116" t="inlineStr">
@@ -49526,11 +49638,11 @@
         </is>
       </c>
       <c r="G142" s="116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H142" s="116" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -49540,12 +49652,12 @@
       </c>
       <c r="B143" s="112" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C143" s="113" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D143" s="113" t="n">
@@ -49560,11 +49672,11 @@
         </is>
       </c>
       <c r="G143" s="113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H143" s="113" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
     </row>
@@ -49574,12 +49686,12 @@
       </c>
       <c r="B144" s="115" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C144" s="116" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D144" s="116" t="n">
@@ -49608,12 +49720,12 @@
       </c>
       <c r="B145" s="112" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C145" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D145" s="113" t="n">
@@ -49628,45 +49740,45 @@
         </is>
       </c>
       <c r="G145" s="113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H145" s="113" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
     <row r="146" ht="16" customHeight="1" s="98">
       <c r="A146" s="114" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B146" s="115" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="C146" s="116" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D146" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E146" s="116" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F146" s="116" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>11,0</t>
         </is>
       </c>
       <c r="G146" s="116" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H146" s="116" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>9%</t>
         </is>
       </c>
     </row>
@@ -49676,23 +49788,23 @@
       </c>
       <c r="B147" s="112" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Kroatia</t>
         </is>
       </c>
       <c r="C147" s="113" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D147" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" s="113" t="n">
         <v>10</v>
       </c>
       <c r="F147" s="113" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="G147" s="113" t="n">
@@ -49706,35 +49818,35 @@
     </row>
     <row r="148" ht="16" customHeight="1" s="98">
       <c r="A148" s="114" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B148" s="115" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
       <c r="C148" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D148" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E148" s="116" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F148" s="116" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G148" s="116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H148" s="116" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -49744,31 +49856,31 @@
       </c>
       <c r="B149" s="112" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C149" s="113" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D149" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" s="113" t="n">
         <v>8</v>
       </c>
       <c r="F149" s="113" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G149" s="113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H149" s="113" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>38%</t>
         </is>
       </c>
     </row>
@@ -49778,7 +49890,7 @@
       </c>
       <c r="B150" s="115" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Usbekistan</t>
         </is>
       </c>
       <c r="C150" s="116" t="inlineStr">
@@ -49812,23 +49924,23 @@
       </c>
       <c r="B151" s="112" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>DR Kongo</t>
         </is>
       </c>
       <c r="C151" s="113" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D151" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" s="113" t="n">
         <v>8</v>
       </c>
       <c r="F151" s="113" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G151" s="113" t="n">
@@ -49842,27 +49954,27 @@
     </row>
     <row r="152" ht="16" customHeight="1" s="98">
       <c r="A152" s="114" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B152" s="115" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C152" s="116" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D152" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" s="116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F152" s="116" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G152" s="116" t="n">
@@ -49870,7 +49982,7 @@
       </c>
       <c r="H152" s="116" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>
@@ -49880,12 +49992,12 @@
       </c>
       <c r="B153" s="112" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C153" s="113" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D153" s="113" t="n">
@@ -49900,11 +50012,11 @@
         </is>
       </c>
       <c r="G153" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H153" s="113" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
@@ -49914,12 +50026,12 @@
       </c>
       <c r="B154" s="115" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C154" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D154" s="116" t="n">
@@ -49944,102 +50056,113 @@
     </row>
     <row r="155" ht="16" customHeight="1" s="98">
       <c r="A155" s="111" t="n">
+        <v>45</v>
+      </c>
+      <c r="B155" s="112" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+      <c r="C155" s="113" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="D155" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" s="113" t="n">
+        <v>7</v>
+      </c>
+      <c r="F155" s="113" t="inlineStr">
+        <is>
+          <t>7,0</t>
+        </is>
+      </c>
+      <c r="G155" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" s="113" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1" s="98">
+      <c r="A156" s="114" t="n">
         <v>48</v>
       </c>
-      <c r="B155" s="112" t="inlineStr">
+      <c r="B156" s="115" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C155" s="113" t="inlineStr">
+      <c r="C156" s="116" t="inlineStr">
         <is>
           <t>Gruppe I</t>
         </is>
       </c>
-      <c r="D155" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" s="113" t="n">
+      <c r="D156" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" s="116" t="n">
         <v>6</v>
       </c>
-      <c r="F155" s="113" t="inlineStr">
+      <c r="F156" s="116" t="inlineStr">
         <is>
           <t>6,0</t>
         </is>
       </c>
-      <c r="G155" s="113" t="n">
+      <c r="G156" s="116" t="n">
         <v>2</v>
       </c>
-      <c r="H155" s="113" t="inlineStr">
+      <c r="H156" s="116" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="26" customHeight="1" s="98">
-      <c r="A157" s="105" t="inlineStr">
+    <row r="158" ht="26" customHeight="1" s="98">
+      <c r="A158" s="105" t="inlineStr">
         <is>
           <t>VM 2026 — Formasjoner per lag</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="18" customHeight="1" s="98">
-      <c r="A158" s="106" t="inlineStr">
+    <row r="159" ht="18" customHeight="1" s="98">
+      <c r="A159" s="106" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B158" s="107" t="inlineStr">
+      <c r="B159" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="C158" s="106" t="inlineStr">
+      <c r="C159" s="106" t="inlineStr">
         <is>
           <t>Gruppe</t>
         </is>
       </c>
-      <c r="D158" s="106" t="inlineStr">
+      <c r="D159" s="106" t="inlineStr">
         <is>
           <t>Kamper</t>
         </is>
       </c>
-      <c r="E158" s="107" t="inlineStr">
+      <c r="E159" s="107" t="inlineStr">
         <is>
           <t>Formasjon(er)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="16" customHeight="1" s="98">
-      <c r="A159" s="111" t="n">
-        <v>1</v>
-      </c>
-      <c r="B159" s="112" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="C159" s="113" t="inlineStr">
-        <is>
-          <t>Gruppe F</t>
-        </is>
-      </c>
-      <c r="D159" s="113" t="n">
-        <v>2</v>
-      </c>
-      <c r="E159" s="112" t="inlineStr">
-        <is>
-          <t>3-4-1-2 · 3-5-2</t>
         </is>
       </c>
     </row>
     <row r="160" ht="16" customHeight="1" s="98">
       <c r="A160" s="114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B160" s="115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C160" s="116" t="inlineStr">
@@ -50052,7 +50175,7 @@
       </c>
       <c r="E160" s="115" t="inlineStr">
         <is>
-          <t>3-4-3 (x2)</t>
+          <t>3-4-1-2 · 3-5-2</t>
         </is>
       </c>
     </row>
@@ -50062,20 +50185,20 @@
       </c>
       <c r="B161" s="112" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C161" s="113" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D161" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" s="112" t="inlineStr">
         <is>
-          <t>3-4-3</t>
+          <t>3-4-3 (x2)</t>
         </is>
       </c>
     </row>
@@ -50085,12 +50208,12 @@
       </c>
       <c r="B162" s="115" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C162" s="116" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D162" s="116" t="n">
@@ -50108,7 +50231,7 @@
       </c>
       <c r="B163" s="112" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Kroatia</t>
         </is>
       </c>
       <c r="C163" s="113" t="inlineStr">
@@ -50131,20 +50254,20 @@
       </c>
       <c r="B164" s="115" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C164" s="116" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D164" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" s="115" t="inlineStr">
         <is>
-          <t>3-4-3 (x2)</t>
+          <t>3-4-3</t>
         </is>
       </c>
     </row>
@@ -50154,12 +50277,12 @@
       </c>
       <c r="B165" s="112" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="C165" s="113" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D165" s="113" t="n">
@@ -50167,7 +50290,7 @@
       </c>
       <c r="E165" s="112" t="inlineStr">
         <is>
-          <t>3-4-3 · 4-2-3-1</t>
+          <t>3-4-3 (x2)</t>
         </is>
       </c>
     </row>
@@ -50177,30 +50300,30 @@
       </c>
       <c r="B166" s="115" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="C166" s="116" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D166" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" s="115" t="inlineStr">
         <is>
-          <t>3-4-3</t>
+          <t>3-4-3 · 4-2-3-1</t>
         </is>
       </c>
     </row>
     <row r="167" ht="16" customHeight="1" s="98">
       <c r="A167" s="111" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B167" s="112" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Usbekistan</t>
         </is>
       </c>
       <c r="C167" s="113" t="inlineStr">
@@ -50213,7 +50336,7 @@
       </c>
       <c r="E167" s="112" t="inlineStr">
         <is>
-          <t>4-1-2-3</t>
+          <t>3-4-3</t>
         </is>
       </c>
     </row>
@@ -50223,20 +50346,20 @@
       </c>
       <c r="B168" s="115" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C168" s="116" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D168" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168" s="115" t="inlineStr">
         <is>
-          <t>4-1-2-3 · 5-3-2</t>
+          <t>4-1-2-3</t>
         </is>
       </c>
     </row>
@@ -50246,20 +50369,20 @@
       </c>
       <c r="B169" s="112" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C169" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D169" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" s="112" t="inlineStr">
         <is>
-          <t>4-1-2-3</t>
+          <t>4-1-2-3 · 5-3-2</t>
         </is>
       </c>
     </row>
@@ -50269,20 +50392,20 @@
       </c>
       <c r="B170" s="115" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C170" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D170" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E170" s="115" t="inlineStr">
         <is>
-          <t>4-1-2-3 (x2)</t>
+          <t>4-1-2-3</t>
         </is>
       </c>
     </row>
@@ -50292,12 +50415,12 @@
       </c>
       <c r="B171" s="112" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
       <c r="C171" s="113" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D171" s="113" t="n">
@@ -50315,12 +50438,12 @@
       </c>
       <c r="B172" s="115" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C172" s="116" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D172" s="116" t="n">
@@ -50328,7 +50451,7 @@
       </c>
       <c r="E172" s="115" t="inlineStr">
         <is>
-          <t>4-1-2-3 · 4-3-3</t>
+          <t>4-1-2-3 (x2)</t>
         </is>
       </c>
     </row>
@@ -50338,20 +50461,20 @@
       </c>
       <c r="B173" s="112" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="C173" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D173" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" s="112" t="inlineStr">
         <is>
-          <t>4-1-2-3</t>
+          <t>4-1-2-3 · 4-3-3</t>
         </is>
       </c>
     </row>
@@ -50361,35 +50484,35 @@
       </c>
       <c r="B174" s="115" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C174" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D174" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E174" s="115" t="inlineStr">
         <is>
-          <t>4-1-2-3 (x2)</t>
+          <t>4-1-2-3</t>
         </is>
       </c>
     </row>
     <row r="175" ht="16" customHeight="1" s="98">
       <c r="A175" s="111" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B175" s="112" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>Spania</t>
         </is>
       </c>
       <c r="C175" s="113" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D175" s="113" t="n">
@@ -50397,7 +50520,7 @@
       </c>
       <c r="E175" s="112" t="inlineStr">
         <is>
-          <t>4-2-3-1 (x2)</t>
+          <t>4-1-2-3 (x2)</t>
         </is>
       </c>
     </row>
@@ -50407,7 +50530,7 @@
       </c>
       <c r="B176" s="115" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="C176" s="116" t="inlineStr">
@@ -50430,20 +50553,20 @@
       </c>
       <c r="B177" s="112" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C177" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D177" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" s="112" t="inlineStr">
         <is>
-          <t>4-2-3-1</t>
+          <t>4-2-3-1 (x2)</t>
         </is>
       </c>
     </row>
@@ -50453,12 +50576,12 @@
       </c>
       <c r="B178" s="115" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C178" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D178" s="116" t="n">
@@ -50476,20 +50599,20 @@
       </c>
       <c r="B179" s="112" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C179" s="113" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D179" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E179" s="112" t="inlineStr">
         <is>
-          <t>4-2-3-1 (x2)</t>
+          <t>4-2-3-1</t>
         </is>
       </c>
     </row>
@@ -50499,20 +50622,20 @@
       </c>
       <c r="B180" s="115" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="C180" s="116" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D180" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" s="115" t="inlineStr">
         <is>
-          <t>4-2-3-1</t>
+          <t>4-2-3-1 (x2)</t>
         </is>
       </c>
     </row>
@@ -50522,20 +50645,20 @@
       </c>
       <c r="B181" s="112" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C181" s="113" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D181" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E181" s="112" t="inlineStr">
         <is>
-          <t>4-2-3-1 · 4-3-3</t>
+          <t>4-2-3-1</t>
         </is>
       </c>
     </row>
@@ -50545,12 +50668,12 @@
       </c>
       <c r="B182" s="115" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C182" s="116" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D182" s="116" t="n">
@@ -50558,7 +50681,7 @@
       </c>
       <c r="E182" s="115" t="inlineStr">
         <is>
-          <t>4-2-3-1 (x2)</t>
+          <t>4-2-3-1 · 4-3-3</t>
         </is>
       </c>
     </row>
@@ -50568,7 +50691,7 @@
       </c>
       <c r="B183" s="112" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Tyrkia</t>
         </is>
       </c>
       <c r="C183" s="113" t="inlineStr">
@@ -50581,7 +50704,7 @@
       </c>
       <c r="E183" s="112" t="inlineStr">
         <is>
-          <t>4-2-3-1 · 3-5-2</t>
+          <t>4-2-3-1 (x2)</t>
         </is>
       </c>
     </row>
@@ -50591,30 +50714,30 @@
       </c>
       <c r="B184" s="115" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C184" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D184" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" s="115" t="inlineStr">
         <is>
-          <t>4-2-3-1</t>
+          <t>4-2-3-1 · 3-5-2</t>
         </is>
       </c>
     </row>
     <row r="185" ht="16" customHeight="1" s="98">
       <c r="A185" s="111" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B185" s="112" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="C185" s="113" t="inlineStr">
@@ -50623,11 +50746,11 @@
         </is>
       </c>
       <c r="D185" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" s="112" t="inlineStr">
         <is>
-          <t>4-3-3</t>
+          <t>4-2-3-1 (x2)</t>
         </is>
       </c>
     </row>
@@ -50637,7 +50760,7 @@
       </c>
       <c r="B186" s="115" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Algerie</t>
         </is>
       </c>
       <c r="C186" s="116" t="inlineStr">
@@ -50660,12 +50783,12 @@
       </c>
       <c r="B187" s="112" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C187" s="113" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D187" s="113" t="n">
@@ -50673,7 +50796,7 @@
       </c>
       <c r="E187" s="112" t="inlineStr">
         <is>
-          <t>4-3-3 · 5-2-3</t>
+          <t>4-3-3 · 4-1-3-2</t>
         </is>
       </c>
     </row>
@@ -50683,20 +50806,20 @@
       </c>
       <c r="B188" s="115" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C188" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D188" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" s="115" t="inlineStr">
         <is>
-          <t>4-3-3</t>
+          <t>4-3-3 · 5-2-3</t>
         </is>
       </c>
     </row>
@@ -50706,30 +50829,30 @@
       </c>
       <c r="B189" s="112" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C189" s="113" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D189" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189" s="112" t="inlineStr">
         <is>
-          <t>4-3-3 (x2)</t>
+          <t>4-3-3</t>
         </is>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1" s="98">
       <c r="A190" s="114" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B190" s="115" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Sveits</t>
         </is>
       </c>
       <c r="C190" s="116" t="inlineStr">
@@ -50742,7 +50865,7 @@
       </c>
       <c r="E190" s="115" t="inlineStr">
         <is>
-          <t>4-4-2 (x2)</t>
+          <t>4-3-3 (x2)</t>
         </is>
       </c>
     </row>
@@ -50752,12 +50875,12 @@
       </c>
       <c r="B191" s="112" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="C191" s="113" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D191" s="113" t="n">
@@ -50765,7 +50888,7 @@
       </c>
       <c r="E191" s="112" t="inlineStr">
         <is>
-          <t>4-4-2 · 4-3-3</t>
+          <t>4-4-2 (x2)</t>
         </is>
       </c>
     </row>
@@ -50775,12 +50898,12 @@
       </c>
       <c r="B192" s="115" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="C192" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D192" s="116" t="n">
@@ -50788,7 +50911,7 @@
       </c>
       <c r="E192" s="115" t="inlineStr">
         <is>
-          <t>4-4-2 (x2)</t>
+          <t>4-4-2 · 4-3-3</t>
         </is>
       </c>
     </row>
@@ -50798,12 +50921,12 @@
       </c>
       <c r="B193" s="112" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C193" s="113" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D193" s="113" t="n">
@@ -50811,7 +50934,7 @@
       </c>
       <c r="E193" s="112" t="inlineStr">
         <is>
-          <t>4-4-2 · 3-5-2</t>
+          <t>4-4-2 (x2)</t>
         </is>
       </c>
     </row>
@@ -50821,7 +50944,7 @@
       </c>
       <c r="B194" s="115" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C194" s="116" t="inlineStr">
@@ -50834,7 +50957,7 @@
       </c>
       <c r="E194" s="115" t="inlineStr">
         <is>
-          <t>4-4-2 · 4-1-2-3</t>
+          <t>4-4-2 · 3-5-2</t>
         </is>
       </c>
     </row>
@@ -50844,12 +50967,12 @@
       </c>
       <c r="B195" s="112" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="C195" s="113" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D195" s="113" t="n">
@@ -50857,7 +50980,7 @@
       </c>
       <c r="E195" s="112" t="inlineStr">
         <is>
-          <t>4-4-2 · 5-4-1</t>
+          <t>4-4-2 · 4-1-2-3</t>
         </is>
       </c>
     </row>
@@ -50867,20 +50990,20 @@
       </c>
       <c r="B196" s="115" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C196" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D196" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" s="115" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-4-2 · 5-4-1</t>
         </is>
       </c>
     </row>
@@ -50890,20 +51013,20 @@
       </c>
       <c r="B197" s="112" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="C197" s="113" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D197" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E197" s="112" t="inlineStr">
         <is>
-          <t>4-4-2 (x2)</t>
+          <t>4-4-2</t>
         </is>
       </c>
     </row>
@@ -50913,12 +51036,12 @@
       </c>
       <c r="B198" s="115" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C198" s="116" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D198" s="116" t="n">
@@ -50926,7 +51049,7 @@
       </c>
       <c r="E198" s="115" t="inlineStr">
         <is>
-          <t>4-4-2 · 4-2-3-1</t>
+          <t>4-4-2 (x2)</t>
         </is>
       </c>
     </row>
@@ -50936,12 +51059,12 @@
       </c>
       <c r="B199" s="112" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C199" s="113" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D199" s="113" t="n">
@@ -50949,7 +51072,7 @@
       </c>
       <c r="E199" s="112" t="inlineStr">
         <is>
-          <t>4-4-2 · 5-4-1</t>
+          <t>4-4-2 · 4-2-3-1</t>
         </is>
       </c>
     </row>
@@ -50959,12 +51082,12 @@
       </c>
       <c r="B200" s="115" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
       <c r="C200" s="116" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D200" s="116" t="n">
@@ -50972,7 +51095,7 @@
       </c>
       <c r="E200" s="115" t="inlineStr">
         <is>
-          <t>4-4-2 (x2)</t>
+          <t>4-4-2 · 5-4-1</t>
         </is>
       </c>
     </row>
@@ -50982,12 +51105,12 @@
       </c>
       <c r="B201" s="112" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C201" s="113" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D201" s="113" t="n">
@@ -50995,22 +51118,22 @@
       </c>
       <c r="E201" s="112" t="inlineStr">
         <is>
-          <t>4-4-2 · 4-1-2-3</t>
+          <t>4-4-2 (x2)</t>
         </is>
       </c>
     </row>
     <row r="202" ht="16" customHeight="1" s="98">
       <c r="A202" s="114" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B202" s="115" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C202" s="116" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D202" s="116" t="n">
@@ -51018,30 +51141,30 @@
       </c>
       <c r="E202" s="115" t="inlineStr">
         <is>
-          <t>5-2-3 · 3-5-2</t>
+          <t>4-4-2 · 4-1-2-3</t>
         </is>
       </c>
     </row>
     <row r="203" ht="16" customHeight="1" s="98">
       <c r="A203" s="111" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B203" s="112" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Tsjekkia</t>
         </is>
       </c>
       <c r="C203" s="113" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D203" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" s="112" t="inlineStr">
         <is>
-          <t>5-3-2</t>
+          <t>5-2-3 · 3-5-2</t>
         </is>
       </c>
     </row>
@@ -51051,20 +51174,20 @@
       </c>
       <c r="B204" s="115" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>DR Kongo</t>
         </is>
       </c>
       <c r="C204" s="116" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D204" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E204" s="115" t="inlineStr">
         <is>
-          <t>5-3-2 · 4-3-3</t>
+          <t>5-3-2</t>
         </is>
       </c>
     </row>
@@ -51074,12 +51197,12 @@
       </c>
       <c r="B205" s="112" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
       <c r="C205" s="113" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D205" s="113" t="n">
@@ -51087,22 +51210,22 @@
       </c>
       <c r="E205" s="112" t="inlineStr">
         <is>
-          <t>5-3-2 (x2)</t>
+          <t>5-3-2 · 4-3-3</t>
         </is>
       </c>
     </row>
     <row r="206" ht="16" customHeight="1" s="98">
       <c r="A206" s="114" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B206" s="115" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C206" s="116" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D206" s="116" t="n">
@@ -51110,98 +51233,85 @@
       </c>
       <c r="E206" s="115" t="inlineStr">
         <is>
+          <t>5-3-2 (x2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="16" customHeight="1" s="98">
+      <c r="A207" s="111" t="n">
+        <v>48</v>
+      </c>
+      <c r="B207" s="112" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C207" s="113" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="D207" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="E207" s="112" t="inlineStr">
+        <is>
           <t>5-4-1 (x2)</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="26" customHeight="1" s="98">
-      <c r="A208" s="105" t="inlineStr">
+    <row r="209" ht="26" customHeight="1" s="98">
+      <c r="A209" s="105" t="inlineStr">
         <is>
           <t>VM 2026 — Spillerbytte-timing (sortert etter snitt-minutt)</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="18" customHeight="1" s="98">
-      <c r="A209" s="106" t="inlineStr">
+    <row r="210" ht="18" customHeight="1" s="98">
+      <c r="A210" s="106" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B209" s="107" t="inlineStr">
+      <c r="B210" s="107" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="C209" s="106" t="inlineStr">
+      <c r="C210" s="106" t="inlineStr">
         <is>
           <t>Gruppe</t>
         </is>
       </c>
-      <c r="D209" s="106" t="inlineStr">
+      <c r="D210" s="106" t="inlineStr">
         <is>
           <t>Kamper</t>
         </is>
       </c>
-      <c r="E209" s="106" t="inlineStr">
+      <c r="E210" s="106" t="inlineStr">
         <is>
           <t>Bytter</t>
         </is>
       </c>
-      <c r="F209" s="106" t="inlineStr">
+      <c r="F210" s="106" t="inlineStr">
         <is>
           <t>B/kamp</t>
         </is>
       </c>
-      <c r="G209" s="106" t="inlineStr">
+      <c r="G210" s="106" t="inlineStr">
         <is>
           <t>Snitt-min</t>
         </is>
       </c>
-      <c r="H209" s="106" t="inlineStr">
+      <c r="H210" s="106" t="inlineStr">
         <is>
           <t>Tidligst</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="16" customHeight="1" s="98">
-      <c r="A210" s="114" t="n">
-        <v>1</v>
-      </c>
-      <c r="B210" s="115" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C210" s="116" t="inlineStr">
-        <is>
-          <t>Gruppe J</t>
-        </is>
-      </c>
-      <c r="D210" s="116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E210" s="116" t="n">
-        <v>4</v>
-      </c>
-      <c r="F210" s="116" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="G210" s="116" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H210" s="116" t="inlineStr">
-        <is>
-          <t>59'</t>
         </is>
       </c>
     </row>
     <row r="211" ht="16" customHeight="1" s="98">
       <c r="A211" s="111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B211" s="112" t="inlineStr">
         <is>
@@ -51237,7 +51347,7 @@
     </row>
     <row r="212" ht="16" customHeight="1" s="98">
       <c r="A212" s="114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B212" s="115" t="inlineStr">
         <is>
@@ -51273,7 +51383,7 @@
     </row>
     <row r="213" ht="16" customHeight="1" s="98">
       <c r="A213" s="111" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B213" s="112" t="inlineStr">
         <is>
@@ -51309,7 +51419,7 @@
     </row>
     <row r="214" ht="16" customHeight="1" s="98">
       <c r="A214" s="114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B214" s="115" t="inlineStr">
         <is>
@@ -51345,27 +51455,27 @@
     </row>
     <row r="215" ht="16" customHeight="1" s="98">
       <c r="A215" s="111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B215" s="112" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="C215" s="113" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D215" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E215" s="113" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F215" s="113" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G215" s="113" t="inlineStr">
@@ -51375,29 +51485,29 @@
       </c>
       <c r="H215" s="113" t="inlineStr">
         <is>
-          <t>55'</t>
+          <t>56'</t>
         </is>
       </c>
     </row>
     <row r="216" ht="16" customHeight="1" s="98">
       <c r="A216" s="114" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B216" s="115" t="inlineStr">
         <is>
-          <t>Belgia</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="C216" s="116" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D216" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E216" s="116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F216" s="116" t="inlineStr">
         <is>
@@ -51411,49 +51521,49 @@
       </c>
       <c r="H216" s="116" t="inlineStr">
         <is>
-          <t>56'</t>
+          <t>59'</t>
         </is>
       </c>
     </row>
     <row r="217" ht="16" customHeight="1" s="98">
       <c r="A217" s="111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B217" s="112" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C217" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D217" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" s="113" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F217" s="113" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="G217" s="113" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H217" s="113" t="inlineStr">
         <is>
-          <t>59'</t>
+          <t>55'</t>
         </is>
       </c>
     </row>
     <row r="218" ht="16" customHeight="1" s="98">
       <c r="A218" s="114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B218" s="115" t="inlineStr">
         <is>
@@ -51489,16 +51599,16 @@
     </row>
     <row r="219" ht="16" customHeight="1" s="98">
       <c r="A219" s="111" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B219" s="112" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="C219" s="113" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D219" s="113" t="n">
@@ -51514,38 +51624,38 @@
       </c>
       <c r="G219" s="113" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H219" s="113" t="inlineStr">
         <is>
-          <t>60'</t>
+          <t>59'</t>
         </is>
       </c>
     </row>
     <row r="220" ht="16" customHeight="1" s="98">
       <c r="A220" s="114" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B220" s="115" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Tyskland</t>
         </is>
       </c>
       <c r="C220" s="116" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D220" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E220" s="116" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F220" s="116" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="G220" s="116" t="inlineStr">
@@ -51555,17 +51665,17 @@
       </c>
       <c r="H220" s="116" t="inlineStr">
         <is>
-          <t>56'</t>
+          <t>60'</t>
         </is>
       </c>
     </row>
     <row r="221" ht="16" customHeight="1" s="98">
       <c r="A221" s="111" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B221" s="112" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
       <c r="C221" s="113" t="inlineStr">
@@ -51577,11 +51687,11 @@
         <v>2</v>
       </c>
       <c r="E221" s="113" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F221" s="113" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G221" s="113" t="inlineStr">
@@ -51591,33 +51701,33 @@
       </c>
       <c r="H221" s="113" t="inlineStr">
         <is>
-          <t>57'</t>
+          <t>56'</t>
         </is>
       </c>
     </row>
     <row r="222" ht="16" customHeight="1" s="98">
       <c r="A222" s="114" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B222" s="115" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
       <c r="C222" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D222" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E222" s="116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F222" s="116" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G222" s="116" t="inlineStr">
@@ -51627,33 +51737,33 @@
       </c>
       <c r="H222" s="116" t="inlineStr">
         <is>
-          <t>56'</t>
+          <t>57'</t>
         </is>
       </c>
     </row>
     <row r="223" ht="16" customHeight="1" s="98">
       <c r="A223" s="111" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B223" s="112" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C223" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D223" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E223" s="113" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F223" s="113" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="G223" s="113" t="inlineStr">
@@ -51663,69 +51773,69 @@
       </c>
       <c r="H223" s="113" t="inlineStr">
         <is>
-          <t>58'</t>
+          <t>56'</t>
         </is>
       </c>
     </row>
     <row r="224" ht="16" customHeight="1" s="98">
       <c r="A224" s="114" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B224" s="115" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C224" s="116" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D224" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E224" s="116" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F224" s="116" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G224" s="116" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="H224" s="116" t="inlineStr">
         <is>
-          <t>53'</t>
+          <t>58'</t>
         </is>
       </c>
     </row>
     <row r="225" ht="16" customHeight="1" s="98">
       <c r="A225" s="111" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B225" s="112" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C225" s="113" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D225" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E225" s="113" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F225" s="113" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G225" s="113" t="inlineStr">
@@ -51735,33 +51845,33 @@
       </c>
       <c r="H225" s="113" t="inlineStr">
         <is>
-          <t>64'</t>
+          <t>53'</t>
         </is>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1" s="98">
       <c r="A226" s="114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B226" s="115" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Algerie</t>
         </is>
       </c>
       <c r="C226" s="116" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D226" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E226" s="116" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F226" s="116" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G226" s="116" t="inlineStr">
@@ -51771,22 +51881,22 @@
       </c>
       <c r="H226" s="116" t="inlineStr">
         <is>
-          <t>56'</t>
+          <t>64'</t>
         </is>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1" s="98">
       <c r="A227" s="111" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B227" s="112" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C227" s="113" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D227" s="113" t="n">
@@ -51802,38 +51912,38 @@
       </c>
       <c r="G227" s="113" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H227" s="113" t="inlineStr">
         <is>
-          <t>61'</t>
+          <t>56'</t>
         </is>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1" s="98">
       <c r="A228" s="114" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B228" s="115" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Spania</t>
         </is>
       </c>
       <c r="C228" s="116" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D228" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E228" s="116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F228" s="116" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G228" s="116" t="inlineStr">
@@ -51849,27 +51959,27 @@
     </row>
     <row r="229" ht="16" customHeight="1" s="98">
       <c r="A229" s="111" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B229" s="112" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C229" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D229" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" s="113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F229" s="113" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G229" s="113" t="inlineStr">
@@ -51879,53 +51989,53 @@
       </c>
       <c r="H229" s="113" t="inlineStr">
         <is>
-          <t>63'</t>
+          <t>61'</t>
         </is>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1" s="98">
       <c r="A230" s="114" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B230" s="115" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C230" s="116" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D230" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E230" s="116" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F230" s="116" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G230" s="116" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>72</t>
         </is>
       </c>
       <c r="H230" s="116" t="inlineStr">
         <is>
-          <t>59'</t>
+          <t>63'</t>
         </is>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1" s="98">
       <c r="A231" s="111" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B231" s="112" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="C231" s="113" t="inlineStr">
@@ -51937,11 +52047,11 @@
         <v>2</v>
       </c>
       <c r="E231" s="113" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F231" s="113" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="G231" s="113" t="inlineStr">
@@ -51951,33 +52061,33 @@
       </c>
       <c r="H231" s="113" t="inlineStr">
         <is>
-          <t>55'</t>
+          <t>59'</t>
         </is>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1" s="98">
       <c r="A232" s="114" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B232" s="115" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C232" s="116" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D232" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E232" s="116" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F232" s="116" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G232" s="116" t="inlineStr">
@@ -51987,17 +52097,17 @@
       </c>
       <c r="H232" s="116" t="inlineStr">
         <is>
-          <t>60'</t>
+          <t>55'</t>
         </is>
       </c>
     </row>
     <row r="233" ht="16" customHeight="1" s="98">
       <c r="A233" s="111" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B233" s="112" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Tyrkia</t>
         </is>
       </c>
       <c r="C233" s="113" t="inlineStr">
@@ -52009,11 +52119,11 @@
         <v>2</v>
       </c>
       <c r="E233" s="113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F233" s="113" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G233" s="113" t="inlineStr">
@@ -52023,38 +52133,38 @@
       </c>
       <c r="H233" s="113" t="inlineStr">
         <is>
-          <t>61'</t>
+          <t>60'</t>
         </is>
       </c>
     </row>
     <row r="234" ht="16" customHeight="1" s="98">
       <c r="A234" s="114" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B234" s="115" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C234" s="116" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D234" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E234" s="116" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F234" s="116" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G234" s="116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="H234" s="116" t="inlineStr">
@@ -52065,23 +52175,23 @@
     </row>
     <row r="235" ht="16" customHeight="1" s="98">
       <c r="A235" s="111" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B235" s="112" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="C235" s="113" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D235" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E235" s="113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F235" s="113" t="inlineStr">
         <is>
@@ -52090,34 +52200,34 @@
       </c>
       <c r="G235" s="113" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
       <c r="H235" s="113" t="inlineStr">
         <is>
-          <t>73'</t>
+          <t>61'</t>
         </is>
       </c>
     </row>
     <row r="236" ht="16" customHeight="1" s="98">
       <c r="A236" s="114" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B236" s="115" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C236" s="116" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D236" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E236" s="116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F236" s="116" t="inlineStr">
         <is>
@@ -52131,22 +52241,22 @@
       </c>
       <c r="H236" s="116" t="inlineStr">
         <is>
-          <t>56'</t>
+          <t>73'</t>
         </is>
       </c>
     </row>
     <row r="237" ht="16" customHeight="1" s="98">
       <c r="A237" s="111" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B237" s="112" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="C237" s="113" t="inlineStr">
         <is>
-          <t>Gruppe A</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D237" s="113" t="n">
@@ -52167,29 +52277,29 @@
       </c>
       <c r="H237" s="113" t="inlineStr">
         <is>
-          <t>66'</t>
+          <t>56'</t>
         </is>
       </c>
     </row>
     <row r="238" ht="16" customHeight="1" s="98">
       <c r="A238" s="114" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B238" s="115" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C238" s="116" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe A</t>
         </is>
       </c>
       <c r="D238" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E238" s="116" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F238" s="116" t="inlineStr">
         <is>
@@ -52203,17 +52313,17 @@
       </c>
       <c r="H238" s="116" t="inlineStr">
         <is>
-          <t>57'</t>
+          <t>66'</t>
         </is>
       </c>
     </row>
     <row r="239" ht="16" customHeight="1" s="98">
       <c r="A239" s="111" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B239" s="112" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>DR Kongo</t>
         </is>
       </c>
       <c r="C239" s="113" t="inlineStr">
@@ -52225,47 +52335,47 @@
         <v>1</v>
       </c>
       <c r="E239" s="113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F239" s="113" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G239" s="113" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H239" s="113" t="inlineStr">
         <is>
-          <t>72'</t>
+          <t>57'</t>
         </is>
       </c>
     </row>
     <row r="240" ht="16" customHeight="1" s="98">
       <c r="A240" s="114" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B240" s="115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C240" s="116" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D240" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E240" s="116" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F240" s="116" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G240" s="116" t="inlineStr">
@@ -52275,29 +52385,29 @@
       </c>
       <c r="H240" s="116" t="inlineStr">
         <is>
-          <t>66'</t>
+          <t>72'</t>
         </is>
       </c>
     </row>
     <row r="241" ht="16" customHeight="1" s="98">
       <c r="A241" s="111" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B241" s="112" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C241" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D241" s="113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E241" s="113" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F241" s="113" t="inlineStr">
         <is>
@@ -52311,29 +52421,29 @@
       </c>
       <c r="H241" s="113" t="inlineStr">
         <is>
-          <t>72'</t>
+          <t>66'</t>
         </is>
       </c>
     </row>
     <row r="242" ht="16" customHeight="1" s="98">
       <c r="A242" s="114" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B242" s="115" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C242" s="116" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D242" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" s="116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F242" s="116" t="inlineStr">
         <is>
@@ -52342,38 +52452,38 @@
       </c>
       <c r="G242" s="116" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>76</t>
         </is>
       </c>
       <c r="H242" s="116" t="inlineStr">
         <is>
-          <t>60'</t>
+          <t>72'</t>
         </is>
       </c>
     </row>
     <row r="243" ht="16" customHeight="1" s="98">
       <c r="A243" s="111" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B243" s="112" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C243" s="113" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D243" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E243" s="113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F243" s="113" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G243" s="113" t="inlineStr">
@@ -52383,33 +52493,33 @@
       </c>
       <c r="H243" s="113" t="inlineStr">
         <is>
-          <t>65'</t>
+          <t>60'</t>
         </is>
       </c>
     </row>
     <row r="244" ht="16" customHeight="1" s="98">
       <c r="A244" s="114" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B244" s="115" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C244" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D244" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E244" s="116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F244" s="116" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>3,5</t>
         </is>
       </c>
       <c r="G244" s="116" t="inlineStr">
@@ -52419,69 +52529,69 @@
       </c>
       <c r="H244" s="116" t="inlineStr">
         <is>
-          <t>70'</t>
+          <t>65'</t>
         </is>
       </c>
     </row>
     <row r="245" ht="16" customHeight="1" s="98">
       <c r="A245" s="111" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B245" s="112" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C245" s="113" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D245" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E245" s="113" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F245" s="113" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G245" s="113" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>77</t>
         </is>
       </c>
       <c r="H245" s="113" t="inlineStr">
         <is>
-          <t>65'</t>
+          <t>70'</t>
         </is>
       </c>
     </row>
     <row r="246" ht="16" customHeight="1" s="98">
       <c r="A246" s="114" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B246" s="115" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sveits</t>
         </is>
       </c>
       <c r="C246" s="116" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D246" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E246" s="116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F246" s="116" t="inlineStr">
         <is>
-          <t>5,5</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G246" s="116" t="inlineStr">
@@ -52491,33 +52601,33 @@
       </c>
       <c r="H246" s="116" t="inlineStr">
         <is>
-          <t>41'</t>
+          <t>65'</t>
         </is>
       </c>
     </row>
     <row r="247" ht="16" customHeight="1" s="98">
       <c r="A247" s="111" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B247" s="112" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C247" s="113" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D247" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E247" s="113" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F247" s="113" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>5,5</t>
         </is>
       </c>
       <c r="G247" s="113" t="inlineStr">
@@ -52527,33 +52637,33 @@
       </c>
       <c r="H247" s="113" t="inlineStr">
         <is>
-          <t>64'</t>
+          <t>41'</t>
         </is>
       </c>
     </row>
     <row r="248" ht="16" customHeight="1" s="98">
       <c r="A248" s="114" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B248" s="115" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C248" s="116" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D248" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E248" s="116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F248" s="116" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G248" s="116" t="inlineStr">
@@ -52563,58 +52673,58 @@
       </c>
       <c r="H248" s="116" t="inlineStr">
         <is>
-          <t>66'</t>
+          <t>64'</t>
         </is>
       </c>
     </row>
     <row r="249" ht="16" customHeight="1" s="98">
       <c r="A249" s="111" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B249" s="112" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="C249" s="113" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D249" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E249" s="113" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F249" s="113" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G249" s="113" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>78</t>
         </is>
       </c>
       <c r="H249" s="113" t="inlineStr">
         <is>
-          <t>62'</t>
+          <t>66'</t>
         </is>
       </c>
     </row>
     <row r="250" ht="16" customHeight="1" s="98">
       <c r="A250" s="114" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B250" s="115" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C250" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D250" s="116" t="n">
@@ -52635,141 +52745,141 @@
       </c>
       <c r="H250" s="116" t="inlineStr">
         <is>
-          <t>60'</t>
+          <t>62'</t>
         </is>
       </c>
     </row>
     <row r="251" ht="16" customHeight="1" s="98">
       <c r="A251" s="111" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B251" s="112" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
       <c r="C251" s="113" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D251" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E251" s="113" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F251" s="113" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G251" s="113" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H251" s="113" t="inlineStr">
         <is>
-          <t>64'</t>
+          <t>60'</t>
         </is>
       </c>
     </row>
     <row r="252" ht="16" customHeight="1" s="98">
       <c r="A252" s="114" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B252" s="115" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Marokko</t>
         </is>
       </c>
       <c r="C252" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D252" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E252" s="116" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F252" s="116" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="G252" s="116" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="H252" s="116" t="inlineStr">
         <is>
-          <t>75'</t>
+          <t>64'</t>
         </is>
       </c>
     </row>
     <row r="253" ht="16" customHeight="1" s="98">
       <c r="A253" s="111" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B253" s="112" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C253" s="113" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D253" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E253" s="113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F253" s="113" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G253" s="113" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H253" s="113" t="inlineStr">
         <is>
-          <t>72'</t>
+          <t>75'</t>
         </is>
       </c>
     </row>
     <row r="254" ht="16" customHeight="1" s="98">
       <c r="A254" s="114" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B254" s="115" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C254" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D254" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254" s="116" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F254" s="116" t="inlineStr">
         <is>
-          <t>5,0</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G254" s="116" t="inlineStr">
@@ -52785,27 +52895,27 @@
     </row>
     <row r="255" ht="16" customHeight="1" s="98">
       <c r="A255" s="111" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B255" s="112" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C255" s="113" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D255" s="113" t="n">
         <v>1</v>
       </c>
       <c r="E255" s="113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F255" s="113" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G255" s="113" t="inlineStr">
@@ -52815,77 +52925,113 @@
       </c>
       <c r="H255" s="113" t="inlineStr">
         <is>
-          <t>77'</t>
+          <t>72'</t>
         </is>
       </c>
     </row>
     <row r="256" ht="16" customHeight="1" s="98">
       <c r="A256" s="114" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B256" s="115" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Usbekistan</t>
         </is>
       </c>
       <c r="C256" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D256" s="116" t="n">
         <v>1</v>
       </c>
       <c r="E256" s="116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F256" s="116" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G256" s="116" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H256" s="116" t="inlineStr">
         <is>
-          <t>80'</t>
+          <t>77'</t>
         </is>
       </c>
     </row>
     <row r="257" ht="16" customHeight="1" s="98">
       <c r="A257" s="111" t="n">
+        <v>47</v>
+      </c>
+      <c r="B257" s="112" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C257" s="113" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
+      <c r="D257" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E257" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="F257" s="113" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="G257" s="113" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H257" s="113" t="inlineStr">
+        <is>
+          <t>80'</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="16" customHeight="1" s="98">
+      <c r="A258" s="114" t="n">
         <v>48</v>
       </c>
-      <c r="B257" s="112" t="inlineStr">
+      <c r="B258" s="115" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
-      <c r="C257" s="113" t="inlineStr">
+      <c r="C258" s="116" t="inlineStr">
         <is>
           <t>Gruppe K</t>
         </is>
       </c>
-      <c r="D257" s="113" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" s="113" t="n">
+      <c r="D258" s="116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" s="116" t="n">
         <v>5</v>
       </c>
-      <c r="F257" s="113" t="inlineStr">
+      <c r="F258" s="116" t="inlineStr">
         <is>
           <t>5,0</t>
         </is>
       </c>
-      <c r="G257" s="113" t="inlineStr">
+      <c r="G258" s="116" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="H257" s="113" t="inlineStr">
+      <c r="H258" s="116" t="inlineStr">
         <is>
           <t>72'</t>
         </is>
@@ -52893,15 +53039,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A106:H106"/>
+    <mergeCell ref="A209:H209"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A95:H95"/>
-    <mergeCell ref="A157:H157"/>
+    <mergeCell ref="A96:H96"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A107:H107"/>
     <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A208:H208"/>
+    <mergeCell ref="A158:H158"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52955,7 +53101,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="142" t="n">
-        <v>0.1239669421487603</v>
+        <v>0.1219512195121951</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" s="98">
@@ -52968,7 +53114,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="143" t="n">
-        <v>0.1570247933884298</v>
+        <v>0.1544715447154472</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="98">
@@ -52978,10 +53124,10 @@
         </is>
       </c>
       <c r="B5" s="121" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="142" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1869918699186992</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="98">
@@ -52994,7 +53140,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="143" t="n">
-        <v>0.1322314049586777</v>
+        <v>0.1300813008130081</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1" s="98">
@@ -53007,7 +53153,7 @@
         <v>17</v>
       </c>
       <c r="C7" s="142" t="n">
-        <v>0.140495867768595</v>
+        <v>0.1382113821138211</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="98">
@@ -53017,10 +53163,10 @@
         </is>
       </c>
       <c r="B8" s="122" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="143" t="n">
-        <v>0.2644628099173554</v>
+        <v>0.2682926829268293</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="98">
@@ -53030,7 +53176,7 @@
         </is>
       </c>
       <c r="B9" s="106" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C9" s="106" t="inlineStr"/>
     </row>
@@ -53218,8 +53364,8 @@
         <v>2</v>
       </c>
       <c r="H6" s="147" t="n"/>
-      <c r="I6" s="149" t="n">
-        <v>1</v>
+      <c r="I6" s="148" t="n">
+        <v>2</v>
       </c>
       <c r="J6" s="149" t="n">
         <v>1</v>
@@ -53556,8 +53702,8 @@
       <c r="E17" s="148" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="148" t="n">
-        <v>2</v>
+      <c r="F17" s="150" t="n">
+        <v>3</v>
       </c>
       <c r="G17" s="150" t="n">
         <v>3</v>
@@ -60221,7 +60367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="98" min="1" max="1"/>
@@ -62341,57 +62487,108 @@
         <v>0.9882038692544043</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1" s="98">
-      <c r="A44" s="158" t="inlineStr">
+    <row r="43" ht="18" customHeight="1" s="98">
+      <c r="A43" s="173" t="inlineStr">
+        <is>
+          <t>22.06</t>
+        </is>
+      </c>
+      <c r="B43" s="191" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="C43" s="192" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D43" s="172" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="E43" s="193" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="F43" s="192" t="inlineStr">
+        <is>
+          <t>AT&amp;T Stadium</t>
+        </is>
+      </c>
+      <c r="G43" s="194" t="inlineStr">
+        <is>
+          <t>Arlington / Dallas</t>
+        </is>
+      </c>
+      <c r="H43" s="169" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="I43" s="196" t="n">
+        <v>70649</v>
+      </c>
+      <c r="J43" s="197" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K43" s="204" t="n">
+        <v>0.8831125</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="98">
+      <c r="A45" s="158" t="inlineStr">
         <is>
           <t>Belegg:</t>
         </is>
       </c>
-      <c r="B44" s="208" t="inlineStr">
+      <c r="B45" s="208" t="inlineStr">
         <is>
           <t>≥97% (praktisk utsolgt)</t>
         </is>
       </c>
-      <c r="C44" s="209" t="inlineStr">
+      <c r="C45" s="209" t="inlineStr">
         <is>
           <t>92–96%</t>
         </is>
       </c>
-      <c r="D44" s="210" t="inlineStr">
+      <c r="D45" s="210" t="inlineStr">
         <is>
           <t>87–91%</t>
         </is>
       </c>
-      <c r="E44" s="211" t="inlineStr">
+      <c r="E45" s="211" t="inlineStr">
         <is>
           <t>&lt;87%</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1" s="98">
-      <c r="A45" s="166" t="inlineStr">
+    <row r="46" ht="14" customHeight="1" s="98">
+      <c r="A46" s="166" t="inlineStr">
         <is>
           <t>Kapasitetstall: offisielle arenakapasiteter (ikke FIFA-sertifisert VM-kapasitet som kan avvike noe)</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1" s="98">
-      <c r="A47" s="212" t="inlineStr">
-        <is>
-          <t>Totalt tilskuere: 2 563 003</t>
-        </is>
-      </c>
-      <c r="C47" s="212" t="inlineStr">
-        <is>
-          <t>Snitt belegg: 95.6%</t>
-        </is>
-      </c>
-      <c r="E47" s="212" t="inlineStr">
+    <row r="48" ht="18" customHeight="1" s="98">
+      <c r="A48" s="212" t="inlineStr">
+        <is>
+          <t>Totalt tilskuere: 2 633 652</t>
+        </is>
+      </c>
+      <c r="C48" s="212" t="inlineStr">
+        <is>
+          <t>Snitt belegg: 95.5%</t>
+        </is>
+      </c>
+      <c r="E48" s="212" t="inlineStr">
         <is>
           <t>Høyest: 80 824 (Mexico – Sør-Afrika)</t>
         </is>
       </c>
-      <c r="H47" s="212" t="inlineStr">
+      <c r="H48" s="212" t="inlineStr">
         <is>
           <t>Lavest: 42 942 (Ghana – Panama)</t>
         </is>
@@ -62399,8 +62596,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A45:K45"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A46:K46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -82734,7 +82931,7 @@
       <c r="H120" s="3" t="n"/>
       <c r="I120" s="3" t="n"/>
       <c r="J120" s="137" t="n">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1" s="98">

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -49346,31 +49346,31 @@
       </c>
       <c r="B134" s="115" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C134" s="116" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D134" s="116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" s="116" t="n">
         <v>18</v>
       </c>
       <c r="F134" s="116" t="inlineStr">
         <is>
-          <t>9,0</t>
+          <t>18,0</t>
         </is>
       </c>
       <c r="G134" s="116" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H134" s="116" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -49380,12 +49380,12 @@
       </c>
       <c r="B135" s="112" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
       <c r="C135" s="113" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="D135" s="113" t="n">
@@ -49410,27 +49410,27 @@
     </row>
     <row r="136" ht="16" customHeight="1" s="98">
       <c r="A136" s="114" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B136" s="115" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="C136" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="D136" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E136" s="116" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F136" s="116" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="G136" s="116" t="n">
@@ -49438,22 +49438,22 @@
       </c>
       <c r="H136" s="116" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>28%</t>
         </is>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1" s="98">
       <c r="A137" s="111" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B137" s="112" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Østerrike</t>
         </is>
       </c>
       <c r="C137" s="113" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D137" s="113" t="n">
@@ -49468,113 +49468,113 @@
         </is>
       </c>
       <c r="G137" s="113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H137" s="113" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
     <row r="138" ht="16" customHeight="1" s="98">
       <c r="A138" s="114" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B138" s="115" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C138" s="116" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D138" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" s="116" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F138" s="116" t="inlineStr">
         <is>
-          <t>15,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G138" s="116" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H138" s="116" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>19%</t>
         </is>
       </c>
     </row>
     <row r="139" ht="16" customHeight="1" s="98">
       <c r="A139" s="111" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B139" s="112" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C139" s="113" t="inlineStr">
         <is>
-          <t>Gruppe C</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="D139" s="113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E139" s="113" t="n">
         <v>15</v>
       </c>
       <c r="F139" s="113" t="inlineStr">
         <is>
-          <t>7,5</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="G139" s="113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H139" s="113" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>27%</t>
         </is>
       </c>
     </row>
     <row r="140" ht="16" customHeight="1" s="98">
       <c r="A140" s="114" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B140" s="115" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C140" s="116" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="D140" s="116" t="n">
         <v>2</v>
       </c>
       <c r="E140" s="116" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F140" s="116" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>7,5</t>
         </is>
       </c>
       <c r="G140" s="116" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H140" s="116" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>13%</t>
         </is>
       </c>
     </row>
@@ -49584,23 +49584,23 @@
       </c>
       <c r="B141" s="112" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C141" s="113" t="inlineStr">
         <is>
-          <t>Gruppe B</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="D141" s="113" t="n">
         <v>2</v>
       </c>
       <c r="E141" s="113" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F141" s="113" t="inlineStr">
         <is>
-          <t>6,5</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="G141" s="113" t="n">
@@ -49608,7 +49608,7 @@
       </c>
       <c r="H141" s="113" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -49618,31 +49618,31 @@
       </c>
       <c r="B142" s="115" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
       <c r="C142" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe B</t>
         </is>
       </c>
       <c r="D142" s="116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" s="116" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F142" s="116" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="G142" s="116" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H142" s="116" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -49652,7 +49652,7 @@
       </c>
       <c r="B143" s="112" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="C143" s="113" t="inlineStr">
@@ -49664,34 +49664,34 @@
         <v>1</v>
       </c>
       <c r="E143" s="113" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F143" s="113" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>13,0</t>
         </is>
       </c>
       <c r="G143" s="113" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H143" s="113" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>8%</t>
         </is>
       </c>
     </row>
     <row r="144" ht="16" customHeight="1" s="98">
       <c r="A144" s="114" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B144" s="115" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Norge</t>
         </is>
       </c>
       <c r="C144" s="116" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D144" s="116" t="n">
@@ -49706,26 +49706,26 @@
         </is>
       </c>
       <c r="G144" s="116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H144" s="116" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>45%</t>
         </is>
       </c>
     </row>
     <row r="145" ht="16" customHeight="1" s="98">
       <c r="A145" s="111" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B145" s="112" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C145" s="113" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="D145" s="113" t="n">
@@ -49750,16 +49750,16 @@
     </row>
     <row r="146" ht="16" customHeight="1" s="98">
       <c r="A146" s="114" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B146" s="115" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C146" s="116" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D146" s="116" t="n">
@@ -49774,11 +49774,11 @@
         </is>
       </c>
       <c r="G146" s="116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H146" s="116" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -54108,7 +54108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="98" min="1" max="1"/>
@@ -55944,68 +55944,64 @@
       <c r="A39" s="178" t="inlineStr"/>
       <c r="B39" s="179" t="inlineStr">
         <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C39" s="171" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D39" s="180" t="n">
-        <v>9</v>
-      </c>
-      <c r="E39" s="180" t="n">
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C39" s="187" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D39" s="181" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" s="181" t="n">
         <v>3</v>
       </c>
       <c r="F39" s="180" t="n">
         <v>4</v>
       </c>
       <c r="G39" s="182" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39" s="183" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>2–0</t>
         </is>
       </c>
       <c r="I39" s="184" t="n">
         <v>3</v>
       </c>
       <c r="J39" s="180" t="n">
-        <v>4</v>
-      </c>
-      <c r="K39" s="181" t="n">
-        <v>4</v>
-      </c>
-      <c r="L39" s="181" t="n">
-        <v>11</v>
-      </c>
-      <c r="M39" s="177" t="n">
-        <v>0.38</v>
+        <v>2</v>
+      </c>
+      <c r="K39" s="180" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="180" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="187" t="n">
+        <v>0.46</v>
       </c>
       <c r="N39" s="179" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Østerrike</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="98">
-      <c r="A40" s="169" t="inlineStr">
-        <is>
-          <t>Gruppe K</t>
-        </is>
-      </c>
+      <c r="A40" s="185" t="inlineStr"/>
       <c r="B40" s="170" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C40" s="186" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D40" s="172" t="n">
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C40" s="171" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D40" s="173" t="n">
         <v>9</v>
       </c>
-      <c r="E40" s="172" t="n">
+      <c r="E40" s="173" t="n">
         <v>3</v>
       </c>
       <c r="F40" s="173" t="n">
@@ -56016,207 +56012,259 @@
       </c>
       <c r="H40" s="175" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I40" s="176" t="n">
         <v>3</v>
       </c>
       <c r="J40" s="173" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" s="172" t="n">
+        <v>4</v>
+      </c>
+      <c r="L40" s="172" t="n">
+        <v>11</v>
+      </c>
+      <c r="M40" s="177" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N40" s="170" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="98">
+      <c r="A41" s="169" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="B41" s="179" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C41" s="186" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D41" s="181" t="n">
+        <v>9</v>
+      </c>
+      <c r="E41" s="181" t="n">
         <v>3</v>
       </c>
-      <c r="K40" s="173" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="173" t="n">
-        <v>8</v>
-      </c>
-      <c r="M40" s="177" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N40" s="170" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="18" customHeight="1" s="98">
-      <c r="A41" s="178" t="inlineStr"/>
-      <c r="B41" s="179" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C41" s="177" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D41" s="180" t="n">
-        <v>7</v>
-      </c>
-      <c r="E41" s="180" t="n">
-        <v>3</v>
-      </c>
       <c r="F41" s="180" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" s="182" t="n">
         <v>2</v>
       </c>
       <c r="H41" s="183" t="inlineStr">
         <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I41" s="184" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" s="180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="180" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" s="180" t="n">
+        <v>8</v>
+      </c>
+      <c r="M41" s="177" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N41" s="179" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="98">
+      <c r="A42" s="185" t="inlineStr"/>
+      <c r="B42" s="170" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C42" s="177" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D42" s="173" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" s="173" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="174" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="175" t="inlineStr">
+        <is>
           <t>1–3</t>
         </is>
       </c>
-      <c r="I41" s="184" t="n">
+      <c r="I42" s="176" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="180" t="n">
+      <c r="J42" s="173" t="n">
         <v>5</v>
       </c>
-      <c r="K41" s="181" t="n">
+      <c r="K42" s="172" t="n">
         <v>6</v>
       </c>
-      <c r="L41" s="181" t="n">
+      <c r="L42" s="172" t="n">
         <v>15</v>
       </c>
-      <c r="M41" s="186" t="n">
+      <c r="M42" s="186" t="n">
         <v>0.67</v>
       </c>
-      <c r="N41" s="179" t="inlineStr">
+      <c r="N42" s="170" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1" s="98">
-      <c r="A42" s="169" t="inlineStr">
+    <row r="43" ht="18" customHeight="1" s="98">
+      <c r="A43" s="169" t="inlineStr">
         <is>
           <t>Gruppe L</t>
         </is>
       </c>
-      <c r="B42" s="170" t="inlineStr">
+      <c r="B43" s="179" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="C42" s="187" t="n">
+      <c r="C43" s="187" t="n">
         <v>0.54</v>
       </c>
-      <c r="D42" s="172" t="n">
+      <c r="D43" s="181" t="n">
         <v>20</v>
       </c>
-      <c r="E42" s="172" t="n">
+      <c r="E43" s="181" t="n">
         <v>12</v>
       </c>
-      <c r="F42" s="173" t="n">
+      <c r="F43" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="174" t="n">
+      <c r="G43" s="182" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="175" t="inlineStr">
+      <c r="H43" s="183" t="inlineStr">
         <is>
           <t>4–2</t>
         </is>
       </c>
-      <c r="I42" s="176" t="n">
+      <c r="I43" s="184" t="n">
         <v>3</v>
       </c>
-      <c r="J42" s="173" t="n">
+      <c r="J43" s="180" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="173" t="n">
+      <c r="K43" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="L42" s="173" t="n">
+      <c r="L43" s="180" t="n">
         <v>11</v>
       </c>
-      <c r="M42" s="187" t="n">
+      <c r="M43" s="187" t="n">
         <v>0.46</v>
       </c>
-      <c r="N42" s="170" t="inlineStr">
+      <c r="N43" s="179" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="18" customHeight="1" s="98">
-      <c r="A43" s="178" t="inlineStr"/>
-      <c r="B43" s="179" t="inlineStr">
+    <row r="44" ht="18" customHeight="1" s="98">
+      <c r="A44" s="185" t="inlineStr"/>
+      <c r="B44" s="170" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C43" s="177" t="n">
+      <c r="C44" s="177" t="n">
         <v>0.37</v>
       </c>
-      <c r="D43" s="180" t="n">
+      <c r="D44" s="173" t="n">
         <v>8</v>
       </c>
-      <c r="E43" s="180" t="n">
+      <c r="E44" s="173" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="180" t="n">
+      <c r="F44" s="173" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="182" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="183" t="inlineStr">
+      <c r="G44" s="174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="175" t="inlineStr">
         <is>
           <t>1–0</t>
         </is>
       </c>
-      <c r="I43" s="184" t="n">
+      <c r="I44" s="176" t="n">
         <v>2</v>
       </c>
-      <c r="J43" s="180" t="n">
+      <c r="J44" s="173" t="n">
         <v>5</v>
       </c>
-      <c r="K43" s="181" t="n">
+      <c r="K44" s="172" t="n">
         <v>4</v>
       </c>
-      <c r="L43" s="181" t="n">
+      <c r="L44" s="172" t="n">
         <v>11</v>
       </c>
-      <c r="M43" s="171" t="n">
+      <c r="M44" s="171" t="n">
         <v>0.63</v>
       </c>
-      <c r="N43" s="179" t="inlineStr">
+      <c r="N44" s="170" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1" s="98">
-      <c r="A45" s="166" t="inlineStr">
+    <row r="46" ht="14" customHeight="1" s="98">
+      <c r="A46" s="166" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="18" customHeight="1" s="98">
-      <c r="A46" s="158" t="inlineStr">
+    <row r="47" ht="18" customHeight="1" s="98">
+      <c r="A47" s="158" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B46" s="165" t="inlineStr">
+      <c r="B47" s="165" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C46" s="164" t="inlineStr">
+      <c r="C47" s="164" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D46" s="161" t="inlineStr">
+      <c r="D47" s="161" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E46" s="188" t="inlineStr">
+      <c r="E47" s="188" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -56224,7 +56272,7 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A46:N46"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:N1"/>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -54415,7 +54415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="98" min="1" max="1"/>
@@ -56151,99 +56151,95 @@
       <c r="A37" s="178" t="inlineStr"/>
       <c r="B37" s="179" t="inlineStr">
         <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C37" s="171" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D37" s="181" t="n">
+        <v>19</v>
+      </c>
+      <c r="E37" s="181" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="180" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" s="182" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="183" t="inlineStr">
+        <is>
+          <t>3–0</t>
+        </is>
+      </c>
+      <c r="I37" s="184" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K37" s="180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="180" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" s="177" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N37" s="179" t="inlineStr">
+        <is>
           <t>Irak</t>
         </is>
       </c>
-      <c r="C37" s="177" t="n">
+    </row>
+    <row r="38" ht="18" customHeight="1" s="98">
+      <c r="A38" s="185" t="inlineStr"/>
+      <c r="B38" s="170" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C38" s="177" t="n">
         <v>0.37</v>
       </c>
-      <c r="D37" s="180" t="n">
+      <c r="D38" s="173" t="n">
         <v>11</v>
       </c>
-      <c r="E37" s="180" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="180" t="n">
+      <c r="E38" s="173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="173" t="n">
         <v>8</v>
       </c>
-      <c r="G37" s="182" t="n">
+      <c r="G38" s="174" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="183" t="inlineStr">
+      <c r="H38" s="175" t="inlineStr">
         <is>
           <t>1–4</t>
         </is>
       </c>
-      <c r="I37" s="184" t="n">
+      <c r="I38" s="176" t="n">
         <v>2</v>
       </c>
-      <c r="J37" s="180" t="n">
+      <c r="J38" s="173" t="n">
         <v>4</v>
       </c>
-      <c r="K37" s="181" t="n">
+      <c r="K38" s="172" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="181" t="n">
+      <c r="L38" s="172" t="n">
         <v>12</v>
       </c>
-      <c r="M37" s="171" t="n">
+      <c r="M38" s="171" t="n">
         <v>0.63</v>
       </c>
-      <c r="N37" s="179" t="inlineStr">
+      <c r="N38" s="170" t="inlineStr">
         <is>
           <t>Norge</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1" s="98">
-      <c r="A38" s="169" t="inlineStr">
-        <is>
-          <t>Gruppe J</t>
-        </is>
-      </c>
-      <c r="B38" s="170" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="C38" s="187" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D38" s="172" t="n">
-        <v>9</v>
-      </c>
-      <c r="E38" s="172" t="n">
-        <v>6</v>
-      </c>
-      <c r="F38" s="173" t="n">
-        <v>3</v>
-      </c>
-      <c r="G38" s="174" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="175" t="inlineStr">
-        <is>
-          <t>3–0</t>
-        </is>
-      </c>
-      <c r="I38" s="176" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="173" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" s="173" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="173" t="n">
-        <v>6</v>
-      </c>
-      <c r="M38" s="187" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N38" s="170" t="inlineStr">
-        <is>
-          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -56251,114 +56247,114 @@
       <c r="A39" s="178" t="inlineStr"/>
       <c r="B39" s="179" t="inlineStr">
         <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C39" s="177" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D39" s="180" t="n">
+        <v>12</v>
+      </c>
+      <c r="E39" s="180" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" s="180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="182" t="n">
+        <v>4</v>
+      </c>
+      <c r="H39" s="183" t="inlineStr">
+        <is>
+          <t>3–2</t>
+        </is>
+      </c>
+      <c r="I39" s="184" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" s="180" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="180" t="n">
+        <v>6</v>
+      </c>
+      <c r="L39" s="181" t="n">
+        <v>17</v>
+      </c>
+      <c r="M39" s="171" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N39" s="179" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="98">
+      <c r="A40" s="169" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="B40" s="170" t="inlineStr">
+        <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="C39" s="187" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D39" s="181" t="n">
-        <v>12</v>
-      </c>
-      <c r="E39" s="181" t="n">
+      <c r="C40" s="187" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D40" s="172" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" s="172" t="n">
+        <v>6</v>
+      </c>
+      <c r="F40" s="173" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="180" t="n">
-        <v>4</v>
-      </c>
-      <c r="G39" s="182" t="n">
-        <v>5</v>
-      </c>
-      <c r="H39" s="183" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I39" s="184" t="n">
-        <v>3</v>
-      </c>
-      <c r="J39" s="180" t="n">
-        <v>2</v>
-      </c>
-      <c r="K39" s="180" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="180" t="n">
-        <v>6</v>
-      </c>
-      <c r="M39" s="187" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N39" s="179" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="18" customHeight="1" s="98">
-      <c r="A40" s="185" t="inlineStr"/>
-      <c r="B40" s="170" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C40" s="171" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D40" s="173" t="n">
-        <v>9</v>
-      </c>
-      <c r="E40" s="173" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="173" t="n">
-        <v>4</v>
-      </c>
       <c r="G40" s="174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H40" s="175" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I40" s="176" t="n">
         <v>3</v>
       </c>
       <c r="J40" s="173" t="n">
-        <v>4</v>
-      </c>
-      <c r="K40" s="172" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" s="172" t="n">
-        <v>11</v>
-      </c>
-      <c r="M40" s="177" t="n">
-        <v>0.38</v>
+        <v>3</v>
+      </c>
+      <c r="K40" s="173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="173" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" s="187" t="n">
+        <v>0.53</v>
       </c>
       <c r="N40" s="170" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="98">
-      <c r="A41" s="169" t="inlineStr">
-        <is>
-          <t>Gruppe K</t>
-        </is>
-      </c>
+      <c r="A41" s="178" t="inlineStr"/>
       <c r="B41" s="179" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C41" s="186" t="n">
-        <v>0.75</v>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C41" s="187" t="n">
+        <v>0.54</v>
       </c>
       <c r="D41" s="181" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E41" s="181" t="n">
         <v>3</v>
@@ -56367,31 +56363,31 @@
         <v>4</v>
       </c>
       <c r="G41" s="182" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H41" s="183" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>2–0</t>
         </is>
       </c>
       <c r="I41" s="184" t="n">
         <v>3</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" s="180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41" s="180" t="n">
-        <v>8</v>
-      </c>
-      <c r="M41" s="177" t="n">
-        <v>0.25</v>
+        <v>6</v>
+      </c>
+      <c r="M41" s="187" t="n">
+        <v>0.46</v>
       </c>
       <c r="N41" s="179" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Østerrike</t>
         </is>
       </c>
     </row>
@@ -56399,179 +56395,327 @@
       <c r="A42" s="185" t="inlineStr"/>
       <c r="B42" s="170" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C42" s="177" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="D42" s="173" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" s="173" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" s="173" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" s="174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="175" t="inlineStr">
+        <is>
+          <t>1–2</t>
+        </is>
+      </c>
+      <c r="I42" s="176" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" s="173" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="173" t="n">
+      <c r="K42" s="172" t="n">
+        <v>8</v>
+      </c>
+      <c r="L42" s="172" t="n">
+        <v>17</v>
+      </c>
+      <c r="M42" s="186" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N42" s="170" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="98">
+      <c r="A43" s="178" t="inlineStr"/>
+      <c r="B43" s="179" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C43" s="171" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D43" s="180" t="n">
+        <v>9</v>
+      </c>
+      <c r="E43" s="180" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="180" t="n">
+        <v>4</v>
+      </c>
+      <c r="G43" s="182" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="174" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="175" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="I42" s="176" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="173" t="n">
-        <v>5</v>
-      </c>
-      <c r="K42" s="172" t="n">
-        <v>6</v>
-      </c>
-      <c r="L42" s="172" t="n">
-        <v>15</v>
-      </c>
-      <c r="M42" s="186" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="N42" s="170" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1" s="98">
-      <c r="A43" s="169" t="inlineStr">
-        <is>
-          <t>Gruppe L</t>
-        </is>
-      </c>
-      <c r="B43" s="179" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C43" s="187" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D43" s="181" t="n">
-        <v>20</v>
-      </c>
-      <c r="E43" s="181" t="n">
-        <v>12</v>
-      </c>
-      <c r="F43" s="180" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" s="182" t="n">
-        <v>5</v>
-      </c>
       <c r="H43" s="183" t="inlineStr">
         <is>
-          <t>4–2</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I43" s="184" t="n">
         <v>3</v>
       </c>
       <c r="J43" s="180" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" s="180" t="n">
-        <v>5</v>
-      </c>
-      <c r="L43" s="180" t="n">
+        <v>4</v>
+      </c>
+      <c r="K43" s="181" t="n">
+        <v>4</v>
+      </c>
+      <c r="L43" s="181" t="n">
         <v>11</v>
       </c>
-      <c r="M43" s="187" t="n">
-        <v>0.46</v>
+      <c r="M43" s="177" t="n">
+        <v>0.38</v>
       </c>
       <c r="N43" s="179" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Jordan</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="98">
-      <c r="A44" s="185" t="inlineStr"/>
+      <c r="A44" s="169" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
       <c r="B44" s="170" t="inlineStr">
         <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C44" s="177" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D44" s="173" t="n">
-        <v>8</v>
-      </c>
-      <c r="E44" s="173" t="n">
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C44" s="186" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D44" s="172" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" s="172" t="n">
         <v>3</v>
       </c>
       <c r="F44" s="173" t="n">
         <v>4</v>
       </c>
       <c r="G44" s="174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="175" t="inlineStr">
         <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I44" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K44" s="173" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" s="173" t="n">
+        <v>8</v>
+      </c>
+      <c r="M44" s="177" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N44" s="170" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="98">
+      <c r="A45" s="178" t="inlineStr"/>
+      <c r="B45" s="179" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C45" s="177" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D45" s="180" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" s="180" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="183" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I45" s="184" t="n">
+        <v>4</v>
+      </c>
+      <c r="J45" s="180" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="181" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" s="181" t="n">
+        <v>15</v>
+      </c>
+      <c r="M45" s="186" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N45" s="179" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="98">
+      <c r="A46" s="169" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="B46" s="170" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C46" s="187" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D46" s="172" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" s="172" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" s="173" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="174" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" s="175" t="inlineStr">
+        <is>
+          <t>4–2</t>
+        </is>
+      </c>
+      <c r="I46" s="176" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" s="173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K46" s="173" t="n">
+        <v>5</v>
+      </c>
+      <c r="L46" s="173" t="n">
+        <v>11</v>
+      </c>
+      <c r="M46" s="187" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N46" s="170" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" s="98">
+      <c r="A47" s="178" t="inlineStr"/>
+      <c r="B47" s="179" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C47" s="177" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D47" s="180" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" s="180" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="180" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="183" t="inlineStr">
+        <is>
           <t>1–0</t>
         </is>
       </c>
-      <c r="I44" s="176" t="n">
+      <c r="I47" s="184" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="173" t="n">
+      <c r="J47" s="180" t="n">
         <v>5</v>
       </c>
-      <c r="K44" s="172" t="n">
+      <c r="K47" s="181" t="n">
         <v>4</v>
       </c>
-      <c r="L44" s="172" t="n">
+      <c r="L47" s="181" t="n">
         <v>11</v>
       </c>
-      <c r="M44" s="171" t="n">
+      <c r="M47" s="171" t="n">
         <v>0.63</v>
       </c>
-      <c r="N44" s="170" t="inlineStr">
+      <c r="N47" s="179" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1" s="98">
-      <c r="A46" s="166" t="inlineStr">
+    <row r="49" ht="14" customHeight="1" s="98">
+      <c r="A49" s="166" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1" s="98">
-      <c r="A47" s="158" t="inlineStr">
+    <row r="50" ht="18" customHeight="1" s="98">
+      <c r="A50" s="158" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B47" s="165" t="inlineStr">
+      <c r="B50" s="165" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C47" s="164" t="inlineStr">
+      <c r="C50" s="164" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D47" s="161" t="inlineStr">
+      <c r="D50" s="161" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E47" s="188" t="inlineStr">
+      <c r="E50" s="188" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -56579,9 +56723,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A46:N46"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:N2"/>
+    <mergeCell ref="A49:N49"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,38 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Kort" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Scorere og assists" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Alder" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Lagstatistikk" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Scoringstidspunkt" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Heatmap" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Ballbesittelse" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Stadionoversikt" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,13 +842,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -867,7 +867,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -891,12 +891,12 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -910,7 +910,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
-        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -923,8 +922,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -938,7 +937,6 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -948,7 +946,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -963,9 +961,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -32407,35 +32405,35 @@
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>30,0</t>
         </is>
       </c>
       <c r="G122" s="14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>40%</t>
         </is>
       </c>
     </row>
@@ -32445,31 +32443,31 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F123" s="15" t="inlineStr">
         <is>
-          <t>28,0</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="G123" s="15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H123" s="15" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>52%</t>
         </is>
       </c>
     </row>
@@ -33635,23 +33633,23 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" s="14" t="n">
         <v>8</v>
       </c>
       <c r="F158" s="14" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G158" s="14" t="n">
@@ -33665,27 +33663,27 @@
     </row>
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C159" s="15" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F159" s="15" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G159" s="15" t="n">
@@ -33693,7 +33691,7 @@
       </c>
       <c r="H159" s="15" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -32343,65 +32343,65 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>England</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" s="14" t="n">
         <v>33</v>
       </c>
       <c r="F120" s="14" t="inlineStr">
         <is>
-          <t>16,5</t>
+          <t>33,0</t>
         </is>
       </c>
       <c r="G120" s="14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
     <row r="121" ht="16" customHeight="1">
       <c r="A121" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t>Frankrike</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C121" s="15" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="D121" s="15" t="n">
         <v>2</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F121" s="15" t="inlineStr">
         <is>
-          <t>15,0</t>
+          <t>16,5</t>
         </is>
       </c>
       <c r="G121" s="15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H121" s="15" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
@@ -32411,31 +32411,31 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E122" s="14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F122" s="14" t="inlineStr">
         <is>
-          <t>14,5</t>
+          <t>15,0</t>
         </is>
       </c>
       <c r="G122" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -32445,31 +32445,31 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C123" s="15" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D123" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F123" s="15" t="inlineStr">
         <is>
-          <t>28,0</t>
+          <t>14,5</t>
         </is>
       </c>
       <c r="G123" s="15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H123" s="15" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>52%</t>
         </is>
       </c>
     </row>
@@ -33635,23 +33635,23 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C158" s="14" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe L</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" s="14" t="n">
         <v>8</v>
       </c>
       <c r="F158" s="14" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>8,0</t>
         </is>
       </c>
       <c r="G158" s="14" t="n">
@@ -33665,27 +33665,27 @@
     </row>
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C159" s="15" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="D159" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F159" s="15" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G159" s="15" t="n">
@@ -33693,7 +33693,7 @@
       </c>
       <c r="H159" s="15" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>25%</t>
         </is>
       </c>
     </row>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -19,8 +19,8 @@
     <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="16-delsfinale" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinale" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
@@ -17742,7 +17742,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>VM 2026 — 16-delsfinale</t>
+          <t>VM 2026 — 16-delsfinaler</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>VM 2026 — 8-delsfinale</t>
+          <t>VM 2026 — 8-delsfinaler</t>
         </is>
       </c>
     </row>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -37689,7 +37689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39769,31 +39769,31 @@
       </c>
       <c r="B44" s="67" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C44" s="83" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="D44" s="69" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="E44" s="69" t="n">
-        <v>3</v>
-      </c>
       <c r="F44" s="70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G44" s="71" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" s="72" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I44" s="73" t="n">
         <v>2</v>
-      </c>
-      <c r="H44" s="72" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I44" s="73" t="n">
-        <v>3</v>
       </c>
       <c r="J44" s="70" t="n">
         <v>3</v>
@@ -39802,10 +39802,10 @@
         <v>2</v>
       </c>
       <c r="L44" s="70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M44" s="74" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="N44" s="67" t="inlineStr">
         <is>
@@ -39821,43 +39821,43 @@
         </is>
       </c>
       <c r="C45" s="83" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="D45" s="78" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E45" s="78" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F45" s="77" t="n">
         <v>4</v>
       </c>
       <c r="G45" s="79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="80" t="inlineStr">
         <is>
-          <t>5–0</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I45" s="81" t="n">
         <v>3</v>
       </c>
       <c r="J45" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="77" t="n">
         <v>2</v>
       </c>
       <c r="L45" s="77" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M45" s="74" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="N45" s="76" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -39865,179 +39865,323 @@
       <c r="A46" s="82" t="inlineStr"/>
       <c r="B46" s="67" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C46" s="83" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D46" s="69" t="n">
+        <v>16</v>
+      </c>
+      <c r="E46" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G46" s="71" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="72" t="inlineStr">
+        <is>
+          <t>5–0</t>
+        </is>
+      </c>
+      <c r="I46" s="73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" s="70" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" s="74" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N46" s="67" t="inlineStr">
+        <is>
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="C46" s="74" t="n">
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="75" t="inlineStr"/>
+      <c r="B47" s="76" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C47" s="74" t="n">
         <v>0.33</v>
       </c>
-      <c r="D46" s="70" t="n">
+      <c r="D47" s="77" t="n">
         <v>7</v>
       </c>
-      <c r="E46" s="70" t="n">
+      <c r="E47" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="F46" s="70" t="n">
+      <c r="F47" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="G46" s="71" t="n">
+      <c r="G47" s="79" t="n">
         <v>2</v>
       </c>
-      <c r="H46" s="72" t="inlineStr">
+      <c r="H47" s="80" t="inlineStr">
         <is>
           <t>1–3</t>
         </is>
       </c>
-      <c r="I46" s="73" t="n">
+      <c r="I47" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="J46" s="70" t="n">
+      <c r="J47" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="K46" s="69" t="n">
+      <c r="K47" s="78" t="n">
         <v>6</v>
       </c>
-      <c r="L46" s="69" t="n">
+      <c r="L47" s="78" t="n">
         <v>15</v>
       </c>
-      <c r="M46" s="83" t="n">
+      <c r="M47" s="83" t="n">
         <v>0.67</v>
       </c>
-      <c r="N46" s="67" t="inlineStr">
+      <c r="N47" s="76" t="inlineStr">
         <is>
           <t>Colombia</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="66" t="inlineStr">
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="66" t="inlineStr">
         <is>
           <t>Gruppe L</t>
         </is>
       </c>
-      <c r="B47" s="76" t="inlineStr">
+      <c r="B48" s="67" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="C47" s="84" t="n">
+      <c r="C48" s="84" t="n">
         <v>0.54</v>
       </c>
-      <c r="D47" s="78" t="n">
+      <c r="D48" s="69" t="n">
         <v>20</v>
       </c>
-      <c r="E47" s="78" t="n">
+      <c r="E48" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="F47" s="77" t="n">
+      <c r="F48" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="G47" s="79" t="n">
+      <c r="G48" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="H47" s="80" t="inlineStr">
+      <c r="H48" s="72" t="inlineStr">
         <is>
           <t>4–2</t>
         </is>
       </c>
-      <c r="I47" s="81" t="n">
+      <c r="I48" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="77" t="n">
+      <c r="J48" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="K47" s="77" t="n">
+      <c r="K48" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="L47" s="77" t="n">
+      <c r="L48" s="70" t="n">
         <v>11</v>
       </c>
-      <c r="M47" s="84" t="n">
+      <c r="M48" s="84" t="n">
         <v>0.46</v>
       </c>
-      <c r="N47" s="76" t="inlineStr">
+      <c r="N48" s="67" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="82" t="inlineStr"/>
-      <c r="B48" s="67" t="inlineStr">
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="75" t="inlineStr"/>
+      <c r="B49" s="76" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C49" s="83" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D49" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E49" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="79" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I49" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M49" s="74" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N49" s="76" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C48" s="74" t="n">
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="82" t="inlineStr"/>
+      <c r="B50" s="67" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C50" s="74" t="n">
         <v>0.37</v>
       </c>
-      <c r="D48" s="70" t="n">
+      <c r="D50" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="E48" s="70" t="n">
+      <c r="E50" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="F48" s="70" t="n">
+      <c r="F50" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="G48" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="72" t="inlineStr">
+      <c r="G50" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="72" t="inlineStr">
         <is>
           <t>1–0</t>
         </is>
       </c>
-      <c r="I48" s="73" t="n">
+      <c r="I50" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="70" t="n">
+      <c r="J50" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="K48" s="69" t="n">
+      <c r="K50" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="L48" s="69" t="n">
+      <c r="L50" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="M48" s="68" t="n">
+      <c r="M50" s="68" t="n">
         <v>0.63</v>
       </c>
-      <c r="N48" s="67" t="inlineStr">
+      <c r="N50" s="67" t="inlineStr">
         <is>
           <t>Panama</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="63" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="75" t="inlineStr"/>
+      <c r="B51" s="76" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C51" s="74" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D51" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="80" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I51" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" s="68" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N51" s="76" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="63" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="55" t="inlineStr">
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="55" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B51" s="62" t="inlineStr">
+      <c r="B54" s="62" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C51" s="61" t="inlineStr">
+      <c r="C54" s="61" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D51" s="58" t="inlineStr">
+      <c r="D54" s="58" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E51" s="85" t="inlineStr">
+      <c r="E54" s="85" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -40045,9 +40189,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A50:N50"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:N2"/>
+    <mergeCell ref="A53:N53"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -37998,7 +37998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -38214,47 +38214,47 @@
       <c r="A6" s="82" t="inlineStr"/>
       <c r="B6" s="67" t="inlineStr">
         <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="C6" s="68" t="n">
-        <v>0.62</v>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="C6" s="74" t="n">
+        <v>0.31</v>
       </c>
       <c r="D6" s="69" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" s="70" t="n">
         <v>5</v>
       </c>
       <c r="G6" s="71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" s="72" t="inlineStr">
         <is>
-          <t>2–1</t>
+          <t>1–0</t>
         </is>
       </c>
       <c r="I6" s="73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" s="70" t="n">
         <v>3</v>
       </c>
       <c r="K6" s="70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L6" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="M6" s="74" t="n">
-        <v>0.38</v>
+        <v>7</v>
+      </c>
+      <c r="M6" s="83" t="n">
+        <v>0.6899999999999999</v>
       </c>
       <c r="N6" s="67" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
+          <t>Sør-Korea</t>
         </is>
       </c>
     </row>
@@ -38262,75 +38262,71 @@
       <c r="A7" s="75" t="inlineStr"/>
       <c r="B7" s="76" t="inlineStr">
         <is>
-          <t>Tsjekkia</t>
-        </is>
-      </c>
-      <c r="C7" s="74" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D7" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E7" s="77" t="n">
-        <v>3</v>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="C7" s="68" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D7" s="78" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="78" t="n">
+        <v>7</v>
       </c>
       <c r="F7" s="77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="79" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="80" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>2–1</t>
         </is>
       </c>
       <c r="I7" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" s="78" t="n">
-        <v>5</v>
-      </c>
-      <c r="L7" s="78" t="n">
-        <v>17</v>
-      </c>
-      <c r="M7" s="68" t="n">
-        <v>0.61</v>
+      <c r="M7" s="74" t="n">
+        <v>0.38</v>
       </c>
       <c r="N7" s="76" t="inlineStr">
         <is>
-          <t>Sør-Afrika</t>
+          <t>Tsjekkia</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe B</t>
-        </is>
-      </c>
+      <c r="A8" s="82" t="inlineStr"/>
       <c r="B8" s="67" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C8" s="68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D8" s="69" t="n">
-        <v>13</v>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="C8" s="74" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D8" s="70" t="n">
+        <v>12</v>
       </c>
       <c r="E8" s="70" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H8" s="72" t="inlineStr">
         <is>
@@ -38338,23 +38334,23 @@
         </is>
       </c>
       <c r="I8" s="73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J8" s="70" t="n">
         <v>4</v>
       </c>
       <c r="K8" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="M8" s="74" t="n">
-        <v>0.4</v>
+        <v>5</v>
+      </c>
+      <c r="L8" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="M8" s="68" t="n">
+        <v>0.61</v>
       </c>
       <c r="N8" s="67" t="inlineStr">
         <is>
-          <t>Bosnia-Hercegovina</t>
+          <t>Sør-Afrika</t>
         </is>
       </c>
     </row>
@@ -38362,95 +38358,99 @@
       <c r="A9" s="75" t="inlineStr"/>
       <c r="B9" s="76" t="inlineStr">
         <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="C9" s="83" t="n">
-        <v>0.78</v>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="C9" s="84" t="n">
+        <v>0.51</v>
       </c>
       <c r="D9" s="78" t="n">
-        <v>31</v>
-      </c>
-      <c r="E9" s="78" t="n">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="E9" s="77" t="n">
+        <v>1</v>
       </c>
       <c r="F9" s="77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" s="79" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H9" s="80" t="inlineStr">
         <is>
-          <t>6–0</t>
+          <t>0–3</t>
         </is>
       </c>
       <c r="I9" s="81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="77" t="n">
+        <v>11</v>
+      </c>
+      <c r="M9" s="84" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N9" s="76" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="C10" s="68" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D10" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="72" t="inlineStr">
+        <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="I10" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="74" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N9" s="76" t="inlineStr">
+      <c r="J10" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="70" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" s="84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N10" s="67" t="inlineStr">
         <is>
           <t>Qatar</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="82" t="inlineStr"/>
-      <c r="B10" s="67" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="C10" s="74" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D10" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="72" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I10" s="73" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="L10" s="69" t="n">
-        <v>27</v>
-      </c>
-      <c r="M10" s="83" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N10" s="67" t="inlineStr">
-        <is>
-          <t>Sveits</t>
         </is>
       </c>
     </row>
@@ -38458,99 +38458,95 @@
       <c r="A11" s="75" t="inlineStr"/>
       <c r="B11" s="76" t="inlineStr">
         <is>
-          <t>Sveits</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C11" s="68" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="D11" s="78" t="n">
         <v>13</v>
       </c>
-      <c r="E11" s="78" t="n">
+      <c r="E11" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="80" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I11" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="F11" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" s="79" t="n">
+      <c r="M11" s="74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N11" s="76" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="82" t="inlineStr"/>
+      <c r="B12" s="67" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C12" s="83" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D12" s="69" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" s="71" t="n">
+        <v>13</v>
+      </c>
+      <c r="H12" s="72" t="inlineStr">
+        <is>
+          <t>6–0</t>
+        </is>
+      </c>
+      <c r="I12" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="80" t="inlineStr">
-        <is>
-          <t>4–1</t>
-        </is>
-      </c>
-      <c r="I11" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="L11" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="74" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N11" s="76" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe C</t>
-        </is>
-      </c>
-      <c r="B12" s="67" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="C12" s="84" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D12" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="E12" s="69" t="n">
-        <v>5</v>
-      </c>
-      <c r="F12" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="72" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I12" s="73" t="n">
-        <v>6</v>
-      </c>
-      <c r="J12" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="M12" s="84" t="n">
-        <v>0.46</v>
+      <c r="M12" s="74" t="n">
+        <v>0.22</v>
       </c>
       <c r="N12" s="67" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Qatar</t>
         </is>
       </c>
     </row>
@@ -38558,47 +38554,47 @@
       <c r="A13" s="75" t="inlineStr"/>
       <c r="B13" s="76" t="inlineStr">
         <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="C13" s="68" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="D13" s="78" t="n">
-        <v>9</v>
-      </c>
-      <c r="E13" s="78" t="n">
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C13" s="74" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D13" s="77" t="n">
         <v>5</v>
+      </c>
+      <c r="E13" s="77" t="n">
+        <v>3</v>
       </c>
       <c r="F13" s="77" t="n">
         <v>2</v>
       </c>
       <c r="G13" s="79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" s="80" t="inlineStr">
         <is>
-          <t>3–0</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I13" s="81" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J13" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K13" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="M13" s="74" t="n">
-        <v>0.43</v>
+      <c r="K13" s="78" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="78" t="n">
+        <v>27</v>
+      </c>
+      <c r="M13" s="83" t="n">
+        <v>0.7</v>
       </c>
       <c r="N13" s="76" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Sveits</t>
         </is>
       </c>
     </row>
@@ -38606,47 +38602,47 @@
       <c r="A14" s="82" t="inlineStr"/>
       <c r="B14" s="67" t="inlineStr">
         <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="C14" s="84" t="n">
-        <v>0.5</v>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="C14" s="68" t="n">
+        <v>0.62</v>
       </c>
       <c r="D14" s="69" t="n">
         <v>13</v>
       </c>
-      <c r="E14" s="70" t="n">
+      <c r="E14" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="70" t="n">
-        <v>7</v>
-      </c>
       <c r="G14" s="71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="72" t="inlineStr">
         <is>
-          <t>0–1</t>
+          <t>4–1</t>
         </is>
       </c>
       <c r="I14" s="73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="70" t="n">
         <v>3</v>
       </c>
       <c r="L14" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="M14" s="84" t="n">
-        <v>0.5</v>
+        <v>4</v>
+      </c>
+      <c r="M14" s="74" t="n">
+        <v>0.38</v>
       </c>
       <c r="N14" s="67" t="inlineStr">
         <is>
-          <t>Skottland</t>
+          <t>Bosnia-Hercegovina</t>
         </is>
       </c>
     </row>
@@ -38654,99 +38650,99 @@
       <c r="A15" s="75" t="inlineStr"/>
       <c r="B15" s="76" t="inlineStr">
         <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="C15" s="74" t="n">
-        <v>0.4</v>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="C15" s="68" t="n">
+        <v>0.55</v>
       </c>
       <c r="D15" s="77" t="n">
         <v>6</v>
       </c>
       <c r="E15" s="77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F15" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="80" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="I15" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="79" t="n">
+      <c r="J15" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="80" t="inlineStr">
-        <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="I15" s="81" t="n">
-        <v>4</v>
-      </c>
-      <c r="J15" s="77" t="n">
-        <v>5</v>
-      </c>
       <c r="K15" s="78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L15" s="78" t="n">
-        <v>12</v>
-      </c>
-      <c r="M15" s="68" t="n">
-        <v>0.6</v>
+        <v>13</v>
+      </c>
+      <c r="M15" s="84" t="n">
+        <v>0.45</v>
       </c>
       <c r="N15" s="76" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Canada</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="66" t="inlineStr">
         <is>
-          <t>Gruppe D</t>
+          <t>Gruppe C</t>
         </is>
       </c>
       <c r="B16" s="67" t="inlineStr">
         <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="C16" s="74" t="n">
-        <v>0.37</v>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C16" s="84" t="n">
+        <v>0.54</v>
       </c>
       <c r="D16" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="E16" s="70" t="n">
+      <c r="E16" s="69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="72" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I16" s="73" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="72" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I16" s="73" t="n">
-        <v>11</v>
-      </c>
-      <c r="J16" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="K16" s="69" t="n">
-        <v>7</v>
-      </c>
       <c r="L16" s="69" t="n">
-        <v>28</v>
-      </c>
-      <c r="M16" s="68" t="n">
-        <v>0.63</v>
+        <v>13</v>
+      </c>
+      <c r="M16" s="84" t="n">
+        <v>0.46</v>
       </c>
       <c r="N16" s="67" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
@@ -38754,27 +38750,27 @@
       <c r="A17" s="75" t="inlineStr"/>
       <c r="B17" s="76" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="C17" s="83" t="n">
-        <v>0.78</v>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C17" s="68" t="n">
+        <v>0.57</v>
       </c>
       <c r="D17" s="78" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E17" s="78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="77" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G17" s="79" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H17" s="80" t="inlineStr">
         <is>
-          <t>0–1</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I17" s="81" t="n">
@@ -38784,17 +38780,17 @@
         <v>2</v>
       </c>
       <c r="K17" s="77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L17" s="77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M17" s="74" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="N17" s="76" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Haiti</t>
         </is>
       </c>
     </row>
@@ -38802,47 +38798,47 @@
       <c r="A18" s="82" t="inlineStr"/>
       <c r="B18" s="67" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C18" s="68" t="n">
-        <v>0.63</v>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C18" s="84" t="n">
+        <v>0.5</v>
       </c>
       <c r="D18" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E18" s="69" t="n">
-        <v>6</v>
+        <v>13</v>
+      </c>
+      <c r="E18" s="70" t="n">
+        <v>3</v>
       </c>
       <c r="F18" s="70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H18" s="72" t="inlineStr">
         <is>
-          <t>4–1</t>
+          <t>0–1</t>
         </is>
       </c>
       <c r="I18" s="73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18" s="70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" s="70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="M18" s="74" t="n">
-        <v>0.37</v>
+      <c r="M18" s="84" t="n">
+        <v>0.5</v>
       </c>
       <c r="N18" s="67" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Skottland</t>
         </is>
       </c>
     </row>
@@ -38850,99 +38846,99 @@
       <c r="A19" s="75" t="inlineStr"/>
       <c r="B19" s="76" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C19" s="68" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D19" s="78" t="n">
-        <v>8</v>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="C19" s="74" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D19" s="77" t="n">
+        <v>6</v>
       </c>
       <c r="E19" s="77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="80" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I19" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="77" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="80" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I19" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="77" t="n">
+      <c r="K19" s="78" t="n">
         <v>3</v>
       </c>
-      <c r="K19" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" s="74" t="n">
-        <v>0.37</v>
+      <c r="L19" s="78" t="n">
+        <v>12</v>
+      </c>
+      <c r="M19" s="68" t="n">
+        <v>0.6</v>
       </c>
       <c r="N19" s="76" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="66" t="inlineStr">
         <is>
-          <t>Gruppe E</t>
+          <t>Gruppe D</t>
         </is>
       </c>
       <c r="B20" s="67" t="inlineStr">
         <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="C20" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D20" s="69" t="n">
-        <v>26</v>
-      </c>
-      <c r="E20" s="69" t="n">
-        <v>15</v>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C20" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D20" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E20" s="70" t="n">
+        <v>4</v>
       </c>
       <c r="F20" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="72" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I20" s="73" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="G20" s="71" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="72" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I20" s="73" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" s="70" t="n">
-        <v>10</v>
-      </c>
-      <c r="M20" s="74" t="n">
-        <v>0.25</v>
+      <c r="L20" s="69" t="n">
+        <v>28</v>
+      </c>
+      <c r="M20" s="68" t="n">
+        <v>0.63</v>
       </c>
       <c r="N20" s="67" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Tyrkia</t>
         </is>
       </c>
     </row>
@@ -38950,47 +38946,47 @@
       <c r="A21" s="75" t="inlineStr"/>
       <c r="B21" s="76" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="C21" s="84" t="n">
-        <v>0.49</v>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="C21" s="83" t="n">
+        <v>0.78</v>
       </c>
       <c r="D21" s="78" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="E21" s="78" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F21" s="77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G21" s="79" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H21" s="80" t="inlineStr">
         <is>
-          <t>1–0</t>
+          <t>0–1</t>
         </is>
       </c>
       <c r="I21" s="81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="77" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K21" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="M21" s="84" t="n">
-        <v>0.51</v>
+        <v>6</v>
+      </c>
+      <c r="M21" s="74" t="n">
+        <v>0.22</v>
       </c>
       <c r="N21" s="76" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -38998,47 +38994,47 @@
       <c r="A22" s="82" t="inlineStr"/>
       <c r="B22" s="67" t="inlineStr">
         <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="C22" s="83" t="n">
-        <v>0.65</v>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C22" s="68" t="n">
+        <v>0.63</v>
       </c>
       <c r="D22" s="69" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E22" s="69" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F22" s="70" t="n">
         <v>5</v>
       </c>
       <c r="G22" s="71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H22" s="72" t="inlineStr">
         <is>
-          <t>7–1</t>
+          <t>4–1</t>
         </is>
       </c>
       <c r="I22" s="73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K22" s="70" t="n">
         <v>2</v>
       </c>
       <c r="L22" s="70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M22" s="74" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="N22" s="67" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -39046,99 +39042,99 @@
       <c r="A23" s="75" t="inlineStr"/>
       <c r="B23" s="76" t="inlineStr">
         <is>
-          <t>Tyskland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C23" s="68" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
       <c r="D23" s="78" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" s="78" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E23" s="77" t="n">
+        <v>2</v>
       </c>
       <c r="F23" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="79" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="79" t="n">
-        <v>4</v>
-      </c>
       <c r="H23" s="80" t="inlineStr">
         <is>
-          <t>2–1</t>
+          <t>2–0</t>
         </is>
       </c>
       <c r="I23" s="81" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J23" s="77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="77" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="M23" s="84" t="n">
-        <v>0.45</v>
+        <v>5</v>
+      </c>
+      <c r="M23" s="74" t="n">
+        <v>0.37</v>
       </c>
       <c r="N23" s="76" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
+          <t>Australia</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="66" t="inlineStr">
         <is>
-          <t>Gruppe F</t>
+          <t>Gruppe E</t>
         </is>
       </c>
       <c r="B24" s="67" t="inlineStr">
         <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="C24" s="68" t="n">
-        <v>0.6</v>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C24" s="83" t="n">
+        <v>0.75</v>
       </c>
       <c r="D24" s="69" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E24" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" s="70" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="70" t="n">
+      <c r="G24" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="G24" s="71" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" s="72" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>0–0</t>
         </is>
       </c>
       <c r="I24" s="73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" s="70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K24" s="70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L24" s="70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M24" s="74" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="N24" s="67" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -39146,47 +39142,47 @@
       <c r="A25" s="75" t="inlineStr"/>
       <c r="B25" s="76" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
       <c r="C25" s="84" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D25" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E25" s="77" t="n">
-        <v>7</v>
+        <v>0.49</v>
+      </c>
+      <c r="D25" s="78" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" s="78" t="n">
+        <v>4</v>
       </c>
       <c r="F25" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G25" s="79" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="79" t="n">
-        <v>2</v>
-      </c>
       <c r="H25" s="80" t="inlineStr">
         <is>
-          <t>5–1</t>
+          <t>1–0</t>
         </is>
       </c>
       <c r="I25" s="81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="K25" s="78" t="n">
-        <v>9</v>
-      </c>
-      <c r="L25" s="78" t="n">
-        <v>20</v>
+        <v>8</v>
+      </c>
+      <c r="K25" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="77" t="n">
+        <v>10</v>
       </c>
       <c r="M25" s="84" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="N25" s="76" t="inlineStr">
         <is>
-          <t>Sverige</t>
+          <t>Ecuador</t>
         </is>
       </c>
     </row>
@@ -39194,47 +39190,47 @@
       <c r="A26" s="82" t="inlineStr"/>
       <c r="B26" s="67" t="inlineStr">
         <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="C26" s="84" t="n">
-        <v>0.49</v>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C26" s="83" t="n">
+        <v>0.65</v>
       </c>
       <c r="D26" s="69" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E26" s="69" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F26" s="70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" s="71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H26" s="72" t="inlineStr">
         <is>
-          <t>5–1</t>
+          <t>7–1</t>
         </is>
       </c>
       <c r="I26" s="73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K26" s="70" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="M26" s="84" t="n">
-        <v>0.51</v>
+        <v>7</v>
+      </c>
+      <c r="M26" s="74" t="n">
+        <v>0.35</v>
       </c>
       <c r="N26" s="67" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -39242,99 +39238,99 @@
       <c r="A27" s="75" t="inlineStr"/>
       <c r="B27" s="76" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="C27" s="74" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D27" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="77" t="n">
-        <v>1</v>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C27" s="68" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D27" s="78" t="n">
+        <v>16</v>
+      </c>
+      <c r="E27" s="78" t="n">
+        <v>7</v>
       </c>
       <c r="F27" s="77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G27" s="79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H27" s="80" t="inlineStr">
         <is>
-          <t>0–4</t>
+          <t>2–1</t>
         </is>
       </c>
       <c r="I27" s="81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="K27" s="78" t="n">
-        <v>5</v>
-      </c>
-      <c r="L27" s="78" t="n">
-        <v>10</v>
-      </c>
-      <c r="M27" s="68" t="n">
-        <v>0.57</v>
+      <c r="K27" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="M27" s="84" t="n">
+        <v>0.45</v>
       </c>
       <c r="N27" s="76" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Elfenbenskysten</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="66" t="inlineStr">
         <is>
-          <t>Gruppe G</t>
+          <t>Gruppe F</t>
         </is>
       </c>
       <c r="B28" s="67" t="inlineStr">
         <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C28" s="84" t="n">
-        <v>0.53</v>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C28" s="68" t="n">
+        <v>0.6</v>
       </c>
       <c r="D28" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="E28" s="70" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="F28" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="72" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I28" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="G28" s="71" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="72" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I28" s="73" t="n">
+      <c r="L28" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="J28" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L28" s="70" t="n">
-        <v>14</v>
-      </c>
-      <c r="M28" s="84" t="n">
-        <v>0.47</v>
+      <c r="M28" s="74" t="n">
+        <v>0.4</v>
       </c>
       <c r="N28" s="67" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -39342,47 +39338,47 @@
       <c r="A29" s="75" t="inlineStr"/>
       <c r="B29" s="76" t="inlineStr">
         <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C29" s="83" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D29" s="78" t="n">
-        <v>22</v>
-      </c>
-      <c r="E29" s="78" t="n">
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C29" s="84" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D29" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E29" s="77" t="n">
         <v>7</v>
       </c>
       <c r="F29" s="77" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G29" s="79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H29" s="80" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>5–1</t>
         </is>
       </c>
       <c r="I29" s="81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="L29" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="M29" s="74" t="n">
-        <v>0.32</v>
+        <v>9</v>
+      </c>
+      <c r="K29" s="78" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" s="78" t="n">
+        <v>20</v>
+      </c>
+      <c r="M29" s="84" t="n">
+        <v>0.48</v>
       </c>
       <c r="N29" s="76" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Sverige</t>
         </is>
       </c>
     </row>
@@ -39390,47 +39386,47 @@
       <c r="A30" s="82" t="inlineStr"/>
       <c r="B30" s="67" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Sverige</t>
         </is>
       </c>
       <c r="C30" s="84" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="D30" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E30" s="70" t="n">
-        <v>4</v>
+        <v>13</v>
+      </c>
+      <c r="E30" s="69" t="n">
+        <v>8</v>
       </c>
       <c r="F30" s="70" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G30" s="71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H30" s="72" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>5–1</t>
         </is>
       </c>
       <c r="I30" s="73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="K30" s="69" t="n">
-        <v>8</v>
+      <c r="K30" s="70" t="n">
+        <v>2</v>
       </c>
       <c r="L30" s="70" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M30" s="84" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="N30" s="67" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tunisia</t>
         </is>
       </c>
     </row>
@@ -39438,75 +39434,75 @@
       <c r="A31" s="75" t="inlineStr"/>
       <c r="B31" s="76" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C31" s="74" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="D31" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="80" t="inlineStr">
+        <is>
+          <t>0–4</t>
+        </is>
+      </c>
+      <c r="I31" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="E31" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="79" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="80" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="I31" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="J31" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K31" s="78" t="n">
-        <v>7</v>
-      </c>
-      <c r="L31" s="78" t="n">
-        <v>19</v>
-      </c>
       <c r="M31" s="68" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="N31" s="76" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="66" t="inlineStr">
         <is>
-          <t>Gruppe H</t>
+          <t>Gruppe G</t>
         </is>
       </c>
       <c r="B32" s="67" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="C32" s="74" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D32" s="70" t="n">
-        <v>7</v>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C32" s="84" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D32" s="69" t="n">
+        <v>15</v>
       </c>
       <c r="E32" s="70" t="n">
         <v>3</v>
       </c>
       <c r="F32" s="70" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G32" s="71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H32" s="72" t="inlineStr">
         <is>
@@ -39514,23 +39510,23 @@
         </is>
       </c>
       <c r="I32" s="73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J32" s="70" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K32" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="69" t="n">
-        <v>27</v>
-      </c>
-      <c r="M32" s="83" t="n">
-        <v>0.65</v>
+        <v>4</v>
+      </c>
+      <c r="L32" s="70" t="n">
+        <v>14</v>
+      </c>
+      <c r="M32" s="84" t="n">
+        <v>0.47</v>
       </c>
       <c r="N32" s="67" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Egypt</t>
         </is>
       </c>
     </row>
@@ -39538,20 +39534,20 @@
       <c r="A33" s="75" t="inlineStr"/>
       <c r="B33" s="76" t="inlineStr">
         <is>
-          <t>Spania</t>
+          <t>Belgia</t>
         </is>
       </c>
       <c r="C33" s="83" t="n">
-        <v>0.74</v>
+        <v>0.68</v>
       </c>
       <c r="D33" s="78" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" s="78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="77" t="n">
         <v>8</v>
-      </c>
-      <c r="F33" s="77" t="n">
-        <v>9</v>
       </c>
       <c r="G33" s="79" t="n">
         <v>6</v>
@@ -39562,23 +39558,23 @@
         </is>
       </c>
       <c r="I33" s="81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="77" t="n">
         <v>3</v>
       </c>
       <c r="K33" s="77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M33" s="74" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="N33" s="76" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Iran</t>
         </is>
       </c>
     </row>
@@ -39586,47 +39582,47 @@
       <c r="A34" s="82" t="inlineStr"/>
       <c r="B34" s="67" t="inlineStr">
         <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C34" s="83" t="n">
-        <v>0.65</v>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C34" s="84" t="n">
+        <v>0.47</v>
       </c>
       <c r="D34" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="E34" s="69" t="n">
-        <v>9</v>
+        <v>17</v>
+      </c>
+      <c r="E34" s="70" t="n">
+        <v>4</v>
       </c>
       <c r="F34" s="70" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G34" s="71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H34" s="72" t="inlineStr">
         <is>
-          <t>4–0</t>
+          <t>2–2</t>
         </is>
       </c>
       <c r="I34" s="73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J34" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" s="70" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="K34" s="69" t="n">
+        <v>8</v>
       </c>
       <c r="L34" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="M34" s="74" t="n">
-        <v>0.35</v>
+        <v>13</v>
+      </c>
+      <c r="M34" s="84" t="n">
+        <v>0.53</v>
       </c>
       <c r="N34" s="67" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>New Zealand</t>
         </is>
       </c>
     </row>
@@ -39634,99 +39630,99 @@
       <c r="A35" s="75" t="inlineStr"/>
       <c r="B35" s="76" t="inlineStr">
         <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="C35" s="83" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D35" s="78" t="n">
-        <v>16</v>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C35" s="74" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D35" s="77" t="n">
+        <v>10</v>
       </c>
       <c r="E35" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="77" t="n">
+      <c r="G35" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="80" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I35" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="78" t="n">
         <v>7</v>
       </c>
-      <c r="G35" s="79" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="80" t="inlineStr">
-        <is>
-          <t>2–2</t>
-        </is>
-      </c>
-      <c r="I35" s="81" t="n">
-        <v>4</v>
-      </c>
-      <c r="J35" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" s="78" t="n">
-        <v>4</v>
-      </c>
-      <c r="L35" s="77" t="n">
-        <v>11</v>
-      </c>
-      <c r="M35" s="74" t="n">
-        <v>0.34</v>
+      <c r="L35" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="M35" s="68" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="N35" s="76" t="inlineStr">
         <is>
-          <t>Kapp Verde</t>
+          <t>Egypt</t>
         </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
       <c r="A36" s="66" t="inlineStr">
         <is>
-          <t>Gruppe I</t>
+          <t>Gruppe H</t>
         </is>
       </c>
       <c r="B36" s="67" t="inlineStr">
         <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C36" s="84" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D36" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="E36" s="69" t="n">
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C36" s="74" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D36" s="70" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="72" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I36" s="73" t="n">
         <v>9</v>
       </c>
-      <c r="F36" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="72" t="inlineStr">
-        <is>
-          <t>3–1</t>
-        </is>
-      </c>
-      <c r="I36" s="73" t="n">
-        <v>1</v>
-      </c>
       <c r="J36" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="70" t="n">
-        <v>6</v>
-      </c>
-      <c r="M36" s="84" t="n">
-        <v>0.46</v>
+        <v>8</v>
+      </c>
+      <c r="K36" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="L36" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="M36" s="83" t="n">
+        <v>0.65</v>
       </c>
       <c r="N36" s="67" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Uruguay</t>
         </is>
       </c>
     </row>
@@ -39734,47 +39730,47 @@
       <c r="A37" s="75" t="inlineStr"/>
       <c r="B37" s="76" t="inlineStr">
         <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C37" s="68" t="n">
-        <v>0.5600000000000001</v>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C37" s="83" t="n">
+        <v>0.74</v>
       </c>
       <c r="D37" s="78" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E37" s="78" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F37" s="77" t="n">
         <v>9</v>
       </c>
       <c r="G37" s="79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H37" s="80" t="inlineStr">
         <is>
-          <t>3–0</t>
+          <t>0–0</t>
         </is>
       </c>
       <c r="I37" s="81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J37" s="77" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M37" s="74" t="n">
-        <v>0.44</v>
+        <v>0.26</v>
       </c>
       <c r="N37" s="76" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
@@ -39782,47 +39778,47 @@
       <c r="A38" s="82" t="inlineStr"/>
       <c r="B38" s="67" t="inlineStr">
         <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C38" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D38" s="70" t="n">
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C38" s="83" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D38" s="69" t="n">
+        <v>21</v>
+      </c>
+      <c r="E38" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="F38" s="70" t="n">
         <v>11</v>
       </c>
-      <c r="E38" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="70" t="n">
-        <v>8</v>
-      </c>
       <c r="G38" s="71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="72" t="inlineStr">
         <is>
-          <t>1–4</t>
+          <t>4–0</t>
         </is>
       </c>
       <c r="I38" s="73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="K38" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="L38" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="M38" s="68" t="n">
-        <v>0.63</v>
+        <v>1</v>
+      </c>
+      <c r="K38" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="74" t="n">
+        <v>0.35</v>
       </c>
       <c r="N38" s="67" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
     </row>
@@ -39830,99 +39826,99 @@
       <c r="A39" s="75" t="inlineStr"/>
       <c r="B39" s="76" t="inlineStr">
         <is>
-          <t>Norge</t>
-        </is>
-      </c>
-      <c r="C39" s="74" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D39" s="77" t="n">
-        <v>12</v>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="C39" s="83" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D39" s="78" t="n">
+        <v>16</v>
       </c>
       <c r="E39" s="77" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F39" s="77" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G39" s="79" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="80" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I39" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="80" t="inlineStr">
-        <is>
-          <t>3–2</t>
-        </is>
-      </c>
-      <c r="I39" s="81" t="n">
-        <v>5</v>
-      </c>
       <c r="J39" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K39" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="L39" s="78" t="n">
-        <v>17</v>
-      </c>
-      <c r="M39" s="68" t="n">
-        <v>0.57</v>
+        <v>3</v>
+      </c>
+      <c r="K39" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L39" s="77" t="n">
+        <v>11</v>
+      </c>
+      <c r="M39" s="74" t="n">
+        <v>0.34</v>
       </c>
       <c r="N39" s="76" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="66" t="inlineStr">
         <is>
-          <t>Gruppe J</t>
+          <t>Gruppe I</t>
         </is>
       </c>
       <c r="B40" s="67" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Frankrike</t>
         </is>
       </c>
       <c r="C40" s="84" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="D40" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="E40" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="E40" s="69" t="n">
-        <v>6</v>
-      </c>
       <c r="F40" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="72" t="inlineStr">
+        <is>
+          <t>3–1</t>
+        </is>
+      </c>
+      <c r="I40" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="70" t="n">
         <v>3</v>
-      </c>
-      <c r="G40" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="72" t="inlineStr">
-        <is>
-          <t>3–0</t>
-        </is>
-      </c>
-      <c r="I40" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="K40" s="70" t="n">
-        <v>0</v>
       </c>
       <c r="L40" s="70" t="n">
         <v>6</v>
       </c>
       <c r="M40" s="84" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="N40" s="67" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
@@ -39930,47 +39926,47 @@
       <c r="A41" s="75" t="inlineStr"/>
       <c r="B41" s="76" t="inlineStr">
         <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="C41" s="84" t="n">
-        <v>0.54</v>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C41" s="68" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="D41" s="78" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E41" s="78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" s="77" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G41" s="79" t="n">
         <v>5</v>
       </c>
       <c r="H41" s="80" t="inlineStr">
         <is>
-          <t>2–0</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I41" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="77" t="n">
-        <v>2</v>
-      </c>
       <c r="K41" s="77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="M41" s="84" t="n">
-        <v>0.46</v>
+        <v>4</v>
+      </c>
+      <c r="M41" s="74" t="n">
+        <v>0.44</v>
       </c>
       <c r="N41" s="76" t="inlineStr">
         <is>
-          <t>Østerrike</t>
+          <t>Irak</t>
         </is>
       </c>
     </row>
@@ -39978,47 +39974,47 @@
       <c r="A42" s="82" t="inlineStr"/>
       <c r="B42" s="67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Irak</t>
         </is>
       </c>
       <c r="C42" s="74" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="D42" s="70" t="n">
+        <v>11</v>
+      </c>
+      <c r="E42" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="E42" s="70" t="n">
+      <c r="G42" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="72" t="inlineStr">
+        <is>
+          <t>1–4</t>
+        </is>
+      </c>
+      <c r="I42" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G42" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="72" t="inlineStr">
-        <is>
-          <t>1–2</t>
-        </is>
-      </c>
-      <c r="I42" s="73" t="n">
+      <c r="K42" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="J42" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="K42" s="69" t="n">
-        <v>8</v>
-      </c>
       <c r="L42" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="M42" s="83" t="n">
-        <v>0.75</v>
+        <v>12</v>
+      </c>
+      <c r="M42" s="68" t="n">
+        <v>0.63</v>
       </c>
       <c r="N42" s="67" t="inlineStr">
         <is>
-          <t>Algerie</t>
+          <t>Norge</t>
         </is>
       </c>
     </row>
@@ -40026,99 +40022,99 @@
       <c r="A43" s="75" t="inlineStr"/>
       <c r="B43" s="76" t="inlineStr">
         <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C43" s="68" t="n">
-        <v>0.62</v>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C43" s="74" t="n">
+        <v>0.43</v>
       </c>
       <c r="D43" s="77" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E43" s="77" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F43" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="79" t="n">
         <v>4</v>
       </c>
-      <c r="G43" s="79" t="n">
-        <v>2</v>
-      </c>
       <c r="H43" s="80" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>3–2</t>
         </is>
       </c>
       <c r="I43" s="81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J43" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="K43" s="78" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="K43" s="77" t="n">
+        <v>6</v>
       </c>
       <c r="L43" s="78" t="n">
-        <v>11</v>
-      </c>
-      <c r="M43" s="74" t="n">
-        <v>0.38</v>
+        <v>17</v>
+      </c>
+      <c r="M43" s="68" t="n">
+        <v>0.57</v>
       </c>
       <c r="N43" s="76" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="66" t="inlineStr">
         <is>
-          <t>Gruppe K</t>
+          <t>Gruppe J</t>
         </is>
       </c>
       <c r="B44" s="67" t="inlineStr">
         <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C44" s="83" t="n">
-        <v>0.66</v>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C44" s="84" t="n">
+        <v>0.47</v>
       </c>
       <c r="D44" s="69" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E44" s="69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F44" s="70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G44" s="71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H44" s="72" t="inlineStr">
         <is>
-          <t>1–0</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I44" s="73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" s="70" t="n">
         <v>3</v>
       </c>
       <c r="K44" s="70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="M44" s="74" t="n">
-        <v>0.34</v>
+        <v>6</v>
+      </c>
+      <c r="M44" s="84" t="n">
+        <v>0.53</v>
       </c>
       <c r="N44" s="67" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -40126,14 +40122,14 @@
       <c r="A45" s="75" t="inlineStr"/>
       <c r="B45" s="76" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C45" s="83" t="n">
-        <v>0.75</v>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C45" s="84" t="n">
+        <v>0.54</v>
       </c>
       <c r="D45" s="78" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E45" s="78" t="n">
         <v>3</v>
@@ -40142,31 +40138,31 @@
         <v>4</v>
       </c>
       <c r="G45" s="79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H45" s="80" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>2–0</t>
         </is>
       </c>
       <c r="I45" s="81" t="n">
         <v>3</v>
       </c>
       <c r="J45" s="77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K45" s="77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="77" t="n">
-        <v>8</v>
-      </c>
-      <c r="M45" s="74" t="n">
-        <v>0.25</v>
+        <v>6</v>
+      </c>
+      <c r="M45" s="84" t="n">
+        <v>0.46</v>
       </c>
       <c r="N45" s="76" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Østerrike</t>
         </is>
       </c>
     </row>
@@ -40174,47 +40170,47 @@
       <c r="A46" s="82" t="inlineStr"/>
       <c r="B46" s="67" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C46" s="83" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D46" s="69" t="n">
-        <v>16</v>
-      </c>
-      <c r="E46" s="69" t="n">
-        <v>9</v>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C46" s="74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D46" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="70" t="n">
+        <v>4</v>
       </c>
       <c r="F46" s="70" t="n">
         <v>4</v>
       </c>
       <c r="G46" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="72" t="inlineStr">
+        <is>
+          <t>1–2</t>
+        </is>
+      </c>
+      <c r="I46" s="73" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="72" t="inlineStr">
-        <is>
-          <t>5–0</t>
-        </is>
-      </c>
-      <c r="I46" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K46" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L46" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="M46" s="74" t="n">
-        <v>0.34</v>
+      <c r="K46" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L46" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="M46" s="83" t="n">
+        <v>0.75</v>
       </c>
       <c r="N46" s="67" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -40222,99 +40218,99 @@
       <c r="A47" s="75" t="inlineStr"/>
       <c r="B47" s="76" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C47" s="74" t="n">
-        <v>0.33</v>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C47" s="68" t="n">
+        <v>0.62</v>
       </c>
       <c r="D47" s="77" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E47" s="77" t="n">
         <v>3</v>
       </c>
       <c r="F47" s="77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G47" s="79" t="n">
         <v>2</v>
       </c>
       <c r="H47" s="80" t="inlineStr">
         <is>
-          <t>1–3</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I47" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="J47" s="77" t="n">
-        <v>5</v>
-      </c>
       <c r="K47" s="78" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L47" s="78" t="n">
-        <v>15</v>
-      </c>
-      <c r="M47" s="83" t="n">
-        <v>0.67</v>
+        <v>11</v>
+      </c>
+      <c r="M47" s="74" t="n">
+        <v>0.38</v>
       </c>
       <c r="N47" s="76" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Jordan</t>
         </is>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="66" t="inlineStr">
         <is>
-          <t>Gruppe L</t>
+          <t>Gruppe K</t>
         </is>
       </c>
       <c r="B48" s="67" t="inlineStr">
         <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C48" s="84" t="n">
-        <v>0.54</v>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C48" s="83" t="n">
+        <v>0.66</v>
       </c>
       <c r="D48" s="69" t="n">
         <v>20</v>
       </c>
       <c r="E48" s="69" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F48" s="70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G48" s="71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H48" s="72" t="inlineStr">
         <is>
-          <t>4–2</t>
+          <t>1–0</t>
         </is>
       </c>
       <c r="I48" s="73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" s="70" t="n">
         <v>3</v>
       </c>
       <c r="K48" s="70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L48" s="70" t="n">
-        <v>11</v>
-      </c>
-      <c r="M48" s="84" t="n">
-        <v>0.46</v>
+        <v>7</v>
+      </c>
+      <c r="M48" s="74" t="n">
+        <v>0.34</v>
       </c>
       <c r="N48" s="67" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -40322,47 +40318,47 @@
       <c r="A49" s="75" t="inlineStr"/>
       <c r="B49" s="76" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C49" s="83" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="D49" s="78" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E49" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="F49" s="77" t="n">
+      <c r="G49" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="80" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I49" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J49" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K49" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" s="77" t="n">
         <v>8</v>
       </c>
-      <c r="G49" s="79" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" s="80" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I49" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" s="77" t="n">
-        <v>2</v>
-      </c>
       <c r="M49" s="74" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="N49" s="76" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -40370,47 +40366,47 @@
       <c r="A50" s="82" t="inlineStr"/>
       <c r="B50" s="67" t="inlineStr">
         <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C50" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D50" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" s="70" t="n">
-        <v>3</v>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C50" s="83" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D50" s="69" t="n">
+        <v>16</v>
+      </c>
+      <c r="E50" s="69" t="n">
+        <v>9</v>
       </c>
       <c r="F50" s="70" t="n">
         <v>4</v>
       </c>
       <c r="G50" s="71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H50" s="72" t="inlineStr">
         <is>
-          <t>1–0</t>
+          <t>5–0</t>
         </is>
       </c>
       <c r="I50" s="73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="K50" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L50" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="M50" s="68" t="n">
-        <v>0.63</v>
+      <c r="K50" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" s="70" t="n">
+        <v>7</v>
+      </c>
+      <c r="M50" s="74" t="n">
+        <v>0.34</v>
       </c>
       <c r="N50" s="67" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Usbekistan</t>
         </is>
       </c>
     </row>
@@ -40418,79 +40414,275 @@
       <c r="A51" s="75" t="inlineStr"/>
       <c r="B51" s="76" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Usbekistan</t>
         </is>
       </c>
       <c r="C51" s="74" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D51" s="78" t="n">
-        <v>8</v>
+        <v>0.33</v>
+      </c>
+      <c r="D51" s="77" t="n">
+        <v>7</v>
       </c>
       <c r="E51" s="77" t="n">
         <v>3</v>
       </c>
       <c r="F51" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="80" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I51" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="G51" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="80" t="inlineStr">
+      <c r="J51" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" s="78" t="n">
+        <v>6</v>
+      </c>
+      <c r="L51" s="78" t="n">
+        <v>15</v>
+      </c>
+      <c r="M51" s="83" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N51" s="76" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="B52" s="67" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C52" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D52" s="69" t="n">
+        <v>20</v>
+      </c>
+      <c r="E52" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="F52" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H52" s="72" t="inlineStr">
+        <is>
+          <t>4–2</t>
+        </is>
+      </c>
+      <c r="I52" s="73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" s="70" t="n">
+        <v>11</v>
+      </c>
+      <c r="M52" s="84" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N52" s="67" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="75" t="inlineStr"/>
+      <c r="B53" s="76" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C53" s="83" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D53" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E53" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G53" s="79" t="n">
+        <v>7</v>
+      </c>
+      <c r="H53" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I53" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="74" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N53" s="76" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="82" t="inlineStr"/>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C54" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D54" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G54" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="72" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I54" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="M54" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N54" s="67" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="75" t="inlineStr"/>
+      <c r="B55" s="76" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C55" s="74" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D55" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="G55" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="80" t="inlineStr">
         <is>
           <t>0–1</t>
         </is>
       </c>
-      <c r="I51" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="77" t="n">
+      <c r="I55" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="K51" s="77" t="n">
+      <c r="K55" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="L51" s="77" t="n">
+      <c r="L55" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="M51" s="68" t="n">
+      <c r="M55" s="68" t="n">
         <v>0.58</v>
       </c>
-      <c r="N51" s="76" t="inlineStr">
+      <c r="N55" s="76" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="63" t="inlineStr">
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="63" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="55" t="inlineStr">
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="55" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B54" s="62" t="inlineStr">
+      <c r="B58" s="62" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C54" s="61" t="inlineStr">
+      <c r="C58" s="61" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D54" s="58" t="inlineStr">
+      <c r="D58" s="58" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E54" s="85" t="inlineStr">
+      <c r="E58" s="85" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -40499,8 +40691,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:G2"/>
+    <mergeCell ref="A57:N57"/>
     <mergeCell ref="I2:N2"/>
-    <mergeCell ref="A53:N53"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,38 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Kort" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Scorere og assists" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Alder" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Lagstatistikk" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Scoringstidspunkt" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Heatmap" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Ballbesittelse" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Stadionoversikt" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,13 +846,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -870,7 +871,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -898,8 +899,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -925,8 +926,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -949,7 +950,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -964,9 +965,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -38781,7 +38782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -39629,99 +39630,95 @@
       <c r="A19" s="75" t="inlineStr"/>
       <c r="B19" s="76" t="inlineStr">
         <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="C19" s="74" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D19" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" s="77" t="n">
-        <v>0</v>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="C19" s="83" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D19" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E19" s="78" t="n">
+        <v>12</v>
       </c>
       <c r="F19" s="77" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="80" t="inlineStr">
+        <is>
+          <t>4–2</t>
+        </is>
+      </c>
+      <c r="I19" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="80" t="inlineStr">
-        <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="I19" s="81" t="n">
-        <v>4</v>
-      </c>
       <c r="J19" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" s="78" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="78" t="n">
-        <v>12</v>
-      </c>
-      <c r="M19" s="68" t="n">
-        <v>0.6</v>
+        <v>2</v>
+      </c>
+      <c r="K19" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" s="74" t="n">
+        <v>0.31</v>
       </c>
       <c r="N19" s="76" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Haiti</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe D</t>
-        </is>
-      </c>
+      <c r="A20" s="82" t="inlineStr"/>
       <c r="B20" s="67" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C20" s="74" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="D20" s="70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20" s="70" t="n">
         <v>3</v>
       </c>
       <c r="G20" s="71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="72" t="inlineStr">
         <is>
-          <t>2–0</t>
+          <t>0–1</t>
         </is>
       </c>
       <c r="I20" s="73" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J20" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K20" s="69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L20" s="69" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="M20" s="68" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="N20" s="67" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
@@ -39729,95 +39726,99 @@
       <c r="A21" s="75" t="inlineStr"/>
       <c r="B21" s="76" t="inlineStr">
         <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="C21" s="84" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D21" s="77" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="80" t="inlineStr">
+        <is>
+          <t>0–3</t>
+        </is>
+      </c>
+      <c r="I21" s="81" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="78" t="n">
+        <v>21</v>
+      </c>
+      <c r="M21" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N21" s="76" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C22" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D22" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="72" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I22" s="73" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="K22" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" s="69" t="n">
+        <v>28</v>
+      </c>
+      <c r="M22" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N22" s="67" t="inlineStr">
+        <is>
           <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="C21" s="83" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D21" s="78" t="n">
-        <v>33</v>
-      </c>
-      <c r="E21" s="78" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="77" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" s="79" t="n">
-        <v>12</v>
-      </c>
-      <c r="H21" s="80" t="inlineStr">
-        <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="I21" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="M21" s="74" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N21" s="76" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="82" t="inlineStr"/>
-      <c r="B22" s="67" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C22" s="68" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D22" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E22" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="F22" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" s="71" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" s="72" t="inlineStr">
-        <is>
-          <t>4–1</t>
-        </is>
-      </c>
-      <c r="I22" s="73" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N22" s="67" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -39825,79 +39826,75 @@
       <c r="A23" s="75" t="inlineStr"/>
       <c r="B23" s="76" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C23" s="68" t="n">
-        <v>0.63</v>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="C23" s="83" t="n">
+        <v>0.78</v>
       </c>
       <c r="D23" s="78" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="E23" s="78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="77" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="79" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" s="80" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I23" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="79" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="80" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I23" s="81" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" s="77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="77" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="74" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N23" s="76" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="82" t="inlineStr"/>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C24" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D24" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N23" s="76" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe E</t>
-        </is>
-      </c>
-      <c r="B24" s="67" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="C24" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D24" s="69" t="n">
-        <v>26</v>
-      </c>
-      <c r="E24" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="F24" s="70" t="n">
-        <v>7</v>
-      </c>
       <c r="G24" s="71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H24" s="72" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>4–1</t>
         </is>
       </c>
       <c r="I24" s="73" t="n">
@@ -39907,17 +39904,17 @@
         <v>2</v>
       </c>
       <c r="K24" s="70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L24" s="70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M24" s="74" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="N24" s="67" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -39925,91 +39922,95 @@
       <c r="A25" s="75" t="inlineStr"/>
       <c r="B25" s="76" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="C25" s="84" t="n">
-        <v>0.49</v>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C25" s="68" t="n">
+        <v>0.63</v>
       </c>
       <c r="D25" s="78" t="n">
-        <v>16</v>
-      </c>
-      <c r="E25" s="78" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="E25" s="77" t="n">
+        <v>2</v>
       </c>
       <c r="F25" s="77" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G25" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="80" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I25" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="80" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I25" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="77" t="n">
-        <v>8</v>
-      </c>
       <c r="K25" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" s="84" t="n">
-        <v>0.51</v>
+        <v>5</v>
+      </c>
+      <c r="M25" s="74" t="n">
+        <v>0.37</v>
       </c>
       <c r="N25" s="76" t="inlineStr">
         <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
           <t>Ecuador</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="82" t="inlineStr"/>
-      <c r="B26" s="67" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
       <c r="C26" s="83" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="D26" s="69" t="n">
         <v>26</v>
       </c>
       <c r="E26" s="69" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F26" s="70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G26" s="71" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="72" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I26" s="73" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="H26" s="72" t="inlineStr">
-        <is>
-          <t>7–1</t>
-        </is>
-      </c>
-      <c r="I26" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" s="70" t="n">
-        <v>7</v>
-      </c>
       <c r="M26" s="74" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="N26" s="67" t="inlineStr">
         <is>
@@ -40021,79 +40022,75 @@
       <c r="A27" s="75" t="inlineStr"/>
       <c r="B27" s="76" t="inlineStr">
         <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="C27" s="68" t="n">
-        <v>0.55</v>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="C27" s="84" t="n">
+        <v>0.49</v>
       </c>
       <c r="D27" s="78" t="n">
         <v>16</v>
       </c>
       <c r="E27" s="78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F27" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="80" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I27" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" s="84" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N27" s="76" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="82" t="inlineStr"/>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C28" s="83" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D28" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="E28" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="79" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="80" t="inlineStr">
-        <is>
-          <t>2–1</t>
-        </is>
-      </c>
-      <c r="I27" s="81" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="M27" s="84" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N27" s="76" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe F</t>
-        </is>
-      </c>
-      <c r="B28" s="67" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="C28" s="68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D28" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" s="69" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="70" t="n">
-        <v>4</v>
-      </c>
       <c r="G28" s="71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H28" s="72" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>7–1</t>
         </is>
       </c>
       <c r="I28" s="73" t="n">
@@ -40103,17 +40100,17 @@
         <v>5</v>
       </c>
       <c r="K28" s="70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" s="70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M28" s="74" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="N28" s="67" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -40121,95 +40118,99 @@
       <c r="A29" s="75" t="inlineStr"/>
       <c r="B29" s="76" t="inlineStr">
         <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D29" s="78" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" s="78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="80" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="I29" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="M29" s="84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N29" s="76" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="C29" s="84" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D29" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E29" s="77" t="n">
+      <c r="C30" s="68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="F29" s="77" t="n">
+      <c r="F30" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="72" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I30" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="80" t="inlineStr">
-        <is>
-          <t>5–1</t>
-        </is>
-      </c>
-      <c r="I29" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="K29" s="78" t="n">
-        <v>9</v>
-      </c>
-      <c r="L29" s="78" t="n">
-        <v>20</v>
-      </c>
-      <c r="M29" s="84" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="N29" s="76" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="82" t="inlineStr"/>
-      <c r="B30" s="67" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="C30" s="84" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D30" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" s="69" t="n">
+      <c r="L30" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="72" t="inlineStr">
-        <is>
-          <t>5–1</t>
-        </is>
-      </c>
-      <c r="I30" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" s="84" t="n">
-        <v>0.51</v>
+      <c r="M30" s="74" t="n">
+        <v>0.4</v>
       </c>
       <c r="N30" s="67" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -40217,99 +40218,95 @@
       <c r="A31" s="75" t="inlineStr"/>
       <c r="B31" s="76" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="C31" s="74" t="n">
-        <v>0.43</v>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C31" s="84" t="n">
+        <v>0.52</v>
       </c>
       <c r="D31" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="77" t="n">
-        <v>1</v>
-      </c>
       <c r="G31" s="79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="80" t="inlineStr">
         <is>
-          <t>0–4</t>
+          <t>5–1</t>
         </is>
       </c>
       <c r="I31" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" s="78" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" s="78" t="n">
+        <v>20</v>
+      </c>
+      <c r="M31" s="84" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N31" s="76" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="82" t="inlineStr"/>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="C32" s="84" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D32" s="69" t="n">
+        <v>13</v>
+      </c>
+      <c r="E32" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="J31" s="77" t="n">
+      <c r="G32" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="78" t="n">
-        <v>5</v>
-      </c>
-      <c r="L31" s="78" t="n">
-        <v>10</v>
-      </c>
-      <c r="M31" s="68" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N31" s="76" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe G</t>
-        </is>
-      </c>
-      <c r="B32" s="67" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C32" s="84" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D32" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="E32" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" s="71" t="n">
-        <v>5</v>
-      </c>
       <c r="H32" s="72" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>5–1</t>
         </is>
       </c>
       <c r="I32" s="73" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J32" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="69" t="n">
-        <v>4</v>
+      <c r="K32" s="70" t="n">
+        <v>2</v>
       </c>
       <c r="L32" s="70" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M32" s="84" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="N32" s="67" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tunisia</t>
         </is>
       </c>
     </row>
@@ -40317,95 +40314,99 @@
       <c r="A33" s="75" t="inlineStr"/>
       <c r="B33" s="76" t="inlineStr">
         <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C33" s="74" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D33" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="80" t="inlineStr">
+        <is>
+          <t>0–4</t>
+        </is>
+      </c>
+      <c r="I33" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" s="78" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" s="68" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N33" s="76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="B34" s="67" t="inlineStr">
+        <is>
           <t>Belgia</t>
         </is>
       </c>
-      <c r="C33" s="83" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D33" s="78" t="n">
-        <v>22</v>
-      </c>
-      <c r="E33" s="78" t="n">
+      <c r="C34" s="84" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D34" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="70" t="n">
         <v>7</v>
-      </c>
-      <c r="F33" s="77" t="n">
-        <v>8</v>
-      </c>
-      <c r="G33" s="79" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" s="80" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I33" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="M33" s="74" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N33" s="76" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="82" t="inlineStr"/>
-      <c r="B34" s="67" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="C34" s="84" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D34" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E34" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" s="70" t="n">
-        <v>8</v>
       </c>
       <c r="G34" s="71" t="n">
         <v>5</v>
       </c>
       <c r="H34" s="72" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I34" s="73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J34" s="70" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L34" s="70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M34" s="84" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="N34" s="67" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Egypt</t>
         </is>
       </c>
     </row>
@@ -40413,99 +40414,95 @@
       <c r="A35" s="75" t="inlineStr"/>
       <c r="B35" s="76" t="inlineStr">
         <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C35" s="83" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D35" s="78" t="n">
+        <v>22</v>
+      </c>
+      <c r="E35" s="78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="79" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I35" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="M35" s="74" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N35" s="76" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="82" t="inlineStr"/>
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D36" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="E36" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="72" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I36" s="73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="70" t="n">
+        <v>13</v>
+      </c>
+      <c r="M36" s="84" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N36" s="67" t="inlineStr">
+        <is>
           <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="C35" s="74" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="D35" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="79" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="80" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="I35" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K35" s="78" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" s="78" t="n">
-        <v>19</v>
-      </c>
-      <c r="M35" s="68" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N35" s="76" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe H</t>
-        </is>
-      </c>
-      <c r="B36" s="67" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="C36" s="74" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D36" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="E36" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="72" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I36" s="73" t="n">
-        <v>9</v>
-      </c>
-      <c r="J36" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="K36" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="69" t="n">
-        <v>27</v>
-      </c>
-      <c r="M36" s="83" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N36" s="67" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
         </is>
       </c>
     </row>
@@ -40513,95 +40510,99 @@
       <c r="A37" s="75" t="inlineStr"/>
       <c r="B37" s="76" t="inlineStr">
         <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C37" s="83" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D37" s="78" t="n">
-        <v>23</v>
-      </c>
-      <c r="E37" s="78" t="n">
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C37" s="74" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D37" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="80" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I37" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K37" s="78" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="M37" s="68" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N37" s="76" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C38" s="74" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D38" s="70" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="72" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I38" s="73" t="n">
+        <v>9</v>
+      </c>
+      <c r="J38" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="F37" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" s="79" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="80" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I37" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K37" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="M37" s="74" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N37" s="76" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="82" t="inlineStr"/>
-      <c r="B38" s="67" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C38" s="83" t="n">
+      <c r="K38" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="L38" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="M38" s="83" t="n">
         <v>0.65</v>
       </c>
-      <c r="D38" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="E38" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="F38" s="70" t="n">
-        <v>11</v>
-      </c>
-      <c r="G38" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="72" t="inlineStr">
-        <is>
-          <t>4–0</t>
-        </is>
-      </c>
-      <c r="I38" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="M38" s="74" t="n">
-        <v>0.35</v>
-      </c>
       <c r="N38" s="67" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Uruguay</t>
         </is>
       </c>
     </row>
@@ -40609,43 +40610,43 @@
       <c r="A39" s="75" t="inlineStr"/>
       <c r="B39" s="76" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Spania</t>
         </is>
       </c>
       <c r="C39" s="83" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="D39" s="78" t="n">
-        <v>16</v>
-      </c>
-      <c r="E39" s="77" t="n">
+        <v>23</v>
+      </c>
+      <c r="E39" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" s="79" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I39" s="81" t="n">
         <v>2</v>
-      </c>
-      <c r="F39" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="G39" s="79" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" s="80" t="inlineStr">
-        <is>
-          <t>2–2</t>
-        </is>
-      </c>
-      <c r="I39" s="81" t="n">
-        <v>4</v>
       </c>
       <c r="J39" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="78" t="n">
-        <v>4</v>
+      <c r="K39" s="77" t="n">
+        <v>1</v>
       </c>
       <c r="L39" s="77" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M39" s="74" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="N39" s="76" t="inlineStr">
         <is>
@@ -40654,54 +40655,50 @@
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe I</t>
-        </is>
-      </c>
+      <c r="A40" s="82" t="inlineStr"/>
       <c r="B40" s="67" t="inlineStr">
         <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C40" s="84" t="n">
-        <v>0.54</v>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C40" s="83" t="n">
+        <v>0.65</v>
       </c>
       <c r="D40" s="69" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E40" s="69" t="n">
         <v>9</v>
       </c>
       <c r="F40" s="70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G40" s="71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="72" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>4–0</t>
         </is>
       </c>
       <c r="I40" s="73" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="L40" s="70" t="n">
-        <v>6</v>
-      </c>
-      <c r="M40" s="84" t="n">
-        <v>0.46</v>
+      <c r="M40" s="74" t="n">
+        <v>0.35</v>
       </c>
       <c r="N40" s="67" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
     </row>
@@ -40709,95 +40706,99 @@
       <c r="A41" s="75" t="inlineStr"/>
       <c r="B41" s="76" t="inlineStr">
         <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C41" s="68" t="n">
-        <v>0.5600000000000001</v>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="C41" s="83" t="n">
+        <v>0.66</v>
       </c>
       <c r="D41" s="78" t="n">
-        <v>19</v>
-      </c>
-      <c r="E41" s="78" t="n">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E41" s="77" t="n">
+        <v>2</v>
       </c>
       <c r="F41" s="77" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G41" s="79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H41" s="80" t="inlineStr">
         <is>
-          <t>3–0</t>
+          <t>2–2</t>
         </is>
       </c>
       <c r="I41" s="81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J41" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="K41" s="77" t="n">
-        <v>0</v>
+      <c r="K41" s="78" t="n">
+        <v>4</v>
       </c>
       <c r="L41" s="77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M41" s="74" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="N41" s="76" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="82" t="inlineStr"/>
+      <c r="A42" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
       <c r="B42" s="67" t="inlineStr">
         <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C42" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D42" s="70" t="n">
-        <v>11</v>
-      </c>
-      <c r="E42" s="70" t="n">
-        <v>1</v>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C42" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D42" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="E42" s="69" t="n">
+        <v>9</v>
       </c>
       <c r="F42" s="70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G42" s="71" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="72" t="inlineStr">
         <is>
-          <t>1–4</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I42" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="K42" s="69" t="n">
+      <c r="K42" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" s="70" t="n">
         <v>6</v>
       </c>
-      <c r="L42" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="M42" s="68" t="n">
-        <v>0.63</v>
+      <c r="M42" s="84" t="n">
+        <v>0.46</v>
       </c>
       <c r="N42" s="67" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
@@ -40805,99 +40806,95 @@
       <c r="A43" s="75" t="inlineStr"/>
       <c r="B43" s="76" t="inlineStr">
         <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C43" s="68" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D43" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E43" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="80" t="inlineStr">
+        <is>
+          <t>3–0</t>
+        </is>
+      </c>
+      <c r="I43" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" s="74" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N43" s="76" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="82" t="inlineStr"/>
+      <c r="B44" s="67" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C44" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D44" s="70" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="72" t="inlineStr">
+        <is>
+          <t>1–4</t>
+        </is>
+      </c>
+      <c r="I44" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="M44" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N44" s="67" t="inlineStr">
+        <is>
           <t>Norge</t>
-        </is>
-      </c>
-      <c r="C43" s="74" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D43" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E43" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="F43" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" s="79" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="80" t="inlineStr">
-        <is>
-          <t>3–2</t>
-        </is>
-      </c>
-      <c r="I43" s="81" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K43" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="L43" s="78" t="n">
-        <v>17</v>
-      </c>
-      <c r="M43" s="68" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N43" s="76" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe J</t>
-        </is>
-      </c>
-      <c r="B44" s="67" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="C44" s="84" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D44" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="E44" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="F44" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="72" t="inlineStr">
-        <is>
-          <t>3–0</t>
-        </is>
-      </c>
-      <c r="I44" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="K44" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="70" t="n">
-        <v>6</v>
-      </c>
-      <c r="M44" s="84" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N44" s="67" t="inlineStr">
-        <is>
-          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -40905,91 +40902,95 @@
       <c r="A45" s="75" t="inlineStr"/>
       <c r="B45" s="76" t="inlineStr">
         <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C45" s="74" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D45" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E45" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" s="80" t="inlineStr">
+        <is>
+          <t>3–2</t>
+        </is>
+      </c>
+      <c r="I45" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" s="78" t="n">
+        <v>17</v>
+      </c>
+      <c r="M45" s="68" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N45" s="76" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="B46" s="67" t="inlineStr">
+        <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="C45" s="84" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D45" s="78" t="n">
-        <v>12</v>
-      </c>
-      <c r="E45" s="78" t="n">
+      <c r="C46" s="84" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D46" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" s="70" t="n">
         <v>3</v>
-      </c>
-      <c r="F45" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" s="79" t="n">
-        <v>5</v>
-      </c>
-      <c r="H45" s="80" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I45" s="81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="M45" s="84" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N45" s="76" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="82" t="inlineStr"/>
-      <c r="B46" s="67" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="C46" s="74" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D46" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="E46" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="70" t="n">
-        <v>4</v>
       </c>
       <c r="G46" s="71" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="72" t="inlineStr">
         <is>
-          <t>1–2</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I46" s="73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J46" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="69" t="n">
-        <v>8</v>
-      </c>
-      <c r="L46" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="M46" s="83" t="n">
-        <v>0.75</v>
+      <c r="K46" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" s="84" t="n">
+        <v>0.53</v>
       </c>
       <c r="N46" s="67" t="inlineStr">
         <is>
@@ -41001,99 +41002,95 @@
       <c r="A47" s="75" t="inlineStr"/>
       <c r="B47" s="76" t="inlineStr">
         <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C47" s="68" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D47" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="E47" s="77" t="n">
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C47" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D47" s="78" t="n">
+        <v>12</v>
+      </c>
+      <c r="E47" s="78" t="n">
         <v>3</v>
       </c>
       <c r="F47" s="77" t="n">
         <v>4</v>
       </c>
       <c r="G47" s="79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H47" s="80" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>2–0</t>
         </is>
       </c>
       <c r="I47" s="81" t="n">
         <v>3</v>
       </c>
       <c r="J47" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="84" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N47" s="76" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="82" t="inlineStr"/>
+      <c r="B48" s="67" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C48" s="74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D48" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="K47" s="78" t="n">
+      <c r="F48" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L47" s="78" t="n">
-        <v>11</v>
-      </c>
-      <c r="M47" s="74" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N47" s="76" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe K</t>
-        </is>
-      </c>
-      <c r="B48" s="67" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C48" s="83" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D48" s="69" t="n">
-        <v>20</v>
-      </c>
-      <c r="E48" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="F48" s="70" t="n">
-        <v>5</v>
-      </c>
       <c r="G48" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="72" t="inlineStr">
+        <is>
+          <t>1–2</t>
+        </is>
+      </c>
+      <c r="I48" s="73" t="n">
         <v>6</v>
-      </c>
-      <c r="H48" s="72" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I48" s="73" t="n">
-        <v>2</v>
       </c>
       <c r="J48" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="K48" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="M48" s="74" t="n">
-        <v>0.34</v>
+      <c r="K48" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L48" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="M48" s="83" t="n">
+        <v>0.75</v>
       </c>
       <c r="N48" s="67" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -41101,16 +41098,16 @@
       <c r="A49" s="75" t="inlineStr"/>
       <c r="B49" s="76" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C49" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D49" s="78" t="n">
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C49" s="68" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D49" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="E49" s="78" t="n">
+      <c r="E49" s="77" t="n">
         <v>3</v>
       </c>
       <c r="F49" s="77" t="n">
@@ -41121,62 +41118,66 @@
       </c>
       <c r="H49" s="80" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I49" s="81" t="n">
         <v>3</v>
       </c>
       <c r="J49" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K49" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="77" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="K49" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" s="78" t="n">
+        <v>11</v>
       </c>
       <c r="M49" s="74" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="N49" s="76" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Jordan</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="82" t="inlineStr"/>
+      <c r="A50" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
       <c r="B50" s="67" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C50" s="83" t="n">
         <v>0.66</v>
       </c>
       <c r="D50" s="69" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E50" s="69" t="n">
         <v>9</v>
       </c>
       <c r="F50" s="70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G50" s="71" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="72" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I50" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="70" t="n">
         <v>3</v>
-      </c>
-      <c r="H50" s="72" t="inlineStr">
-        <is>
-          <t>5–0</t>
-        </is>
-      </c>
-      <c r="I50" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="70" t="n">
-        <v>2</v>
       </c>
       <c r="K50" s="70" t="n">
         <v>2</v>
@@ -41189,7 +41190,7 @@
       </c>
       <c r="N50" s="67" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -41197,99 +41198,95 @@
       <c r="A51" s="75" t="inlineStr"/>
       <c r="B51" s="76" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C51" s="74" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D51" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="E51" s="77" t="n">
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C51" s="83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D51" s="78" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" s="78" t="n">
         <v>3</v>
       </c>
       <c r="F51" s="77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G51" s="79" t="n">
         <v>2</v>
       </c>
       <c r="H51" s="80" t="inlineStr">
         <is>
-          <t>1–3</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I51" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" s="74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N51" s="76" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="82" t="inlineStr"/>
+      <c r="B52" s="67" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C52" s="83" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D52" s="69" t="n">
+        <v>16</v>
+      </c>
+      <c r="E52" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="F52" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="J51" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="K51" s="78" t="n">
-        <v>6</v>
-      </c>
-      <c r="L51" s="78" t="n">
-        <v>15</v>
-      </c>
-      <c r="M51" s="83" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="N51" s="76" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe L</t>
-        </is>
-      </c>
-      <c r="B52" s="67" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C52" s="84" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D52" s="69" t="n">
-        <v>20</v>
-      </c>
-      <c r="E52" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="F52" s="70" t="n">
+      <c r="G52" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G52" s="71" t="n">
-        <v>5</v>
-      </c>
       <c r="H52" s="72" t="inlineStr">
         <is>
-          <t>4–2</t>
+          <t>5–0</t>
         </is>
       </c>
       <c r="I52" s="73" t="n">
         <v>3</v>
       </c>
       <c r="J52" s="70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K52" s="70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L52" s="70" t="n">
-        <v>11</v>
-      </c>
-      <c r="M52" s="84" t="n">
-        <v>0.46</v>
+        <v>7</v>
+      </c>
+      <c r="M52" s="74" t="n">
+        <v>0.34</v>
       </c>
       <c r="N52" s="67" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Usbekistan</t>
         </is>
       </c>
     </row>
@@ -41297,95 +41294,99 @@
       <c r="A53" s="75" t="inlineStr"/>
       <c r="B53" s="76" t="inlineStr">
         <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C53" s="74" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D53" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="80" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I53" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="78" t="n">
+        <v>6</v>
+      </c>
+      <c r="L53" s="78" t="n">
+        <v>15</v>
+      </c>
+      <c r="M53" s="83" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N53" s="76" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="C53" s="83" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D53" s="78" t="n">
-        <v>19</v>
-      </c>
-      <c r="E53" s="78" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="77" t="n">
-        <v>8</v>
-      </c>
-      <c r="G53" s="79" t="n">
-        <v>7</v>
-      </c>
-      <c r="H53" s="80" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I53" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" s="74" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N53" s="76" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="82" t="inlineStr"/>
-      <c r="B54" s="67" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C54" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D54" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="E54" s="70" t="n">
+      <c r="C54" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D54" s="69" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="F54" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="F54" s="70" t="n">
-        <v>4</v>
-      </c>
       <c r="G54" s="71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H54" s="72" t="inlineStr">
         <is>
-          <t>1–0</t>
+          <t>4–2</t>
         </is>
       </c>
       <c r="I54" s="73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="K54" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L54" s="69" t="n">
+      <c r="L54" s="70" t="n">
         <v>11</v>
       </c>
-      <c r="M54" s="68" t="n">
-        <v>0.63</v>
+      <c r="M54" s="84" t="n">
+        <v>0.46</v>
       </c>
       <c r="N54" s="67" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Kroatia</t>
         </is>
       </c>
     </row>
@@ -41393,79 +41394,175 @@
       <c r="A55" s="75" t="inlineStr"/>
       <c r="B55" s="76" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C55" s="83" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D55" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E55" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" s="79" t="n">
+        <v>7</v>
+      </c>
+      <c r="H55" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I55" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="74" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N55" s="76" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="82" t="inlineStr"/>
+      <c r="B56" s="67" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C56" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D56" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="72" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I56" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="M56" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N56" s="67" t="inlineStr">
+        <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="C55" s="74" t="n">
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="75" t="inlineStr"/>
+      <c r="B57" s="76" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C57" s="74" t="n">
         <v>0.42</v>
       </c>
-      <c r="D55" s="78" t="n">
+      <c r="D57" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="E55" s="77" t="n">
+      <c r="E57" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="F55" s="77" t="n">
+      <c r="F57" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="G55" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="80" t="inlineStr">
+      <c r="G57" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="80" t="inlineStr">
         <is>
           <t>0–1</t>
         </is>
       </c>
-      <c r="I55" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="77" t="n">
+      <c r="I57" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="77" t="n">
+      <c r="K57" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="L55" s="77" t="n">
+      <c r="L57" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="M55" s="68" t="n">
+      <c r="M57" s="68" t="n">
         <v>0.58</v>
       </c>
-      <c r="N55" s="76" t="inlineStr">
+      <c r="N57" s="76" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="63" t="inlineStr">
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="63" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="55" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="55" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="B60" s="62" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C58" s="61" t="inlineStr">
+      <c r="C60" s="61" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D58" s="58" t="inlineStr">
+      <c r="D60" s="58" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E58" s="85" t="inlineStr">
+      <c r="E60" s="85" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -41473,8 +41570,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A59:N59"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A57:N57"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -44382,6 +44479,2248 @@
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A59:K59"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>VM 2026 — Aldersfordeling per lag  (per 12.06.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Lag</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Gruppe</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Snittalder</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Yngste spiller</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Alder</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Eldste spiller</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Alder</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Spillere m/dato</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>25,9</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>Yan Diomande</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>19 år 210 dg</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Jean-Michaël Seri</t>
+        </is>
+      </c>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>34 år 328 dg</t>
+        </is>
+      </c>
+      <c r="I3" s="25" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>26,1</t>
+        </is>
+      </c>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>Kendry Páez</t>
+        </is>
+      </c>
+      <c r="F4" s="30" t="inlineStr">
+        <is>
+          <t>19 år 39 dg</t>
+        </is>
+      </c>
+      <c r="G4" s="29" t="inlineStr">
+        <is>
+          <t>Hernán Galíndez</t>
+        </is>
+      </c>
+      <c r="H4" s="30" t="inlineStr">
+        <is>
+          <t>39 år 74 dg</t>
+        </is>
+      </c>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="inlineStr">
+        <is>
+          <t>26,5</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Mladen Jurkas</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
+        <is>
+          <t>18 år 248 dg</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>Edin Džeko</t>
+        </is>
+      </c>
+      <c r="H5" s="33" t="inlineStr">
+        <is>
+          <t>40 år 86 dg</t>
+        </is>
+      </c>
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>26,6</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Ayyoub Bouaddi</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>18 år 253 dg</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Munir Mohamedi</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>37 år 32 dg</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>26,7</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Rayan Elloumi</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>18 år 268 dg</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Ali Abdi</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>32 år 173 dg</t>
+        </is>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>26,8</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Lamine Yamal</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>18 år 334 dg</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Borja Iglesias</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>33 år 145 dg</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>26,8</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Antonio Nusa</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>21 år 55 dg</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Ørjan Nyland</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>35 år 275 dg</t>
+        </is>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>26,8</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Mbekezeli Mbokazi</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>20 år 265 dg</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Themba Zwane</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>36 år 312 dg</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>26,9</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Ibrahim Maza</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>20 år 199 dg</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Riyad Mahrez</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>35 år 111 dg</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>26,9</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Alex Freeman</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>21 år 306 dg</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Tim Ream</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>38 år 250 dg</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>26,9</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Marko Farji</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>22 år 87 dg</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>Jalal Hassan</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>35 år 25 dg</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>27,0</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Luc de Fougerolles</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>20 år 242 dg</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Jonathan Osorio</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>33 år 364 dg</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>27,0</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Caleb Yirenkyi</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>20 år 147 dg</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Ayew</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>34 år 274 dg</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>27,0</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Warren Zaïre-Emery</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>20 år 95 dg</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>N'Golo Kanté</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>35 år 75 dg</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="C17" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>27,1</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Ibrahim Mbaye</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>18 år 139 dg</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Idrissa Gueye</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>36 år 258 dg</t>
+        </is>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>27,3</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Kobbie Mainoo</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>21 år 53 dg</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Jordan Henderson</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>35 år 360 dg</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>27,4</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Lucas Herrington</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>18 år 280 dg</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>Aziz Behich</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>35 år 178 dg</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>27,5</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Keisuke Goto</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>21 år 8 dg</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Yuto Nagatomo</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>39 år 273 dg</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>27,5</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Keeto Thermoncy</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>20 år 74 dg</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>Johny Placide</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>38 år 134 dg</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>27,6</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Lucas Bergvall</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>20 år 129 dg</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Kristoffer Nordfeldt</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>36 år 353 dg</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>27,6</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Mike Penders</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>20 år 315 dg</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>Axel Witsel</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>37 år 150 dg</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>27,6</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Hugo Sochůrek</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>18 år 4 dg</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Vladimír Darida</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>35 år 308 dg</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>27,7</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Can Uzun</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>20 år 212 dg</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Mert Günok</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>37 år 102 dg</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>27,8</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Jorrel Hato</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>20 år 96 dg</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Marten de Roon</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>35 år 75 dg</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>27,9</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Gilberto Mora</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>17 år 240 dg</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Guillermo Ochoa</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>40 år 333 dg</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>28,0</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Livano Comenencia</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>22 år 129 dg</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Eloy Room</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>37 år 125 dg</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>28,0</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>João Neves</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>21 år 257 dg</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Cristiano Ronaldo</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
+        <is>
+          <t>41 år 126 dg</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>28,0</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Assan Ouédraogo</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>20 år 33 dg</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Manuel Neuer</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>40 år 76 dg</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe A</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>28,1</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Bae Jun-ho</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>22 år 295 dg</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Kim Seung-gyu</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
+        <is>
+          <t>35 år 255 dg</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>28,2</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Behruz Karimov</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>18 år 309 dg</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Utkir Yusupov</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>35 år 159 dg</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>28,3</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Tyler Bindon</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>21 år 135 dg</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Michael Boxall</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
+        <is>
+          <t>37 år 297 dg</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>28,3</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Johan Manzambi</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>20 år 240 dg</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Remo Freuler</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>34 år 57 dg</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>28,3</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Luka Vušković</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>19 år 108 dg</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Luka Modrić</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>40 år 275 dg</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>28,5</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Odeh Al-Fakhouri</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>20 år 201 dg</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Salim Obaid</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>34 år 146 dg</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>28,5</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Musab Al-Juwayr</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
+        <is>
+          <t>22 år 357 dg</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Ahmed Al-Kassar</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>35 år 35 dg</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>28,6</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Paul Wanner</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>20 år 170 dg</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Marko Arnautović</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>37 år 53 dg</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>29,0</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Alexandro Maidana</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>20 år 320 dg</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>Gatito Fernández</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>38 år 74 dg</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>29,0</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Facundo Pellistri</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>24 år 173 dg</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Fernando Muslera</t>
+        </is>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>39 år 361 dg</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>29,1</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Hamza Abdelkarim</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
+        <is>
+          <t>18 år 162 dg</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>El Mahdy Soliman</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>39 år 4 dg</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>29,1</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Matthieu Epolo</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>21 år 147 dg</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>Cédric Bakambu</t>
+        </is>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>35 år 62 dg</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>29,1</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Nico Paz</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
+        <is>
+          <t>21 år 276 dg</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>Lionel Messi</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>38 år 353 dg</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>29,2</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Tyler Fletcher</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>19 år 85 dg</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>Craig Gordon</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>43 år 163 dg</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe B</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>29,5</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Tahsin Jamshid</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>19 år 361 dg</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Abdulaziz Hatem</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>36 år 161 dg</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe C</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>29,6</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Rayan</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>19 år 313 dg</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Weverton</t>
+        </is>
+      </c>
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>38 år 181 dg</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>29,7</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Wagner Pina</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>23 år 221 dg</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>Vozinha</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>40 år 8 dg</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>30,1</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Gustavo Puerta</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>22 år 324 dg</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>David Ospina</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>37 år 284 dg</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>30,3</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Amirmohammad Razzaghinia</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>20 år 61 dg</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>Shojae Khalilzadeh</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>37 år 28 dg</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>30,4</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Edgardo Fariña</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>24 år 235 dg</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Alberto Quintero</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>38 år 176 dg</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -34,8 +34,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubbdominans" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -454,7 +458,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -768,6 +772,36 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -46726,6 +46760,6999 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I70"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>VM 2026 — Spillere etter klubbland   68 land, 1248 spillere</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Spillere</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Nivå 1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Nivå 2</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Nivå 3</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Nivå 4</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Nivå 5</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Nivå 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C3" s="110" t="n">
+        <v>205</v>
+      </c>
+      <c r="D3" s="25" t="n">
+        <v>163</v>
+      </c>
+      <c r="E3" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="F3" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="25" t="inlineStr"/>
+      <c r="H3" s="25" t="inlineStr"/>
+      <c r="I3" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C4" s="111" t="n">
+        <v>111</v>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>93</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" s="30" t="inlineStr"/>
+      <c r="G4" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="30" t="inlineStr"/>
+      <c r="I4" s="30" t="inlineStr"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C5" s="112" t="n">
+        <v>86</v>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>76</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="33" t="inlineStr"/>
+      <c r="H5" s="33" t="inlineStr"/>
+      <c r="I5" s="33" t="inlineStr"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C6" s="113" t="n">
+        <v>85</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="15" t="inlineStr"/>
+      <c r="G6" s="15" t="inlineStr"/>
+      <c r="H6" s="15" t="inlineStr"/>
+      <c r="I6" s="15" t="inlineStr"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="C7" s="114" t="n">
+        <v>70</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C8" s="113" t="n">
+        <v>51</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15" t="inlineStr"/>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+      <c r="I8" s="15" t="inlineStr"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="C9" s="114" t="n">
+        <v>45</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C10" s="113" t="n">
+        <v>41</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr"/>
+      <c r="G10" s="15" t="inlineStr"/>
+      <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="15" t="inlineStr"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C11" s="114" t="n">
+        <v>38</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="14" t="inlineStr"/>
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C12" s="113" t="n">
+        <v>32</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="15" t="inlineStr"/>
+      <c r="H12" s="15" t="inlineStr"/>
+      <c r="I12" s="15" t="inlineStr"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="C13" s="114" t="n">
+        <v>31</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="E13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr"/>
+      <c r="G13" s="14" t="inlineStr"/>
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C14" s="113" t="n">
+        <v>29</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr"/>
+      <c r="G14" s="15" t="inlineStr"/>
+      <c r="H14" s="15" t="inlineStr"/>
+      <c r="I14" s="15" t="inlineStr"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C15" s="114" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr"/>
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C16" s="113" t="n">
+        <v>27</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
+      <c r="G16" s="15" t="inlineStr"/>
+      <c r="H16" s="15" t="inlineStr"/>
+      <c r="I16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="C17" s="114" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="E17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr"/>
+      <c r="G17" s="14" t="inlineStr"/>
+      <c r="H17" s="14" t="inlineStr"/>
+      <c r="I17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C18" s="113" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="15" t="inlineStr"/>
+      <c r="G18" s="15" t="inlineStr"/>
+      <c r="H18" s="15" t="inlineStr"/>
+      <c r="I18" s="15" t="inlineStr"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C19" s="114" t="n">
+        <v>21</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr"/>
+      <c r="G19" s="14" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
+      <c r="I19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="C20" s="113" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" s="15" t="inlineStr"/>
+      <c r="F20" s="15" t="inlineStr"/>
+      <c r="G20" s="15" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr"/>
+      <c r="I20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="C21" s="114" t="n">
+        <v>19</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr"/>
+      <c r="H21" s="14" t="inlineStr"/>
+      <c r="I21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C22" s="113" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" s="15" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr"/>
+      <c r="G22" s="15" t="inlineStr"/>
+      <c r="H22" s="15" t="inlineStr"/>
+      <c r="I22" s="15" t="inlineStr"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Russland</t>
+        </is>
+      </c>
+      <c r="C23" s="114" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="14" t="inlineStr"/>
+      <c r="F23" s="14" t="inlineStr"/>
+      <c r="G23" s="14" t="inlineStr"/>
+      <c r="H23" s="14" t="inlineStr"/>
+      <c r="I23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C24" s="113" t="n">
+        <v>14</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr"/>
+      <c r="G24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr"/>
+      <c r="I24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C25" s="114" t="n">
+        <v>14</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" s="14" t="inlineStr"/>
+      <c r="F25" s="14" t="inlineStr"/>
+      <c r="G25" s="14" t="inlineStr"/>
+      <c r="H25" s="14" t="inlineStr"/>
+      <c r="I25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="C26" s="113" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr"/>
+      <c r="G26" s="15" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr"/>
+      <c r="I26" s="15" t="inlineStr"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Hellas</t>
+        </is>
+      </c>
+      <c r="C27" s="114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E27" s="14" t="inlineStr"/>
+      <c r="F27" s="14" t="inlineStr"/>
+      <c r="G27" s="14" t="inlineStr"/>
+      <c r="H27" s="14" t="inlineStr"/>
+      <c r="I27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="C28" s="113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D28" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E28" s="15" t="inlineStr"/>
+      <c r="F28" s="15" t="inlineStr"/>
+      <c r="G28" s="15" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr"/>
+      <c r="I28" s="15" t="inlineStr"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="C29" s="114" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="14" t="inlineStr"/>
+      <c r="G29" s="14" t="inlineStr"/>
+      <c r="H29" s="14" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C30" s="113" t="n">
+        <v>12</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E30" s="15" t="inlineStr"/>
+      <c r="F30" s="15" t="inlineStr"/>
+      <c r="G30" s="15" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr"/>
+      <c r="I30" s="15" t="inlineStr"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Kypros</t>
+        </is>
+      </c>
+      <c r="C31" s="114" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" s="14" t="inlineStr"/>
+      <c r="F31" s="14" t="inlineStr"/>
+      <c r="G31" s="14" t="inlineStr"/>
+      <c r="H31" s="14" t="inlineStr"/>
+      <c r="I31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="C32" s="113" t="n">
+        <v>9</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="15" t="inlineStr"/>
+      <c r="F32" s="15" t="inlineStr"/>
+      <c r="G32" s="15" t="inlineStr"/>
+      <c r="H32" s="15" t="inlineStr"/>
+      <c r="I32" s="15" t="inlineStr"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Ny-Zealand</t>
+        </is>
+      </c>
+      <c r="C33" s="114" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" s="14" t="inlineStr"/>
+      <c r="F33" s="14" t="inlineStr"/>
+      <c r="G33" s="14" t="inlineStr"/>
+      <c r="H33" s="14" t="inlineStr"/>
+      <c r="I33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C34" s="113" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" s="15" t="inlineStr"/>
+      <c r="F34" s="15" t="inlineStr"/>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr"/>
+      <c r="I34" s="15" t="inlineStr"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C35" s="114" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="14" t="inlineStr"/>
+      <c r="F35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr"/>
+      <c r="H35" s="14" t="inlineStr"/>
+      <c r="I35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="C36" s="113" t="n">
+        <v>7</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="15" t="inlineStr"/>
+      <c r="G36" s="15" t="inlineStr"/>
+      <c r="H36" s="15" t="inlineStr"/>
+      <c r="I36" s="15" t="inlineStr"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="C37" s="114" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E37" s="14" t="inlineStr"/>
+      <c r="F37" s="14" t="inlineStr"/>
+      <c r="G37" s="14" t="inlineStr"/>
+      <c r="H37" s="14" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Polen</t>
+        </is>
+      </c>
+      <c r="C38" s="113" t="n">
+        <v>7</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="15" t="inlineStr"/>
+      <c r="F38" s="15" t="inlineStr"/>
+      <c r="G38" s="15" t="inlineStr"/>
+      <c r="H38" s="15" t="inlineStr"/>
+      <c r="I38" s="15" t="inlineStr"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C39" s="114" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+      <c r="F39" s="14" t="inlineStr"/>
+      <c r="G39" s="14" t="inlineStr"/>
+      <c r="H39" s="14" t="inlineStr"/>
+      <c r="I39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+      <c r="C40" s="113" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E40" s="15" t="inlineStr"/>
+      <c r="F40" s="15" t="inlineStr"/>
+      <c r="G40" s="15" t="inlineStr"/>
+      <c r="H40" s="15" t="inlineStr"/>
+      <c r="I40" s="15" t="inlineStr"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C41" s="114" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+      <c r="F41" s="14" t="inlineStr"/>
+      <c r="G41" s="14" t="inlineStr"/>
+      <c r="H41" s="14" t="inlineStr"/>
+      <c r="I41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="C42" s="113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="15" t="inlineStr"/>
+      <c r="F42" s="15" t="inlineStr"/>
+      <c r="G42" s="15" t="inlineStr"/>
+      <c r="H42" s="15" t="inlineStr"/>
+      <c r="I42" s="15" t="inlineStr"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="C43" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="14" t="inlineStr"/>
+      <c r="F43" s="14" t="inlineStr"/>
+      <c r="G43" s="14" t="inlineStr"/>
+      <c r="H43" s="14" t="inlineStr"/>
+      <c r="I43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="C44" s="113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="15" t="inlineStr"/>
+      <c r="G44" s="15" t="inlineStr"/>
+      <c r="H44" s="15" t="inlineStr"/>
+      <c r="I44" s="15" t="inlineStr"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Aserbajdsjan</t>
+        </is>
+      </c>
+      <c r="C45" s="114" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="14" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="14" t="inlineStr"/>
+      <c r="H45" s="14" t="inlineStr"/>
+      <c r="I45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="C46" s="113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="15" t="inlineStr"/>
+      <c r="F46" s="15" t="inlineStr"/>
+      <c r="G46" s="15" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr"/>
+      <c r="I46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="C47" s="114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="14" t="inlineStr"/>
+      <c r="F47" s="14" t="inlineStr"/>
+      <c r="G47" s="14" t="inlineStr"/>
+      <c r="H47" s="14" t="inlineStr"/>
+      <c r="I47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Ungarn</t>
+        </is>
+      </c>
+      <c r="C48" s="113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" s="15" t="inlineStr"/>
+      <c r="F48" s="15" t="inlineStr"/>
+      <c r="G48" s="15" t="inlineStr"/>
+      <c r="H48" s="15" t="inlineStr"/>
+      <c r="I48" s="15" t="inlineStr"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="C49" s="114" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="14" t="inlineStr"/>
+      <c r="F49" s="14" t="inlineStr"/>
+      <c r="G49" s="14" t="inlineStr"/>
+      <c r="H49" s="14" t="inlineStr"/>
+      <c r="I49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+      <c r="C50" s="113" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" s="15" t="inlineStr"/>
+      <c r="F50" s="15" t="inlineStr"/>
+      <c r="G50" s="15" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr"/>
+      <c r="I50" s="15" t="inlineStr"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C51" s="114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="14" t="inlineStr"/>
+      <c r="F51" s="14" t="inlineStr"/>
+      <c r="G51" s="14" t="inlineStr"/>
+      <c r="H51" s="14" t="inlineStr"/>
+      <c r="I51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C52" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="15" t="inlineStr"/>
+      <c r="F52" s="15" t="inlineStr"/>
+      <c r="G52" s="15" t="inlineStr"/>
+      <c r="H52" s="15" t="inlineStr"/>
+      <c r="I52" s="15" t="inlineStr"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C53" s="114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="14" t="inlineStr"/>
+      <c r="F53" s="14" t="inlineStr"/>
+      <c r="G53" s="14" t="inlineStr"/>
+      <c r="H53" s="14" t="inlineStr"/>
+      <c r="I53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C54" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="15" t="inlineStr"/>
+      <c r="F54" s="15" t="inlineStr"/>
+      <c r="G54" s="15" t="inlineStr"/>
+      <c r="H54" s="15" t="inlineStr"/>
+      <c r="I54" s="15" t="inlineStr"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Irland</t>
+        </is>
+      </c>
+      <c r="C55" s="114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="14" t="inlineStr"/>
+      <c r="F55" s="14" t="inlineStr"/>
+      <c r="G55" s="14" t="inlineStr"/>
+      <c r="H55" s="14" t="inlineStr"/>
+      <c r="I55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C56" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="15" t="inlineStr"/>
+      <c r="F56" s="15" t="inlineStr"/>
+      <c r="G56" s="15" t="inlineStr"/>
+      <c r="H56" s="15" t="inlineStr"/>
+      <c r="I56" s="15" t="inlineStr"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="C57" s="114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="14" t="inlineStr"/>
+      <c r="F57" s="14" t="inlineStr"/>
+      <c r="G57" s="14" t="inlineStr"/>
+      <c r="H57" s="14" t="inlineStr"/>
+      <c r="I57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C58" s="113" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="15" t="inlineStr"/>
+      <c r="F58" s="15" t="inlineStr"/>
+      <c r="G58" s="15" t="inlineStr"/>
+      <c r="H58" s="15" t="inlineStr"/>
+      <c r="I58" s="15" t="inlineStr"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C59" s="114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="14" t="inlineStr"/>
+      <c r="F59" s="14" t="inlineStr"/>
+      <c r="G59" s="14" t="inlineStr"/>
+      <c r="H59" s="14" t="inlineStr"/>
+      <c r="I59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Bosnia og Hercegovina</t>
+        </is>
+      </c>
+      <c r="C60" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15" t="inlineStr"/>
+      <c r="F60" s="15" t="inlineStr"/>
+      <c r="G60" s="15" t="inlineStr"/>
+      <c r="H60" s="15" t="inlineStr"/>
+      <c r="I60" s="15" t="inlineStr"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Kasakhstan</t>
+        </is>
+      </c>
+      <c r="C61" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="14" t="inlineStr"/>
+      <c r="F61" s="14" t="inlineStr"/>
+      <c r="G61" s="14" t="inlineStr"/>
+      <c r="H61" s="14" t="inlineStr"/>
+      <c r="I61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C62" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="15" t="inlineStr"/>
+      <c r="F62" s="15" t="inlineStr"/>
+      <c r="G62" s="15" t="inlineStr"/>
+      <c r="H62" s="15" t="inlineStr"/>
+      <c r="I62" s="15" t="inlineStr"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="C63" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="14" t="inlineStr"/>
+      <c r="F63" s="14" t="inlineStr"/>
+      <c r="G63" s="14" t="inlineStr"/>
+      <c r="H63" s="14" t="inlineStr"/>
+      <c r="I63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C64" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15" t="inlineStr"/>
+      <c r="F64" s="15" t="inlineStr"/>
+      <c r="G64" s="15" t="inlineStr"/>
+      <c r="H64" s="15" t="inlineStr"/>
+      <c r="I64" s="15" t="inlineStr"/>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="C65" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="14" t="inlineStr"/>
+      <c r="F65" s="14" t="inlineStr"/>
+      <c r="G65" s="14" t="inlineStr"/>
+      <c r="H65" s="14" t="inlineStr"/>
+      <c r="I65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="C66" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="15" t="inlineStr"/>
+      <c r="F66" s="15" t="inlineStr"/>
+      <c r="G66" s="15" t="inlineStr"/>
+      <c r="H66" s="15" t="inlineStr"/>
+      <c r="I66" s="15" t="inlineStr"/>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C67" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="14" t="inlineStr"/>
+      <c r="F67" s="14" t="inlineStr"/>
+      <c r="G67" s="14" t="inlineStr"/>
+      <c r="H67" s="14" t="inlineStr"/>
+      <c r="I67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C68" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="15" t="inlineStr"/>
+      <c r="F68" s="15" t="inlineStr"/>
+      <c r="G68" s="15" t="inlineStr"/>
+      <c r="H68" s="15" t="inlineStr"/>
+      <c r="I68" s="15" t="inlineStr"/>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="C69" s="114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="14" t="inlineStr"/>
+      <c r="F69" s="14" t="inlineStr"/>
+      <c r="G69" s="14" t="inlineStr"/>
+      <c r="H69" s="14" t="inlineStr"/>
+      <c r="I69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="C70" s="113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="15" t="inlineStr"/>
+      <c r="F70" s="15" t="inlineStr"/>
+      <c r="G70" s="15" t="inlineStr"/>
+      <c r="H70" s="15" t="inlineStr"/>
+      <c r="I70" s="15" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:I2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E236"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>VM 2026 — Klubbdominans  (klubber med 2+ spillere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Klubb</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Spillere</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Lag i VM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="n">
+        <v>19</v>
+      </c>
+      <c r="E3" s="115" t="inlineStr">
+        <is>
+          <t>Algerie, Belgia, Egypt, England, Frankrike, Ghana, Kroatia, Nederland, Norge, Portugal, Spania, Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" s="116" t="inlineStr">
+        <is>
+          <t>Canada, Colombia, England, Frankrike, Japan, Kroatia, Senegal, Sør-Korea, Tyskland, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>PSG</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D5" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" s="117" t="inlineStr">
+        <is>
+          <t>Brasil, Ecuador, Frankrike, Marokko, Portugal, Senegal, Spania, Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="E6" s="118" t="inlineStr">
+        <is>
+          <t>Belgia, Brasil, Ecuador, England, Frankrike, Norge, Spania, Sverige, Tyskland</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E7" s="119" t="inlineStr">
+        <is>
+          <t>Brasil, Egypt, England, Frankrike, Nederland, Portugal, Spania, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Al-Hilal</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" s="118" t="inlineStr">
+        <is>
+          <t>Colombia, Frankrike, Marokko, Portugal, Saudi-Arabia, Senegal, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E9" s="119" t="inlineStr">
+        <is>
+          <t>Canada, Colombia, Elfenbenskysten, England, Frankrike, Japan, Marokko, Norge, Senegal, Spania, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Mexico, Norge, Spania, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="119" t="inlineStr">
+        <is>
+          <t>Argentina, Belgia, Brasil, Elfenbenskysten, England, Marokko, Portugal, Skottland, Tyrkia, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" s="118" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Curaçao, Kroatia, Marokko, Mexico, Nederland, Tsjekkia, USA, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" s="119" t="inlineStr">
+        <is>
+          <t>Algerie, Norge, Sveits, Sverige, Tyrkia, Tyskland, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" s="118" t="inlineStr">
+        <is>
+          <t>Belgia, Brasil, England, Frankrike, Marokko, Tyrkia, Tyskland, Uruguay, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="119" t="inlineStr">
+        <is>
+          <t>Colombia, Elfenbenskysten, Nederland, Senegal, Tyrkia, Tyskland</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" s="118" t="inlineStr">
+        <is>
+          <t>Brasil, Frankrike, Mexico, Portugal, Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="119" t="inlineStr">
+        <is>
+          <t>Belgia, Ecuador, Frankrike, Kroatia, Mexico, Portugal, Sveits, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Slavia Prague</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="118" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Ecuador, Haiti, Marokko, Nederland, Paraguay, Senegal, Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="14" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Brasil, Egypt, Frankrike, Nederland, Skottland, Sverige, Tyskland</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="15" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" s="119" t="inlineStr">
+        <is>
+          <t>Argentina, Ecuador, England, Frankrike, Nederland, Portugal, Senegal, Spania</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Al-Nassr</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" s="118" t="inlineStr">
+        <is>
+          <t>Iran, Portugal, Saudi-Arabia, Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="119" t="inlineStr">
+        <is>
+          <t>Canada, Japan, Skottland, Sverige, Sør-Korea, Tunisia, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Belgia, England, Frankrike, Skottland, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="119" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Orlando Pirates</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="118" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="119" t="inlineStr">
+        <is>
+          <t>Argentina, England, Senegal, Spania, Sverige, Sør-Korea, Uruguay, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E28" s="118" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Kroatia, Tsjekkia, Tyrkia, Tyskland, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" s="119" t="inlineStr">
+        <is>
+          <t>Canada, Elfenbenskysten, Ghana, Kapp Verde, Portugal, Senegal, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" s="118" t="inlineStr">
+        <is>
+          <t>Algerie, Canada, Egypt, Elfenbenskysten, Ghana, Senegal, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="119" t="inlineStr">
+        <is>
+          <t>Argentina, Belgia, Bosnia-Hercegovina, Colombia, Kapp Verde, Norge, Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="118" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Ecuador, Marokko, Sveits, Tyskland</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="15" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" s="119" t="inlineStr">
+        <is>
+          <t>Algerie, Belgia, Japan, Marokko, Sveits, Tunisia, Tyrkia, Tyskland</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Al-Ahli</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E34" s="118" t="inlineStr">
+        <is>
+          <t>Algerie, Brasil, Elfenbenskysten, England, Saudi-Arabia, Senegal, Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="119" t="inlineStr">
+        <is>
+          <t>Algerie, Belgia, DR Kongo, Marokko</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Al Ahly</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E36" s="118" t="inlineStr">
+        <is>
+          <t>Egypt, Marokko</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="15" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E37" s="119" t="inlineStr">
+        <is>
+          <t>Argentina, Colombia, Paraguay, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E38" s="118" t="inlineStr">
+        <is>
+          <t>Belgia, Nederland, Paraguay, Sverige, Tyrkia, Tyskland</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" s="119" t="inlineStr">
+        <is>
+          <t>Belgia, Canada, Marokko, Mexico, Norge, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Al-Qadsiah</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" s="118" t="inlineStr">
+        <is>
+          <t>Ghana, Mexico, Saudi-Arabia, Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="119" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Norge, Sør-Korea, Tyskland, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" s="118" t="inlineStr">
+        <is>
+          <t>Algerie, Argentina, England, Nederland, Spania, Tsjekkia, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="15" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Viktoria Plzeň</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E43" s="119" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Ghana, Irak, Tsjekkia, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" s="118" t="inlineStr">
+        <is>
+          <t>Belgia, Bosnia-Hercegovina, Elfenbenskysten, Ghana, Kroatia, Nederland, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Al-Duhail</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E45" s="119" t="inlineStr">
+        <is>
+          <t>Algerie, Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" s="118" t="inlineStr">
+        <is>
+          <t>Brasil, Ecuador, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="15" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E47" s="119" t="inlineStr">
+        <is>
+          <t>Brasil, DR Kongo, England, Sverige, Tyskland</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Belgia, Elfenbenskysten, Marokko, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="15" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Persepolis</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" s="119" t="inlineStr">
+        <is>
+          <t>Iran, Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Chivas</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E50" s="118" t="inlineStr">
+        <is>
+          <t>Colombia, Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="15" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E51" s="119" t="inlineStr">
+        <is>
+          <t>Japan, Sveits, Sør-Korea, Tyskland, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Borussia Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" s="118" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Japan, Sveits, Sør-Korea, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E53" s="119" t="inlineStr">
+        <is>
+          <t>Brasil, Canada, Nederland, Portugal, Tyrkia, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E54" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Canada, Nederland, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="15" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>BSC Young Boys</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" s="119" t="inlineStr">
+        <is>
+          <t>Algerie, Bosnia-Hercegovina, Haiti, Sveits, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" s="118" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Frankrike, Senegal, Sveits, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E57" s="119" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, England, New Zealand, Skottland, Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E58" s="118" t="inlineStr">
+        <is>
+          <t>Belgia, Elfenbenskysten, Portugal, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" s="119" t="inlineStr">
+        <is>
+          <t>Belgia, Ecuador, Jordan, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Auckland FC</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Ny-Zealand</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" s="118" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Al-Hussein</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E61" s="119" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E62" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, DR Kongo, Marokko, Mexico, Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Sveits, Sverige, Sør-Afrika, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="14" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Ulsan HD</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" s="118" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Feyenoord</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E65" s="119" t="inlineStr">
+        <is>
+          <t>Algerie, Australia, Japan, Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Wolverhampton</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" s="118" t="inlineStr">
+        <is>
+          <t>Colombia, Haiti, Norge, Portugal, Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" s="119" t="inlineStr">
+        <is>
+          <t>Argentina, Brasil, Ghana, Senegal, Tsjekkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" s="118" t="inlineStr">
+        <is>
+          <t>Canada, Elfenbenskysten, Portugal, Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E69" s="119" t="inlineStr">
+        <is>
+          <t>Australia, Canada, Panama, Skottland, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="14" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Al-Sadd</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E70" s="118" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Al-Arabi</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" s="119" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" s="118" t="inlineStr">
+        <is>
+          <t>Colombia, Kroatia, Norge, Skottland, Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="15" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" s="119" t="inlineStr">
+        <is>
+          <t>Brasil, Nederland, Skottland, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Roma</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="118" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Frankrike, Marokko, Nederland, Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Esteghlal</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" s="119" t="inlineStr">
+        <is>
+          <t>Haiti, Iran, Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" s="118" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Ghana, Kapp Verde, Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" s="119" t="inlineStr">
+        <is>
+          <t>Japan, Kroatia, Portugal, Spania</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>VfL Wolfsburg</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="118" t="inlineStr">
+        <is>
+          <t>Algerie, Ghana, Japan, Sverige, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Pyramids</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Egypt, Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Tractor</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" s="118" t="inlineStr">
+        <is>
+          <t>Iran, Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Club América</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E81" s="119" t="inlineStr">
+        <is>
+          <t>Mexico, USA, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Dynamo Moscow</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Russland</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" s="118" t="inlineStr">
+        <is>
+          <t>Colombia, Mexico, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>West Ham</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E83" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Nederland, Senegal, Tsjekkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E84" s="118" t="inlineStr">
+        <is>
+          <t>Sverige, Tsjekkia, Uruguay, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="15" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E85" s="119" t="inlineStr">
+        <is>
+          <t>Australia, Bosnia-Hercegovina, Canada, Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" s="118" t="inlineStr">
+        <is>
+          <t>Canada, Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>FC St. Pauli</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" s="119" t="inlineStr">
+        <is>
+          <t>Australia, Bosnia-Hercegovina, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Al-Wakrah</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="118" t="inlineStr">
+        <is>
+          <t>Egypt, Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="15" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>SC Freiburg</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" s="119" t="inlineStr">
+        <is>
+          <t>Japan, Kroatia, Sveits, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E90" s="118" t="inlineStr">
+        <is>
+          <t>Japan, Sveits, Sverige, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="15" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" s="119" t="inlineStr">
+        <is>
+          <t>Kroatia, Sveits, Tunisia, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Al-Ittihad</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" s="118" t="inlineStr">
+        <is>
+          <t>Algerie, Brasil, Saudi-Arabia</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" s="119" t="inlineStr">
+        <is>
+          <t>Brasil, England, Norge, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Genk</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" s="118" t="inlineStr">
+        <is>
+          <t>DR Kongo, Ecuador, Japan, Marokko</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="15" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Auxerre</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" s="119" t="inlineStr">
+        <is>
+          <t>Ghana, Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" s="118" t="inlineStr">
+        <is>
+          <t>Belgia, Skottland, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Rangers</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" s="119" t="inlineStr">
+        <is>
+          <t>Belgia, Norge, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="14" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" s="118" t="inlineStr">
+        <is>
+          <t>England, Senegal, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="17" customHeight="1">
+      <c r="A99" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Atlético Mineiro</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" s="119" t="inlineStr">
+        <is>
+          <t>Ecuador, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="17" customHeight="1">
+      <c r="A100" s="14" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Melbourne City</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" s="118" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Al-Faisaly</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" s="119" t="inlineStr">
+        <is>
+          <t>Australia, Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" s="118" t="inlineStr">
+        <is>
+          <t>Japan, Kroatia, Nederland</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E103" s="119" t="inlineStr">
+        <is>
+          <t>Ghana, Spania</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Pakhtakor</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E104" s="118" t="inlineStr">
+        <is>
+          <t>Irak, Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="17" customHeight="1">
+      <c r="A105" s="15" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>Al-Zawraa</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" s="119" t="inlineStr">
+        <is>
+          <t>Irak, Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Al-Shorta</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" s="118" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>AEL Limassol</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Kypros</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Mexico, Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Chicago Fire</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" s="118" t="inlineStr">
+        <is>
+          <t>Canada, Sør-Afrika, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="17" customHeight="1">
+      <c r="A109" s="15" t="n">
+        <v>107</v>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" s="119" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Kapp Verde, Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="17" customHeight="1">
+      <c r="A110" s="14" t="n">
+        <v>108</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" s="118" t="inlineStr">
+        <is>
+          <t>Canada, Curaçao, Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="17" customHeight="1">
+      <c r="A111" s="15" t="n">
+        <v>109</v>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>Sparta Prague</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" s="119" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="17" customHeight="1">
+      <c r="A112" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Inter Miami</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="17" customHeight="1">
+      <c r="A113" s="15" t="n">
+        <v>111</v>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" s="119" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Canada, Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="17" customHeight="1">
+      <c r="A114" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Orlando City</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="118" t="inlineStr">
+        <is>
+          <t>Canada, Kroatia, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="17" customHeight="1">
+      <c r="A115" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>Union Saint-Gilloise</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" s="119" t="inlineStr">
+        <is>
+          <t>Canada, Ecuador, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="17" customHeight="1">
+      <c r="A116" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" s="118" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="17" customHeight="1">
+      <c r="A117" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Pafos</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Kypros</t>
+        </is>
+      </c>
+      <c r="D117" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" s="119" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Ghana, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="17" customHeight="1">
+      <c r="A118" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Rijeka</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" s="118" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="17" customHeight="1">
+      <c r="A119" s="15" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>Al-Gharafa</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" s="119" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="17" customHeight="1">
+      <c r="A120" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Internazionale</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Sveits, Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="17" customHeight="1">
+      <c r="A121" s="15" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>Lorient</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" s="119" t="inlineStr">
+        <is>
+          <t>Senegal, Sveits, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="17" customHeight="1">
+      <c r="A122" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="118" t="inlineStr">
+        <is>
+          <t>Norge, Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="17" customHeight="1">
+      <c r="A123" s="15" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>Al-Ain</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" s="119" t="inlineStr">
+        <is>
+          <t>Egypt, Marokko, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="17" customHeight="1">
+      <c r="A124" s="14" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Dallas</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" s="118" t="inlineStr">
+        <is>
+          <t>Haiti, Kroatia, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="17" customHeight="1">
+      <c r="A125" s="15" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>Çaykur Rizespor</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" s="119" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Haiti, Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="17" customHeight="1">
+      <c r="A126" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" s="118" t="inlineStr">
+        <is>
+          <t>Kroatia, Norge, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="17" customHeight="1">
+      <c r="A127" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" s="119" t="inlineStr">
+        <is>
+          <t>Paraguay, Tunisia, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="17" customHeight="1">
+      <c r="A128" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" s="118" t="inlineStr">
+        <is>
+          <t>Australia, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="17" customHeight="1">
+      <c r="A129" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" s="119" t="inlineStr">
+        <is>
+          <t>Australia, DR Kongo, Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="17" customHeight="1">
+      <c r="A130" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Beşiktaş</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" s="118" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Panama, Tyrkia</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="17" customHeight="1">
+      <c r="A131" s="15" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D131" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="119" t="inlineStr">
+        <is>
+          <t>Curaçao, Kapp Verde, New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="17" customHeight="1">
+      <c r="A132" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Inter Milan</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" s="118" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Frankrike, Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="17" customHeight="1">
+      <c r="A133" s="15" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E133" s="119" t="inlineStr">
+        <is>
+          <t>Ecuador, Irak, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="17" customHeight="1">
+      <c r="A134" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" s="118" t="inlineStr">
+        <is>
+          <t>Argentina, Ecuador, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="17" customHeight="1">
+      <c r="A135" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D135" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E135" s="119" t="inlineStr">
+        <is>
+          <t>Japan, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="17" customHeight="1">
+      <c r="A136" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Le Havre</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" s="118" t="inlineStr">
+        <is>
+          <t>DR Kongo, Japan, Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="17" customHeight="1">
+      <c r="A137" s="15" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D137" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E137" s="119" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="17" customHeight="1">
+      <c r="A138" s="14" t="n">
+        <v>136</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" s="118" t="inlineStr">
+        <is>
+          <t>Egypt, Ghana, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="17" customHeight="1">
+      <c r="A139" s="15" t="n">
+        <v>137</v>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>Sepahan</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="D139" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" s="119" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="17" customHeight="1">
+      <c r="A140" s="14" t="n">
+        <v>138</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Wellington Phoenix</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Ny-Zealand</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" s="118" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="17" customHeight="1">
+      <c r="A141" s="15" t="n">
+        <v>139</v>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>Minnesota United</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D141" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" s="119" t="inlineStr">
+        <is>
+          <t>Colombia, New Zealand, Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="17" customHeight="1">
+      <c r="A142" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Russland</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E142" s="118" t="inlineStr">
+        <is>
+          <t>Colombia, Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="17" customHeight="1">
+      <c r="A143" s="15" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Frankrike, Saudi-Arabia</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="17" customHeight="1">
+      <c r="A144" s="14" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E144" s="118" t="inlineStr">
+        <is>
+          <t>Ghana, Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="17" customHeight="1">
+      <c r="A145" s="15" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>Pogoń Szczecin</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>Polen</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" s="119" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="17" customHeight="1">
+      <c r="A146" s="14" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Al-Karma</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E146" s="118" t="inlineStr">
+        <is>
+          <t>Irak, Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="17" customHeight="1">
+      <c r="A147" s="15" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
+        <is>
+          <t>Bodø/Glimt</t>
+        </is>
+      </c>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E147" s="119" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="17" customHeight="1">
+      <c r="A148" s="14" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Selangor</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" s="118" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="17" customHeight="1">
+      <c r="A149" s="15" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
+        <is>
+          <t>Neftchi</t>
+        </is>
+      </c>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>Aserbajdsjan</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E149" s="119" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="17" customHeight="1">
+      <c r="A150" s="14" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Nasaf</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E150" s="118" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="17" customHeight="1">
+      <c r="A151" s="15" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>Hellas</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" s="119" t="inlineStr">
+        <is>
+          <t>Ghana, Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="17" customHeight="1">
+      <c r="A152" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" s="118" t="inlineStr">
+        <is>
+          <t>Mexico, Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="17" customHeight="1">
+      <c r="A153" s="15" t="n">
+        <v>151</v>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" s="119" t="inlineStr">
+        <is>
+          <t>Colombia, Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="17" customHeight="1">
+      <c r="A154" s="14" t="n">
+        <v>152</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" s="118" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="17" customHeight="1">
+      <c r="A155" s="15" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
+        <is>
+          <t>Club Tijuana</t>
+        </is>
+      </c>
+      <c r="C155" s="8" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" s="119" t="inlineStr">
+        <is>
+          <t>Ecuador, Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="17" customHeight="1">
+      <c r="A156" s="14" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" s="118" t="inlineStr">
+        <is>
+          <t>Canada, Mexico</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="17" customHeight="1">
+      <c r="A157" s="15" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D157" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" s="119" t="inlineStr">
+        <is>
+          <t>Sør-Afrika, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="17" customHeight="1">
+      <c r="A158" s="14" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E158" s="118" t="inlineStr">
+        <is>
+          <t>Haiti, Sør-Afrika</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="17" customHeight="1">
+      <c r="A159" s="15" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" s="119" t="inlineStr">
+        <is>
+          <t>Japan, Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="17" customHeight="1">
+      <c r="A160" s="14" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>Jeonbuk</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D160" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E160" s="118" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="17" customHeight="1">
+      <c r="A161" s="15" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
+        <is>
+          <t>Wolves</t>
+        </is>
+      </c>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" s="119" t="inlineStr">
+        <is>
+          <t>Tsjekkia, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="17" customHeight="1">
+      <c r="A162" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D162" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E162" s="118" t="inlineStr">
+        <is>
+          <t>Canada, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="17" customHeight="1">
+      <c r="A163" s="15" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
+        <is>
+          <t>Bröndby IF</t>
+        </is>
+      </c>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="D163" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" s="119" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="17" customHeight="1">
+      <c r="A164" s="14" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>RB Salzburg</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="D164" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E164" s="118" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="17" customHeight="1">
+      <c r="A165" s="15" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
+        <is>
+          <t>Al Rayyan</t>
+        </is>
+      </c>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D165" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" s="119" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="17" customHeight="1">
+      <c r="A166" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Hamburg</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D166" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" s="118" t="inlineStr">
+        <is>
+          <t>Kroatia, Sveits</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="17" customHeight="1">
+      <c r="A167" s="15" t="n">
+        <v>165</v>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
+        <is>
+          <t>Grêmio</t>
+        </is>
+      </c>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D167" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E167" s="119" t="inlineStr">
+        <is>
+          <t>Brasil, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="17" customHeight="1">
+      <c r="A168" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D168" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" s="118" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="17" customHeight="1">
+      <c r="A169" s="15" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t>Zenit</t>
+        </is>
+      </c>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>Russland</t>
+        </is>
+      </c>
+      <c r="D169" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" s="119" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="17" customHeight="1">
+      <c r="A170" s="14" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D170" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" s="118" t="inlineStr">
+        <is>
+          <t>Belgia, Marokko</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="17" customHeight="1">
+      <c r="A171" s="15" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D171" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" s="119" t="inlineStr">
+        <is>
+          <t>Haiti, Marokko</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="17" customHeight="1">
+      <c r="A172" s="14" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Hellas</t>
+        </is>
+      </c>
+      <c r="D172" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E172" s="118" t="inlineStr">
+        <is>
+          <t>Iran, Marokko</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="17" customHeight="1">
+      <c r="A173" s="15" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
+        <is>
+          <t>LDU Quito</t>
+        </is>
+      </c>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D173" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" s="119" t="inlineStr">
+        <is>
+          <t>Ecuador, Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="17" customHeight="1">
+      <c r="A174" s="14" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Lugano</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D174" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" s="118" t="inlineStr">
+        <is>
+          <t>Haiti, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="17" customHeight="1">
+      <c r="A175" s="15" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
+        <is>
+          <t>FC Sochaux</t>
+        </is>
+      </c>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D175" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E175" s="119" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="17" customHeight="1">
+      <c r="A176" s="14" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>Colorado Springs Switchbacks</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D176" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" s="118" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="17" customHeight="1">
+      <c r="A177" s="15" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D177" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E177" s="119" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="17" customHeight="1">
+      <c r="A178" s="14" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D178" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E178" s="118" t="inlineStr">
+        <is>
+          <t>New Zealand, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="17" customHeight="1">
+      <c r="A179" s="15" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
+        <is>
+          <t>Ipswich Town</t>
+        </is>
+      </c>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D179" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" s="119" t="inlineStr">
+        <is>
+          <t>Irak, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="17" customHeight="1">
+      <c r="A180" s="14" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>Hearts</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D180" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E180" s="118" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="17" customHeight="1">
+      <c r="A181" s="15" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>Kilmarnock</t>
+        </is>
+      </c>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D181" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E181" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="17" customHeight="1">
+      <c r="A182" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+      <c r="D182" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E182" s="118" t="inlineStr">
+        <is>
+          <t>Kroatia, Skottland</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="17" customHeight="1">
+      <c r="A183" s="15" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D183" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" s="119" t="inlineStr">
+        <is>
+          <t>Kapp Verde, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="17" customHeight="1">
+      <c r="A184" s="14" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>Coventry City</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D184" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E184" s="118" t="inlineStr">
+        <is>
+          <t>Ghana, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="17" customHeight="1">
+      <c r="A185" s="15" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D185" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" s="119" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="17" customHeight="1">
+      <c r="A186" s="14" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D186" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" s="118" t="inlineStr">
+        <is>
+          <t>Norge, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="17" customHeight="1">
+      <c r="A187" s="15" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>Atlanta United</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D187" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E187" s="119" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="17" customHeight="1">
+      <c r="A188" s="14" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D188" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E188" s="118" t="inlineStr">
+        <is>
+          <t>Ecuador, Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="17" customHeight="1">
+      <c r="A189" s="15" t="n">
+        <v>187</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D189" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E189" s="119" t="inlineStr">
+        <is>
+          <t>Australia, Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="17" customHeight="1">
+      <c r="A190" s="14" t="n">
+        <v>188</v>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D190" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E190" s="118" t="inlineStr">
+        <is>
+          <t>Australia, DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="17" customHeight="1">
+      <c r="A191" s="15" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D191" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" s="119" t="inlineStr">
+        <is>
+          <t>Australia, Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="17" customHeight="1">
+      <c r="A192" s="14" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D192" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E192" s="118" t="inlineStr">
+        <is>
+          <t>Australia, New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="17" customHeight="1">
+      <c r="A193" s="15" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D193" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E193" s="119" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="17" customHeight="1">
+      <c r="A194" s="14" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D194" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E194" s="118" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="17" customHeight="1">
+      <c r="A195" s="15" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D195" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E195" s="119" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="17" customHeight="1">
+      <c r="A196" s="14" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>Iğdır</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D196" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E196" s="118" t="inlineStr">
+        <is>
+          <t>Curaçao, Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="17" customHeight="1">
+      <c r="A197" s="15" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
+        <is>
+          <t>AE Kifisia</t>
+        </is>
+      </c>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>Hellas</t>
+        </is>
+      </c>
+      <c r="D197" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E197" s="119" t="inlineStr">
+        <is>
+          <t>Curaçao, Ecuador</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="17" customHeight="1">
+      <c r="A198" s="14" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>SC Telstar</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D198" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E198" s="118" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="17" customHeight="1">
+      <c r="A199" s="15" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
+        <is>
+          <t>Maccabi Haifa</t>
+        </is>
+      </c>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="D199" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E199" s="119" t="inlineStr">
+        <is>
+          <t>Curaçao, Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="17" customHeight="1">
+      <c r="A200" s="14" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>Nijmegen</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D200" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E200" s="118" t="inlineStr">
+        <is>
+          <t>Curaçao, Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="17" customHeight="1">
+      <c r="A201" s="15" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t>NK Maribor</t>
+        </is>
+      </c>
+      <c r="C201" s="8" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="D201" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E201" s="119" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="17" customHeight="1">
+      <c r="A202" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>Royal Charleroi</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E202" s="118" t="inlineStr">
+        <is>
+          <t>Algerie, Elfenbenskysten</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="17" customHeight="1">
+      <c r="A203" s="15" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>Hellas</t>
+        </is>
+      </c>
+      <c r="D203" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E203" s="119" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="17" customHeight="1">
+      <c r="A204" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>Huracán</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D204" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E204" s="118" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="17" customHeight="1">
+      <c r="A205" s="15" t="n">
+        <v>203</v>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D205" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E205" s="119" t="inlineStr">
+        <is>
+          <t>Ecuador, Uruguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="17" customHeight="1">
+      <c r="A206" s="14" t="n">
+        <v>204</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D206" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E206" s="118" t="inlineStr">
+        <is>
+          <t>Ecuador, Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="17" customHeight="1">
+      <c r="A207" s="15" t="n">
+        <v>205</v>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
+        <is>
+          <t>Midtjylland</t>
+        </is>
+      </c>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="D207" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E207" s="119" t="inlineStr">
+        <is>
+          <t>Ecuador, Kroatia</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="17" customHeight="1">
+      <c r="A208" s="14" t="n">
+        <v>206</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>Sint-Truiden</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D208" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E208" s="118" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="17" customHeight="1">
+      <c r="A209" s="15" t="n">
+        <v>207</v>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>Derby County</t>
+        </is>
+      </c>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D209" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E209" s="119" t="inlineStr">
+        <is>
+          <t>Norge, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="17" customHeight="1">
+      <c r="A210" s="14" t="n">
+        <v>208</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D210" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E210" s="118" t="inlineStr">
+        <is>
+          <t>Spania, Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="17" customHeight="1">
+      <c r="A211" s="15" t="n">
+        <v>209</v>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
+        <is>
+          <t>Club Africain</t>
+        </is>
+      </c>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D211" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E211" s="119" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="17" customHeight="1">
+      <c r="A212" s="14" t="n">
+        <v>210</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>Kasimpasa</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D212" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E212" s="118" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="17" customHeight="1">
+      <c r="A213" s="15" t="n">
+        <v>211</v>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="C213" s="8" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="D213" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E213" s="119" t="inlineStr">
+        <is>
+          <t>Kroatia, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="17" customHeight="1">
+      <c r="A214" s="14" t="n">
+        <v>212</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>Espérance de Tunis</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D214" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E214" s="118" t="inlineStr">
+        <is>
+          <t>Algerie, Tunisia</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="17" customHeight="1">
+      <c r="A215" s="15" t="n">
+        <v>213</v>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
+        <is>
+          <t>El Gouna</t>
+        </is>
+      </c>
+      <c r="C215" s="8" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D215" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E215" s="119" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="17" customHeight="1">
+      <c r="A216" s="14" t="n">
+        <v>214</v>
+      </c>
+      <c r="B216" s="5" t="inlineStr">
+        <is>
+          <t>Nordsjaelland</t>
+        </is>
+      </c>
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>Danmark</t>
+        </is>
+      </c>
+      <c r="D216" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E216" s="118" t="inlineStr">
+        <is>
+          <t>Egypt, Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="17" customHeight="1">
+      <c r="A217" s="15" t="n">
+        <v>215</v>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
+        <is>
+          <t>Zed</t>
+        </is>
+      </c>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D217" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E217" s="119" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="17" customHeight="1">
+      <c r="A218" s="14" t="n">
+        <v>216</v>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>Kalba</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D218" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E218" s="118" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="17" customHeight="1">
+      <c r="A219" s="15" t="n">
+        <v>217</v>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t>Standard Liege</t>
+        </is>
+      </c>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D219" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E219" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo, Iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="17" customHeight="1">
+      <c r="A220" s="14" t="n">
+        <v>218</v>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="D220" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E220" s="118" t="inlineStr">
+        <is>
+          <t>New Zealand, Norge</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="17" customHeight="1">
+      <c r="A221" s="15" t="n">
+        <v>219</v>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
+        <is>
+          <t>Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="C221" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D221" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E221" s="119" t="inlineStr">
+        <is>
+          <t>Ghana, New Zealand</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="17" customHeight="1">
+      <c r="A222" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D222" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E222" s="118" t="inlineStr">
+        <is>
+          <t>Kroatia, Spania</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="17" customHeight="1">
+      <c r="A223" s="15" t="n">
+        <v>221</v>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="C223" s="8" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D223" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E223" s="119" t="inlineStr">
+        <is>
+          <t>Algerie, Kapp Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="17" customHeight="1">
+      <c r="A224" s="14" t="n">
+        <v>222</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D224" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E224" s="118" t="inlineStr">
+        <is>
+          <t>Kapp Verde, Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="17" customHeight="1">
+      <c r="A225" s="15" t="n">
+        <v>223</v>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
+        <is>
+          <t>Rennes</t>
+        </is>
+      </c>
+      <c r="C225" s="8" t="inlineStr">
+        <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="D225" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E225" s="119" t="inlineStr">
+        <is>
+          <t>Frankrike, Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="17" customHeight="1">
+      <c r="A226" s="14" t="n">
+        <v>224</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>Italia</t>
+        </is>
+      </c>
+      <c r="D226" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E226" s="118" t="inlineStr">
+        <is>
+          <t>Kroatia, Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="17" customHeight="1">
+      <c r="A227" s="15" t="n">
+        <v>225</v>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>Al-Talaba</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D227" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E227" s="119" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="17" customHeight="1">
+      <c r="A228" s="14" t="n">
+        <v>226</v>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>Dibba</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="D228" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E228" s="118" t="inlineStr">
+        <is>
+          <t>Irak, Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="17" customHeight="1">
+      <c r="A229" s="15" t="n">
+        <v>227</v>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>LASK</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="D229" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E229" s="119" t="inlineStr">
+        <is>
+          <t>Panama, Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="17" customHeight="1">
+      <c r="A230" s="14" t="n">
+        <v>228</v>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>Al-Wehdat</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="D230" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E230" s="118" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="17" customHeight="1">
+      <c r="A231" s="15" t="n">
+        <v>229</v>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>Hellas</t>
+        </is>
+      </c>
+      <c r="D231" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E231" s="119" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="17" customHeight="1">
+      <c r="A232" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>Navbahor</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D232" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E232" s="118" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="17" customHeight="1">
+      <c r="A233" s="15" t="n">
+        <v>231</v>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
+        <is>
+          <t>Bukhara</t>
+        </is>
+      </c>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D233" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E233" s="119" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="17" customHeight="1">
+      <c r="A234" s="14" t="n">
+        <v>232</v>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>Deportivo Saprissa</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="D234" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E234" s="118" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="17" customHeight="1">
+      <c r="A235" s="15" t="n">
+        <v>233</v>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>CD Plaza Amador</t>
+        </is>
+      </c>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="D235" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E235" s="119" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="17" customHeight="1">
+      <c r="A236" s="14" t="n">
+        <v>234</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>CD Universidad Catolica</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D236" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E236" s="118" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -48051,7 +48051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -48899,99 +48899,95 @@
       <c r="A19" s="75" t="inlineStr"/>
       <c r="B19" s="76" t="inlineStr">
         <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="C19" s="74" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D19" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="E19" s="77" t="n">
-        <v>0</v>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="C19" s="83" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D19" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E19" s="78" t="n">
+        <v>12</v>
       </c>
       <c r="F19" s="77" t="n">
         <v>3</v>
       </c>
       <c r="G19" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="80" t="inlineStr">
+        <is>
+          <t>4–2</t>
+        </is>
+      </c>
+      <c r="I19" s="81" t="n">
         <v>3</v>
       </c>
-      <c r="H19" s="80" t="inlineStr">
-        <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="I19" s="81" t="n">
-        <v>4</v>
-      </c>
       <c r="J19" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="K19" s="78" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="78" t="n">
-        <v>12</v>
-      </c>
-      <c r="M19" s="68" t="n">
-        <v>0.6</v>
+        <v>2</v>
+      </c>
+      <c r="K19" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" s="74" t="n">
+        <v>0.31</v>
       </c>
       <c r="N19" s="76" t="inlineStr">
         <is>
-          <t>Marokko</t>
+          <t>Haiti</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe D</t>
-        </is>
-      </c>
+      <c r="A20" s="82" t="inlineStr"/>
       <c r="B20" s="67" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Skottland</t>
         </is>
       </c>
       <c r="C20" s="74" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="D20" s="70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" s="70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20" s="70" t="n">
         <v>3</v>
       </c>
       <c r="G20" s="71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="72" t="inlineStr">
         <is>
-          <t>2–0</t>
+          <t>0–1</t>
         </is>
       </c>
       <c r="I20" s="73" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J20" s="70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K20" s="69" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L20" s="69" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="M20" s="68" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="N20" s="67" t="inlineStr">
         <is>
-          <t>Tyrkia</t>
+          <t>Marokko</t>
         </is>
       </c>
     </row>
@@ -48999,95 +48995,99 @@
       <c r="A21" s="75" t="inlineStr"/>
       <c r="B21" s="76" t="inlineStr">
         <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="C21" s="84" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D21" s="77" t="n">
+        <v>11</v>
+      </c>
+      <c r="E21" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F21" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="80" t="inlineStr">
+        <is>
+          <t>0–3</t>
+        </is>
+      </c>
+      <c r="I21" s="81" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K21" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="78" t="n">
+        <v>21</v>
+      </c>
+      <c r="M21" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N21" s="76" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe D</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C22" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D22" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="72" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I22" s="73" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" s="70" t="n">
+        <v>10</v>
+      </c>
+      <c r="K22" s="69" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" s="69" t="n">
+        <v>28</v>
+      </c>
+      <c r="M22" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N22" s="67" t="inlineStr">
+        <is>
           <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="C21" s="83" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D21" s="78" t="n">
-        <v>33</v>
-      </c>
-      <c r="E21" s="78" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" s="77" t="n">
-        <v>15</v>
-      </c>
-      <c r="G21" s="79" t="n">
-        <v>12</v>
-      </c>
-      <c r="H21" s="80" t="inlineStr">
-        <is>
-          <t>0–1</t>
-        </is>
-      </c>
-      <c r="I21" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J21" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L21" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="M21" s="74" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N21" s="76" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="82" t="inlineStr"/>
-      <c r="B22" s="67" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C22" s="68" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="D22" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E22" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="F22" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="G22" s="71" t="n">
-        <v>6</v>
-      </c>
-      <c r="H22" s="72" t="inlineStr">
-        <is>
-          <t>4–1</t>
-        </is>
-      </c>
-      <c r="I22" s="73" t="n">
-        <v>4</v>
-      </c>
-      <c r="J22" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="M22" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N22" s="67" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -49095,79 +49095,75 @@
       <c r="A23" s="75" t="inlineStr"/>
       <c r="B23" s="76" t="inlineStr">
         <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="C23" s="68" t="n">
-        <v>0.63</v>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="C23" s="83" t="n">
+        <v>0.78</v>
       </c>
       <c r="D23" s="78" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" s="77" t="n">
+        <v>33</v>
+      </c>
+      <c r="E23" s="78" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="77" t="n">
+        <v>15</v>
+      </c>
+      <c r="G23" s="79" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" s="80" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="I23" s="81" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="79" t="n">
-        <v>5</v>
-      </c>
-      <c r="H23" s="80" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I23" s="81" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" s="77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="77" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="74" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N23" s="76" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="82" t="inlineStr"/>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C24" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D24" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="E24" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="N23" s="76" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe E</t>
-        </is>
-      </c>
-      <c r="B24" s="67" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="C24" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D24" s="69" t="n">
-        <v>26</v>
-      </c>
-      <c r="E24" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="F24" s="70" t="n">
-        <v>7</v>
-      </c>
       <c r="G24" s="71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H24" s="72" t="inlineStr">
         <is>
-          <t>0–0</t>
+          <t>4–1</t>
         </is>
       </c>
       <c r="I24" s="73" t="n">
@@ -49177,17 +49173,17 @@
         <v>2</v>
       </c>
       <c r="K24" s="70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L24" s="70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M24" s="74" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="N24" s="67" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Paraguay</t>
         </is>
       </c>
     </row>
@@ -49195,91 +49191,95 @@
       <c r="A25" s="75" t="inlineStr"/>
       <c r="B25" s="76" t="inlineStr">
         <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="C25" s="84" t="n">
-        <v>0.49</v>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="C25" s="68" t="n">
+        <v>0.63</v>
       </c>
       <c r="D25" s="78" t="n">
-        <v>16</v>
-      </c>
-      <c r="E25" s="78" t="n">
-        <v>4</v>
+        <v>8</v>
+      </c>
+      <c r="E25" s="77" t="n">
+        <v>2</v>
       </c>
       <c r="F25" s="77" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G25" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H25" s="80" t="inlineStr">
+        <is>
+          <t>2–0</t>
+        </is>
+      </c>
+      <c r="I25" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="H25" s="80" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I25" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="77" t="n">
-        <v>8</v>
-      </c>
       <c r="K25" s="77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="M25" s="84" t="n">
-        <v>0.51</v>
+        <v>5</v>
+      </c>
+      <c r="M25" s="74" t="n">
+        <v>0.37</v>
       </c>
       <c r="N25" s="76" t="inlineStr">
         <is>
+          <t>Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe E</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
           <t>Ecuador</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="82" t="inlineStr"/>
-      <c r="B26" s="67" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
       <c r="C26" s="83" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="D26" s="69" t="n">
         <v>26</v>
       </c>
       <c r="E26" s="69" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F26" s="70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G26" s="71" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="72" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I26" s="73" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="H26" s="72" t="inlineStr">
-        <is>
-          <t>7–1</t>
-        </is>
-      </c>
-      <c r="I26" s="73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="K26" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L26" s="70" t="n">
-        <v>7</v>
-      </c>
       <c r="M26" s="74" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="N26" s="67" t="inlineStr">
         <is>
@@ -49291,79 +49291,75 @@
       <c r="A27" s="75" t="inlineStr"/>
       <c r="B27" s="76" t="inlineStr">
         <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="C27" s="68" t="n">
-        <v>0.55</v>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="C27" s="84" t="n">
+        <v>0.49</v>
       </c>
       <c r="D27" s="78" t="n">
         <v>16</v>
       </c>
       <c r="E27" s="78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F27" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="80" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I27" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="M27" s="84" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N27" s="76" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="82" t="inlineStr"/>
+      <c r="B28" s="67" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C28" s="83" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D28" s="69" t="n">
+        <v>26</v>
+      </c>
+      <c r="E28" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="79" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" s="80" t="inlineStr">
-        <is>
-          <t>2–1</t>
-        </is>
-      </c>
-      <c r="I27" s="81" t="n">
-        <v>5</v>
-      </c>
-      <c r="J27" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L27" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="M27" s="84" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N27" s="76" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe F</t>
-        </is>
-      </c>
-      <c r="B28" s="67" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="C28" s="68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D28" s="69" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" s="69" t="n">
-        <v>7</v>
-      </c>
-      <c r="F28" s="70" t="n">
-        <v>4</v>
-      </c>
       <c r="G28" s="71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H28" s="72" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>7–1</t>
         </is>
       </c>
       <c r="I28" s="73" t="n">
@@ -49373,17 +49369,17 @@
         <v>5</v>
       </c>
       <c r="K28" s="70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" s="70" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M28" s="74" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="N28" s="67" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Curaçao</t>
         </is>
       </c>
     </row>
@@ -49391,95 +49387,99 @@
       <c r="A29" s="75" t="inlineStr"/>
       <c r="B29" s="76" t="inlineStr">
         <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D29" s="78" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" s="78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F29" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G29" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="80" t="inlineStr">
+        <is>
+          <t>2–1</t>
+        </is>
+      </c>
+      <c r="I29" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L29" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="M29" s="84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N29" s="76" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe F</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
           <t>Nederland</t>
         </is>
       </c>
-      <c r="C29" s="84" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="D29" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E29" s="77" t="n">
+      <c r="C30" s="68" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="F29" s="77" t="n">
+      <c r="F30" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="72" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I30" s="73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="80" t="inlineStr">
-        <is>
-          <t>5–1</t>
-        </is>
-      </c>
-      <c r="I29" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="K29" s="78" t="n">
-        <v>9</v>
-      </c>
-      <c r="L29" s="78" t="n">
-        <v>20</v>
-      </c>
-      <c r="M29" s="84" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="N29" s="76" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="82" t="inlineStr"/>
-      <c r="B30" s="67" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="C30" s="84" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="D30" s="69" t="n">
-        <v>13</v>
-      </c>
-      <c r="E30" s="69" t="n">
+      <c r="L30" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="F30" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" s="71" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="72" t="inlineStr">
-        <is>
-          <t>5–1</t>
-        </is>
-      </c>
-      <c r="I30" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" s="70" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" s="84" t="n">
-        <v>0.51</v>
+      <c r="M30" s="74" t="n">
+        <v>0.4</v>
       </c>
       <c r="N30" s="67" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Japan</t>
         </is>
       </c>
     </row>
@@ -49487,99 +49487,95 @@
       <c r="A31" s="75" t="inlineStr"/>
       <c r="B31" s="76" t="inlineStr">
         <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="C31" s="74" t="n">
-        <v>0.43</v>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="C31" s="84" t="n">
+        <v>0.52</v>
       </c>
       <c r="D31" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="F31" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="77" t="n">
-        <v>1</v>
-      </c>
       <c r="G31" s="79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="80" t="inlineStr">
         <is>
-          <t>0–4</t>
+          <t>5–1</t>
         </is>
       </c>
       <c r="I31" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" s="78" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" s="78" t="n">
+        <v>20</v>
+      </c>
+      <c r="M31" s="84" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N31" s="76" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="82" t="inlineStr"/>
+      <c r="B32" s="67" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="C32" s="84" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="D32" s="69" t="n">
+        <v>13</v>
+      </c>
+      <c r="E32" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="J31" s="77" t="n">
+      <c r="G32" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="K31" s="78" t="n">
-        <v>5</v>
-      </c>
-      <c r="L31" s="78" t="n">
-        <v>10</v>
-      </c>
-      <c r="M31" s="68" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N31" s="76" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe G</t>
-        </is>
-      </c>
-      <c r="B32" s="67" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="C32" s="84" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="D32" s="69" t="n">
-        <v>15</v>
-      </c>
-      <c r="E32" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="F32" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" s="71" t="n">
-        <v>5</v>
-      </c>
       <c r="H32" s="72" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>5–1</t>
         </is>
       </c>
       <c r="I32" s="73" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J32" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="K32" s="69" t="n">
-        <v>4</v>
+      <c r="K32" s="70" t="n">
+        <v>2</v>
       </c>
       <c r="L32" s="70" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M32" s="84" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="N32" s="67" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Tunisia</t>
         </is>
       </c>
     </row>
@@ -49587,95 +49583,99 @@
       <c r="A33" s="75" t="inlineStr"/>
       <c r="B33" s="76" t="inlineStr">
         <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="C33" s="74" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D33" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="80" t="inlineStr">
+        <is>
+          <t>0–4</t>
+        </is>
+      </c>
+      <c r="I33" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" s="78" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" s="68" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N33" s="76" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe G</t>
+        </is>
+      </c>
+      <c r="B34" s="67" t="inlineStr">
+        <is>
           <t>Belgia</t>
         </is>
       </c>
-      <c r="C33" s="83" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="D33" s="78" t="n">
-        <v>22</v>
-      </c>
-      <c r="E33" s="78" t="n">
+      <c r="C34" s="84" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D34" s="69" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="70" t="n">
         <v>7</v>
-      </c>
-      <c r="F33" s="77" t="n">
-        <v>8</v>
-      </c>
-      <c r="G33" s="79" t="n">
-        <v>6</v>
-      </c>
-      <c r="H33" s="80" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I33" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="M33" s="74" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N33" s="76" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="82" t="inlineStr"/>
-      <c r="B34" s="67" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="C34" s="84" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D34" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="E34" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F34" s="70" t="n">
-        <v>8</v>
       </c>
       <c r="G34" s="71" t="n">
         <v>5</v>
       </c>
       <c r="H34" s="72" t="inlineStr">
         <is>
-          <t>2–2</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I34" s="73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J34" s="70" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L34" s="70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M34" s="84" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="N34" s="67" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Egypt</t>
         </is>
       </c>
     </row>
@@ -49683,99 +49683,95 @@
       <c r="A35" s="75" t="inlineStr"/>
       <c r="B35" s="76" t="inlineStr">
         <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="C35" s="83" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D35" s="78" t="n">
+        <v>22</v>
+      </c>
+      <c r="E35" s="78" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G35" s="79" t="n">
+        <v>6</v>
+      </c>
+      <c r="H35" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I35" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L35" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="M35" s="74" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N35" s="76" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="82" t="inlineStr"/>
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="C36" s="84" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D36" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="E36" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G36" s="71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H36" s="72" t="inlineStr">
+        <is>
+          <t>2–2</t>
+        </is>
+      </c>
+      <c r="I36" s="73" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="70" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L36" s="70" t="n">
+        <v>13</v>
+      </c>
+      <c r="M36" s="84" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N36" s="67" t="inlineStr">
+        <is>
           <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="C35" s="74" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="D35" s="77" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="F35" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="79" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="80" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="I35" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="J35" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K35" s="78" t="n">
-        <v>7</v>
-      </c>
-      <c r="L35" s="78" t="n">
-        <v>19</v>
-      </c>
-      <c r="M35" s="68" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="N35" s="76" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe H</t>
-        </is>
-      </c>
-      <c r="B36" s="67" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="C36" s="74" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D36" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="E36" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="72" t="inlineStr">
-        <is>
-          <t>1–1</t>
-        </is>
-      </c>
-      <c r="I36" s="73" t="n">
-        <v>9</v>
-      </c>
-      <c r="J36" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="K36" s="69" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="69" t="n">
-        <v>27</v>
-      </c>
-      <c r="M36" s="83" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="N36" s="67" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
         </is>
       </c>
     </row>
@@ -49783,95 +49779,99 @@
       <c r="A37" s="75" t="inlineStr"/>
       <c r="B37" s="76" t="inlineStr">
         <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C37" s="83" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="D37" s="78" t="n">
-        <v>23</v>
-      </c>
-      <c r="E37" s="78" t="n">
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C37" s="74" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D37" s="77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="80" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I37" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K37" s="78" t="n">
+        <v>7</v>
+      </c>
+      <c r="L37" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="M37" s="68" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="N37" s="76" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe H</t>
+        </is>
+      </c>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C38" s="74" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D38" s="70" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="72" t="inlineStr">
+        <is>
+          <t>1–1</t>
+        </is>
+      </c>
+      <c r="I38" s="73" t="n">
+        <v>9</v>
+      </c>
+      <c r="J38" s="70" t="n">
         <v>8</v>
       </c>
-      <c r="F37" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="G37" s="79" t="n">
-        <v>6</v>
-      </c>
-      <c r="H37" s="80" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I37" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J37" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K37" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="M37" s="74" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="N37" s="76" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="82" t="inlineStr"/>
-      <c r="B38" s="67" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="C38" s="83" t="n">
+      <c r="K38" s="69" t="n">
+        <v>10</v>
+      </c>
+      <c r="L38" s="69" t="n">
+        <v>27</v>
+      </c>
+      <c r="M38" s="83" t="n">
         <v>0.65</v>
       </c>
-      <c r="D38" s="69" t="n">
-        <v>21</v>
-      </c>
-      <c r="E38" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="F38" s="70" t="n">
-        <v>11</v>
-      </c>
-      <c r="G38" s="71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="72" t="inlineStr">
-        <is>
-          <t>4–0</t>
-        </is>
-      </c>
-      <c r="I38" s="73" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="M38" s="74" t="n">
-        <v>0.35</v>
-      </c>
       <c r="N38" s="67" t="inlineStr">
         <is>
-          <t>Saudi-Arabia</t>
+          <t>Uruguay</t>
         </is>
       </c>
     </row>
@@ -49879,43 +49879,43 @@
       <c r="A39" s="75" t="inlineStr"/>
       <c r="B39" s="76" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Spania</t>
         </is>
       </c>
       <c r="C39" s="83" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="D39" s="78" t="n">
-        <v>16</v>
-      </c>
-      <c r="E39" s="77" t="n">
+        <v>23</v>
+      </c>
+      <c r="E39" s="78" t="n">
+        <v>8</v>
+      </c>
+      <c r="F39" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" s="79" t="n">
+        <v>6</v>
+      </c>
+      <c r="H39" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I39" s="81" t="n">
         <v>2</v>
-      </c>
-      <c r="F39" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="G39" s="79" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" s="80" t="inlineStr">
-        <is>
-          <t>2–2</t>
-        </is>
-      </c>
-      <c r="I39" s="81" t="n">
-        <v>4</v>
       </c>
       <c r="J39" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="K39" s="78" t="n">
-        <v>4</v>
+      <c r="K39" s="77" t="n">
+        <v>1</v>
       </c>
       <c r="L39" s="77" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M39" s="74" t="n">
-        <v>0.34</v>
+        <v>0.26</v>
       </c>
       <c r="N39" s="76" t="inlineStr">
         <is>
@@ -49924,54 +49924,50 @@
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe I</t>
-        </is>
-      </c>
+      <c r="A40" s="82" t="inlineStr"/>
       <c r="B40" s="67" t="inlineStr">
         <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C40" s="84" t="n">
-        <v>0.54</v>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="C40" s="83" t="n">
+        <v>0.65</v>
       </c>
       <c r="D40" s="69" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E40" s="69" t="n">
         <v>9</v>
       </c>
       <c r="F40" s="70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G40" s="71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="72" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>4–0</t>
         </is>
       </c>
       <c r="I40" s="73" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="L40" s="70" t="n">
-        <v>6</v>
-      </c>
-      <c r="M40" s="84" t="n">
-        <v>0.46</v>
+      <c r="M40" s="74" t="n">
+        <v>0.35</v>
       </c>
       <c r="N40" s="67" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Saudi-Arabia</t>
         </is>
       </c>
     </row>
@@ -49979,95 +49975,99 @@
       <c r="A41" s="75" t="inlineStr"/>
       <c r="B41" s="76" t="inlineStr">
         <is>
-          <t>Frankrike</t>
-        </is>
-      </c>
-      <c r="C41" s="68" t="n">
-        <v>0.5600000000000001</v>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="C41" s="83" t="n">
+        <v>0.66</v>
       </c>
       <c r="D41" s="78" t="n">
-        <v>19</v>
-      </c>
-      <c r="E41" s="78" t="n">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="E41" s="77" t="n">
+        <v>2</v>
       </c>
       <c r="F41" s="77" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G41" s="79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H41" s="80" t="inlineStr">
         <is>
-          <t>3–0</t>
+          <t>2–2</t>
         </is>
       </c>
       <c r="I41" s="81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J41" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="K41" s="77" t="n">
-        <v>0</v>
+      <c r="K41" s="78" t="n">
+        <v>4</v>
       </c>
       <c r="L41" s="77" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M41" s="74" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="N41" s="76" t="inlineStr">
         <is>
-          <t>Irak</t>
+          <t>Kapp Verde</t>
         </is>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="82" t="inlineStr"/>
+      <c r="A42" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe I</t>
+        </is>
+      </c>
       <c r="B42" s="67" t="inlineStr">
         <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="C42" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D42" s="70" t="n">
-        <v>11</v>
-      </c>
-      <c r="E42" s="70" t="n">
-        <v>1</v>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C42" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D42" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="E42" s="69" t="n">
+        <v>9</v>
       </c>
       <c r="F42" s="70" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G42" s="71" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="72" t="inlineStr">
         <is>
-          <t>1–4</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I42" s="73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="70" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="K42" s="69" t="n">
+      <c r="K42" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" s="70" t="n">
         <v>6</v>
       </c>
-      <c r="L42" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="M42" s="68" t="n">
-        <v>0.63</v>
+      <c r="M42" s="84" t="n">
+        <v>0.46</v>
       </c>
       <c r="N42" s="67" t="inlineStr">
         <is>
-          <t>Norge</t>
+          <t>Senegal</t>
         </is>
       </c>
     </row>
@@ -50075,99 +50075,95 @@
       <c r="A43" s="75" t="inlineStr"/>
       <c r="B43" s="76" t="inlineStr">
         <is>
+          <t>Frankrike</t>
+        </is>
+      </c>
+      <c r="C43" s="68" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D43" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E43" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" s="77" t="n">
+        <v>9</v>
+      </c>
+      <c r="G43" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="H43" s="80" t="inlineStr">
+        <is>
+          <t>3–0</t>
+        </is>
+      </c>
+      <c r="I43" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="77" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" s="74" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N43" s="76" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="82" t="inlineStr"/>
+      <c r="B44" s="67" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="C44" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D44" s="70" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" s="70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="G44" s="71" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="72" t="inlineStr">
+        <is>
+          <t>1–4</t>
+        </is>
+      </c>
+      <c r="I44" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="L44" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="M44" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N44" s="67" t="inlineStr">
+        <is>
           <t>Norge</t>
-        </is>
-      </c>
-      <c r="C43" s="74" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D43" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E43" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="F43" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" s="79" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="80" t="inlineStr">
-        <is>
-          <t>3–2</t>
-        </is>
-      </c>
-      <c r="I43" s="81" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="K43" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="L43" s="78" t="n">
-        <v>17</v>
-      </c>
-      <c r="M43" s="68" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="N43" s="76" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe J</t>
-        </is>
-      </c>
-      <c r="B44" s="67" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="C44" s="84" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="D44" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="E44" s="69" t="n">
-        <v>6</v>
-      </c>
-      <c r="F44" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" s="71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="72" t="inlineStr">
-        <is>
-          <t>3–0</t>
-        </is>
-      </c>
-      <c r="I44" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="70" t="n">
-        <v>3</v>
-      </c>
-      <c r="K44" s="70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="70" t="n">
-        <v>6</v>
-      </c>
-      <c r="M44" s="84" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="N44" s="67" t="inlineStr">
-        <is>
-          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -50175,91 +50171,95 @@
       <c r="A45" s="75" t="inlineStr"/>
       <c r="B45" s="76" t="inlineStr">
         <is>
+          <t>Norge</t>
+        </is>
+      </c>
+      <c r="C45" s="74" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D45" s="77" t="n">
+        <v>12</v>
+      </c>
+      <c r="E45" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H45" s="80" t="inlineStr">
+        <is>
+          <t>3–2</t>
+        </is>
+      </c>
+      <c r="I45" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="L45" s="78" t="n">
+        <v>17</v>
+      </c>
+      <c r="M45" s="68" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N45" s="76" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe J</t>
+        </is>
+      </c>
+      <c r="B46" s="67" t="inlineStr">
+        <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="C45" s="84" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D45" s="78" t="n">
-        <v>12</v>
-      </c>
-      <c r="E45" s="78" t="n">
+      <c r="C46" s="84" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D46" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" s="69" t="n">
+        <v>6</v>
+      </c>
+      <c r="F46" s="70" t="n">
         <v>3</v>
-      </c>
-      <c r="F45" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="G45" s="79" t="n">
-        <v>5</v>
-      </c>
-      <c r="H45" s="80" t="inlineStr">
-        <is>
-          <t>2–0</t>
-        </is>
-      </c>
-      <c r="I45" s="81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="M45" s="84" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="N45" s="76" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="82" t="inlineStr"/>
-      <c r="B46" s="67" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="C46" s="74" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D46" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="E46" s="70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F46" s="70" t="n">
-        <v>4</v>
       </c>
       <c r="G46" s="71" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="72" t="inlineStr">
         <is>
-          <t>1–2</t>
+          <t>3–0</t>
         </is>
       </c>
       <c r="I46" s="73" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J46" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="69" t="n">
-        <v>8</v>
-      </c>
-      <c r="L46" s="69" t="n">
-        <v>17</v>
-      </c>
-      <c r="M46" s="83" t="n">
-        <v>0.75</v>
+      <c r="K46" s="70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="70" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" s="84" t="n">
+        <v>0.53</v>
       </c>
       <c r="N46" s="67" t="inlineStr">
         <is>
@@ -50271,99 +50271,95 @@
       <c r="A47" s="75" t="inlineStr"/>
       <c r="B47" s="76" t="inlineStr">
         <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="C47" s="68" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="D47" s="77" t="n">
-        <v>9</v>
-      </c>
-      <c r="E47" s="77" t="n">
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C47" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D47" s="78" t="n">
+        <v>12</v>
+      </c>
+      <c r="E47" s="78" t="n">
         <v>3</v>
       </c>
       <c r="F47" s="77" t="n">
         <v>4</v>
       </c>
       <c r="G47" s="79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H47" s="80" t="inlineStr">
         <is>
-          <t>3–1</t>
+          <t>2–0</t>
         </is>
       </c>
       <c r="I47" s="81" t="n">
         <v>3</v>
       </c>
       <c r="J47" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="K47" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" s="77" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="84" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N47" s="76" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="82" t="inlineStr"/>
+      <c r="B48" s="67" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="C48" s="74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D48" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="K47" s="78" t="n">
+      <c r="F48" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="L47" s="78" t="n">
-        <v>11</v>
-      </c>
-      <c r="M47" s="74" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N47" s="76" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe K</t>
-        </is>
-      </c>
-      <c r="B48" s="67" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C48" s="83" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="D48" s="69" t="n">
-        <v>20</v>
-      </c>
-      <c r="E48" s="69" t="n">
-        <v>9</v>
-      </c>
-      <c r="F48" s="70" t="n">
-        <v>5</v>
-      </c>
       <c r="G48" s="71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="72" t="inlineStr">
+        <is>
+          <t>1–2</t>
+        </is>
+      </c>
+      <c r="I48" s="73" t="n">
         <v>6</v>
-      </c>
-      <c r="H48" s="72" t="inlineStr">
-        <is>
-          <t>1–0</t>
-        </is>
-      </c>
-      <c r="I48" s="73" t="n">
-        <v>2</v>
       </c>
       <c r="J48" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="K48" s="70" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" s="70" t="n">
-        <v>7</v>
-      </c>
-      <c r="M48" s="74" t="n">
-        <v>0.34</v>
+      <c r="K48" s="69" t="n">
+        <v>8</v>
+      </c>
+      <c r="L48" s="69" t="n">
+        <v>17</v>
+      </c>
+      <c r="M48" s="83" t="n">
+        <v>0.75</v>
       </c>
       <c r="N48" s="67" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Algerie</t>
         </is>
       </c>
     </row>
@@ -50371,16 +50367,16 @@
       <c r="A49" s="75" t="inlineStr"/>
       <c r="B49" s="76" t="inlineStr">
         <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="C49" s="83" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D49" s="78" t="n">
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="C49" s="68" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="D49" s="77" t="n">
         <v>9</v>
       </c>
-      <c r="E49" s="78" t="n">
+      <c r="E49" s="77" t="n">
         <v>3</v>
       </c>
       <c r="F49" s="77" t="n">
@@ -50391,62 +50387,66 @@
       </c>
       <c r="H49" s="80" t="inlineStr">
         <is>
-          <t>1–1</t>
+          <t>3–1</t>
         </is>
       </c>
       <c r="I49" s="81" t="n">
         <v>3</v>
       </c>
       <c r="J49" s="77" t="n">
-        <v>3</v>
-      </c>
-      <c r="K49" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="77" t="n">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="K49" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" s="78" t="n">
+        <v>11</v>
       </c>
       <c r="M49" s="74" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="N49" s="76" t="inlineStr">
         <is>
-          <t>DR Kongo</t>
+          <t>Jordan</t>
         </is>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="82" t="inlineStr"/>
+      <c r="A50" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe K</t>
+        </is>
+      </c>
       <c r="B50" s="67" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C50" s="83" t="n">
         <v>0.66</v>
       </c>
       <c r="D50" s="69" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E50" s="69" t="n">
         <v>9</v>
       </c>
       <c r="F50" s="70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G50" s="71" t="n">
+        <v>6</v>
+      </c>
+      <c r="H50" s="72" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I50" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="70" t="n">
         <v>3</v>
-      </c>
-      <c r="H50" s="72" t="inlineStr">
-        <is>
-          <t>5–0</t>
-        </is>
-      </c>
-      <c r="I50" s="73" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="70" t="n">
-        <v>2</v>
       </c>
       <c r="K50" s="70" t="n">
         <v>2</v>
@@ -50459,7 +50459,7 @@
       </c>
       <c r="N50" s="67" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
+          <t>DR Kongo</t>
         </is>
       </c>
     </row>
@@ -50467,99 +50467,95 @@
       <c r="A51" s="75" t="inlineStr"/>
       <c r="B51" s="76" t="inlineStr">
         <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="C51" s="74" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D51" s="77" t="n">
-        <v>7</v>
-      </c>
-      <c r="E51" s="77" t="n">
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C51" s="83" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D51" s="78" t="n">
+        <v>9</v>
+      </c>
+      <c r="E51" s="78" t="n">
         <v>3</v>
       </c>
       <c r="F51" s="77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G51" s="79" t="n">
         <v>2</v>
       </c>
       <c r="H51" s="80" t="inlineStr">
         <is>
-          <t>1–3</t>
+          <t>1–1</t>
         </is>
       </c>
       <c r="I51" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K51" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" s="74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N51" s="76" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="82" t="inlineStr"/>
+      <c r="B52" s="67" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C52" s="83" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="D52" s="69" t="n">
+        <v>16</v>
+      </c>
+      <c r="E52" s="69" t="n">
+        <v>9</v>
+      </c>
+      <c r="F52" s="70" t="n">
         <v>4</v>
       </c>
-      <c r="J51" s="77" t="n">
-        <v>5</v>
-      </c>
-      <c r="K51" s="78" t="n">
-        <v>6</v>
-      </c>
-      <c r="L51" s="78" t="n">
-        <v>15</v>
-      </c>
-      <c r="M51" s="83" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="N51" s="76" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="66" t="inlineStr">
-        <is>
-          <t>Gruppe L</t>
-        </is>
-      </c>
-      <c r="B52" s="67" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="C52" s="84" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D52" s="69" t="n">
-        <v>20</v>
-      </c>
-      <c r="E52" s="69" t="n">
-        <v>12</v>
-      </c>
-      <c r="F52" s="70" t="n">
+      <c r="G52" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="G52" s="71" t="n">
-        <v>5</v>
-      </c>
       <c r="H52" s="72" t="inlineStr">
         <is>
-          <t>4–2</t>
+          <t>5–0</t>
         </is>
       </c>
       <c r="I52" s="73" t="n">
         <v>3</v>
       </c>
       <c r="J52" s="70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K52" s="70" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L52" s="70" t="n">
-        <v>11</v>
-      </c>
-      <c r="M52" s="84" t="n">
-        <v>0.46</v>
+        <v>7</v>
+      </c>
+      <c r="M52" s="74" t="n">
+        <v>0.34</v>
       </c>
       <c r="N52" s="67" t="inlineStr">
         <is>
-          <t>Kroatia</t>
+          <t>Usbekistan</t>
         </is>
       </c>
     </row>
@@ -50567,95 +50563,99 @@
       <c r="A53" s="75" t="inlineStr"/>
       <c r="B53" s="76" t="inlineStr">
         <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="C53" s="74" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D53" s="77" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" s="77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="80" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="I53" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="J53" s="77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" s="78" t="n">
+        <v>6</v>
+      </c>
+      <c r="L53" s="78" t="n">
+        <v>15</v>
+      </c>
+      <c r="M53" s="83" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N53" s="76" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="66" t="inlineStr">
+        <is>
+          <t>Gruppe L</t>
+        </is>
+      </c>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
           <t>England</t>
         </is>
       </c>
-      <c r="C53" s="83" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="D53" s="78" t="n">
-        <v>19</v>
-      </c>
-      <c r="E53" s="78" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="77" t="n">
-        <v>8</v>
-      </c>
-      <c r="G53" s="79" t="n">
-        <v>7</v>
-      </c>
-      <c r="H53" s="80" t="inlineStr">
-        <is>
-          <t>0–0</t>
-        </is>
-      </c>
-      <c r="I53" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" s="74" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="N53" s="76" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="82" t="inlineStr"/>
-      <c r="B54" s="67" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="C54" s="74" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="D54" s="70" t="n">
-        <v>8</v>
-      </c>
-      <c r="E54" s="70" t="n">
+      <c r="C54" s="84" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D54" s="69" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="F54" s="70" t="n">
         <v>3</v>
       </c>
-      <c r="F54" s="70" t="n">
-        <v>4</v>
-      </c>
       <c r="G54" s="71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H54" s="72" t="inlineStr">
         <is>
-          <t>1–0</t>
+          <t>4–2</t>
         </is>
       </c>
       <c r="I54" s="73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J54" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="K54" s="70" t="n">
         <v>5</v>
       </c>
-      <c r="K54" s="69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L54" s="69" t="n">
+      <c r="L54" s="70" t="n">
         <v>11</v>
       </c>
-      <c r="M54" s="68" t="n">
-        <v>0.63</v>
+      <c r="M54" s="84" t="n">
+        <v>0.46</v>
       </c>
       <c r="N54" s="67" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Kroatia</t>
         </is>
       </c>
     </row>
@@ -50663,79 +50663,175 @@
       <c r="A55" s="75" t="inlineStr"/>
       <c r="B55" s="76" t="inlineStr">
         <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C55" s="83" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D55" s="78" t="n">
+        <v>19</v>
+      </c>
+      <c r="E55" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" s="77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G55" s="79" t="n">
+        <v>7</v>
+      </c>
+      <c r="H55" s="80" t="inlineStr">
+        <is>
+          <t>0–0</t>
+        </is>
+      </c>
+      <c r="I55" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M55" s="74" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N55" s="76" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="82" t="inlineStr"/>
+      <c r="B56" s="67" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="C56" s="74" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="D56" s="70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E56" s="70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="70" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" s="71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="72" t="inlineStr">
+        <is>
+          <t>1–0</t>
+        </is>
+      </c>
+      <c r="I56" s="73" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L56" s="69" t="n">
+        <v>11</v>
+      </c>
+      <c r="M56" s="68" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N56" s="67" t="inlineStr">
+        <is>
           <t>Panama</t>
         </is>
       </c>
-      <c r="C55" s="74" t="n">
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="75" t="inlineStr"/>
+      <c r="B57" s="76" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="C57" s="74" t="n">
         <v>0.42</v>
       </c>
-      <c r="D55" s="78" t="n">
+      <c r="D57" s="78" t="n">
         <v>8</v>
       </c>
-      <c r="E55" s="77" t="n">
+      <c r="E57" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="F55" s="77" t="n">
+      <c r="F57" s="77" t="n">
         <v>4</v>
       </c>
-      <c r="G55" s="79" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" s="80" t="inlineStr">
+      <c r="G57" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="80" t="inlineStr">
         <is>
           <t>0–1</t>
         </is>
       </c>
-      <c r="I55" s="81" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="77" t="n">
+      <c r="I57" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="77" t="n">
         <v>2</v>
       </c>
-      <c r="K55" s="77" t="n">
+      <c r="K57" s="77" t="n">
         <v>3</v>
       </c>
-      <c r="L55" s="77" t="n">
+      <c r="L57" s="77" t="n">
         <v>6</v>
       </c>
-      <c r="M55" s="68" t="n">
+      <c r="M57" s="68" t="n">
         <v>0.58</v>
       </c>
-      <c r="N55" s="76" t="inlineStr">
+      <c r="N57" s="76" t="inlineStr">
         <is>
           <t>Kroatia</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="63" t="inlineStr">
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="63" t="inlineStr">
         <is>
           <t>Treff = skudd på mål  |  Bom = utenfor  |  Blk. = blokkert  |  Grønn bold = flest skudd/treff</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="A58" s="55" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="55" t="inlineStr">
         <is>
           <t>Besittelse:</t>
         </is>
       </c>
-      <c r="B58" s="62" t="inlineStr">
+      <c r="B60" s="62" t="inlineStr">
         <is>
           <t>≥65% (dominerende)</t>
         </is>
       </c>
-      <c r="C58" s="61" t="inlineStr">
+      <c r="C60" s="61" t="inlineStr">
         <is>
           <t>55–64%</t>
         </is>
       </c>
-      <c r="D58" s="58" t="inlineStr">
+      <c r="D60" s="58" t="inlineStr">
         <is>
           <t>45–54% (jevnt)</t>
         </is>
       </c>
-      <c r="E58" s="85" t="inlineStr">
+      <c r="E60" s="85" t="inlineStr">
         <is>
           <t>≤44%</t>
         </is>
@@ -50743,8 +50839,8 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A59:N59"/>
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="A57:N57"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -17953,7 +17953,11 @@
       </c>
       <c r="E3" s="4" t="inlineStr"/>
       <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Joao Pinheiro</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="7" t="inlineStr">

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Kort" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Alder" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
@@ -883,13 +883,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -908,7 +908,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -936,8 +936,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -963,8 +963,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -987,7 +987,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1002,9 +1002,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1644,42 +1644,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -1689,31 +1689,31 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>3</v>
+      <c r="B12" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -1722,12 +1722,12 @@
           <t>Sør-Afrika</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
@@ -1735,18 +1735,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -1755,31 +1755,31 @@
           <t>Sør-Korea</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1788,33 +1788,34 @@
           <t>Tsjekkia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -5798,42 +5799,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -5843,31 +5844,31 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>2</v>
+      <c r="B12" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -5876,31 +5877,31 @@
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="F13" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -5909,31 +5910,31 @@
           <t>Algerie</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -5942,33 +5943,34 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -9922,42 +9924,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -9967,31 +9969,31 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>2</v>
+      <c r="B12" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -10000,31 +10002,31 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="G13" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -10033,15 +10035,15 @@
           <t>DR Kongo</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
@@ -10049,15 +10051,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -10066,33 +10068,34 @@
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -14062,42 +14065,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -14107,31 +14110,31 @@
           <t>England</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -14140,31 +14143,31 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="G13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -14173,31 +14176,31 @@
           <t>Kroatia</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -14206,33 +14209,34 @@
           <t>Panama</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -21554,42 +21558,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -21599,31 +21603,31 @@
           <t>Sveits</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -21632,12 +21636,12 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
@@ -21645,18 +21649,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -21665,12 +21669,12 @@
           <t>Bosnia-Hercegovina</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -21678,18 +21682,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -21698,33 +21702,34 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -55289,42 +55294,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -55334,31 +55339,31 @@
           <t>Brasil</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -55367,31 +55372,31 @@
           <t>Marokko</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="D13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="G13" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -55400,31 +55405,31 @@
           <t>Skottland</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -55433,33 +55438,34 @@
           <t>Haiti</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -59473,42 +59479,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -59518,31 +59524,31 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -59551,12 +59557,12 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
@@ -59564,18 +59570,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -59584,12 +59590,12 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -59597,18 +59603,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -59617,33 +59623,34 @@
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -63671,42 +63678,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -63716,31 +63723,31 @@
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -63749,31 +63756,31 @@
           <t>Elfenbenskysten</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="D13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="E13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="F13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -63782,12 +63789,12 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -63795,18 +63802,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -63815,33 +63822,34 @@
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -67861,42 +67869,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -67906,31 +67914,31 @@
           <t>Nederland</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -67939,31 +67947,31 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="G13" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -67972,12 +67980,12 @@
           <t>Sverige</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -67985,18 +67993,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -68005,33 +68013,34 @@
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -72039,42 +72048,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -72084,31 +72093,31 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -72117,31 +72126,31 @@
           <t>Iran</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="F13" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>2</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -72150,31 +72159,31 @@
           <t>Belgia</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -72183,33 +72192,34 @@
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -76177,42 +76187,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -76222,31 +76232,31 @@
           <t>Spania</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -76255,31 +76265,31 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="F13" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>3</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -76288,31 +76298,31 @@
           <t>Kapp Verde</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -76321,15 +76331,15 @@
           <t>Saudi-Arabia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
         <v>1</v>
       </c>
@@ -76337,17 +76347,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -80299,42 +80310,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -80344,31 +80355,31 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>2</v>
+      <c r="B12" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -80377,31 +80388,31 @@
           <t>Norge</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
-        <v>2</v>
+      <c r="B13" s="19" t="n">
+        <v>6</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -80410,31 +80421,31 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -80443,33 +80454,34 @@
           <t>Irak</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Kort" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Alder" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
@@ -883,13 +883,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -908,7 +908,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -936,8 +936,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -963,8 +963,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -987,7 +987,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1002,9 +1002,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1644,42 +1644,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -1689,31 +1689,31 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>3</v>
+      <c r="B12" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -1722,12 +1722,12 @@
           <t>Sør-Afrika</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
@@ -1735,18 +1735,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -1755,31 +1755,31 @@
           <t>Sør-Korea</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1788,33 +1788,34 @@
           <t>Tsjekkia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -5798,42 +5799,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -5843,31 +5844,31 @@
           <t>Argentina</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>2</v>
+      <c r="B12" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -5876,31 +5877,31 @@
           <t>Østerrike</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="F13" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -5909,31 +5910,31 @@
           <t>Algerie</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -5942,33 +5943,34 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -9922,42 +9924,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -9967,31 +9969,31 @@
           <t>Colombia</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>2</v>
+      <c r="B12" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -10000,31 +10002,31 @@
           <t>Portugal</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="G13" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -10033,15 +10035,15 @@
           <t>DR Kongo</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
@@ -10049,15 +10051,15 @@
         <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -10066,33 +10068,34 @@
           <t>Usbekistan</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -14062,42 +14065,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -14107,31 +14110,31 @@
           <t>England</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -14140,31 +14143,31 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="G13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -14173,31 +14176,31 @@
           <t>Kroatia</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -14206,33 +14209,34 @@
           <t>Panama</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -21558,42 +21562,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -21603,31 +21607,31 @@
           <t>Sveits</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -21636,12 +21640,12 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
@@ -21649,18 +21653,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -21669,12 +21673,12 @@
           <t>Bosnia-Hercegovina</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -21682,18 +21686,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -21702,33 +21706,34 @@
           <t>Qatar</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -55293,42 +55298,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -55338,31 +55343,31 @@
           <t>Brasil</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -55371,31 +55376,31 @@
           <t>Marokko</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="D13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="E13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="G13" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+3</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -55404,31 +55409,31 @@
           <t>Skottland</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -55437,33 +55442,34 @@
           <t>Haiti</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -59477,42 +59483,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -59522,31 +59528,31 @@
           <t>USA</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -59555,12 +59561,12 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
         <v>1</v>
       </c>
@@ -59568,18 +59574,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -59588,12 +59594,12 @@
           <t>Paraguay</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -59601,18 +59607,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -59621,33 +59627,34 @@
           <t>Tyrkia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="7" t="n">
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -63675,42 +63682,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -63720,31 +63727,31 @@
           <t>Tyskland</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -63753,31 +63760,31 @@
           <t>Elfenbenskysten</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="D13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="E13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="F13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -63786,12 +63793,12 @@
           <t>Ecuador</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -63799,18 +63806,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -63819,33 +63826,34 @@
           <t>Curaçao</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -67865,42 +67873,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -67910,31 +67918,31 @@
           <t>Nederland</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="D12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -67943,31 +67951,31 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>1</v>
-      </c>
       <c r="D13" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="F13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="G13" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -67976,12 +67984,12 @@
           <t>Sverige</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="4" t="n">
         <v>1</v>
       </c>
@@ -67989,18 +67997,18 @@
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -68009,33 +68017,34 @@
           <t>Tunisia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -72043,42 +72052,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -72088,31 +72097,31 @@
           <t>Egypt</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -72121,31 +72130,31 @@
           <t>Iran</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="F13" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>2</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -72154,31 +72163,31 @@
           <t>Belgia</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -72187,33 +72196,34 @@
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -76181,42 +76191,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -76226,31 +76236,31 @@
           <t>Spania</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B12" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="G12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="H12" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -76259,31 +76269,31 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="E13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="F13" s="18" t="n">
         <v>0</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>3</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H13" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -76292,31 +76302,31 @@
           <t>Kapp Verde</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -76325,15 +76335,15 @@
           <t>Saudi-Arabia</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="E15" s="7" t="n">
         <v>1</v>
       </c>
@@ -76341,17 +76351,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -80303,42 +80314,42 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>K</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>MF</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>MM</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>MD</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
         </is>
       </c>
     </row>
@@ -80348,31 +80359,31 @@
           <t>Frankrike</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
-        <v>2</v>
+      <c r="B12" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>2</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -80381,31 +80392,31 @@
           <t>Norge</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
-        <v>2</v>
+      <c r="B13" s="19" t="n">
+        <v>6</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="H13" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
-      </c>
-      <c r="I13" s="19" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -80414,31 +80425,31 @@
           <t>Senegal</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -80447,33 +80458,34 @@
           <t>Irak</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    </row>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Kort" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Alder" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
@@ -883,13 +883,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -908,7 +908,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -936,8 +936,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -963,8 +963,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -987,7 +987,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1002,9 +1002,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1815,7 +1815,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -5970,7 +5969,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -10095,7 +10093,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -14236,7 +14233,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -21733,7 +21729,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -55469,7 +55464,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -59654,7 +59648,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -63853,7 +63846,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -68044,7 +68036,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -72223,7 +72214,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -76362,7 +76352,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -80485,7 +80474,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -28,9 +28,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
@@ -1815,7 +1815,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -5970,7 +5969,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -10095,7 +10093,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -14236,7 +14233,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -21733,7 +21729,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -32412,2745 +32407,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>VM 2026 — Kort  (141 spillere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Spiller</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Lag</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Gule</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Røde</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>Miguel Almiron</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Assim Madibo</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>Cesar Montes</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>Homam Ahmed</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Nathan Ngoy</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>Sphephelo Sithole</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>Tarik Muharemovic</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>Themba Zwane</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Ahmed Fathy</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Diego Gomez</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="15" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Gervane Kastaneer</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="14" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Juninho Bacuna</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Sidny Lopes Cabral</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Teboho Mokoena</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Aaron Hickey</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Abdukodir Khusanov</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Abdulelah Alamri</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="14" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Ahmed Fatouh</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Alan Franco</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Aleksandar Pavlovic</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Alessandro Circati</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Alex Arce</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Alistair Johnston</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="14" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Amar Dedic</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Amir Alammari</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Andy Robertson</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Antonee Robinson</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Aubrey Modiba</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Bernardo Silva</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14" t="n"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Brian Gutierrez</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15" t="n"/>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Caleb Yirenkyi</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Callum Mccowatt</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Carlens Arcus</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D35" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="14" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Carlos Harvey</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="D36" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="15" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Casemiro</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="14" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Cesar Blackman</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="D38" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="15" t="n"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Chancel Mbemba</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-      <c r="D39" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="14" t="n"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Charles Pickel</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-      <c r="D40" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="15" t="n"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Cho Guesung</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D41" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="14" t="n"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Chris Richards</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D42" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="15" t="n"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Crysencio Summerville</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D43" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="14" t="n"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Cyle Larin</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="15" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Danilo</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D45" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="14" t="n"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Danley Jean Jacques</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="15" t="n"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Declan Rice</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D47" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="14" t="n"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Denis Zakaria</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D48" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="15" t="n"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Derek Cornelius</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D49" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="14" t="n"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Diney Borges</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-      <c r="D50" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="15" t="n"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Douglas Santos</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="14" t="n"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Duckens Nazon</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="15" t="n"/>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Edgar Yoel Barcenas</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="D53" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="14" t="n"/>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Edin Dzeko</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D54" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="15" t="n"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Edson Alvarez</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="D55" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="14" t="n"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Ehsan Hajisafi</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="15" t="n"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Eren Elmali</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D57" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="14" t="n"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Ermedin Demirovic</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D58" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15" t="n"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Ermin Mahmic</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D59" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="14" t="n"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Fabinho</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D60" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="15" t="n"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Facundo Medina</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D61" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="14" t="n"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Findlay Curtis</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D62" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="15" t="n"/>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Folarin Balogun</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D63" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="14" t="n"/>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Franck Kessie</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="15" t="n"/>
-    </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Frantzdy Pierrot</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D65" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="14" t="n"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Gabriel Gudmundsson</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D66" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="15" t="n"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Gonzalo Plata</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D67" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="14" t="n"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Granit Xhaka</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D68" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="15" t="n"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>Guela Doue</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D69" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="14" t="n"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Harry Souttar</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D70" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="15" t="n"/>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Husam Abudahab</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="D71" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="14" t="n"/>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Inaki Williams</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="D72" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="15" t="n"/>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>Isak Hien</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D73" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="14" t="n"/>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Issa Diop</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="D74" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="15" t="n"/>
-    </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Jackson Irvine</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D75" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="14" t="n"/>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Jackson Porozo</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D76" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="15" t="n"/>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Jacob Italiano</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D77" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="14" t="n"/>
-    </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Jassem Gaber</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D78" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="15" t="n"/>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Jean-Ricner Bellegarde</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D79" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="14" t="n"/>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Jefferson Lerma</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D80" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="15" t="n"/>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>Jhon Lucumi</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D81" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="14" t="n"/>
-    </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Johan Mojica</t>
-        </is>
-      </c>
-      <c r="C82" s="15" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="15" t="n"/>
-    </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>Johny Placide</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D83" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="14" t="n"/>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Bos</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D84" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="15" t="n"/>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>Jordy Alcivar</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D85" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="14" t="n"/>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Josue Casimir</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D86" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="15" t="n"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>Jovo Lukic</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D87" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="14" t="n"/>
-    </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Juan Jose Caceres</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D88" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="15" t="n"/>
-    </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>Junior Alonso</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D89" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="14" t="n"/>
-    </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Jurien Gaari</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D90" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="15" t="n"/>
-    </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>Kenny Mclean</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D91" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="14" t="n"/>
-    </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Konrad Laimer</t>
-        </is>
-      </c>
-      <c r="C92" s="15" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="D92" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="15" t="n"/>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>Ladislav Krejci</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="inlineStr">
-        <is>
-          <t>Tsjekkia</t>
-        </is>
-      </c>
-      <c r="D93" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="14" t="n"/>
-    </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Leandro Bacuna</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D94" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="15" t="n"/>
-    </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Leandro Paredes</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D95" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="14" t="n"/>
-    </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Lee Gihyuk</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D96" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="15" t="n"/>
-    </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Lee Kangin</t>
-        </is>
-      </c>
-      <c r="C97" s="14" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D97" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="14" t="n"/>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Liam Millar</t>
-        </is>
-      </c>
-      <c r="C98" s="15" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D98" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="15" t="n"/>
-    </row>
-    <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>Livano Comenencia</t>
-        </is>
-      </c>
-      <c r="C99" s="14" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D99" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="14" t="n"/>
-    </row>
-    <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Luc De Fougerolles</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D100" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="15" t="n"/>
-    </row>
-    <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>Lucas Bergvall</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D101" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="14" t="n"/>
-    </row>
-    <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Mahmoud Abunada</t>
-        </is>
-      </c>
-      <c r="C102" s="15" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D102" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="15" t="n"/>
-    </row>
-    <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Marawan Attia</t>
-        </is>
-      </c>
-      <c r="C103" s="14" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="D103" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="14" t="n"/>
-    </row>
-    <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Marcel Sabitzer</t>
-        </is>
-      </c>
-      <c r="C104" s="15" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="D104" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="15" t="n"/>
-    </row>
-    <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>Mathias Olivera</t>
-        </is>
-      </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="D105" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="14" t="n"/>
-    </row>
-    <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Matias Galarza</t>
-        </is>
-      </c>
-      <c r="C106" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D106" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="15" t="n"/>
-    </row>
-    <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>Maxim De Cuyper</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D107" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="14" t="n"/>
-    </row>
-    <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Memphis Depay</t>
-        </is>
-      </c>
-      <c r="C108" s="15" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D108" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="15" t="n"/>
-    </row>
-    <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>Micky Van De Ven</t>
-        </is>
-      </c>
-      <c r="C109" s="14" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D109" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="14" t="n"/>
-    </row>
-    <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Mohamed Kanno</t>
-        </is>
-      </c>
-      <c r="C110" s="15" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="D110" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="15" t="n"/>
-    </row>
-    <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>Mohanad Lashin</t>
-        </is>
-      </c>
-      <c r="C111" s="14" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="D111" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="14" t="n"/>
-    </row>
-    <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>Nelson Semedo</t>
-        </is>
-      </c>
-      <c r="C112" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D112" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="15" t="n"/>
-    </row>
-    <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Nico Elvedi</t>
-        </is>
-      </c>
-      <c r="C113" s="14" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D113" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="14" t="n"/>
-    </row>
-    <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>Nicolas Pepe</t>
-        </is>
-      </c>
-      <c r="C114" s="15" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D114" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="15" t="n"/>
-    </row>
-    <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>Nikola Katic</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D115" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="14" t="n"/>
-    </row>
-    <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>Nkosinathi Sibisi</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D116" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="15" t="n"/>
-    </row>
-    <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>Odiljon Xamrobekov</t>
-        </is>
-      </c>
-      <c r="C117" s="14" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="D117" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="14" t="n"/>
-    </row>
-    <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>Paik Seungho</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D118" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="15" t="n"/>
-    </row>
-    <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>Pedri</t>
-        </is>
-      </c>
-      <c r="C119" s="14" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D119" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="14" t="n"/>
-    </row>
-    <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>Petar Sucic</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="inlineStr">
-        <is>
-          <t>Kroatia</t>
-        </is>
-      </c>
-      <c r="D120" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="15" t="n"/>
-    </row>
-    <row r="121" ht="17" customHeight="1">
-      <c r="A121" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>Piero Hincapie</t>
-        </is>
-      </c>
-      <c r="C121" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D121" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="14" t="n"/>
-    </row>
-    <row r="122" ht="17" customHeight="1">
-      <c r="A122" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>Ramiz Zerrouki</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-      <c r="D122" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="15" t="n"/>
-    </row>
-    <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>Rani Khedira</t>
-        </is>
-      </c>
-      <c r="C123" s="14" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="D123" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="14" t="n"/>
-    </row>
-    <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>Renato Veiga</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D124" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="15" t="n"/>
-    </row>
-    <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>Rodrigo Bentancur</t>
-        </is>
-      </c>
-      <c r="C125" s="14" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="D125" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="14" t="n"/>
-    </row>
-    <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>Roger Ibanez</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D126" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="15" t="n"/>
-    </row>
-    <row r="127" ht="17" customHeight="1">
-      <c r="A127" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>Romelu Lukaku</t>
-        </is>
-      </c>
-      <c r="C127" s="14" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D127" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="14" t="n"/>
-    </row>
-    <row r="128" ht="17" customHeight="1">
-      <c r="A128" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>Ryan Christie</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D128" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="15" t="n"/>
-    </row>
-    <row r="129" ht="17" customHeight="1">
-      <c r="A129" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>Saeid Ezatolahi</t>
-        </is>
-      </c>
-      <c r="C129" s="14" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="D129" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="14" t="n"/>
-    </row>
-    <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>Salem Aldawsari</t>
-        </is>
-      </c>
-      <c r="C130" s="15" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="D130" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" s="15" t="n"/>
-    </row>
-    <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>Sarpreet Singh</t>
-        </is>
-      </c>
-      <c r="C131" s="14" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="D131" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" s="14" t="n"/>
-    </row>
-    <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>Sebastian Berhalter</t>
-        </is>
-      </c>
-      <c r="C132" s="15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D132" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" s="15" t="n"/>
-    </row>
-    <row r="133" ht="17" customHeight="1">
-      <c r="A133" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>Seko Fofana</t>
-        </is>
-      </c>
-      <c r="C133" s="14" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D133" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" s="14" t="n"/>
-    </row>
-    <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>Shogo Taniguchi</t>
-        </is>
-      </c>
-      <c r="C134" s="15" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D134" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="15" t="n"/>
-    </row>
-    <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>Stefan Posch</t>
-        </is>
-      </c>
-      <c r="C135" s="14" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="D135" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="14" t="n"/>
-    </row>
-    <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B136" s="8" t="inlineStr">
-        <is>
-          <t>Thalente Mbatha</t>
-        </is>
-      </c>
-      <c r="C136" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D136" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="15" t="n"/>
-    </row>
-    <row r="137" ht="17" customHeight="1">
-      <c r="A137" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>Timothy Castagne</t>
-        </is>
-      </c>
-      <c r="C137" s="14" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D137" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="14" t="n"/>
-    </row>
-    <row r="138" ht="17" customHeight="1">
-      <c r="A138" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Tomas Araujo</t>
-        </is>
-      </c>
-      <c r="C138" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D138" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="15" t="n"/>
-    </row>
-    <row r="139" ht="17" customHeight="1">
-      <c r="A139" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>Tyler Adams</t>
-        </is>
-      </c>
-      <c r="C139" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D139" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" s="14" t="n"/>
-    </row>
-    <row r="140" ht="17" customHeight="1">
-      <c r="A140" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>Viktor Gyokeres</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D140" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="15" t="n"/>
-    </row>
-    <row r="141" ht="17" customHeight="1">
-      <c r="A141" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>Yasin Ayari</t>
-        </is>
-      </c>
-      <c r="C141" s="14" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D141" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" s="14" t="n"/>
-    </row>
-    <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Yunus Akgun</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D142" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" s="15" t="n"/>
-    </row>
-    <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>Zaid Tahseen</t>
-        </is>
-      </c>
-      <c r="C143" s="14" t="inlineStr">
-        <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="D143" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" s="14" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -38892,7 +36148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39599,6 +36855,2745 @@
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E143"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>VM 2026 — Kort  (141 spillere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Spiller</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Lag</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Gule</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Røde</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Miguel Almiron</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Assim Madibo</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="n"/>
+      <c r="E4" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Cesar Montes</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Homam Ahmed</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Nathan Ngoy</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="n"/>
+      <c r="E7" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Sphephelo Sithole</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="n"/>
+      <c r="E8" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Tarik Muharemovic</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Themba Zwane</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Ahmed Fathy</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Diego Gomez</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Gervane Kastaneer</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Juninho Bacuna</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Sidny Lopes Cabral</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Teboho Mokoena</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Aaron Hickey</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Abdukodir Khusanov</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Abdulelah Alamri</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ahmed Fatouh</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Alan Franco</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Aleksandar Pavlovic</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Alessandro Circati</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Alex Arce</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Alistair Johnston</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Amar Dedic</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Amir Alammari</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Andy Robertson</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Antonee Robinson</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Aubrey Modiba</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Bernardo Silva</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Brian Gutierrez</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Yirenkyi</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Callum Mccowatt</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Carlens Arcus</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Harvey</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Casemiro</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Cesar Blackman</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Chancel Mbemba</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Charles Pickel</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Cho Guesung</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="14" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Chris Richards</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Crysencio Summerville</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="14" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Cyle Larin</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Danilo</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Danley Jean Jacques</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Declan Rice</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="14" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Denis Zakaria</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Derek Cornelius</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="14" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Diney Borges</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Douglas Santos</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="14" t="n"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Duckens Nazon</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15" t="n"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Edgar Yoel Barcenas</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="D53" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="14" t="n"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Edin Dzeko</t>
+        </is>
+      </c>
+      <c r="C54" s="15" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="15" t="n"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Edson Alvarez</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D55" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="14" t="n"/>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Ehsan Hajisafi</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="D56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="15" t="n"/>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Eren Elmali</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D57" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="14" t="n"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Ermedin Demirovic</t>
+        </is>
+      </c>
+      <c r="C58" s="15" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D58" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="15" t="n"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Ermin Mahmic</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D59" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="14" t="n"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Fabinho</t>
+        </is>
+      </c>
+      <c r="C60" s="15" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="15" t="n"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Facundo Medina</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D61" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="14" t="n"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Findlay Curtis</t>
+        </is>
+      </c>
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D62" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="15" t="n"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Folarin Balogun</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="14" t="n"/>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Franck Kessie</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="D64" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="15" t="n"/>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Frantzdy Pierrot</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D65" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="14" t="n"/>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Gabriel Gudmundsson</t>
+        </is>
+      </c>
+      <c r="C66" s="15" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="15" t="n"/>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Gonzalo Plata</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D67" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="14" t="n"/>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Granit Xhaka</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D68" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="15" t="n"/>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Guela Doue</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="D69" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="14" t="n"/>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Harry Souttar</t>
+        </is>
+      </c>
+      <c r="C70" s="15" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="15" t="n"/>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Husam Abudahab</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="D71" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="14" t="n"/>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Inaki Williams</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D72" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="15" t="n"/>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Isak Hien</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D73" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="14" t="n"/>
+    </row>
+    <row r="74" ht="17" customHeight="1">
+      <c r="A74" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Issa Diop</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Marokko</t>
+        </is>
+      </c>
+      <c r="D74" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="15" t="n"/>
+    </row>
+    <row r="75" ht="17" customHeight="1">
+      <c r="A75" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Jackson Irvine</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D75" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="14" t="n"/>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Jackson Porozo</t>
+        </is>
+      </c>
+      <c r="C76" s="15" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D76" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="15" t="n"/>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Jacob Italiano</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D77" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="14" t="n"/>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Jassem Gaber</t>
+        </is>
+      </c>
+      <c r="C78" s="15" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D78" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="15" t="n"/>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Jean-Ricner Bellegarde</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="14" t="n"/>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Jefferson Lerma</t>
+        </is>
+      </c>
+      <c r="C80" s="15" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D80" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" s="15" t="n"/>
+    </row>
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Jhon Lucumi</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D81" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="14" t="n"/>
+    </row>
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Johan Mojica</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="15" t="n"/>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Johny Placide</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D83" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="14" t="n"/>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Jordan Bos</t>
+        </is>
+      </c>
+      <c r="C84" s="15" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D84" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="15" t="n"/>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Jordy Alcivar</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D85" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="14" t="n"/>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Josue Casimir</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D86" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="15" t="n"/>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Jovo Lukic</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D87" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="14" t="n"/>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Juan Jose Caceres</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D88" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="15" t="n"/>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Junior Alonso</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D89" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="14" t="n"/>
+    </row>
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>Jurien Gaari</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D90" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="15" t="n"/>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Kenny Mclean</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D91" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="14" t="n"/>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Konrad Laimer</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="D92" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="15" t="n"/>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Ladislav Krejci</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>Tsjekkia</t>
+        </is>
+      </c>
+      <c r="D93" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="14" t="n"/>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Leandro Bacuna</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D94" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="15" t="n"/>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Leandro Paredes</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D95" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="14" t="n"/>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Lee Gihyuk</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D96" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="15" t="n"/>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Lee Kangin</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D97" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="14" t="n"/>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Liam Millar</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D98" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="15" t="n"/>
+    </row>
+    <row r="99" ht="17" customHeight="1">
+      <c r="A99" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Livano Comenencia</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D99" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="14" t="n"/>
+    </row>
+    <row r="100" ht="17" customHeight="1">
+      <c r="A100" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Luc De Fougerolles</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D100" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="15" t="n"/>
+    </row>
+    <row r="101" ht="17" customHeight="1">
+      <c r="A101" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Lucas Bergvall</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D101" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="14" t="n"/>
+    </row>
+    <row r="102" ht="17" customHeight="1">
+      <c r="A102" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Mahmoud Abunada</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D102" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="15" t="n"/>
+    </row>
+    <row r="103" ht="17" customHeight="1">
+      <c r="A103" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Marawan Attia</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D103" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="14" t="n"/>
+    </row>
+    <row r="104" ht="17" customHeight="1">
+      <c r="A104" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Marcel Sabitzer</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="D104" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="15" t="n"/>
+    </row>
+    <row r="105" ht="17" customHeight="1">
+      <c r="A105" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Mathias Olivera</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="D105" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="14" t="n"/>
+    </row>
+    <row r="106" ht="17" customHeight="1">
+      <c r="A106" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Matias Galarza</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D106" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="15" t="n"/>
+    </row>
+    <row r="107" ht="17" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Maxim De Cuyper</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D107" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="14" t="n"/>
+    </row>
+    <row r="108" ht="17" customHeight="1">
+      <c r="A108" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>Memphis Depay</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D108" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="15" t="n"/>
+    </row>
+    <row r="109" ht="17" customHeight="1">
+      <c r="A109" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Micky Van De Ven</t>
+        </is>
+      </c>
+      <c r="C109" s="14" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D109" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="14" t="n"/>
+    </row>
+    <row r="110" ht="17" customHeight="1">
+      <c r="A110" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>Mohamed Kanno</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D110" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="15" t="n"/>
+    </row>
+    <row r="111" ht="17" customHeight="1">
+      <c r="A111" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Mohanad Lashin</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D111" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="14" t="n"/>
+    </row>
+    <row r="112" ht="17" customHeight="1">
+      <c r="A112" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Nelson Semedo</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D112" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" s="15" t="n"/>
+    </row>
+    <row r="113" ht="17" customHeight="1">
+      <c r="A113" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Nico Elvedi</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D113" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="14" t="n"/>
+    </row>
+    <row r="114" ht="17" customHeight="1">
+      <c r="A114" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>Nicolas Pepe</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="D114" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="15" t="n"/>
+    </row>
+    <row r="115" ht="17" customHeight="1">
+      <c r="A115" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Nikola Katic</t>
+        </is>
+      </c>
+      <c r="C115" s="14" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D115" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="14" t="n"/>
+    </row>
+    <row r="116" ht="17" customHeight="1">
+      <c r="A116" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Nkosinathi Sibisi</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D116" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="15" t="n"/>
+    </row>
+    <row r="117" ht="17" customHeight="1">
+      <c r="A117" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Odiljon Xamrobekov</t>
+        </is>
+      </c>
+      <c r="C117" s="14" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D117" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="14" t="n"/>
+    </row>
+    <row r="118" ht="17" customHeight="1">
+      <c r="A118" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Paik Seungho</t>
+        </is>
+      </c>
+      <c r="C118" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D118" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="15" t="n"/>
+    </row>
+    <row r="119" ht="17" customHeight="1">
+      <c r="A119" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Pedri</t>
+        </is>
+      </c>
+      <c r="C119" s="14" t="inlineStr">
+        <is>
+          <t>Spania</t>
+        </is>
+      </c>
+      <c r="D119" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="14" t="n"/>
+    </row>
+    <row r="120" ht="17" customHeight="1">
+      <c r="A120" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Petar Sucic</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>Kroatia</t>
+        </is>
+      </c>
+      <c r="D120" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="15" t="n"/>
+    </row>
+    <row r="121" ht="17" customHeight="1">
+      <c r="A121" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Piero Hincapie</t>
+        </is>
+      </c>
+      <c r="C121" s="14" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D121" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="14" t="n"/>
+    </row>
+    <row r="122" ht="17" customHeight="1">
+      <c r="A122" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Ramiz Zerrouki</t>
+        </is>
+      </c>
+      <c r="C122" s="15" t="inlineStr">
+        <is>
+          <t>Algerie</t>
+        </is>
+      </c>
+      <c r="D122" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="15" t="n"/>
+    </row>
+    <row r="123" ht="17" customHeight="1">
+      <c r="A123" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Rani Khedira</t>
+        </is>
+      </c>
+      <c r="C123" s="14" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D123" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="14" t="n"/>
+    </row>
+    <row r="124" ht="17" customHeight="1">
+      <c r="A124" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Renato Veiga</t>
+        </is>
+      </c>
+      <c r="C124" s="15" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D124" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="15" t="n"/>
+    </row>
+    <row r="125" ht="17" customHeight="1">
+      <c r="A125" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Rodrigo Bentancur</t>
+        </is>
+      </c>
+      <c r="C125" s="14" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="D125" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="14" t="n"/>
+    </row>
+    <row r="126" ht="17" customHeight="1">
+      <c r="A126" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Roger Ibanez</t>
+        </is>
+      </c>
+      <c r="C126" s="15" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D126" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="15" t="n"/>
+    </row>
+    <row r="127" ht="17" customHeight="1">
+      <c r="A127" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Romelu Lukaku</t>
+        </is>
+      </c>
+      <c r="C127" s="14" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D127" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="14" t="n"/>
+    </row>
+    <row r="128" ht="17" customHeight="1">
+      <c r="A128" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Ryan Christie</t>
+        </is>
+      </c>
+      <c r="C128" s="15" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D128" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="15" t="n"/>
+    </row>
+    <row r="129" ht="17" customHeight="1">
+      <c r="A129" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Saeid Ezatolahi</t>
+        </is>
+      </c>
+      <c r="C129" s="14" t="inlineStr">
+        <is>
+          <t>Iran</t>
+        </is>
+      </c>
+      <c r="D129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="14" t="n"/>
+    </row>
+    <row r="130" ht="17" customHeight="1">
+      <c r="A130" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Salem Aldawsari</t>
+        </is>
+      </c>
+      <c r="C130" s="15" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D130" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="15" t="n"/>
+    </row>
+    <row r="131" ht="17" customHeight="1">
+      <c r="A131" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Sarpreet Singh</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D131" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="14" t="n"/>
+    </row>
+    <row r="132" ht="17" customHeight="1">
+      <c r="A132" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Sebastian Berhalter</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D132" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="15" t="n"/>
+    </row>
+    <row r="133" ht="17" customHeight="1">
+      <c r="A133" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Seko Fofana</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>Elfenbenskysten</t>
+        </is>
+      </c>
+      <c r="D133" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="14" t="n"/>
+    </row>
+    <row r="134" ht="17" customHeight="1">
+      <c r="A134" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Shogo Taniguchi</t>
+        </is>
+      </c>
+      <c r="C134" s="15" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D134" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="15" t="n"/>
+    </row>
+    <row r="135" ht="17" customHeight="1">
+      <c r="A135" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Stefan Posch</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>Østerrike</t>
+        </is>
+      </c>
+      <c r="D135" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="14" t="n"/>
+    </row>
+    <row r="136" ht="17" customHeight="1">
+      <c r="A136" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Thalente Mbatha</t>
+        </is>
+      </c>
+      <c r="C136" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D136" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="15" t="n"/>
+    </row>
+    <row r="137" ht="17" customHeight="1">
+      <c r="A137" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Timothy Castagne</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" s="14" t="n"/>
+    </row>
+    <row r="138" ht="17" customHeight="1">
+      <c r="A138" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>Tomas Araujo</t>
+        </is>
+      </c>
+      <c r="C138" s="15" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D138" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="15" t="n"/>
+    </row>
+    <row r="139" ht="17" customHeight="1">
+      <c r="A139" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Tyler Adams</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D139" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="14" t="n"/>
+    </row>
+    <row r="140" ht="17" customHeight="1">
+      <c r="A140" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>Viktor Gyokeres</t>
+        </is>
+      </c>
+      <c r="C140" s="15" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D140" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="15" t="n"/>
+    </row>
+    <row r="141" ht="17" customHeight="1">
+      <c r="A141" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Yasin Ayari</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>Sverige</t>
+        </is>
+      </c>
+      <c r="D141" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="14" t="n"/>
+    </row>
+    <row r="142" ht="17" customHeight="1">
+      <c r="A142" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Yunus Akgun</t>
+        </is>
+      </c>
+      <c r="C142" s="15" t="inlineStr">
+        <is>
+          <t>Tyrkia</t>
+        </is>
+      </c>
+      <c r="D142" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="15" t="n"/>
+    </row>
+    <row r="143" ht="17" customHeight="1">
+      <c r="A143" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Zaid Tahseen</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D143" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55469,7 +55464,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -59654,7 +59648,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -63853,7 +63846,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -68044,7 +68036,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -72223,7 +72214,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -76362,7 +76352,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
@@ -80485,7 +80474,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="10" t="inlineStr">
         <is>

--- a/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
+++ b/VM2026_avansert_gruppetabeller_og_sluttspill.xlsx
@@ -1,41 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Finale" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Kort" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Scorere og assists" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Alder" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gruppe L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16-delsfinaler" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8-delsfinaler" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kvartfinaler" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semifinaler" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bronsefinale" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Finale" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aldersfordeling" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spillere etter klubbland" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Klubbdominans" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorere og assists" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alder" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kort" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagstatistikk" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scoringstidspunkt" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ballbesittelse" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stadionoversikt" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Spillere etter klubbland'!$A$2:$I$2</definedName>
@@ -883,13 +883,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -908,7 +908,7 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -936,8 +936,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -963,8 +963,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -987,7 +987,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -1002,9 +1002,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -32407,2745 +32407,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>VM 2026 — Kort  (141 spillere)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>Spiller</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Lag</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Gule</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Røde</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="A3" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>Miguel Almiron</t>
-        </is>
-      </c>
-      <c r="C3" s="25" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D3" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="29" t="inlineStr">
-        <is>
-          <t>Assim Madibo</t>
-        </is>
-      </c>
-      <c r="C4" s="30" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="29" t="inlineStr">
-        <is>
-          <t>Cesar Montes</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="29" t="inlineStr">
-        <is>
-          <t>Homam Ahmed</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Nathan Ngoy</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>Sphephelo Sithole</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>Tarik Muharemovic</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B10" s="29" t="inlineStr">
-        <is>
-          <t>Themba Zwane</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Ahmed Fathy</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="14" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Diego Gomez</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="15" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Gervane Kastaneer</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="14" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Juninho Bacuna</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Sidny Lopes Cabral</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Teboho Mokoena</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Aaron Hickey</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Abdukodir Khusanov</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Abdulelah Alamri</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="14" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Ahmed Fatouh</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>Alan Franco</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D21" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Aleksandar Pavlovic</t>
-        </is>
-      </c>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>Tyskland</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Alessandro Circati</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D23" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Alex Arce</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D24" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="15" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Alistair Johnston</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="14" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Amar Dedic</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Amir Alammari</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Andy Robertson</t>
-        </is>
-      </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Antonee Robinson</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="14" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Aubrey Modiba</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>Bernardo Silva</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14" t="n"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Brian Gutierrez</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="15" t="n"/>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>Caleb Yirenkyi</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="14" t="n"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Callum Mccowatt</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="15" t="n"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Carlens Arcus</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D35" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="14" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Carlos Harvey</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="D36" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="15" t="n"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Casemiro</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="14" t="n"/>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Cesar Blackman</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="D38" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="15" t="n"/>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Chancel Mbemba</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-      <c r="D39" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="14" t="n"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Charles Pickel</t>
-        </is>
-      </c>
-      <c r="C40" s="15" t="inlineStr">
-        <is>
-          <t>DR Kongo</t>
-        </is>
-      </c>
-      <c r="D40" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="15" t="n"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>Cho Guesung</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D41" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="14" t="n"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Chris Richards</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D42" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="15" t="n"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Crysencio Summerville</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D43" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="14" t="n"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Cyle Larin</t>
-        </is>
-      </c>
-      <c r="C44" s="15" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="15" t="n"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Danilo</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D45" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="14" t="n"/>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>Danley Jean Jacques</t>
-        </is>
-      </c>
-      <c r="C46" s="15" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="15" t="n"/>
-    </row>
-    <row r="47" ht="17" customHeight="1">
-      <c r="A47" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Declan Rice</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
-      </c>
-      <c r="D47" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="14" t="n"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>Denis Zakaria</t>
-        </is>
-      </c>
-      <c r="C48" s="15" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D48" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="15" t="n"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>Derek Cornelius</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D49" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="14" t="n"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Diney Borges</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Kapp Verde</t>
-        </is>
-      </c>
-      <c r="D50" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="15" t="n"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>Douglas Santos</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="14" t="n"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B52" s="8" t="inlineStr">
-        <is>
-          <t>Duckens Nazon</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" s="15" t="n"/>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>Edgar Yoel Barcenas</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
-      </c>
-      <c r="D53" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="14" t="n"/>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Edin Dzeko</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D54" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" s="15" t="n"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Edson Alvarez</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="D55" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="14" t="n"/>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B56" s="8" t="inlineStr">
-        <is>
-          <t>Ehsan Hajisafi</t>
-        </is>
-      </c>
-      <c r="C56" s="15" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" s="15" t="n"/>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Eren Elmali</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D57" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="14" t="n"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B58" s="8" t="inlineStr">
-        <is>
-          <t>Ermedin Demirovic</t>
-        </is>
-      </c>
-      <c r="C58" s="15" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D58" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="15" t="n"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>Ermin Mahmic</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D59" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="14" t="n"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B60" s="8" t="inlineStr">
-        <is>
-          <t>Fabinho</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D60" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="15" t="n"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>Facundo Medina</t>
-        </is>
-      </c>
-      <c r="C61" s="14" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D61" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="14" t="n"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>Findlay Curtis</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D62" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="15" t="n"/>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>Folarin Balogun</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D63" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="14" t="n"/>
-    </row>
-    <row r="64" ht="17" customHeight="1">
-      <c r="A64" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Franck Kessie</t>
-        </is>
-      </c>
-      <c r="C64" s="15" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="15" t="n"/>
-    </row>
-    <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>Frantzdy Pierrot</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D65" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" s="14" t="n"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B66" s="8" t="inlineStr">
-        <is>
-          <t>Gabriel Gudmundsson</t>
-        </is>
-      </c>
-      <c r="C66" s="15" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D66" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="15" t="n"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>Gonzalo Plata</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D67" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" s="14" t="n"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B68" s="8" t="inlineStr">
-        <is>
-          <t>Granit Xhaka</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D68" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" s="15" t="n"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>Guela Doue</t>
-        </is>
-      </c>
-      <c r="C69" s="14" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D69" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="14" t="n"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Harry Souttar</t>
-        </is>
-      </c>
-      <c r="C70" s="15" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D70" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" s="15" t="n"/>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>Husam Abudahab</t>
-        </is>
-      </c>
-      <c r="C71" s="14" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="D71" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="14" t="n"/>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B72" s="8" t="inlineStr">
-        <is>
-          <t>Inaki Williams</t>
-        </is>
-      </c>
-      <c r="C72" s="15" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
-      </c>
-      <c r="D72" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" s="15" t="n"/>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>Isak Hien</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D73" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="14" t="n"/>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>Issa Diop</t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr">
-        <is>
-          <t>Marokko</t>
-        </is>
-      </c>
-      <c r="D74" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" s="15" t="n"/>
-    </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Jackson Irvine</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D75" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="14" t="n"/>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>Jackson Porozo</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D76" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="15" t="n"/>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Jacob Italiano</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D77" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" s="14" t="n"/>
-    </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>Jassem Gaber</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D78" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" s="15" t="n"/>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Jean-Ricner Bellegarde</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D79" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" s="14" t="n"/>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>Jefferson Lerma</t>
-        </is>
-      </c>
-      <c r="C80" s="15" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D80" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" s="15" t="n"/>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>Jhon Lucumi</t>
-        </is>
-      </c>
-      <c r="C81" s="14" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D81" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" s="14" t="n"/>
-    </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B82" s="8" t="inlineStr">
-        <is>
-          <t>Johan Mojica</t>
-        </is>
-      </c>
-      <c r="C82" s="15" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E82" s="15" t="n"/>
-    </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B83" s="5" t="inlineStr">
-        <is>
-          <t>Johny Placide</t>
-        </is>
-      </c>
-      <c r="C83" s="14" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D83" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" s="14" t="n"/>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>Jordan Bos</t>
-        </is>
-      </c>
-      <c r="C84" s="15" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
-      </c>
-      <c r="D84" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" s="15" t="n"/>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B85" s="5" t="inlineStr">
-        <is>
-          <t>Jordy Alcivar</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D85" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" s="14" t="n"/>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>Josue Casimir</t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
-      </c>
-      <c r="D86" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" s="15" t="n"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>Jovo Lukic</t>
-        </is>
-      </c>
-      <c r="C87" s="14" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D87" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" s="14" t="n"/>
-    </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B88" s="8" t="inlineStr">
-        <is>
-          <t>Juan Jose Caceres</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D88" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="15" t="n"/>
-    </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>Junior Alonso</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D89" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" s="14" t="n"/>
-    </row>
-    <row r="90" ht="17" customHeight="1">
-      <c r="A90" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B90" s="8" t="inlineStr">
-        <is>
-          <t>Jurien Gaari</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D90" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" s="15" t="n"/>
-    </row>
-    <row r="91" ht="17" customHeight="1">
-      <c r="A91" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>Kenny Mclean</t>
-        </is>
-      </c>
-      <c r="C91" s="14" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D91" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" s="14" t="n"/>
-    </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t>Konrad Laimer</t>
-        </is>
-      </c>
-      <c r="C92" s="15" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="D92" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" s="15" t="n"/>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>Ladislav Krejci</t>
-        </is>
-      </c>
-      <c r="C93" s="14" t="inlineStr">
-        <is>
-          <t>Tsjekkia</t>
-        </is>
-      </c>
-      <c r="D93" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E93" s="14" t="n"/>
-    </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B94" s="8" t="inlineStr">
-        <is>
-          <t>Leandro Bacuna</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D94" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E94" s="15" t="n"/>
-    </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Leandro Paredes</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="D95" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" s="14" t="n"/>
-    </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B96" s="8" t="inlineStr">
-        <is>
-          <t>Lee Gihyuk</t>
-        </is>
-      </c>
-      <c r="C96" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D96" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="15" t="n"/>
-    </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>Lee Kangin</t>
-        </is>
-      </c>
-      <c r="C97" s="14" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D97" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" s="14" t="n"/>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B98" s="8" t="inlineStr">
-        <is>
-          <t>Liam Millar</t>
-        </is>
-      </c>
-      <c r="C98" s="15" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D98" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" s="15" t="n"/>
-    </row>
-    <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B99" s="5" t="inlineStr">
-        <is>
-          <t>Livano Comenencia</t>
-        </is>
-      </c>
-      <c r="C99" s="14" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
-      </c>
-      <c r="D99" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" s="14" t="n"/>
-    </row>
-    <row r="100" ht="17" customHeight="1">
-      <c r="A100" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B100" s="8" t="inlineStr">
-        <is>
-          <t>Luc De Fougerolles</t>
-        </is>
-      </c>
-      <c r="C100" s="15" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="D100" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" s="15" t="n"/>
-    </row>
-    <row r="101" ht="17" customHeight="1">
-      <c r="A101" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B101" s="5" t="inlineStr">
-        <is>
-          <t>Lucas Bergvall</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D101" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="14" t="n"/>
-    </row>
-    <row r="102" ht="17" customHeight="1">
-      <c r="A102" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B102" s="8" t="inlineStr">
-        <is>
-          <t>Mahmoud Abunada</t>
-        </is>
-      </c>
-      <c r="C102" s="15" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="D102" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" s="15" t="n"/>
-    </row>
-    <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B103" s="5" t="inlineStr">
-        <is>
-          <t>Marawan Attia</t>
-        </is>
-      </c>
-      <c r="C103" s="14" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="D103" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="14" t="n"/>
-    </row>
-    <row r="104" ht="17" customHeight="1">
-      <c r="A104" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B104" s="8" t="inlineStr">
-        <is>
-          <t>Marcel Sabitzer</t>
-        </is>
-      </c>
-      <c r="C104" s="15" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="D104" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="15" t="n"/>
-    </row>
-    <row r="105" ht="17" customHeight="1">
-      <c r="A105" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B105" s="5" t="inlineStr">
-        <is>
-          <t>Mathias Olivera</t>
-        </is>
-      </c>
-      <c r="C105" s="14" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="D105" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" s="14" t="n"/>
-    </row>
-    <row r="106" ht="17" customHeight="1">
-      <c r="A106" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B106" s="8" t="inlineStr">
-        <is>
-          <t>Matias Galarza</t>
-        </is>
-      </c>
-      <c r="C106" s="15" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="D106" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" s="15" t="n"/>
-    </row>
-    <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B107" s="5" t="inlineStr">
-        <is>
-          <t>Maxim De Cuyper</t>
-        </is>
-      </c>
-      <c r="C107" s="14" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D107" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="14" t="n"/>
-    </row>
-    <row r="108" ht="17" customHeight="1">
-      <c r="A108" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B108" s="8" t="inlineStr">
-        <is>
-          <t>Memphis Depay</t>
-        </is>
-      </c>
-      <c r="C108" s="15" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D108" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="15" t="n"/>
-    </row>
-    <row r="109" ht="17" customHeight="1">
-      <c r="A109" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B109" s="5" t="inlineStr">
-        <is>
-          <t>Micky Van De Ven</t>
-        </is>
-      </c>
-      <c r="C109" s="14" t="inlineStr">
-        <is>
-          <t>Nederland</t>
-        </is>
-      </c>
-      <c r="D109" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="14" t="n"/>
-    </row>
-    <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B110" s="8" t="inlineStr">
-        <is>
-          <t>Mohamed Kanno</t>
-        </is>
-      </c>
-      <c r="C110" s="15" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="D110" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" s="15" t="n"/>
-    </row>
-    <row r="111" ht="17" customHeight="1">
-      <c r="A111" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B111" s="5" t="inlineStr">
-        <is>
-          <t>Mohanad Lashin</t>
-        </is>
-      </c>
-      <c r="C111" s="14" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
-      </c>
-      <c r="D111" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" s="14" t="n"/>
-    </row>
-    <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B112" s="8" t="inlineStr">
-        <is>
-          <t>Nelson Semedo</t>
-        </is>
-      </c>
-      <c r="C112" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D112" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E112" s="15" t="n"/>
-    </row>
-    <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Nico Elvedi</t>
-        </is>
-      </c>
-      <c r="C113" s="14" t="inlineStr">
-        <is>
-          <t>Sveits</t>
-        </is>
-      </c>
-      <c r="D113" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E113" s="14" t="n"/>
-    </row>
-    <row r="114" ht="17" customHeight="1">
-      <c r="A114" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B114" s="8" t="inlineStr">
-        <is>
-          <t>Nicolas Pepe</t>
-        </is>
-      </c>
-      <c r="C114" s="15" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D114" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="15" t="n"/>
-    </row>
-    <row r="115" ht="17" customHeight="1">
-      <c r="A115" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>Nikola Katic</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>Bosnia-Hercegovina</t>
-        </is>
-      </c>
-      <c r="D115" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" s="14" t="n"/>
-    </row>
-    <row r="116" ht="17" customHeight="1">
-      <c r="A116" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B116" s="8" t="inlineStr">
-        <is>
-          <t>Nkosinathi Sibisi</t>
-        </is>
-      </c>
-      <c r="C116" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D116" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="15" t="n"/>
-    </row>
-    <row r="117" ht="17" customHeight="1">
-      <c r="A117" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>Odiljon Xamrobekov</t>
-        </is>
-      </c>
-      <c r="C117" s="14" t="inlineStr">
-        <is>
-          <t>Usbekistan</t>
-        </is>
-      </c>
-      <c r="D117" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E117" s="14" t="n"/>
-    </row>
-    <row r="118" ht="17" customHeight="1">
-      <c r="A118" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B118" s="8" t="inlineStr">
-        <is>
-          <t>Paik Seungho</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Korea</t>
-        </is>
-      </c>
-      <c r="D118" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" s="15" t="n"/>
-    </row>
-    <row r="119" ht="17" customHeight="1">
-      <c r="A119" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>Pedri</t>
-        </is>
-      </c>
-      <c r="C119" s="14" t="inlineStr">
-        <is>
-          <t>Spania</t>
-        </is>
-      </c>
-      <c r="D119" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="14" t="n"/>
-    </row>
-    <row r="120" ht="17" customHeight="1">
-      <c r="A120" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B120" s="8" t="inlineStr">
-        <is>
-          <t>Petar Sucic</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="inlineStr">
-        <is>
-          <t>Kroatia</t>
-        </is>
-      </c>
-      <c r="D120" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="15" t="n"/>
-    </row>
-    <row r="121" ht="17" customHeight="1">
-      <c r="A121" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>Piero Hincapie</t>
-        </is>
-      </c>
-      <c r="C121" s="14" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
-      </c>
-      <c r="D121" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" s="14" t="n"/>
-    </row>
-    <row r="122" ht="17" customHeight="1">
-      <c r="A122" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B122" s="8" t="inlineStr">
-        <is>
-          <t>Ramiz Zerrouki</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="inlineStr">
-        <is>
-          <t>Algerie</t>
-        </is>
-      </c>
-      <c r="D122" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" s="15" t="n"/>
-    </row>
-    <row r="123" ht="17" customHeight="1">
-      <c r="A123" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>Rani Khedira</t>
-        </is>
-      </c>
-      <c r="C123" s="14" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
-      </c>
-      <c r="D123" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" s="14" t="n"/>
-    </row>
-    <row r="124" ht="17" customHeight="1">
-      <c r="A124" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B124" s="8" t="inlineStr">
-        <is>
-          <t>Renato Veiga</t>
-        </is>
-      </c>
-      <c r="C124" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D124" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" s="15" t="n"/>
-    </row>
-    <row r="125" ht="17" customHeight="1">
-      <c r="A125" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>Rodrigo Bentancur</t>
-        </is>
-      </c>
-      <c r="C125" s="14" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="D125" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" s="14" t="n"/>
-    </row>
-    <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B126" s="8" t="inlineStr">
-        <is>
-          <t>Roger Ibanez</t>
-        </is>
-      </c>
-      <c r="C126" s="15" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="D126" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="15" t="n"/>
-    </row>
-    <row r="127" ht="17" customHeight="1">
-      <c r="A127" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>Romelu Lukaku</t>
-        </is>
-      </c>
-      <c r="C127" s="14" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D127" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" s="14" t="n"/>
-    </row>
-    <row r="128" ht="17" customHeight="1">
-      <c r="A128" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B128" s="8" t="inlineStr">
-        <is>
-          <t>Ryan Christie</t>
-        </is>
-      </c>
-      <c r="C128" s="15" t="inlineStr">
-        <is>
-          <t>Skottland</t>
-        </is>
-      </c>
-      <c r="D128" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="15" t="n"/>
-    </row>
-    <row r="129" ht="17" customHeight="1">
-      <c r="A129" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>Saeid Ezatolahi</t>
-        </is>
-      </c>
-      <c r="C129" s="14" t="inlineStr">
-        <is>
-          <t>Iran</t>
-        </is>
-      </c>
-      <c r="D129" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="14" t="n"/>
-    </row>
-    <row r="130" ht="17" customHeight="1">
-      <c r="A130" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t>Salem Aldawsari</t>
-        </is>
-      </c>
-      <c r="C130" s="15" t="inlineStr">
-        <is>
-          <t>Saudi-Arabia</t>
-        </is>
-      </c>
-      <c r="D130" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E130" s="15" t="n"/>
-    </row>
-    <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>Sarpreet Singh</t>
-        </is>
-      </c>
-      <c r="C131" s="14" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
-      </c>
-      <c r="D131" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" s="14" t="n"/>
-    </row>
-    <row r="132" ht="17" customHeight="1">
-      <c r="A132" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B132" s="8" t="inlineStr">
-        <is>
-          <t>Sebastian Berhalter</t>
-        </is>
-      </c>
-      <c r="C132" s="15" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D132" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" s="15" t="n"/>
-    </row>
-    <row r="133" ht="17" customHeight="1">
-      <c r="A133" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B133" s="5" t="inlineStr">
-        <is>
-          <t>Seko Fofana</t>
-        </is>
-      </c>
-      <c r="C133" s="14" t="inlineStr">
-        <is>
-          <t>Elfenbenskysten</t>
-        </is>
-      </c>
-      <c r="D133" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" s="14" t="n"/>
-    </row>
-    <row r="134" ht="17" customHeight="1">
-      <c r="A134" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B134" s="8" t="inlineStr">
-        <is>
-          <t>Shogo Taniguchi</t>
-        </is>
-      </c>
-      <c r="C134" s="15" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="D134" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="15" t="n"/>
-    </row>
-    <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>Stefan Posch</t>
-        </is>
-      </c>
-      <c r="C135" s="14" t="inlineStr">
-        <is>
-          <t>Østerrike</t>
-        </is>
-      </c>
-      <c r="D135" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" s="14" t="n"/>
-    </row>
-    <row r="136" ht="17" customHeight="1">
-      <c r="A136" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B136" s="8" t="inlineStr">
-        <is>
-          <t>Thalente Mbatha</t>
-        </is>
-      </c>
-      <c r="C136" s="15" t="inlineStr">
-        <is>
-          <t>Sør-Afrika</t>
-        </is>
-      </c>
-      <c r="D136" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" s="15" t="n"/>
-    </row>
-    <row r="137" ht="17" customHeight="1">
-      <c r="A137" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B137" s="5" t="inlineStr">
-        <is>
-          <t>Timothy Castagne</t>
-        </is>
-      </c>
-      <c r="C137" s="14" t="inlineStr">
-        <is>
-          <t>Belgia</t>
-        </is>
-      </c>
-      <c r="D137" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" s="14" t="n"/>
-    </row>
-    <row r="138" ht="17" customHeight="1">
-      <c r="A138" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B138" s="8" t="inlineStr">
-        <is>
-          <t>Tomas Araujo</t>
-        </is>
-      </c>
-      <c r="C138" s="15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="D138" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="15" t="n"/>
-    </row>
-    <row r="139" ht="17" customHeight="1">
-      <c r="A139" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B139" s="5" t="inlineStr">
-        <is>
-          <t>Tyler Adams</t>
-        </is>
-      </c>
-      <c r="C139" s="14" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D139" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" s="14" t="n"/>
-    </row>
-    <row r="140" ht="17" customHeight="1">
-      <c r="A140" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B140" s="8" t="inlineStr">
-        <is>
-          <t>Viktor Gyokeres</t>
-        </is>
-      </c>
-      <c r="C140" s="15" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D140" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="15" t="n"/>
-    </row>
-    <row r="141" ht="17" customHeight="1">
-      <c r="A141" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B141" s="5" t="inlineStr">
-        <is>
-          <t>Yasin Ayari</t>
-        </is>
-      </c>
-      <c r="C141" s="14" t="inlineStr">
-        <is>
-          <t>Sverige</t>
-        </is>
-      </c>
-      <c r="D141" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" s="14" t="n"/>
-    </row>
-    <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t>Yunus Akgun</t>
-        </is>
-      </c>
-      <c r="C142" s="15" t="inlineStr">
-        <is>
-          <t>Tyrkia</t>
-        </is>
-      </c>
-      <c r="D142" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" s="15" t="n"/>
-    </row>
-    <row r="143" ht="17" customHeight="1">
-      <c r="A143" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>Zaid Tahseen</t>
-        </is>
-      </c>
-      <c r="C143" s="14" t="inlineStr">
-        <is>
-          <t>Irak</t>
-        </is>
-      </c>
-      <c r="D143" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E143" s="14" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -38887,7 +36148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39594,6 +36855,2745 @@
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E143"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>VM 2026 — Kort  (141 spillere)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Spiller</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Lag</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Gule</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Røde</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Miguel Almiron</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D3" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>Assim Madibo</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="n"/>
+      <c r="E4" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>Cesar Montes</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>Homam Ahmed</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n"/>
+      <c r="E6" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>Nathan Ngoy</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Belgia</t>
+        </is>
+      </c>
+      <c r="D7" s="30" t="n"/>
+      <c r="E7" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Sphephelo Sithole</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="n"/>
+      <c r="E8" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>Tarik Muharemovic</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>Themba Zwane</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Ahmed Fathy</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Diego Gomez</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="15" t="n"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Gervane Kastaneer</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14" t="n"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Juninho Bacuna</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15" t="n"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Sidny Lopes Cabral</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Teboho Mokoena</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Aaron Hickey</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Abdukodir Khusanov</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Usbekistan</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Abdulelah Alamri</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ahmed Fatouh</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Alan Franco</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Aleksandar Pavlovic</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Tyskland</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Alessandro Circati</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Alex Arce</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15" t="n"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Alistair Johnston</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14" t="n"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Amar Dedic</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>Bosnia-Hercegovina</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="n"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Amir Alammari</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Irak</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14" t="n"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Andy Robertson</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Skottland</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15" t="n"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Antonee Robinson</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Aubrey Modiba</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>Sør-Afrika</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15" t="n"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Bernardo Silva</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14" t="n"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Brian Gutierrez</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="15" t="n"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Caleb Yirenkyi</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="14" t="n"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Callum Mccowatt</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15" t="n"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Carlens Arcus</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="14" t="n"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Carlos Harvey</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15" t="n"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Casemiro</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="14" t="n"/>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Cesar Blackman</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="15" t="n"/>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Chancel Mbemba</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="14" t="n"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Charles Pickel</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>DR Kongo</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="15" t="n"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Cho Guesung</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Sør-Korea</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="14" t="n"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Chris Richards</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="15" t="n"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Crysencio Summerville</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Nederland</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="14" t="n"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Cyle Larin</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="15" t="n"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Danilo</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Danley Jean Jacques</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="15" t="n"/>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Declan Rice</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="14" t="n"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Denis Zakaria</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>Sveits</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="15" t="n"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Derek Cornelius</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="14" t="n"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Diney Borges</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>Kapp Verde</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="15" t="n"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Douglas Santos</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="14" t="n"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Duckens Nazon</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="15" t="n"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>15</v>
+ 